--- a/docs/design/ACSMS-SCR-024/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_アカウントマスタ明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-024/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_アカウントマスタ明細検索画面_V1.0.xlsx
@@ -1516,7 +1516,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1870,7 +1870,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -2839,7 +2839,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="C55" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3859,7 +3859,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4427,7 +4427,7 @@
       <c r="U14" s="11" t="n"/>
       <c r="V14" s="19" t="inlineStr">
         <is>
-          <t>このレコードは現在使用中のため、削除できません。</t>
+          <t>関連データが存在するため削除できません。</t>
         </is>
       </c>
       <c r="W14" s="10" t="n"/>
@@ -4674,7 +4674,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4990,7 +4990,7 @@
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="19" t="inlineStr">
         <is>
-          <t>JAプルダウンリストを取得する（都道府県・管理者区分によるカスケード絞込み。共用API：アカウント検索・登録等で使用）</t>
+          <t>JAプルダウンリストを取得する（共用API）。2つのユースケースを1つのエンドポイントで提供：（A）ページング+フリーテキスト検索（SCR-009 等のフォーム用）、（B）都道府県・管理者区分によるカスケード絞込み（SCR-024 アカウント検索／SCR-025 登録用）。両方のレスポンス形状は同一（`{data, meta}`）。</t>
         </is>
       </c>
       <c r="T9" s="10" t="n"/>
@@ -5137,7 +5137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK112"/>
+  <dimension ref="A1:AK115"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -5298,7 +5298,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5652,7 +5652,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="D24" s="10" t="n"/>
@@ -6072,7 +6072,7 @@
       <c r="L24" s="11" t="n"/>
       <c r="M24" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N24" s="10" t="n"/>
@@ -6094,16 +6094,20 @@
       <c r="V24" s="10" t="n"/>
       <c r="W24" s="10" t="n"/>
       <c r="X24" s="11" t="n"/>
-      <c r="Y24" s="17" t="inlineStr"/>
+      <c r="Y24" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="Z24" s="10" t="n"/>
       <c r="AA24" s="10" t="n"/>
       <c r="AB24" s="11" t="n"/>
-      <c r="AC24" s="17" t="inlineStr"/>
+      <c r="AC24" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="AD24" s="10" t="n"/>
       <c r="AE24" s="11" t="n"/>
       <c r="AF24" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>都道府県コード（01〜47）。完全一致。未指定=全て</t>
         </is>
       </c>
       <c r="AG24" s="10" t="n"/>
@@ -6118,7 +6122,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_id</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -6163,7 +6167,7 @@
       <c r="AE25" s="11" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -6178,7 +6182,7 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -6223,7 +6227,7 @@
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（デフォルト: 1）</t>
+          <t>管理支店ID</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -6238,7 +6242,7 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>page</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -6283,7 +6287,7 @@
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数（デフォルト: 20、最大: 100）</t>
+          <t>ページ番号（デフォルト: 1）</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -6298,7 +6302,7 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -6312,7 +6316,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -6343,7 +6347,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>ソート項目（デフォルト: created_at）</t>
+          <t>1ページあたりの件数（デフォルト: 20、最大: 100）</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -6358,7 +6362,7 @@
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>sort_by</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -6403,7 +6407,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>ソート順（asc / desc、デフォルト: desc）</t>
+          <t>ソート項目（デフォルト: created_at）</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -6412,88 +6416,84 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="19.5" customHeight="1"/>
-    <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="27" t="inlineStr">
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="11" t="n"/>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="11" t="n"/>
+      <c r="T30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U30" s="10" t="n"/>
+      <c r="V30" s="10" t="n"/>
+      <c r="W30" s="10" t="n"/>
+      <c r="X30" s="11" t="n"/>
+      <c r="Y30" s="17" t="inlineStr"/>
+      <c r="Z30" s="10" t="n"/>
+      <c r="AA30" s="10" t="n"/>
+      <c r="AB30" s="11" t="n"/>
+      <c r="AC30" s="17" t="inlineStr"/>
+      <c r="AD30" s="10" t="n"/>
+      <c r="AE30" s="11" t="n"/>
+      <c r="AF30" s="19" t="inlineStr">
+        <is>
+          <t>ソート順（asc / desc、デフォルト: desc）</t>
+        </is>
+      </c>
+      <c r="AG30" s="10" t="n"/>
+      <c r="AH30" s="10" t="n"/>
+      <c r="AI30" s="10" t="n"/>
+      <c r="AJ30" s="10" t="n"/>
+      <c r="AK30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="19.5" customHeight="1"/>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="19.5" customHeight="1"/>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="B33" s="30" t="inlineStr">
+    <row r="33" ht="19.5" customHeight="1"/>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N33" s="10" t="n"/>
-      <c r="O33" s="10" t="n"/>
-      <c r="P33" s="11" t="n"/>
-      <c r="Q33" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R33" s="10" t="n"/>
-      <c r="S33" s="11" t="n"/>
-      <c r="T33" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U33" s="10" t="n"/>
-      <c r="V33" s="10" t="n"/>
-      <c r="W33" s="10" t="n"/>
-      <c r="X33" s="11" t="n"/>
-      <c r="Y33" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z33" s="10" t="n"/>
-      <c r="AA33" s="10" t="n"/>
-      <c r="AB33" s="10" t="n"/>
-      <c r="AC33" s="10" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="11" t="n"/>
-      <c r="AF33" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG33" s="10" t="n"/>
-      <c r="AH33" s="10" t="n"/>
-      <c r="AI33" s="10" t="n"/>
-      <c r="AJ33" s="10" t="n"/>
-      <c r="AK33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
         </is>
       </c>
       <c r="D34" s="10" t="n"/>
@@ -6505,29 +6505,33 @@
       <c r="J34" s="10" t="n"/>
       <c r="K34" s="10" t="n"/>
       <c r="L34" s="11" t="n"/>
-      <c r="M34" s="17" t="inlineStr">
-        <is>
-          <t>Array</t>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
       <c r="P34" s="11" t="n"/>
-      <c r="Q34" s="17" t="inlineStr">
-        <is>
-          <t>○</t>
+      <c r="Q34" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R34" s="10" t="n"/>
       <c r="S34" s="11" t="n"/>
-      <c r="T34" s="17" t="inlineStr"/>
+      <c r="T34" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U34" s="10" t="n"/>
       <c r="V34" s="10" t="n"/>
       <c r="W34" s="10" t="n"/>
       <c r="X34" s="11" t="n"/>
-      <c r="Y34" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y34" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z34" s="10" t="n"/>
@@ -6536,9 +6540,9 @@
       <c r="AC34" s="10" t="n"/>
       <c r="AD34" s="10" t="n"/>
       <c r="AE34" s="11" t="n"/>
-      <c r="AF34" s="19" t="inlineStr">
-        <is>
-          <t>アカウント一覧</t>
+      <c r="AF34" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -6549,14 +6553,14 @@
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" s="37" t="n"/>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>account_id</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n"/>
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
@@ -6567,7 +6571,7 @@
       <c r="L35" s="11" t="n"/>
       <c r="M35" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N35" s="10" t="n"/>
@@ -6575,7 +6579,7 @@
       <c r="P35" s="11" t="n"/>
       <c r="Q35" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="R35" s="10" t="n"/>
@@ -6598,7 +6602,7 @@
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>アカウントID</t>
+          <t>アカウント一覧</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -6609,12 +6613,12 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C36" s="37" t="n"/>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>login_id</t>
+          <t>account_id</t>
         </is>
       </c>
       <c r="E36" s="10" t="n"/>
@@ -6627,7 +6631,7 @@
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N36" s="10" t="n"/>
@@ -6658,7 +6662,7 @@
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>ログインID</t>
+          <t>アカウントID</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -6669,12 +6673,12 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>account_name</t>
+          <t>login_id</t>
         </is>
       </c>
       <c r="E37" s="10" t="n"/>
@@ -6718,7 +6722,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>アカウント名</t>
+          <t>ログインID</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -6729,12 +6733,12 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>account_name</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -6747,7 +6751,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -6778,7 +6782,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>管理者区分ID</t>
+          <t>アカウント名</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -6789,12 +6793,12 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -6807,7 +6811,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -6838,7 +6842,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>管理者区分名称</t>
+          <t>管理者区分ID</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -6849,12 +6853,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>todofuken_code</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -6887,7 +6891,7 @@
       <c r="X40" s="11" t="n"/>
       <c r="Y40" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z40" s="10" t="n"/>
@@ -6898,7 +6902,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード</t>
+          <t>管理者区分名称</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -6909,12 +6913,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>todofuken_name</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -6958,7 +6962,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>都道府県名</t>
+          <t>都道府県コード</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -6969,12 +6973,12 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>todofuken_name</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -6987,7 +6991,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -7018,7 +7022,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>都道府県名</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -7029,12 +7033,12 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>ja_name</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -7047,7 +7051,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N43" s="10" t="n"/>
@@ -7078,7 +7082,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>JA名称</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -7089,12 +7093,12 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_id</t>
+          <t>ja_name</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -7107,7 +7111,7 @@
       <c r="L44" s="11" t="n"/>
       <c r="M44" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N44" s="10" t="n"/>
@@ -7138,7 +7142,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID</t>
+          <t>JA名称</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -7149,12 +7153,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -7167,7 +7171,7 @@
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N45" s="10" t="n"/>
@@ -7198,7 +7202,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>管理支店名称</t>
+          <t>管理支店ID</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -7209,12 +7213,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>paper_flg</t>
+          <t>kanri_shiten_name</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -7227,7 +7231,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -7247,7 +7251,7 @@
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z46" s="10" t="n"/>
@@ -7258,7 +7262,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>紙版取扱フラグ</t>
+          <t>管理支店名称</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -7269,12 +7273,12 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>denshi_flg</t>
+          <t>paper_flg</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -7318,7 +7322,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>電子版取扱フラグ</t>
+          <t>紙版取扱フラグ</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -7329,12 +7333,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>denshi_flg</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -7347,7 +7351,7 @@
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N48" s="10" t="n"/>
@@ -7360,11 +7364,7 @@
       </c>
       <c r="R48" s="10" t="n"/>
       <c r="S48" s="11" t="n"/>
-      <c r="T48" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T48" s="17" t="inlineStr"/>
       <c r="U48" s="10" t="n"/>
       <c r="V48" s="10" t="n"/>
       <c r="W48" s="10" t="n"/>
@@ -7382,7 +7382,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>電子版取扱フラグ</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -7393,12 +7393,12 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="C49" s="39" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -7435,7 +7435,7 @@
       <c r="X49" s="11" t="n"/>
       <c r="Y49" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z49" s="10" t="n"/>
@@ -7446,7 +7446,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -7457,14 +7457,14 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="C50" s="39" t="n"/>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
       <c r="E50" s="10" t="n"/>
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
@@ -7475,7 +7475,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -7488,14 +7488,18 @@
       </c>
       <c r="R50" s="10" t="n"/>
       <c r="S50" s="11" t="n"/>
-      <c r="T50" s="17" t="inlineStr"/>
+      <c r="T50" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U50" s="10" t="n"/>
       <c r="V50" s="10" t="n"/>
       <c r="W50" s="10" t="n"/>
       <c r="X50" s="11" t="n"/>
       <c r="Y50" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z50" s="10" t="n"/>
@@ -7506,7 +7510,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>更新日時</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -7517,14 +7521,14 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="C51" s="37" t="n"/>
-      <c r="D51" s="19" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n"/>
       <c r="E51" s="10" t="n"/>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
@@ -7535,7 +7539,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N51" s="10" t="n"/>
@@ -7566,7 +7570,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>ページネーション情報</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -7577,12 +7581,12 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>19</v>
-      </c>
-      <c r="C52" s="38" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="C52" s="37" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -7626,7 +7630,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>現在ページ</t>
+          <t>総件数</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -7637,12 +7641,12 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>page</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -7686,7 +7690,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数</t>
+          <t>現在ページ</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -7697,12 +7701,12 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>21</v>
-      </c>
-      <c r="C54" s="39" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="C54" s="38" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>total_pages</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
@@ -7746,7 +7750,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>1ページあたりの件数</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -7755,64 +7759,124 @@
       <c r="AJ54" s="10" t="n"/>
       <c r="AK54" s="11" t="n"/>
     </row>
-    <row r="55" ht="19.5" customHeight="1"/>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="B56" s="40" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="C55" s="39" t="n"/>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="11" t="n"/>
+      <c r="M55" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="11" t="n"/>
+      <c r="Q55" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="11" t="n"/>
+      <c r="T55" s="17" t="inlineStr"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="11" t="n"/>
+      <c r="Y55" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+      <c r="AC55" s="10" t="n"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="11" t="n"/>
+      <c r="AF55" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
+      <c r="AG55" s="10" t="n"/>
+      <c r="AH55" s="10" t="n"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
+      <c r="AK55" s="11" t="n"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="1"/>
+    <row r="57" ht="19.5" customHeight="1">
+      <c r="B57" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="C57" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/accounts?login_id=admin&amp;role_id=1&amp;page=1&amp;per_page=20&amp;sort_by=created_at&amp;sort_order=desc</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="n"/>
-      <c r="E57" s="10" t="n"/>
-      <c r="F57" s="10" t="n"/>
-      <c r="G57" s="10" t="n"/>
-      <c r="H57" s="10" t="n"/>
-      <c r="I57" s="10" t="n"/>
-      <c r="J57" s="10" t="n"/>
-      <c r="K57" s="10" t="n"/>
-      <c r="L57" s="10" t="n"/>
-      <c r="M57" s="10" t="n"/>
-      <c r="N57" s="10" t="n"/>
-      <c r="O57" s="10" t="n"/>
-      <c r="P57" s="10" t="n"/>
-      <c r="Q57" s="10" t="n"/>
-      <c r="R57" s="10" t="n"/>
-      <c r="S57" s="10" t="n"/>
-      <c r="T57" s="10" t="n"/>
-      <c r="U57" s="10" t="n"/>
-      <c r="V57" s="10" t="n"/>
-      <c r="W57" s="10" t="n"/>
-      <c r="X57" s="10" t="n"/>
-      <c r="Y57" s="10" t="n"/>
-      <c r="Z57" s="10" t="n"/>
-      <c r="AA57" s="10" t="n"/>
-      <c r="AB57" s="10" t="n"/>
-      <c r="AC57" s="10" t="n"/>
-      <c r="AD57" s="10" t="n"/>
-      <c r="AE57" s="10" t="n"/>
-      <c r="AF57" s="10" t="n"/>
-      <c r="AG57" s="10" t="n"/>
-      <c r="AH57" s="10" t="n"/>
-      <c r="AI57" s="10" t="n"/>
-      <c r="AJ57" s="10" t="n"/>
-      <c r="AK57" s="11" t="n"/>
-    </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="B59" s="40" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="C58" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/accounts?login_id=admin&amp;role_id=4&amp;todofuken_code=13&amp;ja_id=10&amp;page=1&amp;per_page=20&amp;sort_by=created_at&amp;sort_order=desc</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="10" t="n"/>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="10" t="n"/>
+      <c r="AF58" s="10" t="n"/>
+      <c r="AG58" s="10" t="n"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
+      <c r="AK58" s="11" t="n"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="409" customHeight="1">
-      <c r="C60" s="19" t="inlineStr">
+    <row r="61" ht="409" customHeight="1">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -7860,50 +7924,50 @@
 }</t>
         </is>
       </c>
-      <c r="D60" s="10" t="n"/>
-      <c r="E60" s="10" t="n"/>
-      <c r="F60" s="10" t="n"/>
-      <c r="G60" s="10" t="n"/>
-      <c r="H60" s="10" t="n"/>
-      <c r="I60" s="10" t="n"/>
-      <c r="J60" s="10" t="n"/>
-      <c r="K60" s="10" t="n"/>
-      <c r="L60" s="10" t="n"/>
-      <c r="M60" s="10" t="n"/>
-      <c r="N60" s="10" t="n"/>
-      <c r="O60" s="10" t="n"/>
-      <c r="P60" s="10" t="n"/>
-      <c r="Q60" s="10" t="n"/>
-      <c r="R60" s="10" t="n"/>
-      <c r="S60" s="10" t="n"/>
-      <c r="T60" s="10" t="n"/>
-      <c r="U60" s="10" t="n"/>
-      <c r="V60" s="10" t="n"/>
-      <c r="W60" s="10" t="n"/>
-      <c r="X60" s="10" t="n"/>
-      <c r="Y60" s="10" t="n"/>
-      <c r="Z60" s="10" t="n"/>
-      <c r="AA60" s="10" t="n"/>
-      <c r="AB60" s="10" t="n"/>
-      <c r="AC60" s="10" t="n"/>
-      <c r="AD60" s="10" t="n"/>
-      <c r="AE60" s="10" t="n"/>
-      <c r="AF60" s="10" t="n"/>
-      <c r="AG60" s="10" t="n"/>
-      <c r="AH60" s="10" t="n"/>
-      <c r="AI60" s="10" t="n"/>
-      <c r="AJ60" s="10" t="n"/>
-      <c r="AK60" s="11" t="n"/>
-    </row>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="B62" s="40" t="inlineStr">
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="10" t="n"/>
+      <c r="J61" s="10" t="n"/>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="10" t="n"/>
+      <c r="X61" s="10" t="n"/>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="10" t="n"/>
+      <c r="AE61" s="10" t="n"/>
+      <c r="AF61" s="10" t="n"/>
+      <c r="AG61" s="10" t="n"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="10" t="n"/>
+      <c r="AJ61" s="10" t="n"/>
+      <c r="AK61" s="11" t="n"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="B63" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="72" customHeight="1">
-      <c r="C63" s="19" t="inlineStr">
+    <row r="64" ht="72" customHeight="1">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -7911,50 +7975,50 @@
 }</t>
         </is>
       </c>
-      <c r="D63" s="10" t="n"/>
-      <c r="E63" s="10" t="n"/>
-      <c r="F63" s="10" t="n"/>
-      <c r="G63" s="10" t="n"/>
-      <c r="H63" s="10" t="n"/>
-      <c r="I63" s="10" t="n"/>
-      <c r="J63" s="10" t="n"/>
-      <c r="K63" s="10" t="n"/>
-      <c r="L63" s="10" t="n"/>
-      <c r="M63" s="10" t="n"/>
-      <c r="N63" s="10" t="n"/>
-      <c r="O63" s="10" t="n"/>
-      <c r="P63" s="10" t="n"/>
-      <c r="Q63" s="10" t="n"/>
-      <c r="R63" s="10" t="n"/>
-      <c r="S63" s="10" t="n"/>
-      <c r="T63" s="10" t="n"/>
-      <c r="U63" s="10" t="n"/>
-      <c r="V63" s="10" t="n"/>
-      <c r="W63" s="10" t="n"/>
-      <c r="X63" s="10" t="n"/>
-      <c r="Y63" s="10" t="n"/>
-      <c r="Z63" s="10" t="n"/>
-      <c r="AA63" s="10" t="n"/>
-      <c r="AB63" s="10" t="n"/>
-      <c r="AC63" s="10" t="n"/>
-      <c r="AD63" s="10" t="n"/>
-      <c r="AE63" s="10" t="n"/>
-      <c r="AF63" s="10" t="n"/>
-      <c r="AG63" s="10" t="n"/>
-      <c r="AH63" s="10" t="n"/>
-      <c r="AI63" s="10" t="n"/>
-      <c r="AJ63" s="10" t="n"/>
-      <c r="AK63" s="11" t="n"/>
-    </row>
-    <row r="65" ht="19.5" customHeight="1">
-      <c r="B65" s="40" t="inlineStr">
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="n"/>
+      <c r="J64" s="10" t="n"/>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="10" t="n"/>
+      <c r="X64" s="10" t="n"/>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="10" t="n"/>
+      <c r="AE64" s="10" t="n"/>
+      <c r="AF64" s="10" t="n"/>
+      <c r="AG64" s="10" t="n"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="10" t="n"/>
+      <c r="AJ64" s="10" t="n"/>
+      <c r="AK64" s="11" t="n"/>
+    </row>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="B66" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="72" customHeight="1">
-      <c r="C66" s="19" t="inlineStr">
+    <row r="67" ht="72" customHeight="1">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -7962,50 +8026,50 @@
 }</t>
         </is>
       </c>
-      <c r="D66" s="10" t="n"/>
-      <c r="E66" s="10" t="n"/>
-      <c r="F66" s="10" t="n"/>
-      <c r="G66" s="10" t="n"/>
-      <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="n"/>
-      <c r="J66" s="10" t="n"/>
-      <c r="K66" s="10" t="n"/>
-      <c r="L66" s="10" t="n"/>
-      <c r="M66" s="10" t="n"/>
-      <c r="N66" s="10" t="n"/>
-      <c r="O66" s="10" t="n"/>
-      <c r="P66" s="10" t="n"/>
-      <c r="Q66" s="10" t="n"/>
-      <c r="R66" s="10" t="n"/>
-      <c r="S66" s="10" t="n"/>
-      <c r="T66" s="10" t="n"/>
-      <c r="U66" s="10" t="n"/>
-      <c r="V66" s="10" t="n"/>
-      <c r="W66" s="10" t="n"/>
-      <c r="X66" s="10" t="n"/>
-      <c r="Y66" s="10" t="n"/>
-      <c r="Z66" s="10" t="n"/>
-      <c r="AA66" s="10" t="n"/>
-      <c r="AB66" s="10" t="n"/>
-      <c r="AC66" s="10" t="n"/>
-      <c r="AD66" s="10" t="n"/>
-      <c r="AE66" s="10" t="n"/>
-      <c r="AF66" s="10" t="n"/>
-      <c r="AG66" s="10" t="n"/>
-      <c r="AH66" s="10" t="n"/>
-      <c r="AI66" s="10" t="n"/>
-      <c r="AJ66" s="10" t="n"/>
-      <c r="AK66" s="11" t="n"/>
-    </row>
-    <row r="68" ht="19.5" customHeight="1">
-      <c r="B68" s="40" t="inlineStr">
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="n"/>
+      <c r="J67" s="10" t="n"/>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="10" t="n"/>
+      <c r="Q67" s="10" t="n"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="10" t="n"/>
+      <c r="X67" s="10" t="n"/>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="10" t="n"/>
+      <c r="AE67" s="10" t="n"/>
+      <c r="AF67" s="10" t="n"/>
+      <c r="AG67" s="10" t="n"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="10" t="n"/>
+      <c r="AJ67" s="10" t="n"/>
+      <c r="AK67" s="11" t="n"/>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="B69" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="72" customHeight="1">
-      <c r="C69" s="19" t="inlineStr">
+    <row r="70" ht="72" customHeight="1">
+      <c r="C70" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -8013,294 +8077,309 @@
 }</t>
         </is>
       </c>
-      <c r="D69" s="10" t="n"/>
-      <c r="E69" s="10" t="n"/>
-      <c r="F69" s="10" t="n"/>
-      <c r="G69" s="10" t="n"/>
-      <c r="H69" s="10" t="n"/>
-      <c r="I69" s="10" t="n"/>
-      <c r="J69" s="10" t="n"/>
-      <c r="K69" s="10" t="n"/>
-      <c r="L69" s="10" t="n"/>
-      <c r="M69" s="10" t="n"/>
-      <c r="N69" s="10" t="n"/>
-      <c r="O69" s="10" t="n"/>
-      <c r="P69" s="10" t="n"/>
-      <c r="Q69" s="10" t="n"/>
-      <c r="R69" s="10" t="n"/>
-      <c r="S69" s="10" t="n"/>
-      <c r="T69" s="10" t="n"/>
-      <c r="U69" s="10" t="n"/>
-      <c r="V69" s="10" t="n"/>
-      <c r="W69" s="10" t="n"/>
-      <c r="X69" s="10" t="n"/>
-      <c r="Y69" s="10" t="n"/>
-      <c r="Z69" s="10" t="n"/>
-      <c r="AA69" s="10" t="n"/>
-      <c r="AB69" s="10" t="n"/>
-      <c r="AC69" s="10" t="n"/>
-      <c r="AD69" s="10" t="n"/>
-      <c r="AE69" s="10" t="n"/>
-      <c r="AF69" s="10" t="n"/>
-      <c r="AG69" s="10" t="n"/>
-      <c r="AH69" s="10" t="n"/>
-      <c r="AI69" s="10" t="n"/>
-      <c r="AJ69" s="10" t="n"/>
-      <c r="AK69" s="11" t="n"/>
-    </row>
-    <row r="71" ht="19.5" customHeight="1"/>
-    <row r="72" ht="19.5" customHeight="1">
-      <c r="A72" s="27" t="inlineStr">
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="n"/>
+      <c r="J70" s="10" t="n"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="10" t="n"/>
+      <c r="X70" s="10" t="n"/>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="10" t="n"/>
+      <c r="AE70" s="10" t="n"/>
+      <c r="AF70" s="10" t="n"/>
+      <c r="AG70" s="10" t="n"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="10" t="n"/>
+      <c r="AJ70" s="10" t="n"/>
+      <c r="AK70" s="11" t="n"/>
+    </row>
+    <row r="72" ht="19.5" customHeight="1"/>
+    <row r="73" ht="19.5" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="B73" s="27" t="inlineStr">
+    <row r="74" ht="18" customHeight="1">
+      <c r="B74" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="C74" s="41" t="inlineStr">
+    <row r="75" ht="18" customHeight="1">
+      <c r="C75" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="D75" s="41" t="inlineStr">
-        <is>
-          <t>login_id：最大20桁、文字列</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="D76" s="41" t="inlineStr">
         <is>
-          <t>role_id：1〜5の整数</t>
+          <t>login_id：最大20桁、文字列</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="D77" s="41" t="inlineStr">
         <is>
-          <t>ja_id：数値型チェック</t>
+          <t>role_id：1〜5の整数</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="D78" s="41" t="inlineStr">
         <is>
-          <t>kanri_shiten_id：数値型チェック</t>
+          <t>todofuken_code：2桁の文字列（01〜47）</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="D79" s="41" t="inlineStr">
         <is>
-          <t>page：正の整数（デフォルト: 1）</t>
+          <t>ja_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="D80" s="41" t="inlineStr">
         <is>
-          <t>per_page：1〜100の整数（デフォルト: 20）</t>
+          <t>kanri_shiten_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="D81" s="41" t="inlineStr">
         <is>
-          <t>sort_by：許可されたカラム名（login_id, role_id, created_at）</t>
+          <t>page：正の整数（デフォルト: 1）</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>sort_order：asc または desc（デフォルト: desc）</t>
+          <t>per_page：1〜100の整数（デフォルト: 20）</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="C83" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
+      <c r="D83" s="41" t="inlineStr">
+        <is>
+          <t>sort_by：許可されたカラム名（login_id, role_id, created_at）</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="D84" s="41" t="inlineStr">
         <is>
+          <t>sort_order：asc または desc（デフォルト: desc）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="D86" s="41" t="inlineStr">
+        <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="B85" s="27" t="inlineStr">
+    <row r="87" ht="18" customHeight="1">
+      <c r="B87" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="C87" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="C88" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：`account.view` を保持しているか確認する。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="D89" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
+      <c r="C89" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+          <t>権限チェック：`account.view` を保持しているか確認する。</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="B91" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="C94" s="41" t="inlineStr">
+        <is>
           <t>検索条件を構築する。</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="36" customHeight="1">
-      <c r="D93" s="41" t="inlineStr">
+    <row r="95" ht="36" customHeight="1">
+      <c r="D95" s="41" t="inlineStr">
         <is>
           <t>login_id が指定されている場合：`LIKE '%' || :login_id || '%'`（部分一致）</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="D94" s="41" t="inlineStr">
+    <row r="96" ht="18" customHeight="1">
+      <c r="D96" s="41" t="inlineStr">
         <is>
           <t>role_id が指定されている場合：`= :role_id`（完全一致）</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="D95" s="41" t="inlineStr">
+    <row r="97" ht="36" customHeight="1">
+      <c r="D97" s="41" t="inlineStr">
+        <is>
+          <t>todofuken_code が指定されている場合：`= :todofuken_code`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="D98" s="41" t="inlineStr">
         <is>
           <t>ja_id が指定されている場合：`= :ja_id`（完全一致）</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="36" customHeight="1">
-      <c r="D96" s="41" t="inlineStr">
+    <row r="99" ht="36" customHeight="1">
+      <c r="D99" s="41" t="inlineStr">
         <is>
           <t>kanri_shiten_id が指定されている場合：`= :kanri_shiten_id`（完全一致）</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="18" customHeight="1">
-      <c r="C97" s="41" t="inlineStr">
+    <row r="100" ht="18" customHeight="1">
+      <c r="C100" s="41" t="inlineStr">
         <is>
           <t>常に `deleted_at IS NULL` でフィルタリングする。</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
+    <row r="101" ht="18" customHeight="1">
+      <c r="C101" s="41" t="inlineStr">
         <is>
           <t>NICHINO_ADMINは全アカウントを参照可能（DataScope制限なし）。</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="B99" s="27" t="inlineStr">
+    <row r="102" ht="18" customHeight="1">
+      <c r="B102" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="126" customHeight="1">
-      <c r="C100" s="42" t="inlineStr">
+    <row r="103" ht="144" customHeight="1">
+      <c r="C103" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS total
 FROM m_account a
 WHERE a.deleted_at IS NULL
   AND (:login_id IS NULL OR a.login_id LIKE '%' || :login_id || '%')
   AND (:role_id IS NULL OR a.role_id = :role_id)
+  AND (:todofuken_code IS NULL OR a.todofuken_code = :todofuken_code)
   AND (:ja_id IS NULL OR a.ja_id = :ja_id)
   AND (:kanri_shiten_id IS NULL OR a.kanri_shiten_id = :kanri_shiten_id)</t>
         </is>
       </c>
-      <c r="D100" s="10" t="n"/>
-      <c r="E100" s="10" t="n"/>
-      <c r="F100" s="10" t="n"/>
-      <c r="G100" s="10" t="n"/>
-      <c r="H100" s="10" t="n"/>
-      <c r="I100" s="10" t="n"/>
-      <c r="J100" s="10" t="n"/>
-      <c r="K100" s="10" t="n"/>
-      <c r="L100" s="10" t="n"/>
-      <c r="M100" s="10" t="n"/>
-      <c r="N100" s="10" t="n"/>
-      <c r="O100" s="10" t="n"/>
-      <c r="P100" s="10" t="n"/>
-      <c r="Q100" s="10" t="n"/>
-      <c r="R100" s="10" t="n"/>
-      <c r="S100" s="10" t="n"/>
-      <c r="T100" s="10" t="n"/>
-      <c r="U100" s="10" t="n"/>
-      <c r="V100" s="10" t="n"/>
-      <c r="W100" s="10" t="n"/>
-      <c r="X100" s="10" t="n"/>
-      <c r="Y100" s="10" t="n"/>
-      <c r="Z100" s="10" t="n"/>
-      <c r="AA100" s="10" t="n"/>
-      <c r="AB100" s="10" t="n"/>
-      <c r="AC100" s="10" t="n"/>
-      <c r="AD100" s="10" t="n"/>
-      <c r="AE100" s="10" t="n"/>
-      <c r="AF100" s="10" t="n"/>
-      <c r="AG100" s="10" t="n"/>
-      <c r="AH100" s="10" t="n"/>
-      <c r="AI100" s="10" t="n"/>
-      <c r="AJ100" s="10" t="n"/>
-      <c r="AK100" s="11" t="n"/>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="B101" s="27" t="inlineStr">
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="10" t="n"/>
+      <c r="F103" s="10" t="n"/>
+      <c r="G103" s="10" t="n"/>
+      <c r="H103" s="10" t="n"/>
+      <c r="I103" s="10" t="n"/>
+      <c r="J103" s="10" t="n"/>
+      <c r="K103" s="10" t="n"/>
+      <c r="L103" s="10" t="n"/>
+      <c r="M103" s="10" t="n"/>
+      <c r="N103" s="10" t="n"/>
+      <c r="O103" s="10" t="n"/>
+      <c r="P103" s="10" t="n"/>
+      <c r="Q103" s="10" t="n"/>
+      <c r="R103" s="10" t="n"/>
+      <c r="S103" s="10" t="n"/>
+      <c r="T103" s="10" t="n"/>
+      <c r="U103" s="10" t="n"/>
+      <c r="V103" s="10" t="n"/>
+      <c r="W103" s="10" t="n"/>
+      <c r="X103" s="10" t="n"/>
+      <c r="Y103" s="10" t="n"/>
+      <c r="Z103" s="10" t="n"/>
+      <c r="AA103" s="10" t="n"/>
+      <c r="AB103" s="10" t="n"/>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="10" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="10" t="n"/>
+      <c r="AK103" s="11" t="n"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="B104" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="360" customHeight="1">
-      <c r="C102" s="42" t="inlineStr">
+    <row r="105" ht="378" customHeight="1">
+      <c r="C105" s="42" t="inlineStr">
         <is>
           <t>SELECT a.account_id, a.login_id, a.account_name,
        a.role_id, r.role_name,
@@ -8317,6 +8396,7 @@
 WHERE a.deleted_at IS NULL
   AND (:login_id IS NULL OR a.login_id LIKE '%' || :login_id || '%')
   AND (:role_id IS NULL OR a.role_id = :role_id)
+  AND (:todofuken_code IS NULL OR a.todofuken_code = :todofuken_code)
   AND (:ja_id IS NULL OR a.ja_id = :ja_id)
   AND (:kanri_shiten_id IS NULL OR a.kanri_shiten_id = :kanri_shiten_id)
 ORDER BY a.:sort_by :sort_order
@@ -8324,177 +8404,173 @@
 OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n"/>
-      <c r="E102" s="10" t="n"/>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="10" t="n"/>
-      <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="n"/>
-      <c r="J102" s="10" t="n"/>
-      <c r="K102" s="10" t="n"/>
-      <c r="L102" s="10" t="n"/>
-      <c r="M102" s="10" t="n"/>
-      <c r="N102" s="10" t="n"/>
-      <c r="O102" s="10" t="n"/>
-      <c r="P102" s="10" t="n"/>
-      <c r="Q102" s="10" t="n"/>
-      <c r="R102" s="10" t="n"/>
-      <c r="S102" s="10" t="n"/>
-      <c r="T102" s="10" t="n"/>
-      <c r="U102" s="10" t="n"/>
-      <c r="V102" s="10" t="n"/>
-      <c r="W102" s="10" t="n"/>
-      <c r="X102" s="10" t="n"/>
-      <c r="Y102" s="10" t="n"/>
-      <c r="Z102" s="10" t="n"/>
-      <c r="AA102" s="10" t="n"/>
-      <c r="AB102" s="10" t="n"/>
-      <c r="AC102" s="10" t="n"/>
-      <c r="AD102" s="10" t="n"/>
-      <c r="AE102" s="10" t="n"/>
-      <c r="AF102" s="10" t="n"/>
-      <c r="AG102" s="10" t="n"/>
-      <c r="AH102" s="10" t="n"/>
-      <c r="AI102" s="10" t="n"/>
-      <c r="AJ102" s="10" t="n"/>
-      <c r="AK102" s="11" t="n"/>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="B103" s="27" t="inlineStr">
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="10" t="n"/>
+      <c r="F105" s="10" t="n"/>
+      <c r="G105" s="10" t="n"/>
+      <c r="H105" s="10" t="n"/>
+      <c r="I105" s="10" t="n"/>
+      <c r="J105" s="10" t="n"/>
+      <c r="K105" s="10" t="n"/>
+      <c r="L105" s="10" t="n"/>
+      <c r="M105" s="10" t="n"/>
+      <c r="N105" s="10" t="n"/>
+      <c r="O105" s="10" t="n"/>
+      <c r="P105" s="10" t="n"/>
+      <c r="Q105" s="10" t="n"/>
+      <c r="R105" s="10" t="n"/>
+      <c r="S105" s="10" t="n"/>
+      <c r="T105" s="10" t="n"/>
+      <c r="U105" s="10" t="n"/>
+      <c r="V105" s="10" t="n"/>
+      <c r="W105" s="10" t="n"/>
+      <c r="X105" s="10" t="n"/>
+      <c r="Y105" s="10" t="n"/>
+      <c r="Z105" s="10" t="n"/>
+      <c r="AA105" s="10" t="n"/>
+      <c r="AB105" s="10" t="n"/>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="10" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="10" t="n"/>
+      <c r="AK105" s="11" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="B106" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="C104" s="41" t="inlineStr">
+    <row r="107" ht="18" customHeight="1">
+      <c r="C107" s="41" t="inlineStr">
         <is>
           <t>取得結果を data 配列として返却する。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="C105" s="41" t="inlineStr">
+    <row r="108" ht="18" customHeight="1">
+      <c r="C108" s="41" t="inlineStr">
         <is>
           <t>ページネーション情報を meta オブジェクトとして返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="D106" s="41" t="inlineStr">
-        <is>
-          <t>total：4.4 で取得した総件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="D107" s="41" t="inlineStr">
-        <is>
-          <t>page：リクエストの page</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="D108" s="41" t="inlineStr">
-        <is>
-          <t>per_page：リクエストの per_page</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="D109" s="41" t="inlineStr">
         <is>
+          <t>total：4.4 で取得した総件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="D110" s="41" t="inlineStr">
+        <is>
+          <t>page：リクエストの page</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="D111" s="41" t="inlineStr">
+        <is>
+          <t>per_page：リクエストの per_page</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="D112" s="41" t="inlineStr">
+        <is>
           <t>total_pages：CEIL(total / per_page)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="36" customHeight="1">
-      <c r="C110" s="41" t="inlineStr">
+    <row r="113" ht="36" customHeight="1">
+      <c r="C113" s="41" t="inlineStr">
         <is>
           <t>検索結果が0件の場合：data は空配列 `[]`、meta.total = 0 で返却（HTTP 200）。</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="B111" s="27" t="inlineStr">
+    <row r="114" ht="18" customHeight="1">
+      <c r="B114" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="C112" s="41" t="inlineStr">
+    <row r="115" ht="18" customHeight="1">
+      <c r="C115" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="288">
+  <mergeCells count="297">
+    <mergeCell ref="B102:AK102"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="C57:AK57"/>
+    <mergeCell ref="D78:AK78"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="T24:X24"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="C66:AK66"/>
     <mergeCell ref="Y45:AE45"/>
-    <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D48:L48"/>
     <mergeCell ref="M29:P29"/>
-    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="AF21:AK21"/>
     <mergeCell ref="T53:X53"/>
-    <mergeCell ref="B56:I56"/>
+    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="M46:P46"/>
+    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="D82:AK82"/>
     <mergeCell ref="M43:P43"/>
-    <mergeCell ref="B73:AK73"/>
     <mergeCell ref="Y52:AE52"/>
     <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="C34:L34"/>
     <mergeCell ref="AF50:AK50"/>
+    <mergeCell ref="T55:X55"/>
+    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="C100:AK100"/>
-    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
-    <mergeCell ref="D51:L51"/>
     <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="D106:AK106"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="Y21:AB21"/>
     <mergeCell ref="AF22:AK22"/>
     <mergeCell ref="M35:P35"/>
+    <mergeCell ref="D99:AK99"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="D35:L35"/>
     <mergeCell ref="M54:P54"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
-    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B114:AK114"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="B68:I68"/>
     <mergeCell ref="C22:L22"/>
-    <mergeCell ref="Q33:S33"/>
     <mergeCell ref="D77:AK77"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
@@ -8502,39 +8578,37 @@
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="AF49:AK49"/>
-    <mergeCell ref="B91:AK91"/>
+    <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="D36:L36"/>
-    <mergeCell ref="D75:AK75"/>
-    <mergeCell ref="M33:P33"/>
     <mergeCell ref="M45:P45"/>
+    <mergeCell ref="T30:X30"/>
+    <mergeCell ref="B93:AK93"/>
     <mergeCell ref="T29:X29"/>
+    <mergeCell ref="D112:AK112"/>
     <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="B59:I59"/>
+    <mergeCell ref="A32:AK32"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="M47:P47"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="D53:L53"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="AC29:AE29"/>
-    <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B101:AK101"/>
+    <mergeCell ref="AF55:AK55"/>
     <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="C104:AK104"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="D37:L37"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="T54:X54"/>
-    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="C88:AK88"/>
     <mergeCell ref="Y53:AE53"/>
-    <mergeCell ref="D89:AK89"/>
-    <mergeCell ref="B103:AK103"/>
+    <mergeCell ref="D98:AK98"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
@@ -8542,36 +8616,41 @@
     <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="D39:L39"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="C33:L33"/>
     <mergeCell ref="M44:P44"/>
+    <mergeCell ref="Q48:S48"/>
     <mergeCell ref="AC21:AE21"/>
-    <mergeCell ref="Q48:S48"/>
+    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="D79:AK79"/>
+    <mergeCell ref="C103:AK103"/>
+    <mergeCell ref="C51:L51"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
+    <mergeCell ref="Y55:AE55"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
+    <mergeCell ref="C35:L35"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="C50:L50"/>
+    <mergeCell ref="B104:AK104"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
+    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
-    <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="B106:AK106"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M21:P21"/>
+    <mergeCell ref="C61:AK61"/>
     <mergeCell ref="D76:AK76"/>
-    <mergeCell ref="D107:AK107"/>
     <mergeCell ref="T46:X46"/>
+    <mergeCell ref="B63:I63"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="M27:P27"/>
@@ -8587,21 +8666,20 @@
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="Q50:S50"/>
-    <mergeCell ref="C87:AK87"/>
+    <mergeCell ref="B66:I66"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="T42:X42"/>
+    <mergeCell ref="C28:L28"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="C28:L28"/>
-    <mergeCell ref="D78:AK78"/>
     <mergeCell ref="Y41:AE41"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
     <mergeCell ref="AC25:AE25"/>
-    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="M50:P50"/>
-    <mergeCell ref="A72:AK72"/>
+    <mergeCell ref="C107:AK107"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
@@ -8610,20 +8688,26 @@
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T44:X44"/>
+    <mergeCell ref="C64:AK64"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="Y43:AE43"/>
-    <mergeCell ref="D94:AK94"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="A31:AK31"/>
+    <mergeCell ref="M55:P55"/>
+    <mergeCell ref="D55:L55"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M49:P49"/>
-    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="T21:X21"/>
     <mergeCell ref="M39:P39"/>
+    <mergeCell ref="C52:C55"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
+    <mergeCell ref="B69:I69"/>
     <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="A73:AK73"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
@@ -8639,6 +8723,7 @@
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="Q21:S21"/>
     <mergeCell ref="D96:AK96"/>
+    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="D46:L46"/>
@@ -8650,10 +8735,14 @@
     <mergeCell ref="T27:X27"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="T36:X36"/>
+    <mergeCell ref="Q55:S55"/>
     <mergeCell ref="B14:I17"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="D97:AK97"/>
     <mergeCell ref="Y46:AE46"/>
+    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
@@ -8664,33 +8753,33 @@
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="Y48:AE48"/>
-    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="C92:AK92"/>
-    <mergeCell ref="D93:AK93"/>
-    <mergeCell ref="B111:AK111"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="C35:C49"/>
     <mergeCell ref="D43:L43"/>
+    <mergeCell ref="D83:AK83"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="A19:AK19"/>
-    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
+    <mergeCell ref="B60:I60"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B99:AK99"/>
+    <mergeCell ref="D110:AK110"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="C36:C50"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="B74:AK74"/>
     <mergeCell ref="D109:AK109"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
+    <mergeCell ref="D50:L50"/>
     <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
     <mergeCell ref="Q53:S53"/>
@@ -8698,18 +8787,17 @@
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
+    <mergeCell ref="D111:AK111"/>
     <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="C60:AK60"/>
-    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="AF48:AK48"/>
-    <mergeCell ref="D108:AK108"/>
+    <mergeCell ref="D86:AK86"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
     <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="D95:AK95"/>
     <mergeCell ref="AC28:AE28"/>
-    <mergeCell ref="C110:AK110"/>
+    <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="C21:L21"/>
@@ -8719,6 +8807,7 @@
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="AC30:AE30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8730,7 +8819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK85"/>
+  <dimension ref="A1:AK84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -8891,7 +8980,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -9245,7 +9334,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -9297,7 +9386,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>正常にアカウントを削除しました</t>
+          <t>削除しました</t>
         </is>
       </c>
       <c r="O14" s="10" t="n"/>
@@ -9449,7 +9538,7 @@
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>このレコードは現在使用中のため、削除できません。</t>
+          <t>関連データが存在するため削除できません。</t>
         </is>
       </c>
       <c r="O18" s="10" t="n"/>
@@ -9854,7 +9943,7 @@
       <c r="C35" s="19" t="inlineStr">
         <is>
           <t>{
-  "message": "正常に削除しました"
+  "message": "削除しました。"
 }</t>
         </is>
       </c>
@@ -10058,7 +10147,7 @@
         <is>
           <t>{
   "error_code": "CONFLICT",
-  "message": "このレコードは現在使用中のため、削除できません。"
+  "message": "関連データが存在するため削除できません。"
 }</t>
         </is>
       </c>
@@ -10156,59 +10245,96 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="B54" s="27" t="inlineStr">
+    <row r="54" ht="54" customHeight="1">
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="10" t="n"/>
+      <c r="AF54" s="10" t="n"/>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="C55" s="41" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="C56" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="D56" s="41" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="D57" s="41" t="inlineStr">
         <is>
           <t>account_id：数値型チェック、必須チェック</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="C57" s="41" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="C58" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="D58" s="41" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="D59" s="41" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="B59" s="27" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="C60" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="C61" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -10234,28 +10360,21 @@
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>自分自身のアカウントは削除不可とする。</t>
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定（存在確認・関連データチェック）</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="B66" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定（存在確認・関連データチェック）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="C67" s="41" t="inlineStr">
+      <c r="C66" s="41" t="inlineStr">
         <is>
           <t>対象アカウントの存在を確認する。</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="126" customHeight="1">
-      <c r="C68" s="42" t="inlineStr">
+    <row r="67" ht="126" customHeight="1">
+      <c r="C67" s="42" t="inlineStr">
         <is>
           <t>SELECT a.account_id, a.login_id, a.account_name, a.role_id,
        a.ja_id, a.kanri_shiten_id, a.todofuken_code,
@@ -10266,57 +10385,57 @@
   AND a.deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D68" s="10" t="n"/>
-      <c r="E68" s="10" t="n"/>
-      <c r="F68" s="10" t="n"/>
-      <c r="G68" s="10" t="n"/>
-      <c r="H68" s="10" t="n"/>
-      <c r="I68" s="10" t="n"/>
-      <c r="J68" s="10" t="n"/>
-      <c r="K68" s="10" t="n"/>
-      <c r="L68" s="10" t="n"/>
-      <c r="M68" s="10" t="n"/>
-      <c r="N68" s="10" t="n"/>
-      <c r="O68" s="10" t="n"/>
-      <c r="P68" s="10" t="n"/>
-      <c r="Q68" s="10" t="n"/>
-      <c r="R68" s="10" t="n"/>
-      <c r="S68" s="10" t="n"/>
-      <c r="T68" s="10" t="n"/>
-      <c r="U68" s="10" t="n"/>
-      <c r="V68" s="10" t="n"/>
-      <c r="W68" s="10" t="n"/>
-      <c r="X68" s="10" t="n"/>
-      <c r="Y68" s="10" t="n"/>
-      <c r="Z68" s="10" t="n"/>
-      <c r="AA68" s="10" t="n"/>
-      <c r="AB68" s="10" t="n"/>
-      <c r="AC68" s="10" t="n"/>
-      <c r="AD68" s="10" t="n"/>
-      <c r="AE68" s="10" t="n"/>
-      <c r="AF68" s="10" t="n"/>
-      <c r="AG68" s="10" t="n"/>
-      <c r="AH68" s="10" t="n"/>
-      <c r="AI68" s="10" t="n"/>
-      <c r="AJ68" s="10" t="n"/>
-      <c r="AK68" s="11" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="n"/>
+      <c r="J67" s="10" t="n"/>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="10" t="n"/>
+      <c r="Q67" s="10" t="n"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="10" t="n"/>
+      <c r="X67" s="10" t="n"/>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="10" t="n"/>
+      <c r="AE67" s="10" t="n"/>
+      <c r="AF67" s="10" t="n"/>
+      <c r="AG67" s="10" t="n"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="10" t="n"/>
+      <c r="AJ67" s="10" t="n"/>
+      <c r="AK67" s="11" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="C68" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="C69" s="41" t="inlineStr">
         <is>
-          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="C70" s="41" t="inlineStr">
-        <is>
           <t>関連テーブルに紐づくデータが存在するか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="72" customHeight="1">
-      <c r="C71" s="42" t="inlineStr">
+    <row r="70" ht="72" customHeight="1">
+      <c r="C70" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS related_count
 FROM (
@@ -10324,57 +10443,57 @@
 ) AS related_data</t>
         </is>
       </c>
-      <c r="D71" s="10" t="n"/>
-      <c r="E71" s="10" t="n"/>
-      <c r="F71" s="10" t="n"/>
-      <c r="G71" s="10" t="n"/>
-      <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="n"/>
-      <c r="J71" s="10" t="n"/>
-      <c r="K71" s="10" t="n"/>
-      <c r="L71" s="10" t="n"/>
-      <c r="M71" s="10" t="n"/>
-      <c r="N71" s="10" t="n"/>
-      <c r="O71" s="10" t="n"/>
-      <c r="P71" s="10" t="n"/>
-      <c r="Q71" s="10" t="n"/>
-      <c r="R71" s="10" t="n"/>
-      <c r="S71" s="10" t="n"/>
-      <c r="T71" s="10" t="n"/>
-      <c r="U71" s="10" t="n"/>
-      <c r="V71" s="10" t="n"/>
-      <c r="W71" s="10" t="n"/>
-      <c r="X71" s="10" t="n"/>
-      <c r="Y71" s="10" t="n"/>
-      <c r="Z71" s="10" t="n"/>
-      <c r="AA71" s="10" t="n"/>
-      <c r="AB71" s="10" t="n"/>
-      <c r="AC71" s="10" t="n"/>
-      <c r="AD71" s="10" t="n"/>
-      <c r="AE71" s="10" t="n"/>
-      <c r="AF71" s="10" t="n"/>
-      <c r="AG71" s="10" t="n"/>
-      <c r="AH71" s="10" t="n"/>
-      <c r="AI71" s="10" t="n"/>
-      <c r="AJ71" s="10" t="n"/>
-      <c r="AK71" s="11" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="n"/>
+      <c r="J70" s="10" t="n"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="10" t="n"/>
+      <c r="X70" s="10" t="n"/>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="10" t="n"/>
+      <c r="AE70" s="10" t="n"/>
+      <c r="AF70" s="10" t="n"/>
+      <c r="AG70" s="10" t="n"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="10" t="n"/>
+      <c r="AJ70" s="10" t="n"/>
+      <c r="AK70" s="11" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="C71" s="41" t="inlineStr">
+        <is>
+          <t>関連データが存在する場合：HTTP 409 (`CONFLICT`)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="C72" s="41" t="inlineStr">
-        <is>
-          <t>関連データが存在する場合：HTTP 409 (`CONFLICT`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="B73" s="27" t="inlineStr">
+      <c r="B72" s="27" t="inlineStr">
         <is>
           <t>4.4 論理削除の実行</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="108" customHeight="1">
-      <c r="C74" s="42" t="inlineStr">
+    <row r="73" ht="108" customHeight="1">
+      <c r="C73" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_account
 SET deleted_at = NOW(),
@@ -10384,57 +10503,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D74" s="10" t="n"/>
-      <c r="E74" s="10" t="n"/>
-      <c r="F74" s="10" t="n"/>
-      <c r="G74" s="10" t="n"/>
-      <c r="H74" s="10" t="n"/>
-      <c r="I74" s="10" t="n"/>
-      <c r="J74" s="10" t="n"/>
-      <c r="K74" s="10" t="n"/>
-      <c r="L74" s="10" t="n"/>
-      <c r="M74" s="10" t="n"/>
-      <c r="N74" s="10" t="n"/>
-      <c r="O74" s="10" t="n"/>
-      <c r="P74" s="10" t="n"/>
-      <c r="Q74" s="10" t="n"/>
-      <c r="R74" s="10" t="n"/>
-      <c r="S74" s="10" t="n"/>
-      <c r="T74" s="10" t="n"/>
-      <c r="U74" s="10" t="n"/>
-      <c r="V74" s="10" t="n"/>
-      <c r="W74" s="10" t="n"/>
-      <c r="X74" s="10" t="n"/>
-      <c r="Y74" s="10" t="n"/>
-      <c r="Z74" s="10" t="n"/>
-      <c r="AA74" s="10" t="n"/>
-      <c r="AB74" s="10" t="n"/>
-      <c r="AC74" s="10" t="n"/>
-      <c r="AD74" s="10" t="n"/>
-      <c r="AE74" s="10" t="n"/>
-      <c r="AF74" s="10" t="n"/>
-      <c r="AG74" s="10" t="n"/>
-      <c r="AH74" s="10" t="n"/>
-      <c r="AI74" s="10" t="n"/>
-      <c r="AJ74" s="10" t="n"/>
-      <c r="AK74" s="11" t="n"/>
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="10" t="n"/>
+      <c r="J73" s="10" t="n"/>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="10" t="n"/>
+      <c r="X73" s="10" t="n"/>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="10" t="n"/>
+      <c r="AE73" s="10" t="n"/>
+      <c r="AF73" s="10" t="n"/>
+      <c r="AG73" s="10" t="n"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="10" t="n"/>
+      <c r="AJ73" s="10" t="n"/>
+      <c r="AK73" s="11" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="B74" s="27" t="inlineStr">
+        <is>
+          <t>4.5 操作ログ記録</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="B75" s="27" t="inlineStr">
-        <is>
-          <t>4.5 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="C76" s="41" t="inlineStr">
+      <c r="C75" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="216" customHeight="1">
-      <c r="C77" s="42" t="inlineStr">
+    <row r="76" ht="216" customHeight="1">
+      <c r="C76" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -10448,6 +10567,63 @@
         :before_value_json, '',
         '', '',
         :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="10" t="n"/>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="10" t="n"/>
+      <c r="X76" s="10" t="n"/>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="10" t="n"/>
+      <c r="AE76" s="10" t="n"/>
+      <c r="AF76" s="10" t="n"/>
+      <c r="AG76" s="10" t="n"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="10" t="n"/>
+      <c r="AJ76" s="10" t="n"/>
+      <c r="AK76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="306" customHeight="1">
+      <c r="C77" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+`after_value`：DELETE のため空文字列を設定する。
+{
+  "account_id": 5,
+  "login_id": "ja_shiten001",
+  "account_name": "JA管理支店 次郎",
+  "role_id": 5,
+  "ja_id": 10,
+  "kanri_shiten_id": 20,
+  "todofuken_code": "13",
+  "paper_flg": true,
+  "denshi_flg": false,
+  "email": "shiten001@example.com",
+  "sub_email_1": "",
+  "sub_email_2": "",
+  "sub_email_3": ""
+}</t>
         </is>
       </c>
       <c r="D77" s="10" t="n"/>
@@ -10485,140 +10661,86 @@
       <c r="AJ77" s="10" t="n"/>
       <c r="AK77" s="11" t="n"/>
     </row>
-    <row r="78" ht="252" customHeight="1">
-      <c r="C78" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-`after_value`：DELETE のため空文字列を設定する。
-{
-  "account_id": 5,
-  "login_id": "ja_shiten001",
-  "account_name": "JA管理支店 次郎",
-  "role_id": 5,
-  "ja_id": 10,
-  "kanri_shiten_id": 20,
-  "todofuken_code": "13",
-  "paper_flg": true,
-  "denshi_flg": false,
-  "email": "shiten001@example.com"
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="C79" s="41" t="inlineStr">
+        <is>
+          <t>削除成功メッセージを返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="54" customHeight="1">
+      <c r="C80" s="42" t="inlineStr">
+        <is>
+          <t>{
+  "message": "削除しました。"
 }</t>
         </is>
       </c>
-      <c r="D78" s="10" t="n"/>
-      <c r="E78" s="10" t="n"/>
-      <c r="F78" s="10" t="n"/>
-      <c r="G78" s="10" t="n"/>
-      <c r="H78" s="10" t="n"/>
-      <c r="I78" s="10" t="n"/>
-      <c r="J78" s="10" t="n"/>
-      <c r="K78" s="10" t="n"/>
-      <c r="L78" s="10" t="n"/>
-      <c r="M78" s="10" t="n"/>
-      <c r="N78" s="10" t="n"/>
-      <c r="O78" s="10" t="n"/>
-      <c r="P78" s="10" t="n"/>
-      <c r="Q78" s="10" t="n"/>
-      <c r="R78" s="10" t="n"/>
-      <c r="S78" s="10" t="n"/>
-      <c r="T78" s="10" t="n"/>
-      <c r="U78" s="10" t="n"/>
-      <c r="V78" s="10" t="n"/>
-      <c r="W78" s="10" t="n"/>
-      <c r="X78" s="10" t="n"/>
-      <c r="Y78" s="10" t="n"/>
-      <c r="Z78" s="10" t="n"/>
-      <c r="AA78" s="10" t="n"/>
-      <c r="AB78" s="10" t="n"/>
-      <c r="AC78" s="10" t="n"/>
-      <c r="AD78" s="10" t="n"/>
-      <c r="AE78" s="10" t="n"/>
-      <c r="AF78" s="10" t="n"/>
-      <c r="AG78" s="10" t="n"/>
-      <c r="AH78" s="10" t="n"/>
-      <c r="AI78" s="10" t="n"/>
-      <c r="AJ78" s="10" t="n"/>
-      <c r="AK78" s="11" t="n"/>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="B79" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
-        <is>
-          <t>削除成功メッセージを返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="54" customHeight="1">
-      <c r="C81" s="42" t="inlineStr">
-        <is>
-          <t>{
-  "message": "正常に削除しました"
-}</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="n"/>
-      <c r="E81" s="10" t="n"/>
-      <c r="F81" s="10" t="n"/>
-      <c r="G81" s="10" t="n"/>
-      <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="n"/>
-      <c r="J81" s="10" t="n"/>
-      <c r="K81" s="10" t="n"/>
-      <c r="L81" s="10" t="n"/>
-      <c r="M81" s="10" t="n"/>
-      <c r="N81" s="10" t="n"/>
-      <c r="O81" s="10" t="n"/>
-      <c r="P81" s="10" t="n"/>
-      <c r="Q81" s="10" t="n"/>
-      <c r="R81" s="10" t="n"/>
-      <c r="S81" s="10" t="n"/>
-      <c r="T81" s="10" t="n"/>
-      <c r="U81" s="10" t="n"/>
-      <c r="V81" s="10" t="n"/>
-      <c r="W81" s="10" t="n"/>
-      <c r="X81" s="10" t="n"/>
-      <c r="Y81" s="10" t="n"/>
-      <c r="Z81" s="10" t="n"/>
-      <c r="AA81" s="10" t="n"/>
-      <c r="AB81" s="10" t="n"/>
-      <c r="AC81" s="10" t="n"/>
-      <c r="AD81" s="10" t="n"/>
-      <c r="AE81" s="10" t="n"/>
-      <c r="AF81" s="10" t="n"/>
-      <c r="AG81" s="10" t="n"/>
-      <c r="AH81" s="10" t="n"/>
-      <c r="AI81" s="10" t="n"/>
-      <c r="AJ81" s="10" t="n"/>
-      <c r="AK81" s="11" t="n"/>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="10" t="n"/>
+      <c r="J80" s="10" t="n"/>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="10" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="10" t="n"/>
+      <c r="Q80" s="10" t="n"/>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="10" t="n"/>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="10" t="n"/>
+      <c r="X80" s="10" t="n"/>
+      <c r="Y80" s="10" t="n"/>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="10" t="n"/>
+      <c r="AC80" s="10" t="n"/>
+      <c r="AD80" s="10" t="n"/>
+      <c r="AE80" s="10" t="n"/>
+      <c r="AF80" s="10" t="n"/>
+      <c r="AG80" s="10" t="n"/>
+      <c r="AH80" s="10" t="n"/>
+      <c r="AI80" s="10" t="n"/>
+      <c r="AJ80" s="10" t="n"/>
+      <c r="AK80" s="11" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="B81" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="B82" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
+      <c r="C82" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="C83" s="41" t="inlineStr">
         <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
-        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="216" customHeight="1">
-      <c r="C85" s="42" t="inlineStr">
+    <row r="84" ht="216" customHeight="1">
+      <c r="C84" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -10634,49 +10756,49 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="10" t="n"/>
-      <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="n"/>
-      <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
-      <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
-      <c r="U85" s="10" t="n"/>
-      <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-      <c r="AA85" s="10" t="n"/>
-      <c r="AB85" s="10" t="n"/>
-      <c r="AC85" s="10" t="n"/>
-      <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
-      <c r="AG85" s="10" t="n"/>
-      <c r="AH85" s="10" t="n"/>
-      <c r="AI85" s="10" t="n"/>
-      <c r="AJ85" s="10" t="n"/>
-      <c r="AK85" s="11" t="n"/>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="10" t="n"/>
+      <c r="K84" s="10" t="n"/>
+      <c r="L84" s="10" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="10" t="n"/>
+      <c r="U84" s="10" t="n"/>
+      <c r="V84" s="10" t="n"/>
+      <c r="W84" s="10" t="n"/>
+      <c r="X84" s="10" t="n"/>
+      <c r="Y84" s="10" t="n"/>
+      <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
+      <c r="AB84" s="10" t="n"/>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="10" t="n"/>
+      <c r="AF84" s="10" t="n"/>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="10" t="n"/>
+      <c r="AK84" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="117">
+  <mergeCells count="116">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="A26:AK26"/>
-    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="C66:AK66"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="C77:AK77"/>
@@ -10684,24 +10806,23 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="D58:AK58"/>
     <mergeCell ref="C68:AK68"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="A53:AK53"/>
     <mergeCell ref="N17:AK17"/>
+    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="B73:AK73"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C65:AK65"/>
     <mergeCell ref="C44:AK44"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="B65:AK65"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C80:AK80"/>
@@ -10709,7 +10830,6 @@
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="B66:AK66"/>
     <mergeCell ref="C38:AK38"/>
     <mergeCell ref="A21:AK21"/>
     <mergeCell ref="T29:X29"/>
@@ -10717,51 +10837,54 @@
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D56:AK56"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="D63:AK63"/>
+    <mergeCell ref="B55:AK55"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="B49:I49"/>
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="Y28:AE28"/>
-    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="C32:AK32"/>
-    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="B60:AK60"/>
     <mergeCell ref="C62:AK62"/>
     <mergeCell ref="C28:L28"/>
+    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C64:AK64"/>
+    <mergeCell ref="C79:AK79"/>
+    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C41:AK41"/>
     <mergeCell ref="C50:AK50"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="D57:AK57"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="B54:AK54"/>
+    <mergeCell ref="B72:AK72"/>
     <mergeCell ref="C67:AK67"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
@@ -10771,22 +10894,20 @@
     <mergeCell ref="C83:AK83"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="J14:M14"/>
+    <mergeCell ref="D59:AK59"/>
     <mergeCell ref="C47:AK47"/>
+    <mergeCell ref="B74:AK74"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="C76:AK76"/>
-    <mergeCell ref="B75:AK75"/>
     <mergeCell ref="M28:P28"/>
-    <mergeCell ref="B59:AK59"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10960,7 +11081,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -11314,7 +11435,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -12197,7 +12318,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -12424,7 +12545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK73"/>
+  <dimension ref="A1:AK89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -12585,7 +12706,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -12694,7 +12815,7 @@
       <c r="AJ7" s="10" t="n"/>
       <c r="AK7" s="11" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="B8" s="33" t="inlineStr">
         <is>
           <t>概要</t>
@@ -12709,7 +12830,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>JAプルダウンリストを取得する（都道府県・管理者区分によるカスケード絞込み。共用API：アカウント検索・登録等で使用）</t>
+          <t>JAプルダウンリストを取得する（共用API）。2つのユースケースを1つのエンドポイントで提供：（A）ページング+フリーテキスト検索（SCR-009 等のフォーム用）、（B）都道府県・管理者区分によるカスケード絞込み（SCR-024 アカウント検索／SCR-025 登録用）。両方のレスポンス形状は同一（`{data, meta}`）。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -12939,7 +13060,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -13022,14 +13143,14 @@
       <c r="B15" s="35" t="n"/>
       <c r="I15" s="36" t="n"/>
       <c r="J15" s="17" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="n"/>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>セッションが切れました。再度ログインしてください</t>
+          <t>リクエストパラメータが不正です</t>
         </is>
       </c>
       <c r="O15" s="10" t="n"/>
@@ -13060,14 +13181,14 @@
       <c r="B16" s="35" t="n"/>
       <c r="I16" s="36" t="n"/>
       <c r="J16" s="17" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K16" s="10" t="n"/>
       <c r="L16" s="10" t="n"/>
       <c r="M16" s="11" t="n"/>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>この画面へのアクセス権限がありません</t>
+          <t>セッションが切れました。再度ログインしてください</t>
         </is>
       </c>
       <c r="O16" s="10" t="n"/>
@@ -13095,23 +13216,17 @@
       <c r="AK16" s="11" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="25" t="n"/>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="26" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="I17" s="36" t="n"/>
       <c r="J17" s="17" t="n">
-        <v>500</v>
+        <v>403</v>
       </c>
       <c r="K17" s="10" t="n"/>
       <c r="L17" s="10" t="n"/>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>システムエラーが発生しました</t>
+          <t>この画面へのアクセス権限がありません</t>
         </is>
       </c>
       <c r="O17" s="10" t="n"/>
@@ -13138,92 +13253,68 @@
       <c r="AJ17" s="10" t="n"/>
       <c r="AK17" s="11" t="n"/>
     </row>
-    <row r="18" ht="19.5" customHeight="1"/>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="27" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="26" t="n"/>
+      <c r="J18" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="11" t="n"/>
+      <c r="N18" s="19" t="inlineStr">
+        <is>
+          <t>システムエラーが発生しました</t>
+        </is>
+      </c>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n"/>
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="10" t="n"/>
+      <c r="Y18" s="10" t="n"/>
+      <c r="Z18" s="10" t="n"/>
+      <c r="AA18" s="10" t="n"/>
+      <c r="AB18" s="10" t="n"/>
+      <c r="AC18" s="10" t="n"/>
+      <c r="AD18" s="10" t="n"/>
+      <c r="AE18" s="10" t="n"/>
+      <c r="AF18" s="10" t="n"/>
+      <c r="AG18" s="10" t="n"/>
+      <c r="AH18" s="10" t="n"/>
+      <c r="AI18" s="10" t="n"/>
+      <c r="AJ18" s="10" t="n"/>
+      <c r="AK18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1"/>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>2. リクエストパラメータ</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="19.5" customHeight="1"/>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="B21" s="30" t="inlineStr">
+    <row r="21" ht="19.5" customHeight="1"/>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>パラメーターID</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="n"/>
-      <c r="O21" s="10" t="n"/>
-      <c r="P21" s="11" t="n"/>
-      <c r="Q21" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R21" s="10" t="n"/>
-      <c r="S21" s="11" t="n"/>
-      <c r="T21" s="16" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="U21" s="10" t="n"/>
-      <c r="V21" s="10" t="n"/>
-      <c r="W21" s="10" t="n"/>
-      <c r="X21" s="11" t="n"/>
-      <c r="Y21" s="16" t="inlineStr">
-        <is>
-          <t>最小長</t>
-        </is>
-      </c>
-      <c r="Z21" s="10" t="n"/>
-      <c r="AA21" s="10" t="n"/>
-      <c r="AB21" s="11" t="n"/>
-      <c r="AC21" s="16" t="inlineStr">
-        <is>
-          <t>最大長</t>
-        </is>
-      </c>
-      <c r="AD21" s="10" t="n"/>
-      <c r="AE21" s="11" t="n"/>
-      <c r="AF21" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG21" s="10" t="n"/>
-      <c r="AH21" s="10" t="n"/>
-      <c r="AI21" s="10" t="n"/>
-      <c r="AJ21" s="10" t="n"/>
-      <c r="AK21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>todofuken_code</t>
         </is>
       </c>
       <c r="D22" s="10" t="n"/>
@@ -13235,44 +13326,48 @@
       <c r="J22" s="10" t="n"/>
       <c r="K22" s="10" t="n"/>
       <c r="L22" s="11" t="n"/>
-      <c r="M22" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N22" s="10" t="n"/>
       <c r="O22" s="10" t="n"/>
       <c r="P22" s="11" t="n"/>
-      <c r="Q22" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q22" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R22" s="10" t="n"/>
       <c r="S22" s="11" t="n"/>
-      <c r="T22" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="T22" s="16" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
       <c r="U22" s="10" t="n"/>
       <c r="V22" s="10" t="n"/>
       <c r="W22" s="10" t="n"/>
       <c r="X22" s="11" t="n"/>
-      <c r="Y22" s="17" t="n">
-        <v>2</v>
+      <c r="Y22" s="16" t="inlineStr">
+        <is>
+          <t>最小長</t>
+        </is>
       </c>
       <c r="Z22" s="10" t="n"/>
       <c r="AA22" s="10" t="n"/>
       <c r="AB22" s="11" t="n"/>
-      <c r="AC22" s="17" t="n">
-        <v>2</v>
+      <c r="AC22" s="16" t="inlineStr">
+        <is>
+          <t>最大長</t>
+        </is>
       </c>
       <c r="AD22" s="10" t="n"/>
       <c r="AE22" s="11" t="n"/>
-      <c r="AF22" s="19" t="inlineStr">
-        <is>
-          <t>都道府県コード（01〜47）</t>
+      <c r="AF22" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG22" s="10" t="n"/>
@@ -13283,11 +13378,11 @@
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="B23" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>q</t>
         </is>
       </c>
       <c r="D23" s="10" t="n"/>
@@ -13301,7 +13396,7 @@
       <c r="L23" s="11" t="n"/>
       <c r="M23" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N23" s="10" t="n"/>
@@ -13323,16 +13418,22 @@
       <c r="V23" s="10" t="n"/>
       <c r="W23" s="10" t="n"/>
       <c r="X23" s="11" t="n"/>
-      <c r="Y23" s="17" t="inlineStr"/>
+      <c r="Y23" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z23" s="10" t="n"/>
       <c r="AA23" s="10" t="n"/>
       <c r="AB23" s="11" t="n"/>
-      <c r="AC23" s="17" t="inlineStr"/>
+      <c r="AC23" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AD23" s="10" t="n"/>
       <c r="AE23" s="11" t="n"/>
       <c r="AF23" s="19" t="inlineStr">
         <is>
-          <t>管理者区分（3:中央会→chuokai_flg=true、4,5:JA→chuokai_flg=false）</t>
+          <t>フリーテキスト検索。`ja_code` または `ja_name` に対する部分一致（ILIKE `%q%`）</t>
         </is>
       </c>
       <c r="AG23" s="10" t="n"/>
@@ -13341,24 +13442,193 @@
       <c r="AJ23" s="10" t="n"/>
       <c r="AK23" s="11" t="n"/>
     </row>
-    <row r="24" ht="19.5" customHeight="1"/>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="27" t="inlineStr">
-        <is>
-          <t>3.レスポンスデータ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="19.5" customHeight="1"/>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="B27" s="30" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>項目ID</t>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="n"/>
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="11" t="n"/>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="11" t="n"/>
+      <c r="T24" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="10" t="n"/>
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="11" t="n"/>
+      <c r="Y24" s="17" t="inlineStr"/>
+      <c r="Z24" s="10" t="n"/>
+      <c r="AA24" s="10" t="n"/>
+      <c r="AB24" s="11" t="n"/>
+      <c r="AC24" s="17" t="inlineStr"/>
+      <c r="AD24" s="10" t="n"/>
+      <c r="AE24" s="11" t="n"/>
+      <c r="AF24" s="19" t="inlineStr">
+        <is>
+          <t>ページ番号（1以上、デフォルト=1）</t>
+        </is>
+      </c>
+      <c r="AG24" s="10" t="n"/>
+      <c r="AH24" s="10" t="n"/>
+      <c r="AI24" s="10" t="n"/>
+      <c r="AJ24" s="10" t="n"/>
+      <c r="AK24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="n"/>
+      <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="n"/>
+      <c r="S25" s="11" t="n"/>
+      <c r="T25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U25" s="10" t="n"/>
+      <c r="V25" s="10" t="n"/>
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="11" t="n"/>
+      <c r="Y25" s="17" t="inlineStr"/>
+      <c r="Z25" s="10" t="n"/>
+      <c r="AA25" s="10" t="n"/>
+      <c r="AB25" s="11" t="n"/>
+      <c r="AC25" s="17" t="inlineStr"/>
+      <c r="AD25" s="10" t="n"/>
+      <c r="AE25" s="11" t="n"/>
+      <c r="AF25" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数（1〜100、デフォルト=50）</t>
+        </is>
+      </c>
+      <c r="AG25" s="10" t="n"/>
+      <c r="AH25" s="10" t="n"/>
+      <c r="AI25" s="10" t="n"/>
+      <c r="AJ25" s="10" t="n"/>
+      <c r="AK25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="B26" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>include_id</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="10" t="n"/>
+      <c r="J26" s="10" t="n"/>
+      <c r="K26" s="10" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="n"/>
+      <c r="O26" s="10" t="n"/>
+      <c r="P26" s="11" t="n"/>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R26" s="10" t="n"/>
+      <c r="S26" s="11" t="n"/>
+      <c r="T26" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U26" s="10" t="n"/>
+      <c r="V26" s="10" t="n"/>
+      <c r="W26" s="10" t="n"/>
+      <c r="X26" s="11" t="n"/>
+      <c r="Y26" s="17" t="inlineStr"/>
+      <c r="Z26" s="10" t="n"/>
+      <c r="AA26" s="10" t="n"/>
+      <c r="AB26" s="11" t="n"/>
+      <c r="AC26" s="17" t="inlineStr"/>
+      <c r="AD26" s="10" t="n"/>
+      <c r="AE26" s="11" t="n"/>
+      <c r="AF26" s="19" t="inlineStr">
+        <is>
+          <t>編集フォーム用エスケープハッチ。指定された ja_id がページ範囲に含まれない場合、レスポンス先頭に追加して返す。DataScope 制限により範囲外のIDは無視（silently dropped）</t>
+        </is>
+      </c>
+      <c r="AG26" s="10" t="n"/>
+      <c r="AH26" s="10" t="n"/>
+      <c r="AI26" s="10" t="n"/>
+      <c r="AJ26" s="10" t="n"/>
+      <c r="AK26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -13370,44 +13640,44 @@
       <c r="J27" s="10" t="n"/>
       <c r="K27" s="10" t="n"/>
       <c r="L27" s="11" t="n"/>
-      <c r="M27" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M27" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
         </is>
       </c>
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q27" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R27" s="10" t="n"/>
       <c r="S27" s="11" t="n"/>
-      <c r="T27" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
+      <c r="T27" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n"/>
-      <c r="Y27" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
+      <c r="Y27" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="Z27" s="10" t="n"/>
       <c r="AA27" s="10" t="n"/>
-      <c r="AB27" s="10" t="n"/>
-      <c r="AC27" s="10" t="n"/>
+      <c r="AB27" s="11" t="n"/>
+      <c r="AC27" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="11" t="n"/>
-      <c r="AF27" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF27" s="19" t="inlineStr">
+        <is>
+          <t>都道府県コード（01〜47）。完全一致でカスケード絞込み</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -13416,13 +13686,13 @@
       <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="11" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
+    <row r="28" ht="36" customHeight="1">
       <c r="B28" s="31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -13436,7 +13706,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -13444,30 +13714,30 @@
       <c r="P28" s="11" t="n"/>
       <c r="Q28" s="17" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R28" s="10" t="n"/>
       <c r="S28" s="11" t="n"/>
-      <c r="T28" s="17" t="inlineStr"/>
+      <c r="T28" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="U28" s="10" t="n"/>
       <c r="V28" s="10" t="n"/>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="11" t="n"/>
-      <c r="Y28" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y28" s="17" t="inlineStr"/>
       <c r="Z28" s="10" t="n"/>
       <c r="AA28" s="10" t="n"/>
-      <c r="AB28" s="10" t="n"/>
-      <c r="AC28" s="10" t="n"/>
+      <c r="AB28" s="11" t="n"/>
+      <c r="AC28" s="17" t="inlineStr"/>
       <c r="AD28" s="10" t="n"/>
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>JA一覧</t>
+          <t>管理者区分（3:中央会→`chuokai_flg=TRUE`、4,5:JA→`chuokai_flg=FALSE`、その他/未指定: 絞込みなし）</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -13476,196 +13746,27 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" s="37" t="n"/>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>ja_id</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="10" t="n"/>
-      <c r="K29" s="10" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N29" s="10" t="n"/>
-      <c r="O29" s="10" t="n"/>
-      <c r="P29" s="11" t="n"/>
-      <c r="Q29" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R29" s="10" t="n"/>
-      <c r="S29" s="11" t="n"/>
-      <c r="T29" s="17" t="inlineStr"/>
-      <c r="U29" s="10" t="n"/>
-      <c r="V29" s="10" t="n"/>
-      <c r="W29" s="10" t="n"/>
-      <c r="X29" s="11" t="n"/>
-      <c r="Y29" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z29" s="10" t="n"/>
-      <c r="AA29" s="10" t="n"/>
-      <c r="AB29" s="10" t="n"/>
-      <c r="AC29" s="10" t="n"/>
-      <c r="AD29" s="10" t="n"/>
-      <c r="AE29" s="11" t="n"/>
-      <c r="AF29" s="19" t="inlineStr">
-        <is>
-          <t>JA ID</t>
-        </is>
-      </c>
-      <c r="AG29" s="10" t="n"/>
-      <c r="AH29" s="10" t="n"/>
-      <c r="AI29" s="10" t="n"/>
-      <c r="AJ29" s="10" t="n"/>
-      <c r="AK29" s="11" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>ja_code</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
-      <c r="J30" s="10" t="n"/>
-      <c r="K30" s="10" t="n"/>
-      <c r="L30" s="11" t="n"/>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N30" s="10" t="n"/>
-      <c r="O30" s="10" t="n"/>
-      <c r="P30" s="11" t="n"/>
-      <c r="Q30" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R30" s="10" t="n"/>
-      <c r="S30" s="11" t="n"/>
-      <c r="T30" s="17" t="inlineStr"/>
-      <c r="U30" s="10" t="n"/>
-      <c r="V30" s="10" t="n"/>
-      <c r="W30" s="10" t="n"/>
-      <c r="X30" s="11" t="n"/>
-      <c r="Y30" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z30" s="10" t="n"/>
-      <c r="AA30" s="10" t="n"/>
-      <c r="AB30" s="10" t="n"/>
-      <c r="AC30" s="10" t="n"/>
-      <c r="AD30" s="10" t="n"/>
-      <c r="AE30" s="11" t="n"/>
-      <c r="AF30" s="19" t="inlineStr">
-        <is>
-          <t>JAコード</t>
-        </is>
-      </c>
-      <c r="AG30" s="10" t="n"/>
-      <c r="AH30" s="10" t="n"/>
-      <c r="AI30" s="10" t="n"/>
-      <c r="AJ30" s="10" t="n"/>
-      <c r="AK30" s="11" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="38" t="n"/>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>ja_name</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="10" t="n"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N31" s="10" t="n"/>
-      <c r="O31" s="10" t="n"/>
-      <c r="P31" s="11" t="n"/>
-      <c r="Q31" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R31" s="10" t="n"/>
-      <c r="S31" s="11" t="n"/>
-      <c r="T31" s="17" t="inlineStr"/>
-      <c r="U31" s="10" t="n"/>
-      <c r="V31" s="10" t="n"/>
-      <c r="W31" s="10" t="n"/>
-      <c r="X31" s="11" t="n"/>
-      <c r="Y31" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z31" s="10" t="n"/>
-      <c r="AA31" s="10" t="n"/>
-      <c r="AB31" s="10" t="n"/>
-      <c r="AC31" s="10" t="n"/>
-      <c r="AD31" s="10" t="n"/>
-      <c r="AE31" s="11" t="n"/>
-      <c r="AF31" s="19" t="inlineStr">
-        <is>
-          <t>JA名称</t>
-        </is>
-      </c>
-      <c r="AG31" s="10" t="n"/>
-      <c r="AH31" s="10" t="n"/>
-      <c r="AI31" s="10" t="n"/>
-      <c r="AJ31" s="10" t="n"/>
-      <c r="AK31" s="11" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>todofuken_code</t>
-        </is>
-      </c>
+    <row r="29" ht="19.5" customHeight="1"/>
+    <row r="30" ht="19.5" customHeight="1">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19.5" customHeight="1"/>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
       <c r="E32" s="10" t="n"/>
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="10" t="n"/>
@@ -13674,29 +13775,33 @@
       <c r="J32" s="10" t="n"/>
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="11" t="n"/>
-      <c r="M32" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q32" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R32" s="10" t="n"/>
       <c r="S32" s="11" t="n"/>
-      <c r="T32" s="17" t="inlineStr"/>
+      <c r="T32" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
       <c r="W32" s="10" t="n"/>
       <c r="X32" s="11" t="n"/>
-      <c r="Y32" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y32" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z32" s="10" t="n"/>
@@ -13705,9 +13810,9 @@
       <c r="AC32" s="10" t="n"/>
       <c r="AD32" s="10" t="n"/>
       <c r="AE32" s="11" t="n"/>
-      <c r="AF32" s="19" t="inlineStr">
-        <is>
-          <t>都道府県コード</t>
+      <c r="AF32" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -13718,14 +13823,14 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="C33" s="39" t="n"/>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>chuokai_flg</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n"/>
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
@@ -13736,7 +13841,7 @@
       <c r="L33" s="11" t="n"/>
       <c r="M33" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N33" s="10" t="n"/>
@@ -13744,7 +13849,7 @@
       <c r="P33" s="11" t="n"/>
       <c r="Q33" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="R33" s="10" t="n"/>
@@ -13767,7 +13872,7 @@
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>中央会フラグ</t>
+          <t>JA一覧</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -13776,21 +13881,136 @@
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="11" t="n"/>
     </row>
-    <row r="34" ht="19.5" customHeight="1"/>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="B35" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="37" t="n"/>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>ja_id</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="10" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="11" t="n"/>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="11" t="n"/>
+      <c r="T34" s="17" t="inlineStr"/>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n"/>
+      <c r="W34" s="10" t="n"/>
+      <c r="X34" s="11" t="n"/>
+      <c r="Y34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z34" s="10" t="n"/>
+      <c r="AA34" s="10" t="n"/>
+      <c r="AB34" s="10" t="n"/>
+      <c r="AC34" s="10" t="n"/>
+      <c r="AD34" s="10" t="n"/>
+      <c r="AE34" s="11" t="n"/>
+      <c r="AF34" s="19" t="inlineStr">
+        <is>
+          <t>JA ID</t>
+        </is>
+      </c>
+      <c r="AG34" s="10" t="n"/>
+      <c r="AH34" s="10" t="n"/>
+      <c r="AI34" s="10" t="n"/>
+      <c r="AJ34" s="10" t="n"/>
+      <c r="AK34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>ja_code</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="11" t="n"/>
+      <c r="Q35" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="11" t="n"/>
+      <c r="T35" s="17" t="inlineStr"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="11" t="n"/>
+      <c r="Y35" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n"/>
+      <c r="AB35" s="10" t="n"/>
+      <c r="AC35" s="10" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="11" t="n"/>
+      <c r="AF35" s="19" t="inlineStr">
+        <is>
+          <t>JAコード</t>
+        </is>
+      </c>
+      <c r="AG35" s="10" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="10" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="11" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/ja/dropdown?todofuken_code=13&amp;role_id=3</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="n"/>
+      <c r="B36" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>ja_name</t>
+        </is>
+      </c>
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
@@ -13798,42 +14018,527 @@
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="10" t="n"/>
       <c r="K36" s="10" t="n"/>
-      <c r="L36" s="10" t="n"/>
-      <c r="M36" s="10" t="n"/>
+      <c r="L36" s="11" t="n"/>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
       <c r="N36" s="10" t="n"/>
       <c r="O36" s="10" t="n"/>
-      <c r="P36" s="10" t="n"/>
-      <c r="Q36" s="10" t="n"/>
+      <c r="P36" s="11" t="n"/>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R36" s="10" t="n"/>
-      <c r="S36" s="10" t="n"/>
-      <c r="T36" s="10" t="n"/>
+      <c r="S36" s="11" t="n"/>
+      <c r="T36" s="17" t="inlineStr"/>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
       <c r="W36" s="10" t="n"/>
-      <c r="X36" s="10" t="n"/>
-      <c r="Y36" s="10" t="n"/>
+      <c r="X36" s="11" t="n"/>
+      <c r="Y36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z36" s="10" t="n"/>
       <c r="AA36" s="10" t="n"/>
       <c r="AB36" s="10" t="n"/>
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
-      <c r="AE36" s="10" t="n"/>
-      <c r="AF36" s="10" t="n"/>
+      <c r="AE36" s="11" t="n"/>
+      <c r="AF36" s="19" t="inlineStr">
+        <is>
+          <t>JA名称</t>
+        </is>
+      </c>
       <c r="AG36" s="10" t="n"/>
       <c r="AH36" s="10" t="n"/>
       <c r="AI36" s="10" t="n"/>
       <c r="AJ36" s="10" t="n"/>
       <c r="AK36" s="11" t="n"/>
     </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="B38" s="40" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>todofuken_code</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="10" t="n"/>
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="11" t="n"/>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="11" t="n"/>
+      <c r="T37" s="17" t="inlineStr"/>
+      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="10" t="n"/>
+      <c r="W37" s="10" t="n"/>
+      <c r="X37" s="11" t="n"/>
+      <c r="Y37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z37" s="10" t="n"/>
+      <c r="AA37" s="10" t="n"/>
+      <c r="AB37" s="10" t="n"/>
+      <c r="AC37" s="10" t="n"/>
+      <c r="AD37" s="10" t="n"/>
+      <c r="AE37" s="11" t="n"/>
+      <c r="AF37" s="19" t="inlineStr">
+        <is>
+          <t>都道府県コード</t>
+        </is>
+      </c>
+      <c r="AG37" s="10" t="n"/>
+      <c r="AH37" s="10" t="n"/>
+      <c r="AI37" s="10" t="n"/>
+      <c r="AJ37" s="10" t="n"/>
+      <c r="AK37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C38" s="39" t="n"/>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>chuokai_flg</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="11" t="n"/>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="11" t="n"/>
+      <c r="T38" s="17" t="inlineStr"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="11" t="n"/>
+      <c r="Y38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="10" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="11" t="n"/>
+      <c r="AF38" s="19" t="inlineStr">
+        <is>
+          <t>中央会フラグ</t>
+        </is>
+      </c>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="n"/>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="10" t="n"/>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="17" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="n"/>
+      <c r="O39" s="10" t="n"/>
+      <c r="P39" s="11" t="n"/>
+      <c r="Q39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="11" t="n"/>
+      <c r="T39" s="17" t="inlineStr"/>
+      <c r="U39" s="10" t="n"/>
+      <c r="V39" s="10" t="n"/>
+      <c r="W39" s="10" t="n"/>
+      <c r="X39" s="11" t="n"/>
+      <c r="Y39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z39" s="10" t="n"/>
+      <c r="AA39" s="10" t="n"/>
+      <c r="AB39" s="10" t="n"/>
+      <c r="AC39" s="10" t="n"/>
+      <c r="AD39" s="10" t="n"/>
+      <c r="AE39" s="11" t="n"/>
+      <c r="AF39" s="19" t="inlineStr">
+        <is>
+          <t>ページングメタ</t>
+        </is>
+      </c>
+      <c r="AG39" s="10" t="n"/>
+      <c r="AH39" s="10" t="n"/>
+      <c r="AI39" s="10" t="n"/>
+      <c r="AJ39" s="10" t="n"/>
+      <c r="AK39" s="11" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" s="37" t="n"/>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="11" t="n"/>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="11" t="n"/>
+      <c r="T40" s="17" t="inlineStr"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="10" t="n"/>
+      <c r="X40" s="11" t="n"/>
+      <c r="Y40" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="10" t="n"/>
+      <c r="AB40" s="10" t="n"/>
+      <c r="AC40" s="10" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="19" t="inlineStr">
+        <is>
+          <t>DataScope 適用後の総件数（カスケード絞込み込み）</t>
+        </is>
+      </c>
+      <c r="AG40" s="10" t="n"/>
+      <c r="AH40" s="10" t="n"/>
+      <c r="AI40" s="10" t="n"/>
+      <c r="AJ40" s="10" t="n"/>
+      <c r="AK40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="11" t="n"/>
+      <c r="Q41" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="11" t="n"/>
+      <c r="T41" s="17" t="inlineStr"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="10" t="n"/>
+      <c r="W41" s="10" t="n"/>
+      <c r="X41" s="11" t="n"/>
+      <c r="Y41" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z41" s="10" t="n"/>
+      <c r="AA41" s="10" t="n"/>
+      <c r="AB41" s="10" t="n"/>
+      <c r="AC41" s="10" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="11" t="n"/>
+      <c r="AF41" s="19" t="inlineStr">
+        <is>
+          <t>現在のページ番号</t>
+        </is>
+      </c>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="10" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41" s="10" t="n"/>
+      <c r="AK41" s="11" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="10" t="n"/>
+      <c r="L42" s="11" t="n"/>
+      <c r="M42" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="n"/>
+      <c r="O42" s="10" t="n"/>
+      <c r="P42" s="11" t="n"/>
+      <c r="Q42" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="11" t="n"/>
+      <c r="T42" s="17" t="inlineStr"/>
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="10" t="n"/>
+      <c r="W42" s="10" t="n"/>
+      <c r="X42" s="11" t="n"/>
+      <c r="Y42" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z42" s="10" t="n"/>
+      <c r="AA42" s="10" t="n"/>
+      <c r="AB42" s="10" t="n"/>
+      <c r="AC42" s="10" t="n"/>
+      <c r="AD42" s="10" t="n"/>
+      <c r="AE42" s="11" t="n"/>
+      <c r="AF42" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数</t>
+        </is>
+      </c>
+      <c r="AG42" s="10" t="n"/>
+      <c r="AH42" s="10" t="n"/>
+      <c r="AI42" s="10" t="n"/>
+      <c r="AJ42" s="10" t="n"/>
+      <c r="AK42" s="11" t="n"/>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="B43" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C43" s="39" t="n"/>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>has_more</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="10" t="n"/>
+      <c r="L43" s="11" t="n"/>
+      <c r="M43" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="10" t="n"/>
+      <c r="P43" s="11" t="n"/>
+      <c r="Q43" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="11" t="n"/>
+      <c r="T43" s="17" t="inlineStr"/>
+      <c r="U43" s="10" t="n"/>
+      <c r="V43" s="10" t="n"/>
+      <c r="W43" s="10" t="n"/>
+      <c r="X43" s="11" t="n"/>
+      <c r="Y43" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z43" s="10" t="n"/>
+      <c r="AA43" s="10" t="n"/>
+      <c r="AB43" s="10" t="n"/>
+      <c r="AC43" s="10" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="11" t="n"/>
+      <c r="AF43" s="19" t="inlineStr">
+        <is>
+          <t>次ページが存在するか（`page * per_page &lt; total`）</t>
+        </is>
+      </c>
+      <c r="AG43" s="10" t="n"/>
+      <c r="AH43" s="10" t="n"/>
+      <c r="AI43" s="10" t="n"/>
+      <c r="AJ43" s="10" t="n"/>
+      <c r="AK43" s="11" t="n"/>
+    </row>
+    <row r="44" ht="19.5" customHeight="1"/>
+    <row r="45" ht="19.5" customHeight="1">
+      <c r="B45" s="40" t="inlineStr">
+        <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/ja/dropdown?q=東京&amp;page=1&amp;per_page=50</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="10" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
+      <c r="U46" s="10" t="n"/>
+      <c r="V46" s="10" t="n"/>
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="10" t="n"/>
+      <c r="Y46" s="10" t="n"/>
+      <c r="Z46" s="10" t="n"/>
+      <c r="AA46" s="10" t="n"/>
+      <c r="AB46" s="10" t="n"/>
+      <c r="AC46" s="10" t="n"/>
+      <c r="AD46" s="10" t="n"/>
+      <c r="AE46" s="10" t="n"/>
+      <c r="AF46" s="10" t="n"/>
+      <c r="AG46" s="10" t="n"/>
+      <c r="AH46" s="10" t="n"/>
+      <c r="AI46" s="10" t="n"/>
+      <c r="AJ46" s="10" t="n"/>
+      <c r="AK46" s="11" t="n"/>
+    </row>
+    <row r="48" ht="19.5" customHeight="1">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="198" customHeight="1">
-      <c r="C39" s="19" t="inlineStr">
+    <row r="49" ht="306" customHeight="1">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -13844,54 +14549,60 @@
       "todofuken_code": "13",
       "chuokai_flg": true
     }
-  ]
+  ],
+  "meta": {
+    "total": 1,
+    "page": 1,
+    "per_page": 50,
+    "has_more": false
+  }
 }</t>
         </is>
       </c>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="10" t="n"/>
-      <c r="H39" s="10" t="n"/>
-      <c r="I39" s="10" t="n"/>
-      <c r="J39" s="10" t="n"/>
-      <c r="K39" s="10" t="n"/>
-      <c r="L39" s="10" t="n"/>
-      <c r="M39" s="10" t="n"/>
-      <c r="N39" s="10" t="n"/>
-      <c r="O39" s="10" t="n"/>
-      <c r="P39" s="10" t="n"/>
-      <c r="Q39" s="10" t="n"/>
-      <c r="R39" s="10" t="n"/>
-      <c r="S39" s="10" t="n"/>
-      <c r="T39" s="10" t="n"/>
-      <c r="U39" s="10" t="n"/>
-      <c r="V39" s="10" t="n"/>
-      <c r="W39" s="10" t="n"/>
-      <c r="X39" s="10" t="n"/>
-      <c r="Y39" s="10" t="n"/>
-      <c r="Z39" s="10" t="n"/>
-      <c r="AA39" s="10" t="n"/>
-      <c r="AB39" s="10" t="n"/>
-      <c r="AC39" s="10" t="n"/>
-      <c r="AD39" s="10" t="n"/>
-      <c r="AE39" s="10" t="n"/>
-      <c r="AF39" s="10" t="n"/>
-      <c r="AG39" s="10" t="n"/>
-      <c r="AH39" s="10" t="n"/>
-      <c r="AI39" s="10" t="n"/>
-      <c r="AJ39" s="10" t="n"/>
-      <c r="AK39" s="11" t="n"/>
-    </row>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="B41" s="40" t="inlineStr">
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="10" t="n"/>
+      <c r="K49" s="10" t="n"/>
+      <c r="L49" s="10" t="n"/>
+      <c r="M49" s="10" t="n"/>
+      <c r="N49" s="10" t="n"/>
+      <c r="O49" s="10" t="n"/>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="n"/>
+      <c r="S49" s="10" t="n"/>
+      <c r="T49" s="10" t="n"/>
+      <c r="U49" s="10" t="n"/>
+      <c r="V49" s="10" t="n"/>
+      <c r="W49" s="10" t="n"/>
+      <c r="X49" s="10" t="n"/>
+      <c r="Y49" s="10" t="n"/>
+      <c r="Z49" s="10" t="n"/>
+      <c r="AA49" s="10" t="n"/>
+      <c r="AB49" s="10" t="n"/>
+      <c r="AC49" s="10" t="n"/>
+      <c r="AD49" s="10" t="n"/>
+      <c r="AE49" s="10" t="n"/>
+      <c r="AF49" s="10" t="n"/>
+      <c r="AG49" s="10" t="n"/>
+      <c r="AH49" s="10" t="n"/>
+      <c r="AI49" s="10" t="n"/>
+      <c r="AJ49" s="10" t="n"/>
+      <c r="AK49" s="11" t="n"/>
+    </row>
+    <row r="51" ht="19.5" customHeight="1">
+      <c r="B51" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="72" customHeight="1">
-      <c r="C42" s="19" t="inlineStr">
+    <row r="52" ht="72" customHeight="1">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -13899,50 +14610,50 @@
 }</t>
         </is>
       </c>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="10" t="n"/>
-      <c r="I42" s="10" t="n"/>
-      <c r="J42" s="10" t="n"/>
-      <c r="K42" s="10" t="n"/>
-      <c r="L42" s="10" t="n"/>
-      <c r="M42" s="10" t="n"/>
-      <c r="N42" s="10" t="n"/>
-      <c r="O42" s="10" t="n"/>
-      <c r="P42" s="10" t="n"/>
-      <c r="Q42" s="10" t="n"/>
-      <c r="R42" s="10" t="n"/>
-      <c r="S42" s="10" t="n"/>
-      <c r="T42" s="10" t="n"/>
-      <c r="U42" s="10" t="n"/>
-      <c r="V42" s="10" t="n"/>
-      <c r="W42" s="10" t="n"/>
-      <c r="X42" s="10" t="n"/>
-      <c r="Y42" s="10" t="n"/>
-      <c r="Z42" s="10" t="n"/>
-      <c r="AA42" s="10" t="n"/>
-      <c r="AB42" s="10" t="n"/>
-      <c r="AC42" s="10" t="n"/>
-      <c r="AD42" s="10" t="n"/>
-      <c r="AE42" s="10" t="n"/>
-      <c r="AF42" s="10" t="n"/>
-      <c r="AG42" s="10" t="n"/>
-      <c r="AH42" s="10" t="n"/>
-      <c r="AI42" s="10" t="n"/>
-      <c r="AJ42" s="10" t="n"/>
-      <c r="AK42" s="11" t="n"/>
-    </row>
-    <row r="44" ht="19.5" customHeight="1">
-      <c r="B44" s="40" t="inlineStr">
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="10" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="10" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="10" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="10" t="n"/>
+      <c r="Q52" s="10" t="n"/>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="n"/>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="10" t="n"/>
+      <c r="Y52" s="10" t="n"/>
+      <c r="Z52" s="10" t="n"/>
+      <c r="AA52" s="10" t="n"/>
+      <c r="AB52" s="10" t="n"/>
+      <c r="AC52" s="10" t="n"/>
+      <c r="AD52" s="10" t="n"/>
+      <c r="AE52" s="10" t="n"/>
+      <c r="AF52" s="10" t="n"/>
+      <c r="AG52" s="10" t="n"/>
+      <c r="AH52" s="10" t="n"/>
+      <c r="AI52" s="10" t="n"/>
+      <c r="AJ52" s="10" t="n"/>
+      <c r="AK52" s="11" t="n"/>
+    </row>
+    <row r="54" ht="19.5" customHeight="1">
+      <c r="B54" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="72" customHeight="1">
-      <c r="C45" s="19" t="inlineStr">
+    <row r="55" ht="72" customHeight="1">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -13950,50 +14661,50 @@
 }</t>
         </is>
       </c>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="10" t="n"/>
-      <c r="G45" s="10" t="n"/>
-      <c r="H45" s="10" t="n"/>
-      <c r="I45" s="10" t="n"/>
-      <c r="J45" s="10" t="n"/>
-      <c r="K45" s="10" t="n"/>
-      <c r="L45" s="10" t="n"/>
-      <c r="M45" s="10" t="n"/>
-      <c r="N45" s="10" t="n"/>
-      <c r="O45" s="10" t="n"/>
-      <c r="P45" s="10" t="n"/>
-      <c r="Q45" s="10" t="n"/>
-      <c r="R45" s="10" t="n"/>
-      <c r="S45" s="10" t="n"/>
-      <c r="T45" s="10" t="n"/>
-      <c r="U45" s="10" t="n"/>
-      <c r="V45" s="10" t="n"/>
-      <c r="W45" s="10" t="n"/>
-      <c r="X45" s="10" t="n"/>
-      <c r="Y45" s="10" t="n"/>
-      <c r="Z45" s="10" t="n"/>
-      <c r="AA45" s="10" t="n"/>
-      <c r="AB45" s="10" t="n"/>
-      <c r="AC45" s="10" t="n"/>
-      <c r="AD45" s="10" t="n"/>
-      <c r="AE45" s="10" t="n"/>
-      <c r="AF45" s="10" t="n"/>
-      <c r="AG45" s="10" t="n"/>
-      <c r="AH45" s="10" t="n"/>
-      <c r="AI45" s="10" t="n"/>
-      <c r="AJ45" s="10" t="n"/>
-      <c r="AK45" s="11" t="n"/>
-    </row>
-    <row r="47" ht="19.5" customHeight="1">
-      <c r="B47" s="40" t="inlineStr">
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="10" t="n"/>
+      <c r="M55" s="10" t="n"/>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="10" t="n"/>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="n"/>
+      <c r="T55" s="10" t="n"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="10" t="n"/>
+      <c r="Y55" s="10" t="n"/>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+      <c r="AC55" s="10" t="n"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="10" t="n"/>
+      <c r="AF55" s="10" t="n"/>
+      <c r="AG55" s="10" t="n"/>
+      <c r="AH55" s="10" t="n"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
+      <c r="AK55" s="11" t="n"/>
+    </row>
+    <row r="57" ht="19.5" customHeight="1">
+      <c r="B57" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="72" customHeight="1">
-      <c r="C48" s="19" t="inlineStr">
+    <row r="58" ht="72" customHeight="1">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -14001,387 +14712,503 @@
 }</t>
         </is>
       </c>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="10" t="n"/>
-      <c r="F48" s="10" t="n"/>
-      <c r="G48" s="10" t="n"/>
-      <c r="H48" s="10" t="n"/>
-      <c r="I48" s="10" t="n"/>
-      <c r="J48" s="10" t="n"/>
-      <c r="K48" s="10" t="n"/>
-      <c r="L48" s="10" t="n"/>
-      <c r="M48" s="10" t="n"/>
-      <c r="N48" s="10" t="n"/>
-      <c r="O48" s="10" t="n"/>
-      <c r="P48" s="10" t="n"/>
-      <c r="Q48" s="10" t="n"/>
-      <c r="R48" s="10" t="n"/>
-      <c r="S48" s="10" t="n"/>
-      <c r="T48" s="10" t="n"/>
-      <c r="U48" s="10" t="n"/>
-      <c r="V48" s="10" t="n"/>
-      <c r="W48" s="10" t="n"/>
-      <c r="X48" s="10" t="n"/>
-      <c r="Y48" s="10" t="n"/>
-      <c r="Z48" s="10" t="n"/>
-      <c r="AA48" s="10" t="n"/>
-      <c r="AB48" s="10" t="n"/>
-      <c r="AC48" s="10" t="n"/>
-      <c r="AD48" s="10" t="n"/>
-      <c r="AE48" s="10" t="n"/>
-      <c r="AF48" s="10" t="n"/>
-      <c r="AG48" s="10" t="n"/>
-      <c r="AH48" s="10" t="n"/>
-      <c r="AI48" s="10" t="n"/>
-      <c r="AJ48" s="10" t="n"/>
-      <c r="AK48" s="11" t="n"/>
-    </row>
-    <row r="50" ht="19.5" customHeight="1"/>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="27" t="inlineStr">
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="10" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="10" t="n"/>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="10" t="n"/>
+      <c r="T58" s="10" t="n"/>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="10" t="n"/>
+      <c r="Y58" s="10" t="n"/>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="10" t="n"/>
+      <c r="AF58" s="10" t="n"/>
+      <c r="AG58" s="10" t="n"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
+      <c r="AK58" s="11" t="n"/>
+    </row>
+    <row r="60" ht="19.5" customHeight="1"/>
+    <row r="61" ht="19.5" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="B52" s="27" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="C53" s="41" t="inlineStr">
-        <is>
-          <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="D54" s="41" t="inlineStr">
-        <is>
-          <t>todofuken_code：2桁の文字列（01〜47）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="D55" s="41" t="inlineStr">
-        <is>
-          <t>role_id：1〜5の整数</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="C56" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="D57" s="41" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request を返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="C59" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="C60" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="C61" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：認証済みユーザーであればアクセス可能。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="D62" s="41" t="inlineStr">
-        <is>
-          <t>※ 呼び出し元画面の権限に依存する。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="C63" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+          <t>クエリパラメータの検証：</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="B64" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得</t>
+      <c r="D64" s="41" t="inlineStr">
+        <is>
+          <t>q：最大100文字（部分一致用）</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>管理者区分によりカスケード条件を切り替える。</t>
+      <c r="D65" s="41" t="inlineStr">
+        <is>
+          <t>page：1以上の整数</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="D66" s="41" t="inlineStr">
         <is>
-          <t>role_id = 3（中央会）の場合：`chuokai_flg = true` のJAを取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="36" customHeight="1">
+          <t>per_page：1〜100の整数</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
       <c r="D67" s="41" t="inlineStr">
         <is>
-          <t>role_id = 4（JA本店）または 5（JA管理支店）の場合：`chuokai_flg = false` のJAを取得</t>
+          <t>include_id：1以上の整数</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="D68" s="41" t="inlineStr">
         <is>
-          <t>role_id 未指定またはその他の場合：全てのJAを取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="216" customHeight="1">
-      <c r="C69" s="42" t="inlineStr">
+          <t>todofuken_code：2桁の文字列（01〜47）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="D69" s="41" t="inlineStr">
+        <is>
+          <t>role_id：1以上の整数</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="C70" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="D71" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request を返却する（`VALIDATION_ERROR`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="B72" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="C73" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="C74" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="C75" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：呼び出し元画面のビュー権限（`ja.view`）が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="C76" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="C77" s="41" t="inlineStr">
+        <is>
+          <t>DataScope 適用：非 NICHINO_ADMIN/STAFF は自組織配下の JA のみ取得可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="C79" s="41" t="inlineStr">
+        <is>
+          <t>フィルタ適用順：</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>ソート：`ja_code ASC` 固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
+        <is>
+          <t>ページング：`LIMIT :per_page OFFSET (page-1)*per_page`</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="C82" s="41" t="inlineStr">
+        <is>
+          <t>`meta.total` は LIMIT 適用前の総件数（DataScope + 絞込み適用後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>`meta.has_more = page * per_page &lt; total`</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="C84" s="41" t="inlineStr">
+        <is>
+          <t>`include_id` 指定時：上記ページ範囲に含まれていなければ、別途同一条件で SELECT して先頭に prepend。DataScope 範囲外なら silently 無視。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="342" customHeight="1">
+      <c r="C85" s="42" t="inlineStr">
         <is>
           <t>SELECT ja_id, ja_code, ja_name, todofuken_code, chuokai_flg
 FROM m_ja
 WHERE deleted_at IS NULL
+  -- DataScope (auto-applied per session role)
+  AND (:scope_ja_id IS NULL OR ja_id = :scope_ja_id)
+  -- q: free-text partial match
+  AND (:q IS NULL OR ja_code ILIKE :q_like OR ja_name ILIKE :q_like)
+  -- todofuken cascade
   AND (:todofuken_code IS NULL OR todofuken_code = :todofuken_code)
+  -- role_id cascade
   AND (
     CASE
-      WHEN :role_id = 3 THEN chuokai_flg = true
-      WHEN :role_id IN (4, 5) THEN chuokai_flg = false
-      ELSE true
+      WHEN :role_id = 3 THEN chuokai_flg = TRUE
+      WHEN :role_id IN (4, 5) THEN chuokai_flg = FALSE
+      ELSE TRUE
     END
   )
-ORDER BY ja_code ASC</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="n"/>
-      <c r="E69" s="10" t="n"/>
-      <c r="F69" s="10" t="n"/>
-      <c r="G69" s="10" t="n"/>
-      <c r="H69" s="10" t="n"/>
-      <c r="I69" s="10" t="n"/>
-      <c r="J69" s="10" t="n"/>
-      <c r="K69" s="10" t="n"/>
-      <c r="L69" s="10" t="n"/>
-      <c r="M69" s="10" t="n"/>
-      <c r="N69" s="10" t="n"/>
-      <c r="O69" s="10" t="n"/>
-      <c r="P69" s="10" t="n"/>
-      <c r="Q69" s="10" t="n"/>
-      <c r="R69" s="10" t="n"/>
-      <c r="S69" s="10" t="n"/>
-      <c r="T69" s="10" t="n"/>
-      <c r="U69" s="10" t="n"/>
-      <c r="V69" s="10" t="n"/>
-      <c r="W69" s="10" t="n"/>
-      <c r="X69" s="10" t="n"/>
-      <c r="Y69" s="10" t="n"/>
-      <c r="Z69" s="10" t="n"/>
-      <c r="AA69" s="10" t="n"/>
-      <c r="AB69" s="10" t="n"/>
-      <c r="AC69" s="10" t="n"/>
-      <c r="AD69" s="10" t="n"/>
-      <c r="AE69" s="10" t="n"/>
-      <c r="AF69" s="10" t="n"/>
-      <c r="AG69" s="10" t="n"/>
-      <c r="AH69" s="10" t="n"/>
-      <c r="AI69" s="10" t="n"/>
-      <c r="AJ69" s="10" t="n"/>
-      <c r="AK69" s="11" t="n"/>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="B70" s="27" t="inlineStr">
+ORDER BY ja_code ASC
+LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="10" t="n"/>
+      <c r="J85" s="10" t="n"/>
+      <c r="K85" s="10" t="n"/>
+      <c r="L85" s="10" t="n"/>
+      <c r="M85" s="10" t="n"/>
+      <c r="N85" s="10" t="n"/>
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="10" t="n"/>
+      <c r="S85" s="10" t="n"/>
+      <c r="T85" s="10" t="n"/>
+      <c r="U85" s="10" t="n"/>
+      <c r="V85" s="10" t="n"/>
+      <c r="W85" s="10" t="n"/>
+      <c r="X85" s="10" t="n"/>
+      <c r="Y85" s="10" t="n"/>
+      <c r="Z85" s="10" t="n"/>
+      <c r="AA85" s="10" t="n"/>
+      <c r="AB85" s="10" t="n"/>
+      <c r="AC85" s="10" t="n"/>
+      <c r="AD85" s="10" t="n"/>
+      <c r="AE85" s="10" t="n"/>
+      <c r="AF85" s="10" t="n"/>
+      <c r="AG85" s="10" t="n"/>
+      <c r="AH85" s="10" t="n"/>
+      <c r="AI85" s="10" t="n"/>
+      <c r="AJ85" s="10" t="n"/>
+      <c r="AK85" s="11" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="B86" s="27" t="inlineStr">
         <is>
           <t>4.4 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="C71" s="41" t="inlineStr">
+    <row r="87" ht="18" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
         <is>
           <t>取得結果を data 配列として返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="B72" s="27" t="inlineStr">
+    <row r="88" ht="18" customHeight="1">
+      <c r="B88" s="27" t="inlineStr">
         <is>
           <t>4.5 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="C73" s="41" t="inlineStr">
+    <row r="89" ht="18" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="137">
+  <mergeCells count="204">
     <mergeCell ref="J11:AK11"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Y27:AE27"/>
+    <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="Y36:AE36"/>
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="B54:I54"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C53:AK53"/>
-    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="D71:AK71"/>
     <mergeCell ref="M32:P32"/>
-    <mergeCell ref="M29:P29"/>
+    <mergeCell ref="C77:AK77"/>
+    <mergeCell ref="N18:AK18"/>
+    <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="AF21:AK21"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
+    <mergeCell ref="D64:AK64"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="C45:AK45"/>
+    <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C40:C43"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="C65:AK65"/>
-    <mergeCell ref="D33:L33"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="Y21:AB21"/>
+    <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="C80:AK80"/>
+    <mergeCell ref="AF36:AK36"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="Q43:S43"/>
+    <mergeCell ref="C46:AK46"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="T31:X31"/>
+    <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="D34:L34"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="Q42:S42"/>
+    <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="C48:AK48"/>
+    <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="C70:AK70"/>
+    <mergeCell ref="T37:X37"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="D36:L36"/>
     <mergeCell ref="M33:P33"/>
-    <mergeCell ref="T30:X30"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="C39:L39"/>
+    <mergeCell ref="T38:X38"/>
+    <mergeCell ref="C49:AK49"/>
+    <mergeCell ref="B86:AK86"/>
+    <mergeCell ref="C32:L32"/>
     <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="C42:AK42"/>
+    <mergeCell ref="D37:L37"/>
+    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="AF41:AK41"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="AC21:AE21"/>
+    <mergeCell ref="C33:L33"/>
+    <mergeCell ref="B14:I18"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="AF38:AK38"/>
+    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="Y30:AE30"/>
-    <mergeCell ref="B64:AK64"/>
+    <mergeCell ref="D38:L38"/>
+    <mergeCell ref="T40:X40"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="Y29:AE29"/>
-    <mergeCell ref="C59:AK59"/>
+    <mergeCell ref="D65:AK65"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
-    <mergeCell ref="A25:AK25"/>
+    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="B51:I51"/>
+    <mergeCell ref="C52:AK52"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="M21:P21"/>
-    <mergeCell ref="Y31:AE31"/>
-    <mergeCell ref="C39:AK39"/>
-    <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B35:I35"/>
     <mergeCell ref="D66:AK66"/>
-    <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="B58:AK58"/>
+    <mergeCell ref="M36:P36"/>
+    <mergeCell ref="Y37:AE37"/>
+    <mergeCell ref="T39:X39"/>
+    <mergeCell ref="C81:AK81"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="B52:AK52"/>
+    <mergeCell ref="Q35:S35"/>
     <mergeCell ref="T32:X32"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="T42:X42"/>
     <mergeCell ref="C28:L28"/>
+    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="C82:AK82"/>
+    <mergeCell ref="A20:AK20"/>
+    <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
+    <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="D54:AK54"/>
+    <mergeCell ref="C89:AK89"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="M34:P34"/>
+    <mergeCell ref="C79:AK79"/>
+    <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="C63:AK63"/>
-    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="C34:C38"/>
+    <mergeCell ref="T26:X26"/>
     <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="A51:AK51"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="C56:AK56"/>
+    <mergeCell ref="T41:X41"/>
+    <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="M31:P31"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="C36:AK36"/>
-    <mergeCell ref="D57:AK57"/>
+    <mergeCell ref="M40:P40"/>
+    <mergeCell ref="T43:X43"/>
+    <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
     <mergeCell ref="B72:AK72"/>
-    <mergeCell ref="B14:I17"/>
+    <mergeCell ref="T36:X36"/>
     <mergeCell ref="C27:L27"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B70:AK70"/>
-    <mergeCell ref="D32:L32"/>
-    <mergeCell ref="C69:AK69"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="M41:P41"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="D41:L41"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="M38:P38"/>
+    <mergeCell ref="C83:AK83"/>
+    <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="Y32:AE32"/>
+    <mergeCell ref="D43:L43"/>
     <mergeCell ref="D68:AK68"/>
-    <mergeCell ref="D55:AK55"/>
-    <mergeCell ref="A19:AK19"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="B88:AK88"/>
+    <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="D67:AK67"/>
+    <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B57:I57"/>
+    <mergeCell ref="A30:AK30"/>
+    <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="D69:AK69"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C60:AK60"/>
+    <mergeCell ref="A61:AK61"/>
+    <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="C71:AK71"/>
+    <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
-    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="Y22:AB22"/>
-    <mergeCell ref="C21:L21"/>
-    <mergeCell ref="D31:L31"/>
+    <mergeCell ref="B62:AK62"/>
+    <mergeCell ref="Y34:AE34"/>
+    <mergeCell ref="Q39:S39"/>
     <mergeCell ref="M28:P28"/>
-    <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="M42:P42"/>
+    <mergeCell ref="M37:P37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/design/ACSMS-SCR-024/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_アカウントマスタ明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-024/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_アカウントマスタ明細検索画面_V1.0.xlsx
@@ -1516,7 +1516,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1870,7 +1870,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -2839,7 +2839,7 @@
     <row r="55" ht="18" customHeight="1">
       <c r="C55" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3859,7 +3859,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4427,7 +4427,7 @@
       <c r="U14" s="11" t="n"/>
       <c r="V14" s="19" t="inlineStr">
         <is>
-          <t>関連データが存在するため削除できません。</t>
+          <t>このレコードは現在使用中のため、削除できません。</t>
         </is>
       </c>
       <c r="W14" s="10" t="n"/>
@@ -4674,7 +4674,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4990,7 +4990,7 @@
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="19" t="inlineStr">
         <is>
-          <t>JAプルダウンリストを取得する（共用API）。2つのユースケースを1つのエンドポイントで提供：（A）ページング+フリーテキスト検索（SCR-009 等のフォーム用）、（B）都道府県・管理者区分によるカスケード絞込み（SCR-024 アカウント検索／SCR-025 登録用）。両方のレスポンス形状は同一（`{data, meta}`）。</t>
+          <t>JAプルダウンリストを取得する（都道府県・管理者区分によるカスケード絞込み。共用API：アカウント検索・登録等で使用）</t>
         </is>
       </c>
       <c r="T9" s="10" t="n"/>
@@ -5137,7 +5137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK115"/>
+  <dimension ref="A1:AK112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -5298,7 +5298,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5652,7 +5652,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>todofuken_code</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="D24" s="10" t="n"/>
@@ -6072,7 +6072,7 @@
       <c r="L24" s="11" t="n"/>
       <c r="M24" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N24" s="10" t="n"/>
@@ -6094,20 +6094,16 @@
       <c r="V24" s="10" t="n"/>
       <c r="W24" s="10" t="n"/>
       <c r="X24" s="11" t="n"/>
-      <c r="Y24" s="17" t="n">
-        <v>2</v>
-      </c>
+      <c r="Y24" s="17" t="inlineStr"/>
       <c r="Z24" s="10" t="n"/>
       <c r="AA24" s="10" t="n"/>
       <c r="AB24" s="11" t="n"/>
-      <c r="AC24" s="17" t="n">
-        <v>2</v>
-      </c>
+      <c r="AC24" s="17" t="inlineStr"/>
       <c r="AD24" s="10" t="n"/>
       <c r="AE24" s="11" t="n"/>
       <c r="AF24" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード（01〜47）。完全一致。未指定=全て</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG24" s="10" t="n"/>
@@ -6122,7 +6118,7 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -6167,7 +6163,7 @@
       <c r="AE25" s="11" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>管理支店ID</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -6182,7 +6178,7 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_id</t>
+          <t>page</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -6227,7 +6223,7 @@
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID</t>
+          <t>ページ番号（デフォルト: 1）</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -6242,7 +6238,7 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -6287,7 +6283,7 @@
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（デフォルト: 1）</t>
+          <t>1ページあたりの件数（デフォルト: 20、最大: 100）</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -6302,7 +6298,7 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>sort_by</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -6316,7 +6312,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -6347,7 +6343,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数（デフォルト: 20、最大: 100）</t>
+          <t>ソート項目（デフォルト: created_at）</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -6362,7 +6358,7 @@
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -6407,7 +6403,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>ソート項目（デフォルト: created_at）</t>
+          <t>ソート順（asc / desc、デフォルト: desc）</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -6416,84 +6412,88 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>sort_order</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
-      <c r="J30" s="10" t="n"/>
-      <c r="K30" s="10" t="n"/>
-      <c r="L30" s="11" t="n"/>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N30" s="10" t="n"/>
-      <c r="O30" s="10" t="n"/>
-      <c r="P30" s="11" t="n"/>
-      <c r="Q30" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R30" s="10" t="n"/>
-      <c r="S30" s="11" t="n"/>
-      <c r="T30" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U30" s="10" t="n"/>
-      <c r="V30" s="10" t="n"/>
-      <c r="W30" s="10" t="n"/>
-      <c r="X30" s="11" t="n"/>
-      <c r="Y30" s="17" t="inlineStr"/>
-      <c r="Z30" s="10" t="n"/>
-      <c r="AA30" s="10" t="n"/>
-      <c r="AB30" s="11" t="n"/>
-      <c r="AC30" s="17" t="inlineStr"/>
-      <c r="AD30" s="10" t="n"/>
-      <c r="AE30" s="11" t="n"/>
-      <c r="AF30" s="19" t="inlineStr">
-        <is>
-          <t>ソート順（asc / desc、デフォルト: desc）</t>
-        </is>
-      </c>
-      <c r="AG30" s="10" t="n"/>
-      <c r="AH30" s="10" t="n"/>
-      <c r="AI30" s="10" t="n"/>
-      <c r="AJ30" s="10" t="n"/>
-      <c r="AK30" s="11" t="n"/>
-    </row>
-    <row r="31" ht="19.5" customHeight="1"/>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="A32" s="27" t="inlineStr">
+    <row r="30" ht="19.5" customHeight="1"/>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="19.5" customHeight="1"/>
-    <row r="34" ht="19.5" customHeight="1">
-      <c r="B34" s="30" t="inlineStr">
+    <row r="32" ht="19.5" customHeight="1"/>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="10" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="n"/>
+      <c r="O33" s="10" t="n"/>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="11" t="n"/>
+      <c r="T33" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
+      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="10" t="n"/>
+      <c r="W33" s="10" t="n"/>
+      <c r="X33" s="11" t="n"/>
+      <c r="Y33" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="Z33" s="10" t="n"/>
+      <c r="AA33" s="10" t="n"/>
+      <c r="AB33" s="10" t="n"/>
+      <c r="AC33" s="10" t="n"/>
+      <c r="AD33" s="10" t="n"/>
+      <c r="AE33" s="11" t="n"/>
+      <c r="AF33" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG33" s="10" t="n"/>
+      <c r="AH33" s="10" t="n"/>
+      <c r="AI33" s="10" t="n"/>
+      <c r="AJ33" s="10" t="n"/>
+      <c r="AK33" s="11" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
         </is>
       </c>
       <c r="D34" s="10" t="n"/>
@@ -6505,33 +6505,29 @@
       <c r="J34" s="10" t="n"/>
       <c r="K34" s="10" t="n"/>
       <c r="L34" s="11" t="n"/>
-      <c r="M34" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M34" s="17" t="inlineStr">
+        <is>
+          <t>Array</t>
         </is>
       </c>
       <c r="N34" s="10" t="n"/>
       <c r="O34" s="10" t="n"/>
       <c r="P34" s="11" t="n"/>
-      <c r="Q34" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="R34" s="10" t="n"/>
       <c r="S34" s="11" t="n"/>
-      <c r="T34" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
+      <c r="T34" s="17" t="inlineStr"/>
       <c r="U34" s="10" t="n"/>
       <c r="V34" s="10" t="n"/>
       <c r="W34" s="10" t="n"/>
       <c r="X34" s="11" t="n"/>
-      <c r="Y34" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
+      <c r="Y34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="Z34" s="10" t="n"/>
@@ -6540,9 +6536,9 @@
       <c r="AC34" s="10" t="n"/>
       <c r="AD34" s="10" t="n"/>
       <c r="AE34" s="11" t="n"/>
-      <c r="AF34" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF34" s="19" t="inlineStr">
+        <is>
+          <t>アカウント一覧</t>
         </is>
       </c>
       <c r="AG34" s="10" t="n"/>
@@ -6553,14 +6549,14 @@
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C35" s="37" t="n"/>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>account_id</t>
+        </is>
+      </c>
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
@@ -6571,7 +6567,7 @@
       <c r="L35" s="11" t="n"/>
       <c r="M35" s="17" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N35" s="10" t="n"/>
@@ -6579,7 +6575,7 @@
       <c r="P35" s="11" t="n"/>
       <c r="Q35" s="17" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R35" s="10" t="n"/>
@@ -6602,7 +6598,7 @@
       <c r="AE35" s="11" t="n"/>
       <c r="AF35" s="19" t="inlineStr">
         <is>
-          <t>アカウント一覧</t>
+          <t>アカウントID</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -6613,12 +6609,12 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="37" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="C36" s="38" t="n"/>
       <c r="D36" s="19" t="inlineStr">
         <is>
-          <t>account_id</t>
+          <t>login_id</t>
         </is>
       </c>
       <c r="E36" s="10" t="n"/>
@@ -6631,7 +6627,7 @@
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N36" s="10" t="n"/>
@@ -6662,7 +6658,7 @@
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>アカウントID</t>
+          <t>ログインID</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -6673,12 +6669,12 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>login_id</t>
+          <t>account_name</t>
         </is>
       </c>
       <c r="E37" s="10" t="n"/>
@@ -6722,7 +6718,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>ログインID</t>
+          <t>アカウント名</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -6733,12 +6729,12 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>account_name</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -6751,7 +6747,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -6782,7 +6778,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>アカウント名</t>
+          <t>管理者区分ID</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -6793,12 +6789,12 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -6811,7 +6807,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -6842,7 +6838,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>管理者区分ID</t>
+          <t>管理者区分名称</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -6853,12 +6849,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -6891,7 +6887,7 @@
       <c r="X40" s="11" t="n"/>
       <c r="Y40" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z40" s="10" t="n"/>
@@ -6902,7 +6898,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>管理者区分名称</t>
+          <t>都道府県コード</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -6913,12 +6909,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>todofuken_code</t>
+          <t>todofuken_name</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -6962,7 +6958,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード</t>
+          <t>都道府県名</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -6973,12 +6969,12 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>todofuken_name</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -6991,7 +6987,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -7022,7 +7018,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>都道府県名</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -7033,12 +7029,12 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>ja_name</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -7051,7 +7047,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N43" s="10" t="n"/>
@@ -7082,7 +7078,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>JA名称</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -7093,12 +7089,12 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>ja_name</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -7111,7 +7107,7 @@
       <c r="L44" s="11" t="n"/>
       <c r="M44" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N44" s="10" t="n"/>
@@ -7142,7 +7138,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>JA名称</t>
+          <t>管理支店ID</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -7153,12 +7149,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_id</t>
+          <t>kanri_shiten_name</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -7171,7 +7167,7 @@
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N45" s="10" t="n"/>
@@ -7202,7 +7198,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID</t>
+          <t>管理支店名称</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -7213,12 +7209,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name</t>
+          <t>paper_flg</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -7231,7 +7227,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -7251,7 +7247,7 @@
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z46" s="10" t="n"/>
@@ -7262,7 +7258,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>管理支店名称</t>
+          <t>紙版取扱フラグ</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -7273,12 +7269,12 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>paper_flg</t>
+          <t>denshi_flg</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -7322,7 +7318,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>紙版取扱フラグ</t>
+          <t>電子版取扱フラグ</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -7333,12 +7329,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>denshi_flg</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -7351,7 +7347,7 @@
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N48" s="10" t="n"/>
@@ -7364,7 +7360,11 @@
       </c>
       <c r="R48" s="10" t="n"/>
       <c r="S48" s="11" t="n"/>
-      <c r="T48" s="17" t="inlineStr"/>
+      <c r="T48" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U48" s="10" t="n"/>
       <c r="V48" s="10" t="n"/>
       <c r="W48" s="10" t="n"/>
@@ -7382,7 +7382,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>電子版取扱フラグ</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -7393,12 +7393,12 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="C49" s="38" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="C49" s="39" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -7435,7 +7435,7 @@
       <c r="X49" s="11" t="n"/>
       <c r="Y49" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z49" s="10" t="n"/>
@@ -7446,7 +7446,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>更新日時</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -7457,14 +7457,14 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="C50" s="39" t="n"/>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="n"/>
       <c r="E50" s="10" t="n"/>
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
@@ -7475,7 +7475,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -7488,18 +7488,14 @@
       </c>
       <c r="R50" s="10" t="n"/>
       <c r="S50" s="11" t="n"/>
-      <c r="T50" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T50" s="17" t="inlineStr"/>
       <c r="U50" s="10" t="n"/>
       <c r="V50" s="10" t="n"/>
       <c r="W50" s="10" t="n"/>
       <c r="X50" s="11" t="n"/>
       <c r="Y50" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z50" s="10" t="n"/>
@@ -7510,7 +7506,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>ページネーション情報</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -7521,14 +7517,14 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="C51" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="C51" s="37" t="n"/>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
       <c r="E51" s="10" t="n"/>
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
@@ -7539,7 +7535,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N51" s="10" t="n"/>
@@ -7570,7 +7566,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>総件数</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -7581,12 +7577,12 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="C52" s="37" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="C52" s="38" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>page</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -7630,7 +7626,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>現在ページ</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -7641,12 +7637,12 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -7690,7 +7686,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>現在ページ</t>
+          <t>1ページあたりの件数</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -7701,12 +7697,12 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="C54" s="38" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="C54" s="39" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>total_pages</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
@@ -7750,7 +7746,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数</t>
+          <t>総ページ数</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -7759,124 +7755,64 @@
       <c r="AJ54" s="10" t="n"/>
       <c r="AK54" s="11" t="n"/>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="B55" s="31" t="n">
-        <v>21</v>
-      </c>
-      <c r="C55" s="39" t="n"/>
-      <c r="D55" s="19" t="inlineStr">
-        <is>
-          <t>total_pages</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="10" t="n"/>
-      <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n"/>
-      <c r="I55" s="10" t="n"/>
-      <c r="J55" s="10" t="n"/>
-      <c r="K55" s="10" t="n"/>
-      <c r="L55" s="11" t="n"/>
-      <c r="M55" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N55" s="10" t="n"/>
-      <c r="O55" s="10" t="n"/>
-      <c r="P55" s="11" t="n"/>
-      <c r="Q55" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R55" s="10" t="n"/>
-      <c r="S55" s="11" t="n"/>
-      <c r="T55" s="17" t="inlineStr"/>
-      <c r="U55" s="10" t="n"/>
-      <c r="V55" s="10" t="n"/>
-      <c r="W55" s="10" t="n"/>
-      <c r="X55" s="11" t="n"/>
-      <c r="Y55" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z55" s="10" t="n"/>
-      <c r="AA55" s="10" t="n"/>
-      <c r="AB55" s="10" t="n"/>
-      <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="10" t="n"/>
-      <c r="AE55" s="11" t="n"/>
-      <c r="AF55" s="19" t="inlineStr">
-        <is>
-          <t>総ページ数</t>
-        </is>
-      </c>
-      <c r="AG55" s="10" t="n"/>
-      <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="10" t="n"/>
-      <c r="AJ55" s="10" t="n"/>
-      <c r="AK55" s="11" t="n"/>
-    </row>
-    <row r="56" ht="19.5" customHeight="1"/>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="B57" s="40" t="inlineStr">
+    <row r="55" ht="19.5" customHeight="1"/>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="B56" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="C58" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/accounts?login_id=admin&amp;role_id=4&amp;todofuken_code=13&amp;ja_id=10&amp;page=1&amp;per_page=20&amp;sort_by=created_at&amp;sort_order=desc</t>
-        </is>
-      </c>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
-      <c r="J58" s="10" t="n"/>
-      <c r="K58" s="10" t="n"/>
-      <c r="L58" s="10" t="n"/>
-      <c r="M58" s="10" t="n"/>
-      <c r="N58" s="10" t="n"/>
-      <c r="O58" s="10" t="n"/>
-      <c r="P58" s="10" t="n"/>
-      <c r="Q58" s="10" t="n"/>
-      <c r="R58" s="10" t="n"/>
-      <c r="S58" s="10" t="n"/>
-      <c r="T58" s="10" t="n"/>
-      <c r="U58" s="10" t="n"/>
-      <c r="V58" s="10" t="n"/>
-      <c r="W58" s="10" t="n"/>
-      <c r="X58" s="10" t="n"/>
-      <c r="Y58" s="10" t="n"/>
-      <c r="Z58" s="10" t="n"/>
-      <c r="AA58" s="10" t="n"/>
-      <c r="AB58" s="10" t="n"/>
-      <c r="AC58" s="10" t="n"/>
-      <c r="AD58" s="10" t="n"/>
-      <c r="AE58" s="10" t="n"/>
-      <c r="AF58" s="10" t="n"/>
-      <c r="AG58" s="10" t="n"/>
-      <c r="AH58" s="10" t="n"/>
-      <c r="AI58" s="10" t="n"/>
-      <c r="AJ58" s="10" t="n"/>
-      <c r="AK58" s="11" t="n"/>
-    </row>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="B60" s="40" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/accounts?login_id=admin&amp;role_id=1&amp;page=1&amp;per_page=20&amp;sort_by=created_at&amp;sort_order=desc</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="11" t="n"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="B59" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="409" customHeight="1">
-      <c r="C61" s="19" t="inlineStr">
+    <row r="60" ht="409" customHeight="1">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -7924,50 +7860,50 @@
 }</t>
         </is>
       </c>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="n"/>
-      <c r="L61" s="10" t="n"/>
-      <c r="M61" s="10" t="n"/>
-      <c r="N61" s="10" t="n"/>
-      <c r="O61" s="10" t="n"/>
-      <c r="P61" s="10" t="n"/>
-      <c r="Q61" s="10" t="n"/>
-      <c r="R61" s="10" t="n"/>
-      <c r="S61" s="10" t="n"/>
-      <c r="T61" s="10" t="n"/>
-      <c r="U61" s="10" t="n"/>
-      <c r="V61" s="10" t="n"/>
-      <c r="W61" s="10" t="n"/>
-      <c r="X61" s="10" t="n"/>
-      <c r="Y61" s="10" t="n"/>
-      <c r="Z61" s="10" t="n"/>
-      <c r="AA61" s="10" t="n"/>
-      <c r="AB61" s="10" t="n"/>
-      <c r="AC61" s="10" t="n"/>
-      <c r="AD61" s="10" t="n"/>
-      <c r="AE61" s="10" t="n"/>
-      <c r="AF61" s="10" t="n"/>
-      <c r="AG61" s="10" t="n"/>
-      <c r="AH61" s="10" t="n"/>
-      <c r="AI61" s="10" t="n"/>
-      <c r="AJ61" s="10" t="n"/>
-      <c r="AK61" s="11" t="n"/>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="B63" s="40" t="inlineStr">
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AF60" s="10" t="n"/>
+      <c r="AG60" s="10" t="n"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
+      <c r="AK60" s="11" t="n"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="72" customHeight="1">
-      <c r="C64" s="19" t="inlineStr">
+    <row r="63" ht="72" customHeight="1">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -7975,50 +7911,50 @@
 }</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="10" t="n"/>
-      <c r="F64" s="10" t="n"/>
-      <c r="G64" s="10" t="n"/>
-      <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="n"/>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="10" t="n"/>
-      <c r="L64" s="10" t="n"/>
-      <c r="M64" s="10" t="n"/>
-      <c r="N64" s="10" t="n"/>
-      <c r="O64" s="10" t="n"/>
-      <c r="P64" s="10" t="n"/>
-      <c r="Q64" s="10" t="n"/>
-      <c r="R64" s="10" t="n"/>
-      <c r="S64" s="10" t="n"/>
-      <c r="T64" s="10" t="n"/>
-      <c r="U64" s="10" t="n"/>
-      <c r="V64" s="10" t="n"/>
-      <c r="W64" s="10" t="n"/>
-      <c r="X64" s="10" t="n"/>
-      <c r="Y64" s="10" t="n"/>
-      <c r="Z64" s="10" t="n"/>
-      <c r="AA64" s="10" t="n"/>
-      <c r="AB64" s="10" t="n"/>
-      <c r="AC64" s="10" t="n"/>
-      <c r="AD64" s="10" t="n"/>
-      <c r="AE64" s="10" t="n"/>
-      <c r="AF64" s="10" t="n"/>
-      <c r="AG64" s="10" t="n"/>
-      <c r="AH64" s="10" t="n"/>
-      <c r="AI64" s="10" t="n"/>
-      <c r="AJ64" s="10" t="n"/>
-      <c r="AK64" s="11" t="n"/>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="B66" s="40" t="inlineStr">
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="10" t="n"/>
+      <c r="X63" s="10" t="n"/>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="10" t="n"/>
+      <c r="AE63" s="10" t="n"/>
+      <c r="AF63" s="10" t="n"/>
+      <c r="AG63" s="10" t="n"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="10" t="n"/>
+      <c r="AJ63" s="10" t="n"/>
+      <c r="AK63" s="11" t="n"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="B65" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="72" customHeight="1">
-      <c r="C67" s="19" t="inlineStr">
+    <row r="66" ht="72" customHeight="1">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -8026,50 +7962,50 @@
 }</t>
         </is>
       </c>
-      <c r="D67" s="10" t="n"/>
-      <c r="E67" s="10" t="n"/>
-      <c r="F67" s="10" t="n"/>
-      <c r="G67" s="10" t="n"/>
-      <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="n"/>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
-      <c r="L67" s="10" t="n"/>
-      <c r="M67" s="10" t="n"/>
-      <c r="N67" s="10" t="n"/>
-      <c r="O67" s="10" t="n"/>
-      <c r="P67" s="10" t="n"/>
-      <c r="Q67" s="10" t="n"/>
-      <c r="R67" s="10" t="n"/>
-      <c r="S67" s="10" t="n"/>
-      <c r="T67" s="10" t="n"/>
-      <c r="U67" s="10" t="n"/>
-      <c r="V67" s="10" t="n"/>
-      <c r="W67" s="10" t="n"/>
-      <c r="X67" s="10" t="n"/>
-      <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="10" t="n"/>
-      <c r="AA67" s="10" t="n"/>
-      <c r="AB67" s="10" t="n"/>
-      <c r="AC67" s="10" t="n"/>
-      <c r="AD67" s="10" t="n"/>
-      <c r="AE67" s="10" t="n"/>
-      <c r="AF67" s="10" t="n"/>
-      <c r="AG67" s="10" t="n"/>
-      <c r="AH67" s="10" t="n"/>
-      <c r="AI67" s="10" t="n"/>
-      <c r="AJ67" s="10" t="n"/>
-      <c r="AK67" s="11" t="n"/>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
-      <c r="B69" s="40" t="inlineStr">
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="10" t="n"/>
+      <c r="X66" s="10" t="n"/>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="10" t="n"/>
+      <c r="AE66" s="10" t="n"/>
+      <c r="AF66" s="10" t="n"/>
+      <c r="AG66" s="10" t="n"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="10" t="n"/>
+      <c r="AJ66" s="10" t="n"/>
+      <c r="AK66" s="11" t="n"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="72" customHeight="1">
-      <c r="C70" s="19" t="inlineStr">
+    <row r="69" ht="72" customHeight="1">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -8077,309 +8013,294 @@
 }</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="10" t="n"/>
-      <c r="M70" s="10" t="n"/>
-      <c r="N70" s="10" t="n"/>
-      <c r="O70" s="10" t="n"/>
-      <c r="P70" s="10" t="n"/>
-      <c r="Q70" s="10" t="n"/>
-      <c r="R70" s="10" t="n"/>
-      <c r="S70" s="10" t="n"/>
-      <c r="T70" s="10" t="n"/>
-      <c r="U70" s="10" t="n"/>
-      <c r="V70" s="10" t="n"/>
-      <c r="W70" s="10" t="n"/>
-      <c r="X70" s="10" t="n"/>
-      <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
-      <c r="AA70" s="10" t="n"/>
-      <c r="AB70" s="10" t="n"/>
-      <c r="AC70" s="10" t="n"/>
-      <c r="AD70" s="10" t="n"/>
-      <c r="AE70" s="10" t="n"/>
-      <c r="AF70" s="10" t="n"/>
-      <c r="AG70" s="10" t="n"/>
-      <c r="AH70" s="10" t="n"/>
-      <c r="AI70" s="10" t="n"/>
-      <c r="AJ70" s="10" t="n"/>
-      <c r="AK70" s="11" t="n"/>
-    </row>
-    <row r="72" ht="19.5" customHeight="1"/>
-    <row r="73" ht="19.5" customHeight="1">
-      <c r="A73" s="27" t="inlineStr">
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="10" t="n"/>
+      <c r="X69" s="10" t="n"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="10" t="n"/>
+      <c r="AE69" s="10" t="n"/>
+      <c r="AF69" s="10" t="n"/>
+      <c r="AG69" s="10" t="n"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="10" t="n"/>
+      <c r="AJ69" s="10" t="n"/>
+      <c r="AK69" s="11" t="n"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="1"/>
+    <row r="72" ht="19.5" customHeight="1">
+      <c r="A72" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="B74" s="27" t="inlineStr">
-        <is>
-          <t>4.1 リクエストのバリデーション</t>
+      <c r="C74" s="41" t="inlineStr">
+        <is>
+          <t>クエリパラメータの検証：</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="C75" s="41" t="inlineStr">
-        <is>
-          <t>クエリパラメータの検証：</t>
+      <c r="D75" s="41" t="inlineStr">
+        <is>
+          <t>login_id：最大20桁、文字列</t>
         </is>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1">
       <c r="D76" s="41" t="inlineStr">
         <is>
-          <t>login_id：最大20桁、文字列</t>
+          <t>role_id：1〜5の整数</t>
         </is>
       </c>
     </row>
     <row r="77" ht="18" customHeight="1">
       <c r="D77" s="41" t="inlineStr">
         <is>
-          <t>role_id：1〜5の整数</t>
+          <t>ja_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="D78" s="41" t="inlineStr">
         <is>
-          <t>todofuken_code：2桁の文字列（01〜47）</t>
+          <t>kanri_shiten_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="D79" s="41" t="inlineStr">
         <is>
-          <t>ja_id：数値型チェック</t>
+          <t>page：正の整数（デフォルト: 1）</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="D80" s="41" t="inlineStr">
         <is>
-          <t>kanri_shiten_id：数値型チェック</t>
+          <t>per_page：1〜100の整数（デフォルト: 20）</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="D81" s="41" t="inlineStr">
         <is>
-          <t>page：正の整数（デフォルト: 1）</t>
+          <t>sort_by：許可されたカラム名（login_id, role_id, created_at）</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>per_page：1〜100の整数（デフォルト: 20）</t>
+          <t>sort_order：asc または desc（デフォルト: desc）</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
-      <c r="D83" s="41" t="inlineStr">
-        <is>
-          <t>sort_by：許可されたカラム名（login_id, role_id, created_at）</t>
+      <c r="C83" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="D84" s="41" t="inlineStr">
         <is>
-          <t>sort_order：asc または desc（デフォルト: desc）</t>
+          <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="C85" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
+      <c r="B85" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="D86" s="41" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request を返却する。</t>
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="B87" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="C88" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+          <t>権限チェック：`account.view` を保持しているか確認する。</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="C89" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+      <c r="D89" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="C90" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：`account.view` を保持しているか確認する。</t>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="D91" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="B93" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
+          <t>検索条件を構築する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="36" customHeight="1">
+      <c r="D93" s="41" t="inlineStr">
+        <is>
+          <t>login_id が指定されている場合：`LIKE '%' || :login_id || '%'`（部分一致）</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>検索条件を構築する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="36" customHeight="1">
+      <c r="D94" s="41" t="inlineStr">
+        <is>
+          <t>role_id が指定されている場合：`= :role_id`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
       <c r="D95" s="41" t="inlineStr">
         <is>
-          <t>login_id が指定されている場合：`LIKE '%' || :login_id || '%'`（部分一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
+          <t>ja_id が指定されている場合：`= :ja_id`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
       <c r="D96" s="41" t="inlineStr">
         <is>
-          <t>role_id が指定されている場合：`= :role_id`（完全一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="36" customHeight="1">
-      <c r="D97" s="41" t="inlineStr">
-        <is>
-          <t>todofuken_code が指定されている場合：`= :todofuken_code`（完全一致）</t>
+          <t>kanri_shiten_id が指定されている場合：`= :kanri_shiten_id`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="C97" s="41" t="inlineStr">
+        <is>
+          <t>常に `deleted_at IS NULL` でフィルタリングする。</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
-      <c r="D98" s="41" t="inlineStr">
-        <is>
-          <t>ja_id が指定されている場合：`= :ja_id`（完全一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="36" customHeight="1">
-      <c r="D99" s="41" t="inlineStr">
-        <is>
-          <t>kanri_shiten_id が指定されている場合：`= :kanri_shiten_id`（完全一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="18" customHeight="1">
-      <c r="C100" s="41" t="inlineStr">
-        <is>
-          <t>常に `deleted_at IS NULL` でフィルタリングする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="C101" s="41" t="inlineStr">
+      <c r="C98" s="41" t="inlineStr">
         <is>
           <t>NICHINO_ADMINは全アカウントを参照可能（DataScope制限なし）。</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="18" customHeight="1">
-      <c r="B102" s="27" t="inlineStr">
+    <row r="99" ht="18" customHeight="1">
+      <c r="B99" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="144" customHeight="1">
-      <c r="C103" s="42" t="inlineStr">
+    <row r="100" ht="126" customHeight="1">
+      <c r="C100" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS total
 FROM m_account a
 WHERE a.deleted_at IS NULL
   AND (:login_id IS NULL OR a.login_id LIKE '%' || :login_id || '%')
   AND (:role_id IS NULL OR a.role_id = :role_id)
-  AND (:todofuken_code IS NULL OR a.todofuken_code = :todofuken_code)
   AND (:ja_id IS NULL OR a.ja_id = :ja_id)
   AND (:kanri_shiten_id IS NULL OR a.kanri_shiten_id = :kanri_shiten_id)</t>
         </is>
       </c>
-      <c r="D103" s="10" t="n"/>
-      <c r="E103" s="10" t="n"/>
-      <c r="F103" s="10" t="n"/>
-      <c r="G103" s="10" t="n"/>
-      <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="n"/>
-      <c r="J103" s="10" t="n"/>
-      <c r="K103" s="10" t="n"/>
-      <c r="L103" s="10" t="n"/>
-      <c r="M103" s="10" t="n"/>
-      <c r="N103" s="10" t="n"/>
-      <c r="O103" s="10" t="n"/>
-      <c r="P103" s="10" t="n"/>
-      <c r="Q103" s="10" t="n"/>
-      <c r="R103" s="10" t="n"/>
-      <c r="S103" s="10" t="n"/>
-      <c r="T103" s="10" t="n"/>
-      <c r="U103" s="10" t="n"/>
-      <c r="V103" s="10" t="n"/>
-      <c r="W103" s="10" t="n"/>
-      <c r="X103" s="10" t="n"/>
-      <c r="Y103" s="10" t="n"/>
-      <c r="Z103" s="10" t="n"/>
-      <c r="AA103" s="10" t="n"/>
-      <c r="AB103" s="10" t="n"/>
-      <c r="AC103" s="10" t="n"/>
-      <c r="AD103" s="10" t="n"/>
-      <c r="AE103" s="10" t="n"/>
-      <c r="AF103" s="10" t="n"/>
-      <c r="AG103" s="10" t="n"/>
-      <c r="AH103" s="10" t="n"/>
-      <c r="AI103" s="10" t="n"/>
-      <c r="AJ103" s="10" t="n"/>
-      <c r="AK103" s="11" t="n"/>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="B104" s="27" t="inlineStr">
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="10" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="10" t="n"/>
+      <c r="I100" s="10" t="n"/>
+      <c r="J100" s="10" t="n"/>
+      <c r="K100" s="10" t="n"/>
+      <c r="L100" s="10" t="n"/>
+      <c r="M100" s="10" t="n"/>
+      <c r="N100" s="10" t="n"/>
+      <c r="O100" s="10" t="n"/>
+      <c r="P100" s="10" t="n"/>
+      <c r="Q100" s="10" t="n"/>
+      <c r="R100" s="10" t="n"/>
+      <c r="S100" s="10" t="n"/>
+      <c r="T100" s="10" t="n"/>
+      <c r="U100" s="10" t="n"/>
+      <c r="V100" s="10" t="n"/>
+      <c r="W100" s="10" t="n"/>
+      <c r="X100" s="10" t="n"/>
+      <c r="Y100" s="10" t="n"/>
+      <c r="Z100" s="10" t="n"/>
+      <c r="AA100" s="10" t="n"/>
+      <c r="AB100" s="10" t="n"/>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="10" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="10" t="n"/>
+      <c r="AK100" s="11" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="B101" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="378" customHeight="1">
-      <c r="C105" s="42" t="inlineStr">
+    <row r="102" ht="360" customHeight="1">
+      <c r="C102" s="42" t="inlineStr">
         <is>
           <t>SELECT a.account_id, a.login_id, a.account_name,
        a.role_id, r.role_name,
@@ -8396,7 +8317,6 @@
 WHERE a.deleted_at IS NULL
   AND (:login_id IS NULL OR a.login_id LIKE '%' || :login_id || '%')
   AND (:role_id IS NULL OR a.role_id = :role_id)
-  AND (:todofuken_code IS NULL OR a.todofuken_code = :todofuken_code)
   AND (:ja_id IS NULL OR a.ja_id = :ja_id)
   AND (:kanri_shiten_id IS NULL OR a.kanri_shiten_id = :kanri_shiten_id)
 ORDER BY a.:sort_by :sort_order
@@ -8404,173 +8324,177 @@
 OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D105" s="10" t="n"/>
-      <c r="E105" s="10" t="n"/>
-      <c r="F105" s="10" t="n"/>
-      <c r="G105" s="10" t="n"/>
-      <c r="H105" s="10" t="n"/>
-      <c r="I105" s="10" t="n"/>
-      <c r="J105" s="10" t="n"/>
-      <c r="K105" s="10" t="n"/>
-      <c r="L105" s="10" t="n"/>
-      <c r="M105" s="10" t="n"/>
-      <c r="N105" s="10" t="n"/>
-      <c r="O105" s="10" t="n"/>
-      <c r="P105" s="10" t="n"/>
-      <c r="Q105" s="10" t="n"/>
-      <c r="R105" s="10" t="n"/>
-      <c r="S105" s="10" t="n"/>
-      <c r="T105" s="10" t="n"/>
-      <c r="U105" s="10" t="n"/>
-      <c r="V105" s="10" t="n"/>
-      <c r="W105" s="10" t="n"/>
-      <c r="X105" s="10" t="n"/>
-      <c r="Y105" s="10" t="n"/>
-      <c r="Z105" s="10" t="n"/>
-      <c r="AA105" s="10" t="n"/>
-      <c r="AB105" s="10" t="n"/>
-      <c r="AC105" s="10" t="n"/>
-      <c r="AD105" s="10" t="n"/>
-      <c r="AE105" s="10" t="n"/>
-      <c r="AF105" s="10" t="n"/>
-      <c r="AG105" s="10" t="n"/>
-      <c r="AH105" s="10" t="n"/>
-      <c r="AI105" s="10" t="n"/>
-      <c r="AJ105" s="10" t="n"/>
-      <c r="AK105" s="11" t="n"/>
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="10" t="n"/>
+      <c r="J102" s="10" t="n"/>
+      <c r="K102" s="10" t="n"/>
+      <c r="L102" s="10" t="n"/>
+      <c r="M102" s="10" t="n"/>
+      <c r="N102" s="10" t="n"/>
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="10" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
+      <c r="V102" s="10" t="n"/>
+      <c r="W102" s="10" t="n"/>
+      <c r="X102" s="10" t="n"/>
+      <c r="Y102" s="10" t="n"/>
+      <c r="Z102" s="10" t="n"/>
+      <c r="AA102" s="10" t="n"/>
+      <c r="AB102" s="10" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="10" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="10" t="n"/>
+      <c r="AK102" s="11" t="n"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="C104" s="41" t="inlineStr">
+        <is>
+          <t>取得結果を data 配列として返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="C105" s="41" t="inlineStr">
+        <is>
+          <t>ページネーション情報を meta オブジェクトとして返却する。</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="B106" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
+      <c r="D106" s="41" t="inlineStr">
+        <is>
+          <t>total：4.4 で取得した総件数</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="C107" s="41" t="inlineStr">
-        <is>
-          <t>取得結果を data 配列として返却する。</t>
+      <c r="D107" s="41" t="inlineStr">
+        <is>
+          <t>page：リクエストの page</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="C108" s="41" t="inlineStr">
-        <is>
-          <t>ページネーション情報を meta オブジェクトとして返却する。</t>
+      <c r="D108" s="41" t="inlineStr">
+        <is>
+          <t>per_page：リクエストの per_page</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
       <c r="D109" s="41" t="inlineStr">
         <is>
-          <t>total：4.4 で取得した総件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="18" customHeight="1">
-      <c r="D110" s="41" t="inlineStr">
-        <is>
-          <t>page：リクエストの page</t>
+          <t>total_pages：CEIL(total / per_page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="36" customHeight="1">
+      <c r="C110" s="41" t="inlineStr">
+        <is>
+          <t>検索結果が0件の場合：data は空配列 `[]`、meta.total = 0 で返却（HTTP 200）。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="D111" s="41" t="inlineStr">
-        <is>
-          <t>per_page：リクエストの per_page</t>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
-      <c r="D112" s="41" t="inlineStr">
-        <is>
-          <t>total_pages：CEIL(total / per_page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="36" customHeight="1">
-      <c r="C113" s="41" t="inlineStr">
-        <is>
-          <t>検索結果が0件の場合：data は空配列 `[]`、meta.total = 0 で返却（HTTP 200）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="18" customHeight="1">
-      <c r="B114" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="C115" s="41" t="inlineStr">
+      <c r="C112" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="297">
-    <mergeCell ref="B102:AK102"/>
+  <mergeCells count="288">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="D78:AK78"/>
+    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="T24:X24"/>
+    <mergeCell ref="B62:I62"/>
+    <mergeCell ref="C66:AK66"/>
     <mergeCell ref="Y45:AE45"/>
+    <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="C102:AK102"/>
     <mergeCell ref="D48:L48"/>
     <mergeCell ref="M29:P29"/>
+    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="AF21:AK21"/>
     <mergeCell ref="T53:X53"/>
-    <mergeCell ref="C108:AK108"/>
+    <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="M46:P46"/>
-    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="D82:AK82"/>
     <mergeCell ref="M43:P43"/>
+    <mergeCell ref="B73:AK73"/>
     <mergeCell ref="Y52:AE52"/>
     <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="C34:L34"/>
     <mergeCell ref="AF50:AK50"/>
-    <mergeCell ref="T55:X55"/>
-    <mergeCell ref="C113:AK113"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="C100:AK100"/>
+    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
+    <mergeCell ref="D51:L51"/>
     <mergeCell ref="AF52:AK52"/>
-    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C51:C54"/>
+    <mergeCell ref="D106:AK106"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="Y21:AB21"/>
     <mergeCell ref="AF22:AK22"/>
     <mergeCell ref="M35:P35"/>
-    <mergeCell ref="D99:AK99"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="D35:L35"/>
     <mergeCell ref="M54:P54"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
-    <mergeCell ref="B114:AK114"/>
+    <mergeCell ref="B65:I65"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="B68:I68"/>
     <mergeCell ref="C22:L22"/>
+    <mergeCell ref="Q33:S33"/>
     <mergeCell ref="D77:AK77"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
@@ -8578,37 +8502,39 @@
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="AF49:AK49"/>
-    <mergeCell ref="C70:AK70"/>
+    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
     <mergeCell ref="D36:L36"/>
+    <mergeCell ref="D75:AK75"/>
+    <mergeCell ref="M33:P33"/>
     <mergeCell ref="M45:P45"/>
-    <mergeCell ref="T30:X30"/>
-    <mergeCell ref="B93:AK93"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="D112:AK112"/>
     <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="A32:AK32"/>
+    <mergeCell ref="B59:I59"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="M47:P47"/>
-    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="D53:L53"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="AC29:AE29"/>
+    <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="B101:AK101"/>
     <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="C104:AK104"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="D37:L37"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="T54:X54"/>
+    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="C88:AK88"/>
     <mergeCell ref="Y53:AE53"/>
-    <mergeCell ref="D98:AK98"/>
+    <mergeCell ref="D89:AK89"/>
+    <mergeCell ref="B103:AK103"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="AF41:AK41"/>
@@ -8616,41 +8542,36 @@
     <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="D39:L39"/>
     <mergeCell ref="AD2:AG3"/>
+    <mergeCell ref="C33:L33"/>
     <mergeCell ref="M44:P44"/>
+    <mergeCell ref="AC21:AE21"/>
     <mergeCell ref="Q48:S48"/>
-    <mergeCell ref="AC21:AE21"/>
+    <mergeCell ref="B13:I13"/>
     <mergeCell ref="D79:AK79"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C103:AK103"/>
-    <mergeCell ref="C51:L51"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="Y55:AE55"/>
     <mergeCell ref="D38:L38"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="D81:AK81"/>
     <mergeCell ref="Y39:AE39"/>
-    <mergeCell ref="C35:L35"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="B104:AK104"/>
+    <mergeCell ref="C50:L50"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
-    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="B106:AK106"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M21:P21"/>
-    <mergeCell ref="C61:AK61"/>
     <mergeCell ref="D76:AK76"/>
+    <mergeCell ref="D107:AK107"/>
     <mergeCell ref="T46:X46"/>
-    <mergeCell ref="B63:I63"/>
     <mergeCell ref="AF53:AK53"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="M27:P27"/>
@@ -8666,20 +8587,21 @@
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="Q35:S35"/>
     <mergeCell ref="Q50:S50"/>
-    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="Q34:S34"/>
     <mergeCell ref="T42:X42"/>
+    <mergeCell ref="AF45:AK45"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="D78:AK78"/>
     <mergeCell ref="Y41:AE41"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
     <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="M50:P50"/>
-    <mergeCell ref="C107:AK107"/>
+    <mergeCell ref="A72:AK72"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
@@ -8688,26 +8610,20 @@
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="T44:X44"/>
-    <mergeCell ref="C64:AK64"/>
-    <mergeCell ref="C30:L30"/>
-    <mergeCell ref="Q30:S30"/>
     <mergeCell ref="M34:P34"/>
     <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="D94:AK94"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="M55:P55"/>
-    <mergeCell ref="D55:L55"/>
+    <mergeCell ref="A31:AK31"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="M49:P49"/>
+    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="T21:X21"/>
     <mergeCell ref="M39:P39"/>
-    <mergeCell ref="C52:C55"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
-    <mergeCell ref="B69:I69"/>
     <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="Y30:AB30"/>
-    <mergeCell ref="A73:AK73"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
@@ -8723,7 +8639,6 @@
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="Q21:S21"/>
     <mergeCell ref="D96:AK96"/>
-    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="D46:L46"/>
@@ -8735,14 +8650,10 @@
     <mergeCell ref="T27:X27"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="T36:X36"/>
-    <mergeCell ref="Q55:S55"/>
     <mergeCell ref="B14:I17"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="C67:AK67"/>
-    <mergeCell ref="D97:AK97"/>
     <mergeCell ref="Y46:AE46"/>
-    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
@@ -8753,33 +8664,33 @@
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="Y48:AE48"/>
+    <mergeCell ref="C83:AK83"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="T35:X35"/>
     <mergeCell ref="C92:AK92"/>
+    <mergeCell ref="D93:AK93"/>
+    <mergeCell ref="B111:AK111"/>
     <mergeCell ref="Y23:AB23"/>
+    <mergeCell ref="C35:C49"/>
     <mergeCell ref="D43:L43"/>
-    <mergeCell ref="D83:AK83"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="A19:AK19"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="B60:I60"/>
     <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="D110:AK110"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="C36:C50"/>
+    <mergeCell ref="B99:AK99"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="B74:AK74"/>
     <mergeCell ref="D109:AK109"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
-    <mergeCell ref="D50:L50"/>
     <mergeCell ref="D84:AK84"/>
     <mergeCell ref="D44:L44"/>
     <mergeCell ref="Q53:S53"/>
@@ -8787,17 +8698,18 @@
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
-    <mergeCell ref="D111:AK111"/>
     <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="C60:AK60"/>
+    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="AF48:AK48"/>
-    <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="D108:AK108"/>
     <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
     <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="D95:AK95"/>
     <mergeCell ref="AC28:AE28"/>
-    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="C110:AK110"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="C21:L21"/>
@@ -8807,7 +8719,6 @@
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="AF29:AK29"/>
-    <mergeCell ref="AC30:AE30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8819,7 +8730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK84"/>
+  <dimension ref="A1:AK85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -8980,7 +8891,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -9334,7 +9245,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -9386,7 +9297,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>削除しました</t>
+          <t>正常にアカウントを削除しました</t>
         </is>
       </c>
       <c r="O14" s="10" t="n"/>
@@ -9538,7 +9449,7 @@
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>関連データが存在するため削除できません。</t>
+          <t>このレコードは現在使用中のため、削除できません。</t>
         </is>
       </c>
       <c r="O18" s="10" t="n"/>
@@ -9943,7 +9854,7 @@
       <c r="C35" s="19" t="inlineStr">
         <is>
           <t>{
-  "message": "削除しました。"
+  "message": "正常に削除しました"
 }</t>
         </is>
       </c>
@@ -10147,7 +10058,7 @@
         <is>
           <t>{
   "error_code": "CONFLICT",
-  "message": "関連データが存在するため削除できません。"
+  "message": "このレコードは現在使用中のため、削除できません。"
 }</t>
         </is>
       </c>
@@ -10245,96 +10156,59 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="54" customHeight="1">
-      <c r="B54" s="42" t="inlineStr">
-        <is>
-          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
-いずれかが失敗した場合は全てロールバックすること。
-例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="n"/>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="10" t="n"/>
-      <c r="F54" s="10" t="n"/>
-      <c r="G54" s="10" t="n"/>
-      <c r="H54" s="10" t="n"/>
-      <c r="I54" s="10" t="n"/>
-      <c r="J54" s="10" t="n"/>
-      <c r="K54" s="10" t="n"/>
-      <c r="L54" s="10" t="n"/>
-      <c r="M54" s="10" t="n"/>
-      <c r="N54" s="10" t="n"/>
-      <c r="O54" s="10" t="n"/>
-      <c r="P54" s="10" t="n"/>
-      <c r="Q54" s="10" t="n"/>
-      <c r="R54" s="10" t="n"/>
-      <c r="S54" s="10" t="n"/>
-      <c r="T54" s="10" t="n"/>
-      <c r="U54" s="10" t="n"/>
-      <c r="V54" s="10" t="n"/>
-      <c r="W54" s="10" t="n"/>
-      <c r="X54" s="10" t="n"/>
-      <c r="Y54" s="10" t="n"/>
-      <c r="Z54" s="10" t="n"/>
-      <c r="AA54" s="10" t="n"/>
-      <c r="AB54" s="10" t="n"/>
-      <c r="AC54" s="10" t="n"/>
-      <c r="AD54" s="10" t="n"/>
-      <c r="AE54" s="10" t="n"/>
-      <c r="AF54" s="10" t="n"/>
-      <c r="AG54" s="10" t="n"/>
-      <c r="AH54" s="10" t="n"/>
-      <c r="AI54" s="10" t="n"/>
-      <c r="AJ54" s="10" t="n"/>
-      <c r="AK54" s="11" t="n"/>
+    <row r="54" ht="18" customHeight="1">
+      <c r="B54" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="18" customHeight="1">
-      <c r="B55" s="27" t="inlineStr">
-        <is>
-          <t>4.1 リクエストのバリデーション</t>
+      <c r="C55" s="41" t="inlineStr">
+        <is>
+          <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
-      <c r="C56" s="41" t="inlineStr">
-        <is>
-          <t>パスパラメータの検証：</t>
+      <c r="D56" s="41" t="inlineStr">
+        <is>
+          <t>account_id：数値型チェック、必須チェック</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="D57" s="41" t="inlineStr">
-        <is>
-          <t>account_id：数値型チェック、必須チェック</t>
+      <c r="C57" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
-      <c r="C58" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
+      <c r="D58" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="D59" s="41" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request を返却する。</t>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="B60" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="C60" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="C61" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
@@ -10360,21 +10234,28 @@
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="B65" s="27" t="inlineStr">
+      <c r="C65" s="41" t="inlineStr">
+        <is>
+          <t>自分自身のアカウントは削除不可とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="B66" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得条件の設定（存在確認・関連データチェック）</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="C66" s="41" t="inlineStr">
+    <row r="67" ht="18" customHeight="1">
+      <c r="C67" s="41" t="inlineStr">
         <is>
           <t>対象アカウントの存在を確認する。</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="126" customHeight="1">
-      <c r="C67" s="42" t="inlineStr">
+    <row r="68" ht="126" customHeight="1">
+      <c r="C68" s="42" t="inlineStr">
         <is>
           <t>SELECT a.account_id, a.login_id, a.account_name, a.role_id,
        a.ja_id, a.kanri_shiten_id, a.todofuken_code,
@@ -10385,57 +10266,57 @@
   AND a.deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D67" s="10" t="n"/>
-      <c r="E67" s="10" t="n"/>
-      <c r="F67" s="10" t="n"/>
-      <c r="G67" s="10" t="n"/>
-      <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="n"/>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
-      <c r="L67" s="10" t="n"/>
-      <c r="M67" s="10" t="n"/>
-      <c r="N67" s="10" t="n"/>
-      <c r="O67" s="10" t="n"/>
-      <c r="P67" s="10" t="n"/>
-      <c r="Q67" s="10" t="n"/>
-      <c r="R67" s="10" t="n"/>
-      <c r="S67" s="10" t="n"/>
-      <c r="T67" s="10" t="n"/>
-      <c r="U67" s="10" t="n"/>
-      <c r="V67" s="10" t="n"/>
-      <c r="W67" s="10" t="n"/>
-      <c r="X67" s="10" t="n"/>
-      <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="10" t="n"/>
-      <c r="AA67" s="10" t="n"/>
-      <c r="AB67" s="10" t="n"/>
-      <c r="AC67" s="10" t="n"/>
-      <c r="AD67" s="10" t="n"/>
-      <c r="AE67" s="10" t="n"/>
-      <c r="AF67" s="10" t="n"/>
-      <c r="AG67" s="10" t="n"/>
-      <c r="AH67" s="10" t="n"/>
-      <c r="AI67" s="10" t="n"/>
-      <c r="AJ67" s="10" t="n"/>
-      <c r="AK67" s="11" t="n"/>
-    </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="C68" s="41" t="inlineStr">
-        <is>
-          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
-        </is>
-      </c>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="10" t="n"/>
+      <c r="J68" s="10" t="n"/>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="10" t="n"/>
+      <c r="Q68" s="10" t="n"/>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
+      <c r="U68" s="10" t="n"/>
+      <c r="V68" s="10" t="n"/>
+      <c r="W68" s="10" t="n"/>
+      <c r="X68" s="10" t="n"/>
+      <c r="Y68" s="10" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
+      <c r="AB68" s="10" t="n"/>
+      <c r="AC68" s="10" t="n"/>
+      <c r="AD68" s="10" t="n"/>
+      <c r="AE68" s="10" t="n"/>
+      <c r="AF68" s="10" t="n"/>
+      <c r="AG68" s="10" t="n"/>
+      <c r="AH68" s="10" t="n"/>
+      <c r="AI68" s="10" t="n"/>
+      <c r="AJ68" s="10" t="n"/>
+      <c r="AK68" s="11" t="n"/>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="C69" s="41" t="inlineStr">
         <is>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="C70" s="41" t="inlineStr">
+        <is>
           <t>関連テーブルに紐づくデータが存在するか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="72" customHeight="1">
-      <c r="C70" s="42" t="inlineStr">
+    <row r="71" ht="72" customHeight="1">
+      <c r="C71" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS related_count
 FROM (
@@ -10443,57 +10324,57 @@
 ) AS related_data</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="10" t="n"/>
-      <c r="M70" s="10" t="n"/>
-      <c r="N70" s="10" t="n"/>
-      <c r="O70" s="10" t="n"/>
-      <c r="P70" s="10" t="n"/>
-      <c r="Q70" s="10" t="n"/>
-      <c r="R70" s="10" t="n"/>
-      <c r="S70" s="10" t="n"/>
-      <c r="T70" s="10" t="n"/>
-      <c r="U70" s="10" t="n"/>
-      <c r="V70" s="10" t="n"/>
-      <c r="W70" s="10" t="n"/>
-      <c r="X70" s="10" t="n"/>
-      <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
-      <c r="AA70" s="10" t="n"/>
-      <c r="AB70" s="10" t="n"/>
-      <c r="AC70" s="10" t="n"/>
-      <c r="AD70" s="10" t="n"/>
-      <c r="AE70" s="10" t="n"/>
-      <c r="AF70" s="10" t="n"/>
-      <c r="AG70" s="10" t="n"/>
-      <c r="AH70" s="10" t="n"/>
-      <c r="AI70" s="10" t="n"/>
-      <c r="AJ70" s="10" t="n"/>
-      <c r="AK70" s="11" t="n"/>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="C71" s="41" t="inlineStr">
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="10" t="n"/>
+      <c r="J71" s="10" t="n"/>
+      <c r="K71" s="10" t="n"/>
+      <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="10" t="n"/>
+      <c r="Q71" s="10" t="n"/>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
+      <c r="U71" s="10" t="n"/>
+      <c r="V71" s="10" t="n"/>
+      <c r="W71" s="10" t="n"/>
+      <c r="X71" s="10" t="n"/>
+      <c r="Y71" s="10" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
+      <c r="AB71" s="10" t="n"/>
+      <c r="AC71" s="10" t="n"/>
+      <c r="AD71" s="10" t="n"/>
+      <c r="AE71" s="10" t="n"/>
+      <c r="AF71" s="10" t="n"/>
+      <c r="AG71" s="10" t="n"/>
+      <c r="AH71" s="10" t="n"/>
+      <c r="AI71" s="10" t="n"/>
+      <c r="AJ71" s="10" t="n"/>
+      <c r="AK71" s="11" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="C72" s="41" t="inlineStr">
         <is>
           <t>関連データが存在する場合：HTTP 409 (`CONFLICT`)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="B72" s="27" t="inlineStr">
+    <row r="73" ht="18" customHeight="1">
+      <c r="B73" s="27" t="inlineStr">
         <is>
           <t>4.4 論理削除の実行</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="108" customHeight="1">
-      <c r="C73" s="42" t="inlineStr">
+    <row r="74" ht="108" customHeight="1">
+      <c r="C74" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_account
 SET deleted_at = NOW(),
@@ -10503,57 +10384,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D73" s="10" t="n"/>
-      <c r="E73" s="10" t="n"/>
-      <c r="F73" s="10" t="n"/>
-      <c r="G73" s="10" t="n"/>
-      <c r="H73" s="10" t="n"/>
-      <c r="I73" s="10" t="n"/>
-      <c r="J73" s="10" t="n"/>
-      <c r="K73" s="10" t="n"/>
-      <c r="L73" s="10" t="n"/>
-      <c r="M73" s="10" t="n"/>
-      <c r="N73" s="10" t="n"/>
-      <c r="O73" s="10" t="n"/>
-      <c r="P73" s="10" t="n"/>
-      <c r="Q73" s="10" t="n"/>
-      <c r="R73" s="10" t="n"/>
-      <c r="S73" s="10" t="n"/>
-      <c r="T73" s="10" t="n"/>
-      <c r="U73" s="10" t="n"/>
-      <c r="V73" s="10" t="n"/>
-      <c r="W73" s="10" t="n"/>
-      <c r="X73" s="10" t="n"/>
-      <c r="Y73" s="10" t="n"/>
-      <c r="Z73" s="10" t="n"/>
-      <c r="AA73" s="10" t="n"/>
-      <c r="AB73" s="10" t="n"/>
-      <c r="AC73" s="10" t="n"/>
-      <c r="AD73" s="10" t="n"/>
-      <c r="AE73" s="10" t="n"/>
-      <c r="AF73" s="10" t="n"/>
-      <c r="AG73" s="10" t="n"/>
-      <c r="AH73" s="10" t="n"/>
-      <c r="AI73" s="10" t="n"/>
-      <c r="AJ73" s="10" t="n"/>
-      <c r="AK73" s="11" t="n"/>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="B74" s="27" t="inlineStr">
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="10" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="10" t="n"/>
+      <c r="J74" s="10" t="n"/>
+      <c r="K74" s="10" t="n"/>
+      <c r="L74" s="10" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="10" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="10" t="n"/>
+      <c r="Q74" s="10" t="n"/>
+      <c r="R74" s="10" t="n"/>
+      <c r="S74" s="10" t="n"/>
+      <c r="T74" s="10" t="n"/>
+      <c r="U74" s="10" t="n"/>
+      <c r="V74" s="10" t="n"/>
+      <c r="W74" s="10" t="n"/>
+      <c r="X74" s="10" t="n"/>
+      <c r="Y74" s="10" t="n"/>
+      <c r="Z74" s="10" t="n"/>
+      <c r="AA74" s="10" t="n"/>
+      <c r="AB74" s="10" t="n"/>
+      <c r="AC74" s="10" t="n"/>
+      <c r="AD74" s="10" t="n"/>
+      <c r="AE74" s="10" t="n"/>
+      <c r="AF74" s="10" t="n"/>
+      <c r="AG74" s="10" t="n"/>
+      <c r="AH74" s="10" t="n"/>
+      <c r="AI74" s="10" t="n"/>
+      <c r="AJ74" s="10" t="n"/>
+      <c r="AK74" s="11" t="n"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="B75" s="27" t="inlineStr">
         <is>
           <t>4.5 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="C75" s="41" t="inlineStr">
+    <row r="76" ht="18" customHeight="1">
+      <c r="C76" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="216" customHeight="1">
-      <c r="C76" s="42" t="inlineStr">
+    <row r="77" ht="216" customHeight="1">
+      <c r="C77" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -10567,63 +10448,6 @@
         :before_value_json, '',
         '', '',
         :ip_address, :user_agent)</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="n"/>
-      <c r="E76" s="10" t="n"/>
-      <c r="F76" s="10" t="n"/>
-      <c r="G76" s="10" t="n"/>
-      <c r="H76" s="10" t="n"/>
-      <c r="I76" s="10" t="n"/>
-      <c r="J76" s="10" t="n"/>
-      <c r="K76" s="10" t="n"/>
-      <c r="L76" s="10" t="n"/>
-      <c r="M76" s="10" t="n"/>
-      <c r="N76" s="10" t="n"/>
-      <c r="O76" s="10" t="n"/>
-      <c r="P76" s="10" t="n"/>
-      <c r="Q76" s="10" t="n"/>
-      <c r="R76" s="10" t="n"/>
-      <c r="S76" s="10" t="n"/>
-      <c r="T76" s="10" t="n"/>
-      <c r="U76" s="10" t="n"/>
-      <c r="V76" s="10" t="n"/>
-      <c r="W76" s="10" t="n"/>
-      <c r="X76" s="10" t="n"/>
-      <c r="Y76" s="10" t="n"/>
-      <c r="Z76" s="10" t="n"/>
-      <c r="AA76" s="10" t="n"/>
-      <c r="AB76" s="10" t="n"/>
-      <c r="AC76" s="10" t="n"/>
-      <c r="AD76" s="10" t="n"/>
-      <c r="AE76" s="10" t="n"/>
-      <c r="AF76" s="10" t="n"/>
-      <c r="AG76" s="10" t="n"/>
-      <c r="AH76" s="10" t="n"/>
-      <c r="AI76" s="10" t="n"/>
-      <c r="AJ76" s="10" t="n"/>
-      <c r="AK76" s="11" t="n"/>
-    </row>
-    <row r="77" ht="306" customHeight="1">
-      <c r="C77" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-`after_value`：DELETE のため空文字列を設定する。
-{
-  "account_id": 5,
-  "login_id": "ja_shiten001",
-  "account_name": "JA管理支店 次郎",
-  "role_id": 5,
-  "ja_id": 10,
-  "kanri_shiten_id": 20,
-  "todofuken_code": "13",
-  "paper_flg": true,
-  "denshi_flg": false,
-  "email": "shiten001@example.com",
-  "sub_email_1": "",
-  "sub_email_2": "",
-  "sub_email_3": ""
-}</t>
         </is>
       </c>
       <c r="D77" s="10" t="n"/>
@@ -10661,86 +10485,140 @@
       <c r="AJ77" s="10" t="n"/>
       <c r="AK77" s="11" t="n"/>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="B78" s="27" t="inlineStr">
+    <row r="78" ht="252" customHeight="1">
+      <c r="C78" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+`after_value`：DELETE のため空文字列を設定する。
+{
+  "account_id": 5,
+  "login_id": "ja_shiten001",
+  "account_name": "JA管理支店 次郎",
+  "role_id": 5,
+  "ja_id": 10,
+  "kanri_shiten_id": 20,
+  "todofuken_code": "13",
+  "paper_flg": true,
+  "denshi_flg": false,
+  "email": "shiten001@example.com"
+}</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="10" t="n"/>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="10" t="n"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="10" t="n"/>
+      <c r="Y78" s="10" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="10" t="n"/>
+      <c r="AE78" s="10" t="n"/>
+      <c r="AF78" s="10" t="n"/>
+      <c r="AG78" s="10" t="n"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="10" t="n"/>
+      <c r="AJ78" s="10" t="n"/>
+      <c r="AK78" s="11" t="n"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
         <is>
           <t>削除成功メッセージを返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="54" customHeight="1">
-      <c r="C80" s="42" t="inlineStr">
+    <row r="81" ht="54" customHeight="1">
+      <c r="C81" s="42" t="inlineStr">
         <is>
           <t>{
-  "message": "削除しました。"
+  "message": "正常に削除しました"
 }</t>
         </is>
       </c>
-      <c r="D80" s="10" t="n"/>
-      <c r="E80" s="10" t="n"/>
-      <c r="F80" s="10" t="n"/>
-      <c r="G80" s="10" t="n"/>
-      <c r="H80" s="10" t="n"/>
-      <c r="I80" s="10" t="n"/>
-      <c r="J80" s="10" t="n"/>
-      <c r="K80" s="10" t="n"/>
-      <c r="L80" s="10" t="n"/>
-      <c r="M80" s="10" t="n"/>
-      <c r="N80" s="10" t="n"/>
-      <c r="O80" s="10" t="n"/>
-      <c r="P80" s="10" t="n"/>
-      <c r="Q80" s="10" t="n"/>
-      <c r="R80" s="10" t="n"/>
-      <c r="S80" s="10" t="n"/>
-      <c r="T80" s="10" t="n"/>
-      <c r="U80" s="10" t="n"/>
-      <c r="V80" s="10" t="n"/>
-      <c r="W80" s="10" t="n"/>
-      <c r="X80" s="10" t="n"/>
-      <c r="Y80" s="10" t="n"/>
-      <c r="Z80" s="10" t="n"/>
-      <c r="AA80" s="10" t="n"/>
-      <c r="AB80" s="10" t="n"/>
-      <c r="AC80" s="10" t="n"/>
-      <c r="AD80" s="10" t="n"/>
-      <c r="AE80" s="10" t="n"/>
-      <c r="AF80" s="10" t="n"/>
-      <c r="AG80" s="10" t="n"/>
-      <c r="AH80" s="10" t="n"/>
-      <c r="AI80" s="10" t="n"/>
-      <c r="AJ80" s="10" t="n"/>
-      <c r="AK80" s="11" t="n"/>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
+      <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="11" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="B82" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="C83" s="41" t="inlineStr">
         <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="C84" s="41" t="inlineStr">
+        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="216" customHeight="1">
-      <c r="C84" s="42" t="inlineStr">
+    <row r="85" ht="216" customHeight="1">
+      <c r="C85" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -10756,49 +10634,49 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D84" s="10" t="n"/>
-      <c r="E84" s="10" t="n"/>
-      <c r="F84" s="10" t="n"/>
-      <c r="G84" s="10" t="n"/>
-      <c r="H84" s="10" t="n"/>
-      <c r="I84" s="10" t="n"/>
-      <c r="J84" s="10" t="n"/>
-      <c r="K84" s="10" t="n"/>
-      <c r="L84" s="10" t="n"/>
-      <c r="M84" s="10" t="n"/>
-      <c r="N84" s="10" t="n"/>
-      <c r="O84" s="10" t="n"/>
-      <c r="P84" s="10" t="n"/>
-      <c r="Q84" s="10" t="n"/>
-      <c r="R84" s="10" t="n"/>
-      <c r="S84" s="10" t="n"/>
-      <c r="T84" s="10" t="n"/>
-      <c r="U84" s="10" t="n"/>
-      <c r="V84" s="10" t="n"/>
-      <c r="W84" s="10" t="n"/>
-      <c r="X84" s="10" t="n"/>
-      <c r="Y84" s="10" t="n"/>
-      <c r="Z84" s="10" t="n"/>
-      <c r="AA84" s="10" t="n"/>
-      <c r="AB84" s="10" t="n"/>
-      <c r="AC84" s="10" t="n"/>
-      <c r="AD84" s="10" t="n"/>
-      <c r="AE84" s="10" t="n"/>
-      <c r="AF84" s="10" t="n"/>
-      <c r="AG84" s="10" t="n"/>
-      <c r="AH84" s="10" t="n"/>
-      <c r="AI84" s="10" t="n"/>
-      <c r="AJ84" s="10" t="n"/>
-      <c r="AK84" s="11" t="n"/>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="10" t="n"/>
+      <c r="J85" s="10" t="n"/>
+      <c r="K85" s="10" t="n"/>
+      <c r="L85" s="10" t="n"/>
+      <c r="M85" s="10" t="n"/>
+      <c r="N85" s="10" t="n"/>
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="10" t="n"/>
+      <c r="S85" s="10" t="n"/>
+      <c r="T85" s="10" t="n"/>
+      <c r="U85" s="10" t="n"/>
+      <c r="V85" s="10" t="n"/>
+      <c r="W85" s="10" t="n"/>
+      <c r="X85" s="10" t="n"/>
+      <c r="Y85" s="10" t="n"/>
+      <c r="Z85" s="10" t="n"/>
+      <c r="AA85" s="10" t="n"/>
+      <c r="AB85" s="10" t="n"/>
+      <c r="AC85" s="10" t="n"/>
+      <c r="AD85" s="10" t="n"/>
+      <c r="AE85" s="10" t="n"/>
+      <c r="AF85" s="10" t="n"/>
+      <c r="AG85" s="10" t="n"/>
+      <c r="AH85" s="10" t="n"/>
+      <c r="AI85" s="10" t="n"/>
+      <c r="AJ85" s="10" t="n"/>
+      <c r="AK85" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="116">
+  <mergeCells count="117">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="A26:AK26"/>
+    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="C66:AK66"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="C77:AK77"/>
@@ -10806,23 +10684,24 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
+    <mergeCell ref="D58:AK58"/>
     <mergeCell ref="C68:AK68"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="A53:AK53"/>
     <mergeCell ref="N17:AK17"/>
-    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="J17:M17"/>
+    <mergeCell ref="B73:AK73"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="C65:AK65"/>
     <mergeCell ref="C44:AK44"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="B65:AK65"/>
-    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C80:AK80"/>
@@ -10830,6 +10709,7 @@
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T28:X28"/>
+    <mergeCell ref="B66:AK66"/>
     <mergeCell ref="C38:AK38"/>
     <mergeCell ref="A21:AK21"/>
     <mergeCell ref="T29:X29"/>
@@ -10837,54 +10717,51 @@
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="D56:AK56"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
-    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
+    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="D63:AK63"/>
-    <mergeCell ref="B55:AK55"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="B49:I49"/>
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="Y28:AE28"/>
+    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="C32:AK32"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="J7:AK7"/>
+    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="B60:AK60"/>
     <mergeCell ref="C62:AK62"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C64:AK64"/>
-    <mergeCell ref="C79:AK79"/>
-    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C41:AK41"/>
     <mergeCell ref="C50:AK50"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="D57:AK57"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="B54:AK54"/>
-    <mergeCell ref="B72:AK72"/>
     <mergeCell ref="C67:AK67"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
@@ -10894,20 +10771,22 @@
     <mergeCell ref="C83:AK83"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="D59:AK59"/>
     <mergeCell ref="C47:AK47"/>
-    <mergeCell ref="B74:AK74"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="C76:AK76"/>
+    <mergeCell ref="B75:AK75"/>
     <mergeCell ref="M28:P28"/>
+    <mergeCell ref="B59:AK59"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11081,7 +10960,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -11435,7 +11314,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -12318,7 +12197,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
@@ -12545,7 +12424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK89"/>
+  <dimension ref="A1:AK73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -12706,7 +12585,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -12815,7 +12694,7 @@
       <c r="AJ7" s="10" t="n"/>
       <c r="AK7" s="11" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="18" customHeight="1">
       <c r="B8" s="33" t="inlineStr">
         <is>
           <t>概要</t>
@@ -12830,7 +12709,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>JAプルダウンリストを取得する（共用API）。2つのユースケースを1つのエンドポイントで提供：（A）ページング+フリーテキスト検索（SCR-009 等のフォーム用）、（B）都道府県・管理者区分によるカスケード絞込み（SCR-024 アカウント検索／SCR-025 登録用）。両方のレスポンス形状は同一（`{data, meta}`）。</t>
+          <t>JAプルダウンリストを取得する（都道府県・管理者区分によるカスケード絞込み。共用API：アカウント検索・登録等で使用）</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -13060,7 +12939,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -13143,14 +13022,14 @@
       <c r="B15" s="35" t="n"/>
       <c r="I15" s="36" t="n"/>
       <c r="J15" s="17" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="n"/>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>リクエストパラメータが不正です</t>
+          <t>セッションが切れました。再度ログインしてください</t>
         </is>
       </c>
       <c r="O15" s="10" t="n"/>
@@ -13181,14 +13060,14 @@
       <c r="B16" s="35" t="n"/>
       <c r="I16" s="36" t="n"/>
       <c r="J16" s="17" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K16" s="10" t="n"/>
       <c r="L16" s="10" t="n"/>
       <c r="M16" s="11" t="n"/>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>セッションが切れました。再度ログインしてください</t>
+          <t>この画面へのアクセス権限がありません</t>
         </is>
       </c>
       <c r="O16" s="10" t="n"/>
@@ -13216,17 +13095,23 @@
       <c r="AK16" s="11" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="35" t="n"/>
-      <c r="I17" s="36" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="26" t="n"/>
       <c r="J17" s="17" t="n">
-        <v>403</v>
+        <v>500</v>
       </c>
       <c r="K17" s="10" t="n"/>
       <c r="L17" s="10" t="n"/>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>この画面へのアクセス権限がありません</t>
+          <t>システムエラーが発生しました</t>
         </is>
       </c>
       <c r="O17" s="10" t="n"/>
@@ -13253,68 +13138,92 @@
       <c r="AJ17" s="10" t="n"/>
       <c r="AK17" s="11" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="24" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="n"/>
-      <c r="G18" s="25" t="n"/>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="26" t="n"/>
-      <c r="J18" s="17" t="n">
-        <v>500</v>
-      </c>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="10" t="n"/>
-      <c r="M18" s="11" t="n"/>
-      <c r="N18" s="19" t="inlineStr">
-        <is>
-          <t>システムエラーが発生しました</t>
-        </is>
-      </c>
-      <c r="O18" s="10" t="n"/>
-      <c r="P18" s="10" t="n"/>
-      <c r="Q18" s="10" t="n"/>
-      <c r="R18" s="10" t="n"/>
-      <c r="S18" s="10" t="n"/>
-      <c r="T18" s="10" t="n"/>
-      <c r="U18" s="10" t="n"/>
-      <c r="V18" s="10" t="n"/>
-      <c r="W18" s="10" t="n"/>
-      <c r="X18" s="10" t="n"/>
-      <c r="Y18" s="10" t="n"/>
-      <c r="Z18" s="10" t="n"/>
-      <c r="AA18" s="10" t="n"/>
-      <c r="AB18" s="10" t="n"/>
-      <c r="AC18" s="10" t="n"/>
-      <c r="AD18" s="10" t="n"/>
-      <c r="AE18" s="10" t="n"/>
-      <c r="AF18" s="10" t="n"/>
-      <c r="AG18" s="10" t="n"/>
-      <c r="AH18" s="10" t="n"/>
-      <c r="AI18" s="10" t="n"/>
-      <c r="AJ18" s="10" t="n"/>
-      <c r="AK18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="19.5" customHeight="1"/>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="27" t="inlineStr">
+    <row r="18" ht="19.5" customHeight="1"/>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>2. リクエストパラメータ</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19.5" customHeight="1"/>
-    <row r="22" ht="19.5" customHeight="1">
-      <c r="B22" s="30" t="inlineStr">
+    <row r="20" ht="19.5" customHeight="1"/>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="16" t="inlineStr">
         <is>
           <t>パラメーターID</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="n"/>
+      <c r="O21" s="10" t="n"/>
+      <c r="P21" s="11" t="n"/>
+      <c r="Q21" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="11" t="n"/>
+      <c r="T21" s="16" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="10" t="n"/>
+      <c r="W21" s="10" t="n"/>
+      <c r="X21" s="11" t="n"/>
+      <c r="Y21" s="16" t="inlineStr">
+        <is>
+          <t>最小長</t>
+        </is>
+      </c>
+      <c r="Z21" s="10" t="n"/>
+      <c r="AA21" s="10" t="n"/>
+      <c r="AB21" s="11" t="n"/>
+      <c r="AC21" s="16" t="inlineStr">
+        <is>
+          <t>最大長</t>
+        </is>
+      </c>
+      <c r="AD21" s="10" t="n"/>
+      <c r="AE21" s="11" t="n"/>
+      <c r="AF21" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG21" s="10" t="n"/>
+      <c r="AH21" s="10" t="n"/>
+      <c r="AI21" s="10" t="n"/>
+      <c r="AJ21" s="10" t="n"/>
+      <c r="AK21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="D22" s="10" t="n"/>
@@ -13326,48 +13235,44 @@
       <c r="J22" s="10" t="n"/>
       <c r="K22" s="10" t="n"/>
       <c r="L22" s="11" t="n"/>
-      <c r="M22" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M22" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
         </is>
       </c>
       <c r="N22" s="10" t="n"/>
       <c r="O22" s="10" t="n"/>
       <c r="P22" s="11" t="n"/>
-      <c r="Q22" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q22" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R22" s="10" t="n"/>
       <c r="S22" s="11" t="n"/>
-      <c r="T22" s="16" t="inlineStr">
-        <is>
-          <t>必須</t>
+      <c r="T22" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="U22" s="10" t="n"/>
       <c r="V22" s="10" t="n"/>
       <c r="W22" s="10" t="n"/>
       <c r="X22" s="11" t="n"/>
-      <c r="Y22" s="16" t="inlineStr">
-        <is>
-          <t>最小長</t>
-        </is>
+      <c r="Y22" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="Z22" s="10" t="n"/>
       <c r="AA22" s="10" t="n"/>
       <c r="AB22" s="11" t="n"/>
-      <c r="AC22" s="16" t="inlineStr">
-        <is>
-          <t>最大長</t>
-        </is>
+      <c r="AC22" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="AD22" s="10" t="n"/>
       <c r="AE22" s="11" t="n"/>
-      <c r="AF22" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF22" s="19" t="inlineStr">
+        <is>
+          <t>都道府県コード（01〜47）</t>
         </is>
       </c>
       <c r="AG22" s="10" t="n"/>
@@ -13378,11 +13283,11 @@
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="B23" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>q</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="D23" s="10" t="n"/>
@@ -13396,7 +13301,7 @@
       <c r="L23" s="11" t="n"/>
       <c r="M23" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N23" s="10" t="n"/>
@@ -13418,22 +13323,16 @@
       <c r="V23" s="10" t="n"/>
       <c r="W23" s="10" t="n"/>
       <c r="X23" s="11" t="n"/>
-      <c r="Y23" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y23" s="17" t="inlineStr"/>
       <c r="Z23" s="10" t="n"/>
       <c r="AA23" s="10" t="n"/>
       <c r="AB23" s="11" t="n"/>
-      <c r="AC23" s="17" t="n">
-        <v>100</v>
-      </c>
+      <c r="AC23" s="17" t="inlineStr"/>
       <c r="AD23" s="10" t="n"/>
       <c r="AE23" s="11" t="n"/>
       <c r="AF23" s="19" t="inlineStr">
         <is>
-          <t>フリーテキスト検索。`ja_code` または `ja_name` に対する部分一致（ILIKE `%q%`）</t>
+          <t>管理者区分（3:中央会→chuokai_flg=true、4,5:JA→chuokai_flg=false）</t>
         </is>
       </c>
       <c r="AG23" s="10" t="n"/>
@@ -13442,193 +13341,24 @@
       <c r="AJ23" s="10" t="n"/>
       <c r="AK23" s="11" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>page</t>
-        </is>
-      </c>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="10" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="I24" s="10" t="n"/>
-      <c r="J24" s="10" t="n"/>
-      <c r="K24" s="10" t="n"/>
-      <c r="L24" s="11" t="n"/>
-      <c r="M24" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N24" s="10" t="n"/>
-      <c r="O24" s="10" t="n"/>
-      <c r="P24" s="11" t="n"/>
-      <c r="Q24" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R24" s="10" t="n"/>
-      <c r="S24" s="11" t="n"/>
-      <c r="T24" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U24" s="10" t="n"/>
-      <c r="V24" s="10" t="n"/>
-      <c r="W24" s="10" t="n"/>
-      <c r="X24" s="11" t="n"/>
-      <c r="Y24" s="17" t="inlineStr"/>
-      <c r="Z24" s="10" t="n"/>
-      <c r="AA24" s="10" t="n"/>
-      <c r="AB24" s="11" t="n"/>
-      <c r="AC24" s="17" t="inlineStr"/>
-      <c r="AD24" s="10" t="n"/>
-      <c r="AE24" s="11" t="n"/>
-      <c r="AF24" s="19" t="inlineStr">
-        <is>
-          <t>ページ番号（1以上、デフォルト=1）</t>
-        </is>
-      </c>
-      <c r="AG24" s="10" t="n"/>
-      <c r="AH24" s="10" t="n"/>
-      <c r="AI24" s="10" t="n"/>
-      <c r="AJ24" s="10" t="n"/>
-      <c r="AK24" s="11" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>per_page</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="10" t="n"/>
-      <c r="J25" s="10" t="n"/>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="11" t="n"/>
-      <c r="M25" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N25" s="10" t="n"/>
-      <c r="O25" s="10" t="n"/>
-      <c r="P25" s="11" t="n"/>
-      <c r="Q25" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R25" s="10" t="n"/>
-      <c r="S25" s="11" t="n"/>
-      <c r="T25" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U25" s="10" t="n"/>
-      <c r="V25" s="10" t="n"/>
-      <c r="W25" s="10" t="n"/>
-      <c r="X25" s="11" t="n"/>
-      <c r="Y25" s="17" t="inlineStr"/>
-      <c r="Z25" s="10" t="n"/>
-      <c r="AA25" s="10" t="n"/>
-      <c r="AB25" s="11" t="n"/>
-      <c r="AC25" s="17" t="inlineStr"/>
-      <c r="AD25" s="10" t="n"/>
-      <c r="AE25" s="11" t="n"/>
-      <c r="AF25" s="19" t="inlineStr">
-        <is>
-          <t>1ページの件数（1〜100、デフォルト=50）</t>
-        </is>
-      </c>
-      <c r="AG25" s="10" t="n"/>
-      <c r="AH25" s="10" t="n"/>
-      <c r="AI25" s="10" t="n"/>
-      <c r="AJ25" s="10" t="n"/>
-      <c r="AK25" s="11" t="n"/>
-    </row>
-    <row r="26" ht="54" customHeight="1">
-      <c r="B26" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>include_id</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="10" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="10" t="n"/>
-      <c r="I26" s="10" t="n"/>
-      <c r="J26" s="10" t="n"/>
-      <c r="K26" s="10" t="n"/>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N26" s="10" t="n"/>
-      <c r="O26" s="10" t="n"/>
-      <c r="P26" s="11" t="n"/>
-      <c r="Q26" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R26" s="10" t="n"/>
-      <c r="S26" s="11" t="n"/>
-      <c r="T26" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U26" s="10" t="n"/>
-      <c r="V26" s="10" t="n"/>
-      <c r="W26" s="10" t="n"/>
-      <c r="X26" s="11" t="n"/>
-      <c r="Y26" s="17" t="inlineStr"/>
-      <c r="Z26" s="10" t="n"/>
-      <c r="AA26" s="10" t="n"/>
-      <c r="AB26" s="11" t="n"/>
-      <c r="AC26" s="17" t="inlineStr"/>
-      <c r="AD26" s="10" t="n"/>
-      <c r="AE26" s="11" t="n"/>
-      <c r="AF26" s="19" t="inlineStr">
-        <is>
-          <t>編集フォーム用エスケープハッチ。指定された ja_id がページ範囲に含まれない場合、レスポンス先頭に追加して返す。DataScope 制限により範囲外のIDは無視（silently dropped）</t>
-        </is>
-      </c>
-      <c r="AG26" s="10" t="n"/>
-      <c r="AH26" s="10" t="n"/>
-      <c r="AI26" s="10" t="n"/>
-      <c r="AJ26" s="10" t="n"/>
-      <c r="AK26" s="11" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>todofuken_code</t>
+    <row r="24" ht="19.5" customHeight="1"/>
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19.5" customHeight="1"/>
+    <row r="27" ht="19.5" customHeight="1">
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>項目ID</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -13640,44 +13370,44 @@
       <c r="J27" s="10" t="n"/>
       <c r="K27" s="10" t="n"/>
       <c r="L27" s="11" t="n"/>
-      <c r="M27" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q27" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R27" s="10" t="n"/>
       <c r="S27" s="11" t="n"/>
-      <c r="T27" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="T27" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
         </is>
       </c>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n"/>
-      <c r="Y27" s="17" t="n">
-        <v>2</v>
+      <c r="Y27" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
       </c>
       <c r="Z27" s="10" t="n"/>
       <c r="AA27" s="10" t="n"/>
-      <c r="AB27" s="11" t="n"/>
-      <c r="AC27" s="17" t="n">
-        <v>2</v>
-      </c>
+      <c r="AB27" s="10" t="n"/>
+      <c r="AC27" s="10" t="n"/>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="11" t="n"/>
-      <c r="AF27" s="19" t="inlineStr">
-        <is>
-          <t>都道府県コード（01〜47）。完全一致でカスケード絞込み</t>
+      <c r="AF27" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -13686,13 +13416,13 @@
       <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="11" t="n"/>
     </row>
-    <row r="28" ht="36" customHeight="1">
+    <row r="28" ht="18" customHeight="1">
       <c r="B28" s="31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -13706,7 +13436,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -13714,30 +13444,30 @@
       <c r="P28" s="11" t="n"/>
       <c r="Q28" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="R28" s="10" t="n"/>
       <c r="S28" s="11" t="n"/>
-      <c r="T28" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="T28" s="17" t="inlineStr"/>
       <c r="U28" s="10" t="n"/>
       <c r="V28" s="10" t="n"/>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="11" t="n"/>
-      <c r="Y28" s="17" t="inlineStr"/>
+      <c r="Y28" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z28" s="10" t="n"/>
       <c r="AA28" s="10" t="n"/>
-      <c r="AB28" s="11" t="n"/>
-      <c r="AC28" s="17" t="inlineStr"/>
+      <c r="AB28" s="10" t="n"/>
+      <c r="AC28" s="10" t="n"/>
       <c r="AD28" s="10" t="n"/>
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>管理者区分（3:中央会→`chuokai_flg=TRUE`、4,5:JA→`chuokai_flg=FALSE`、その他/未指定: 絞込みなし）</t>
+          <t>JA一覧</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -13746,27 +13476,196 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="19.5" customHeight="1"/>
-    <row r="30" ht="19.5" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>3.レスポンスデータ</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="19.5" customHeight="1"/>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>項目ID</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="n"/>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>ja_id</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="10" t="n"/>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="n"/>
+      <c r="P29" s="11" t="n"/>
+      <c r="Q29" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="11" t="n"/>
+      <c r="T29" s="17" t="inlineStr"/>
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="10" t="n"/>
+      <c r="W29" s="10" t="n"/>
+      <c r="X29" s="11" t="n"/>
+      <c r="Y29" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z29" s="10" t="n"/>
+      <c r="AA29" s="10" t="n"/>
+      <c r="AB29" s="10" t="n"/>
+      <c r="AC29" s="10" t="n"/>
+      <c r="AD29" s="10" t="n"/>
+      <c r="AE29" s="11" t="n"/>
+      <c r="AF29" s="19" t="inlineStr">
+        <is>
+          <t>JA ID</t>
+        </is>
+      </c>
+      <c r="AG29" s="10" t="n"/>
+      <c r="AH29" s="10" t="n"/>
+      <c r="AI29" s="10" t="n"/>
+      <c r="AJ29" s="10" t="n"/>
+      <c r="AK29" s="11" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="38" t="n"/>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>ja_code</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="11" t="n"/>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="11" t="n"/>
+      <c r="T30" s="17" t="inlineStr"/>
+      <c r="U30" s="10" t="n"/>
+      <c r="V30" s="10" t="n"/>
+      <c r="W30" s="10" t="n"/>
+      <c r="X30" s="11" t="n"/>
+      <c r="Y30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z30" s="10" t="n"/>
+      <c r="AA30" s="10" t="n"/>
+      <c r="AB30" s="10" t="n"/>
+      <c r="AC30" s="10" t="n"/>
+      <c r="AD30" s="10" t="n"/>
+      <c r="AE30" s="11" t="n"/>
+      <c r="AF30" s="19" t="inlineStr">
+        <is>
+          <t>JAコード</t>
+        </is>
+      </c>
+      <c r="AG30" s="10" t="n"/>
+      <c r="AH30" s="10" t="n"/>
+      <c r="AI30" s="10" t="n"/>
+      <c r="AJ30" s="10" t="n"/>
+      <c r="AK30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="38" t="n"/>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>ja_name</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="17" t="inlineStr"/>
+      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="10" t="n"/>
+      <c r="X31" s="11" t="n"/>
+      <c r="Y31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z31" s="10" t="n"/>
+      <c r="AA31" s="10" t="n"/>
+      <c r="AB31" s="10" t="n"/>
+      <c r="AC31" s="10" t="n"/>
+      <c r="AD31" s="10" t="n"/>
+      <c r="AE31" s="11" t="n"/>
+      <c r="AF31" s="19" t="inlineStr">
+        <is>
+          <t>JA名称</t>
+        </is>
+      </c>
+      <c r="AG31" s="10" t="n"/>
+      <c r="AH31" s="10" t="n"/>
+      <c r="AI31" s="10" t="n"/>
+      <c r="AJ31" s="10" t="n"/>
+      <c r="AK31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="38" t="n"/>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>todofuken_code</t>
+        </is>
+      </c>
       <c r="E32" s="10" t="n"/>
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="10" t="n"/>
@@ -13775,33 +13674,29 @@
       <c r="J32" s="10" t="n"/>
       <c r="K32" s="10" t="n"/>
       <c r="L32" s="11" t="n"/>
-      <c r="M32" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
         </is>
       </c>
       <c r="N32" s="10" t="n"/>
       <c r="O32" s="10" t="n"/>
       <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R32" s="10" t="n"/>
       <c r="S32" s="11" t="n"/>
-      <c r="T32" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
+      <c r="T32" s="17" t="inlineStr"/>
       <c r="U32" s="10" t="n"/>
       <c r="V32" s="10" t="n"/>
       <c r="W32" s="10" t="n"/>
       <c r="X32" s="11" t="n"/>
-      <c r="Y32" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
+      <c r="Y32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="Z32" s="10" t="n"/>
@@ -13810,9 +13705,9 @@
       <c r="AC32" s="10" t="n"/>
       <c r="AD32" s="10" t="n"/>
       <c r="AE32" s="11" t="n"/>
-      <c r="AF32" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF32" s="19" t="inlineStr">
+        <is>
+          <t>都道府県コード</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -13823,14 +13718,14 @@
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="C33" s="39" t="n"/>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>chuokai_flg</t>
+        </is>
+      </c>
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
@@ -13841,7 +13736,7 @@
       <c r="L33" s="11" t="n"/>
       <c r="M33" s="17" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N33" s="10" t="n"/>
@@ -13849,7 +13744,7 @@
       <c r="P33" s="11" t="n"/>
       <c r="Q33" s="17" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R33" s="10" t="n"/>
@@ -13872,7 +13767,7 @@
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>JA一覧</t>
+          <t>中央会フラグ</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -13881,136 +13776,21 @@
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="11" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="37" t="n"/>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>ja_id</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="11" t="n"/>
-      <c r="M34" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N34" s="10" t="n"/>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="11" t="n"/>
-      <c r="Q34" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R34" s="10" t="n"/>
-      <c r="S34" s="11" t="n"/>
-      <c r="T34" s="17" t="inlineStr"/>
-      <c r="U34" s="10" t="n"/>
-      <c r="V34" s="10" t="n"/>
-      <c r="W34" s="10" t="n"/>
-      <c r="X34" s="11" t="n"/>
-      <c r="Y34" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z34" s="10" t="n"/>
-      <c r="AA34" s="10" t="n"/>
-      <c r="AB34" s="10" t="n"/>
-      <c r="AC34" s="10" t="n"/>
-      <c r="AD34" s="10" t="n"/>
-      <c r="AE34" s="11" t="n"/>
-      <c r="AF34" s="19" t="inlineStr">
-        <is>
-          <t>JA ID</t>
-        </is>
-      </c>
-      <c r="AG34" s="10" t="n"/>
-      <c r="AH34" s="10" t="n"/>
-      <c r="AI34" s="10" t="n"/>
-      <c r="AJ34" s="10" t="n"/>
-      <c r="AK34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" s="38" t="n"/>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>ja_code</t>
-        </is>
-      </c>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="10" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N35" s="10" t="n"/>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R35" s="10" t="n"/>
-      <c r="S35" s="11" t="n"/>
-      <c r="T35" s="17" t="inlineStr"/>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="10" t="n"/>
-      <c r="W35" s="10" t="n"/>
-      <c r="X35" s="11" t="n"/>
-      <c r="Y35" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z35" s="10" t="n"/>
-      <c r="AA35" s="10" t="n"/>
-      <c r="AB35" s="10" t="n"/>
-      <c r="AC35" s="10" t="n"/>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="19" t="inlineStr">
-        <is>
-          <t>JAコード</t>
-        </is>
-      </c>
-      <c r="AG35" s="10" t="n"/>
-      <c r="AH35" s="10" t="n"/>
-      <c r="AI35" s="10" t="n"/>
-      <c r="AJ35" s="10" t="n"/>
-      <c r="AK35" s="11" t="n"/>
+    <row r="34" ht="19.5" customHeight="1"/>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="B35" s="40" t="inlineStr">
+        <is>
+          <t>リクエスト</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>ja_name</t>
-        </is>
-      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/ja/dropdown?todofuken_code=13&amp;role_id=3</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n"/>
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
@@ -14018,527 +13798,42 @@
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="10" t="n"/>
       <c r="K36" s="10" t="n"/>
-      <c r="L36" s="11" t="n"/>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
+      <c r="L36" s="10" t="n"/>
+      <c r="M36" s="10" t="n"/>
       <c r="N36" s="10" t="n"/>
       <c r="O36" s="10" t="n"/>
-      <c r="P36" s="11" t="n"/>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="P36" s="10" t="n"/>
+      <c r="Q36" s="10" t="n"/>
       <c r="R36" s="10" t="n"/>
-      <c r="S36" s="11" t="n"/>
-      <c r="T36" s="17" t="inlineStr"/>
+      <c r="S36" s="10" t="n"/>
+      <c r="T36" s="10" t="n"/>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
       <c r="W36" s="10" t="n"/>
-      <c r="X36" s="11" t="n"/>
-      <c r="Y36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="X36" s="10" t="n"/>
+      <c r="Y36" s="10" t="n"/>
       <c r="Z36" s="10" t="n"/>
       <c r="AA36" s="10" t="n"/>
       <c r="AB36" s="10" t="n"/>
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
-      <c r="AE36" s="11" t="n"/>
-      <c r="AF36" s="19" t="inlineStr">
-        <is>
-          <t>JA名称</t>
-        </is>
-      </c>
+      <c r="AE36" s="10" t="n"/>
+      <c r="AF36" s="10" t="n"/>
       <c r="AG36" s="10" t="n"/>
       <c r="AH36" s="10" t="n"/>
       <c r="AI36" s="10" t="n"/>
       <c r="AJ36" s="10" t="n"/>
       <c r="AK36" s="11" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C37" s="38" t="n"/>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>todofuken_code</t>
-        </is>
-      </c>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="11" t="n"/>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R37" s="10" t="n"/>
-      <c r="S37" s="11" t="n"/>
-      <c r="T37" s="17" t="inlineStr"/>
-      <c r="U37" s="10" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
-      <c r="X37" s="11" t="n"/>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="10" t="n"/>
-      <c r="AB37" s="10" t="n"/>
-      <c r="AC37" s="10" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="11" t="n"/>
-      <c r="AF37" s="19" t="inlineStr">
-        <is>
-          <t>都道府県コード</t>
-        </is>
-      </c>
-      <c r="AG37" s="10" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="10" t="n"/>
-      <c r="AK37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="C38" s="39" t="n"/>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>chuokai_flg</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="n"/>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="10" t="n"/>
-      <c r="H38" s="10" t="n"/>
-      <c r="I38" s="10" t="n"/>
-      <c r="J38" s="10" t="n"/>
-      <c r="K38" s="10" t="n"/>
-      <c r="L38" s="11" t="n"/>
-      <c r="M38" s="17" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="N38" s="10" t="n"/>
-      <c r="O38" s="10" t="n"/>
-      <c r="P38" s="11" t="n"/>
-      <c r="Q38" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R38" s="10" t="n"/>
-      <c r="S38" s="11" t="n"/>
-      <c r="T38" s="17" t="inlineStr"/>
-      <c r="U38" s="10" t="n"/>
-      <c r="V38" s="10" t="n"/>
-      <c r="W38" s="10" t="n"/>
-      <c r="X38" s="11" t="n"/>
-      <c r="Y38" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z38" s="10" t="n"/>
-      <c r="AA38" s="10" t="n"/>
-      <c r="AB38" s="10" t="n"/>
-      <c r="AC38" s="10" t="n"/>
-      <c r="AD38" s="10" t="n"/>
-      <c r="AE38" s="11" t="n"/>
-      <c r="AF38" s="19" t="inlineStr">
-        <is>
-          <t>中央会フラグ</t>
-        </is>
-      </c>
-      <c r="AG38" s="10" t="n"/>
-      <c r="AH38" s="10" t="n"/>
-      <c r="AI38" s="10" t="n"/>
-      <c r="AJ38" s="10" t="n"/>
-      <c r="AK38" s="11" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="31" t="n">
-        <v>7</v>
-      </c>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="B38" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（成功）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="198" customHeight="1">
       <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="10" t="n"/>
-      <c r="H39" s="10" t="n"/>
-      <c r="I39" s="10" t="n"/>
-      <c r="J39" s="10" t="n"/>
-      <c r="K39" s="10" t="n"/>
-      <c r="L39" s="11" t="n"/>
-      <c r="M39" s="17" t="inlineStr">
-        <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="N39" s="10" t="n"/>
-      <c r="O39" s="10" t="n"/>
-      <c r="P39" s="11" t="n"/>
-      <c r="Q39" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R39" s="10" t="n"/>
-      <c r="S39" s="11" t="n"/>
-      <c r="T39" s="17" t="inlineStr"/>
-      <c r="U39" s="10" t="n"/>
-      <c r="V39" s="10" t="n"/>
-      <c r="W39" s="10" t="n"/>
-      <c r="X39" s="11" t="n"/>
-      <c r="Y39" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z39" s="10" t="n"/>
-      <c r="AA39" s="10" t="n"/>
-      <c r="AB39" s="10" t="n"/>
-      <c r="AC39" s="10" t="n"/>
-      <c r="AD39" s="10" t="n"/>
-      <c r="AE39" s="11" t="n"/>
-      <c r="AF39" s="19" t="inlineStr">
-        <is>
-          <t>ページングメタ</t>
-        </is>
-      </c>
-      <c r="AG39" s="10" t="n"/>
-      <c r="AH39" s="10" t="n"/>
-      <c r="AI39" s="10" t="n"/>
-      <c r="AJ39" s="10" t="n"/>
-      <c r="AK39" s="11" t="n"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="B40" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="C40" s="37" t="n"/>
-      <c r="D40" s="19" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="11" t="n"/>
-      <c r="M40" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N40" s="10" t="n"/>
-      <c r="O40" s="10" t="n"/>
-      <c r="P40" s="11" t="n"/>
-      <c r="Q40" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R40" s="10" t="n"/>
-      <c r="S40" s="11" t="n"/>
-      <c r="T40" s="17" t="inlineStr"/>
-      <c r="U40" s="10" t="n"/>
-      <c r="V40" s="10" t="n"/>
-      <c r="W40" s="10" t="n"/>
-      <c r="X40" s="11" t="n"/>
-      <c r="Y40" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z40" s="10" t="n"/>
-      <c r="AA40" s="10" t="n"/>
-      <c r="AB40" s="10" t="n"/>
-      <c r="AC40" s="10" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="11" t="n"/>
-      <c r="AF40" s="19" t="inlineStr">
-        <is>
-          <t>DataScope 適用後の総件数（カスケード絞込み込み）</t>
-        </is>
-      </c>
-      <c r="AG40" s="10" t="n"/>
-      <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="10" t="n"/>
-      <c r="AJ40" s="10" t="n"/>
-      <c r="AK40" s="11" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="C41" s="38" t="n"/>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>page</t>
-        </is>
-      </c>
-      <c r="E41" s="10" t="n"/>
-      <c r="F41" s="10" t="n"/>
-      <c r="G41" s="10" t="n"/>
-      <c r="H41" s="10" t="n"/>
-      <c r="I41" s="10" t="n"/>
-      <c r="J41" s="10" t="n"/>
-      <c r="K41" s="10" t="n"/>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N41" s="10" t="n"/>
-      <c r="O41" s="10" t="n"/>
-      <c r="P41" s="11" t="n"/>
-      <c r="Q41" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R41" s="10" t="n"/>
-      <c r="S41" s="11" t="n"/>
-      <c r="T41" s="17" t="inlineStr"/>
-      <c r="U41" s="10" t="n"/>
-      <c r="V41" s="10" t="n"/>
-      <c r="W41" s="10" t="n"/>
-      <c r="X41" s="11" t="n"/>
-      <c r="Y41" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z41" s="10" t="n"/>
-      <c r="AA41" s="10" t="n"/>
-      <c r="AB41" s="10" t="n"/>
-      <c r="AC41" s="10" t="n"/>
-      <c r="AD41" s="10" t="n"/>
-      <c r="AE41" s="11" t="n"/>
-      <c r="AF41" s="19" t="inlineStr">
-        <is>
-          <t>現在のページ番号</t>
-        </is>
-      </c>
-      <c r="AG41" s="10" t="n"/>
-      <c r="AH41" s="10" t="n"/>
-      <c r="AI41" s="10" t="n"/>
-      <c r="AJ41" s="10" t="n"/>
-      <c r="AK41" s="11" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="C42" s="38" t="n"/>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>per_page</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="10" t="n"/>
-      <c r="H42" s="10" t="n"/>
-      <c r="I42" s="10" t="n"/>
-      <c r="J42" s="10" t="n"/>
-      <c r="K42" s="10" t="n"/>
-      <c r="L42" s="11" t="n"/>
-      <c r="M42" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N42" s="10" t="n"/>
-      <c r="O42" s="10" t="n"/>
-      <c r="P42" s="11" t="n"/>
-      <c r="Q42" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R42" s="10" t="n"/>
-      <c r="S42" s="11" t="n"/>
-      <c r="T42" s="17" t="inlineStr"/>
-      <c r="U42" s="10" t="n"/>
-      <c r="V42" s="10" t="n"/>
-      <c r="W42" s="10" t="n"/>
-      <c r="X42" s="11" t="n"/>
-      <c r="Y42" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z42" s="10" t="n"/>
-      <c r="AA42" s="10" t="n"/>
-      <c r="AB42" s="10" t="n"/>
-      <c r="AC42" s="10" t="n"/>
-      <c r="AD42" s="10" t="n"/>
-      <c r="AE42" s="11" t="n"/>
-      <c r="AF42" s="19" t="inlineStr">
-        <is>
-          <t>1ページの件数</t>
-        </is>
-      </c>
-      <c r="AG42" s="10" t="n"/>
-      <c r="AH42" s="10" t="n"/>
-      <c r="AI42" s="10" t="n"/>
-      <c r="AJ42" s="10" t="n"/>
-      <c r="AK42" s="11" t="n"/>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="B43" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="C43" s="39" t="n"/>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>has_more</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="n"/>
-      <c r="F43" s="10" t="n"/>
-      <c r="G43" s="10" t="n"/>
-      <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
-      <c r="J43" s="10" t="n"/>
-      <c r="K43" s="10" t="n"/>
-      <c r="L43" s="11" t="n"/>
-      <c r="M43" s="17" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="N43" s="10" t="n"/>
-      <c r="O43" s="10" t="n"/>
-      <c r="P43" s="11" t="n"/>
-      <c r="Q43" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R43" s="10" t="n"/>
-      <c r="S43" s="11" t="n"/>
-      <c r="T43" s="17" t="inlineStr"/>
-      <c r="U43" s="10" t="n"/>
-      <c r="V43" s="10" t="n"/>
-      <c r="W43" s="10" t="n"/>
-      <c r="X43" s="11" t="n"/>
-      <c r="Y43" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z43" s="10" t="n"/>
-      <c r="AA43" s="10" t="n"/>
-      <c r="AB43" s="10" t="n"/>
-      <c r="AC43" s="10" t="n"/>
-      <c r="AD43" s="10" t="n"/>
-      <c r="AE43" s="11" t="n"/>
-      <c r="AF43" s="19" t="inlineStr">
-        <is>
-          <t>次ページが存在するか（`page * per_page &lt; total`）</t>
-        </is>
-      </c>
-      <c r="AG43" s="10" t="n"/>
-      <c r="AH43" s="10" t="n"/>
-      <c r="AI43" s="10" t="n"/>
-      <c r="AJ43" s="10" t="n"/>
-      <c r="AK43" s="11" t="n"/>
-    </row>
-    <row r="44" ht="19.5" customHeight="1"/>
-    <row r="45" ht="19.5" customHeight="1">
-      <c r="B45" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/ja/dropdown?q=東京&amp;page=1&amp;per_page=50</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
-      <c r="K46" s="10" t="n"/>
-      <c r="L46" s="10" t="n"/>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="10" t="n"/>
-      <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
-      <c r="R46" s="10" t="n"/>
-      <c r="S46" s="10" t="n"/>
-      <c r="T46" s="10" t="n"/>
-      <c r="U46" s="10" t="n"/>
-      <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="n"/>
-      <c r="Y46" s="10" t="n"/>
-      <c r="Z46" s="10" t="n"/>
-      <c r="AA46" s="10" t="n"/>
-      <c r="AB46" s="10" t="n"/>
-      <c r="AC46" s="10" t="n"/>
-      <c r="AD46" s="10" t="n"/>
-      <c r="AE46" s="10" t="n"/>
-      <c r="AF46" s="10" t="n"/>
-      <c r="AG46" s="10" t="n"/>
-      <c r="AH46" s="10" t="n"/>
-      <c r="AI46" s="10" t="n"/>
-      <c r="AJ46" s="10" t="n"/>
-      <c r="AK46" s="11" t="n"/>
-    </row>
-    <row r="48" ht="19.5" customHeight="1">
-      <c r="B48" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（成功）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="306" customHeight="1">
-      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -14549,60 +13844,54 @@
       "todofuken_code": "13",
       "chuokai_flg": true
     }
-  ],
-  "meta": {
-    "total": 1,
-    "page": 1,
-    "per_page": 50,
-    "has_more": false
-  }
+  ]
 }</t>
         </is>
       </c>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="10" t="n"/>
-      <c r="H49" s="10" t="n"/>
-      <c r="I49" s="10" t="n"/>
-      <c r="J49" s="10" t="n"/>
-      <c r="K49" s="10" t="n"/>
-      <c r="L49" s="10" t="n"/>
-      <c r="M49" s="10" t="n"/>
-      <c r="N49" s="10" t="n"/>
-      <c r="O49" s="10" t="n"/>
-      <c r="P49" s="10" t="n"/>
-      <c r="Q49" s="10" t="n"/>
-      <c r="R49" s="10" t="n"/>
-      <c r="S49" s="10" t="n"/>
-      <c r="T49" s="10" t="n"/>
-      <c r="U49" s="10" t="n"/>
-      <c r="V49" s="10" t="n"/>
-      <c r="W49" s="10" t="n"/>
-      <c r="X49" s="10" t="n"/>
-      <c r="Y49" s="10" t="n"/>
-      <c r="Z49" s="10" t="n"/>
-      <c r="AA49" s="10" t="n"/>
-      <c r="AB49" s="10" t="n"/>
-      <c r="AC49" s="10" t="n"/>
-      <c r="AD49" s="10" t="n"/>
-      <c r="AE49" s="10" t="n"/>
-      <c r="AF49" s="10" t="n"/>
-      <c r="AG49" s="10" t="n"/>
-      <c r="AH49" s="10" t="n"/>
-      <c r="AI49" s="10" t="n"/>
-      <c r="AJ49" s="10" t="n"/>
-      <c r="AK49" s="11" t="n"/>
-    </row>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="B51" s="40" t="inlineStr">
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="n"/>
+      <c r="J39" s="10" t="n"/>
+      <c r="K39" s="10" t="n"/>
+      <c r="L39" s="10" t="n"/>
+      <c r="M39" s="10" t="n"/>
+      <c r="N39" s="10" t="n"/>
+      <c r="O39" s="10" t="n"/>
+      <c r="P39" s="10" t="n"/>
+      <c r="Q39" s="10" t="n"/>
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="10" t="n"/>
+      <c r="T39" s="10" t="n"/>
+      <c r="U39" s="10" t="n"/>
+      <c r="V39" s="10" t="n"/>
+      <c r="W39" s="10" t="n"/>
+      <c r="X39" s="10" t="n"/>
+      <c r="Y39" s="10" t="n"/>
+      <c r="Z39" s="10" t="n"/>
+      <c r="AA39" s="10" t="n"/>
+      <c r="AB39" s="10" t="n"/>
+      <c r="AC39" s="10" t="n"/>
+      <c r="AD39" s="10" t="n"/>
+      <c r="AE39" s="10" t="n"/>
+      <c r="AF39" s="10" t="n"/>
+      <c r="AG39" s="10" t="n"/>
+      <c r="AH39" s="10" t="n"/>
+      <c r="AI39" s="10" t="n"/>
+      <c r="AJ39" s="10" t="n"/>
+      <c r="AK39" s="11" t="n"/>
+    </row>
+    <row r="41" ht="19.5" customHeight="1">
+      <c r="B41" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="72" customHeight="1">
-      <c r="C52" s="19" t="inlineStr">
+    <row r="42" ht="72" customHeight="1">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -14610,50 +13899,50 @@
 }</t>
         </is>
       </c>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
-      <c r="J52" s="10" t="n"/>
-      <c r="K52" s="10" t="n"/>
-      <c r="L52" s="10" t="n"/>
-      <c r="M52" s="10" t="n"/>
-      <c r="N52" s="10" t="n"/>
-      <c r="O52" s="10" t="n"/>
-      <c r="P52" s="10" t="n"/>
-      <c r="Q52" s="10" t="n"/>
-      <c r="R52" s="10" t="n"/>
-      <c r="S52" s="10" t="n"/>
-      <c r="T52" s="10" t="n"/>
-      <c r="U52" s="10" t="n"/>
-      <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n"/>
-      <c r="X52" s="10" t="n"/>
-      <c r="Y52" s="10" t="n"/>
-      <c r="Z52" s="10" t="n"/>
-      <c r="AA52" s="10" t="n"/>
-      <c r="AB52" s="10" t="n"/>
-      <c r="AC52" s="10" t="n"/>
-      <c r="AD52" s="10" t="n"/>
-      <c r="AE52" s="10" t="n"/>
-      <c r="AF52" s="10" t="n"/>
-      <c r="AG52" s="10" t="n"/>
-      <c r="AH52" s="10" t="n"/>
-      <c r="AI52" s="10" t="n"/>
-      <c r="AJ52" s="10" t="n"/>
-      <c r="AK52" s="11" t="n"/>
-    </row>
-    <row r="54" ht="19.5" customHeight="1">
-      <c r="B54" s="40" t="inlineStr">
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="10" t="n"/>
+      <c r="K42" s="10" t="n"/>
+      <c r="L42" s="10" t="n"/>
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="10" t="n"/>
+      <c r="O42" s="10" t="n"/>
+      <c r="P42" s="10" t="n"/>
+      <c r="Q42" s="10" t="n"/>
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="10" t="n"/>
+      <c r="T42" s="10" t="n"/>
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="10" t="n"/>
+      <c r="W42" s="10" t="n"/>
+      <c r="X42" s="10" t="n"/>
+      <c r="Y42" s="10" t="n"/>
+      <c r="Z42" s="10" t="n"/>
+      <c r="AA42" s="10" t="n"/>
+      <c r="AB42" s="10" t="n"/>
+      <c r="AC42" s="10" t="n"/>
+      <c r="AD42" s="10" t="n"/>
+      <c r="AE42" s="10" t="n"/>
+      <c r="AF42" s="10" t="n"/>
+      <c r="AG42" s="10" t="n"/>
+      <c r="AH42" s="10" t="n"/>
+      <c r="AI42" s="10" t="n"/>
+      <c r="AJ42" s="10" t="n"/>
+      <c r="AK42" s="11" t="n"/>
+    </row>
+    <row r="44" ht="19.5" customHeight="1">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="72" customHeight="1">
-      <c r="C55" s="19" t="inlineStr">
+    <row r="45" ht="72" customHeight="1">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -14661,50 +13950,50 @@
 }</t>
         </is>
       </c>
-      <c r="D55" s="10" t="n"/>
-      <c r="E55" s="10" t="n"/>
-      <c r="F55" s="10" t="n"/>
-      <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n"/>
-      <c r="I55" s="10" t="n"/>
-      <c r="J55" s="10" t="n"/>
-      <c r="K55" s="10" t="n"/>
-      <c r="L55" s="10" t="n"/>
-      <c r="M55" s="10" t="n"/>
-      <c r="N55" s="10" t="n"/>
-      <c r="O55" s="10" t="n"/>
-      <c r="P55" s="10" t="n"/>
-      <c r="Q55" s="10" t="n"/>
-      <c r="R55" s="10" t="n"/>
-      <c r="S55" s="10" t="n"/>
-      <c r="T55" s="10" t="n"/>
-      <c r="U55" s="10" t="n"/>
-      <c r="V55" s="10" t="n"/>
-      <c r="W55" s="10" t="n"/>
-      <c r="X55" s="10" t="n"/>
-      <c r="Y55" s="10" t="n"/>
-      <c r="Z55" s="10" t="n"/>
-      <c r="AA55" s="10" t="n"/>
-      <c r="AB55" s="10" t="n"/>
-      <c r="AC55" s="10" t="n"/>
-      <c r="AD55" s="10" t="n"/>
-      <c r="AE55" s="10" t="n"/>
-      <c r="AF55" s="10" t="n"/>
-      <c r="AG55" s="10" t="n"/>
-      <c r="AH55" s="10" t="n"/>
-      <c r="AI55" s="10" t="n"/>
-      <c r="AJ55" s="10" t="n"/>
-      <c r="AK55" s="11" t="n"/>
-    </row>
-    <row r="57" ht="19.5" customHeight="1">
-      <c r="B57" s="40" t="inlineStr">
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="10" t="n"/>
+      <c r="K45" s="10" t="n"/>
+      <c r="L45" s="10" t="n"/>
+      <c r="M45" s="10" t="n"/>
+      <c r="N45" s="10" t="n"/>
+      <c r="O45" s="10" t="n"/>
+      <c r="P45" s="10" t="n"/>
+      <c r="Q45" s="10" t="n"/>
+      <c r="R45" s="10" t="n"/>
+      <c r="S45" s="10" t="n"/>
+      <c r="T45" s="10" t="n"/>
+      <c r="U45" s="10" t="n"/>
+      <c r="V45" s="10" t="n"/>
+      <c r="W45" s="10" t="n"/>
+      <c r="X45" s="10" t="n"/>
+      <c r="Y45" s="10" t="n"/>
+      <c r="Z45" s="10" t="n"/>
+      <c r="AA45" s="10" t="n"/>
+      <c r="AB45" s="10" t="n"/>
+      <c r="AC45" s="10" t="n"/>
+      <c r="AD45" s="10" t="n"/>
+      <c r="AE45" s="10" t="n"/>
+      <c r="AF45" s="10" t="n"/>
+      <c r="AG45" s="10" t="n"/>
+      <c r="AH45" s="10" t="n"/>
+      <c r="AI45" s="10" t="n"/>
+      <c r="AJ45" s="10" t="n"/>
+      <c r="AK45" s="11" t="n"/>
+    </row>
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="72" customHeight="1">
-      <c r="C58" s="19" t="inlineStr">
+    <row r="48" ht="72" customHeight="1">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -14712,503 +14001,387 @@
 }</t>
         </is>
       </c>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="10" t="n"/>
-      <c r="F58" s="10" t="n"/>
-      <c r="G58" s="10" t="n"/>
-      <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
-      <c r="J58" s="10" t="n"/>
-      <c r="K58" s="10" t="n"/>
-      <c r="L58" s="10" t="n"/>
-      <c r="M58" s="10" t="n"/>
-      <c r="N58" s="10" t="n"/>
-      <c r="O58" s="10" t="n"/>
-      <c r="P58" s="10" t="n"/>
-      <c r="Q58" s="10" t="n"/>
-      <c r="R58" s="10" t="n"/>
-      <c r="S58" s="10" t="n"/>
-      <c r="T58" s="10" t="n"/>
-      <c r="U58" s="10" t="n"/>
-      <c r="V58" s="10" t="n"/>
-      <c r="W58" s="10" t="n"/>
-      <c r="X58" s="10" t="n"/>
-      <c r="Y58" s="10" t="n"/>
-      <c r="Z58" s="10" t="n"/>
-      <c r="AA58" s="10" t="n"/>
-      <c r="AB58" s="10" t="n"/>
-      <c r="AC58" s="10" t="n"/>
-      <c r="AD58" s="10" t="n"/>
-      <c r="AE58" s="10" t="n"/>
-      <c r="AF58" s="10" t="n"/>
-      <c r="AG58" s="10" t="n"/>
-      <c r="AH58" s="10" t="n"/>
-      <c r="AI58" s="10" t="n"/>
-      <c r="AJ58" s="10" t="n"/>
-      <c r="AK58" s="11" t="n"/>
-    </row>
-    <row r="60" ht="19.5" customHeight="1"/>
-    <row r="61" ht="19.5" customHeight="1">
-      <c r="A61" s="27" t="inlineStr">
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="10" t="n"/>
+      <c r="K48" s="10" t="n"/>
+      <c r="L48" s="10" t="n"/>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="10" t="n"/>
+      <c r="O48" s="10" t="n"/>
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="10" t="n"/>
+      <c r="R48" s="10" t="n"/>
+      <c r="S48" s="10" t="n"/>
+      <c r="T48" s="10" t="n"/>
+      <c r="U48" s="10" t="n"/>
+      <c r="V48" s="10" t="n"/>
+      <c r="W48" s="10" t="n"/>
+      <c r="X48" s="10" t="n"/>
+      <c r="Y48" s="10" t="n"/>
+      <c r="Z48" s="10" t="n"/>
+      <c r="AA48" s="10" t="n"/>
+      <c r="AB48" s="10" t="n"/>
+      <c r="AC48" s="10" t="n"/>
+      <c r="AD48" s="10" t="n"/>
+      <c r="AE48" s="10" t="n"/>
+      <c r="AF48" s="10" t="n"/>
+      <c r="AG48" s="10" t="n"/>
+      <c r="AH48" s="10" t="n"/>
+      <c r="AI48" s="10" t="n"/>
+      <c r="AJ48" s="10" t="n"/>
+      <c r="AK48" s="11" t="n"/>
+    </row>
+    <row r="50" ht="19.5" customHeight="1"/>
+    <row r="51" ht="19.5" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="C53" s="41" t="inlineStr">
+        <is>
+          <t>クエリパラメータの検証：</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="D54" s="41" t="inlineStr">
+        <is>
+          <t>todofuken_code：2桁の文字列（01〜47）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="D55" s="41" t="inlineStr">
+        <is>
+          <t>role_id：1〜5の整数</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="D57" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request を返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="C59" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（JWT / Cookie）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="C60" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="C61" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：認証済みユーザーであればアクセス可能。</t>
+        </is>
+      </c>
+    </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="B62" s="27" t="inlineStr">
-        <is>
-          <t>4.1 リクエストのバリデーション</t>
+      <c r="D62" s="41" t="inlineStr">
+        <is>
+          <t>※ 呼び出し元画面の権限に依存する。</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="C63" s="41" t="inlineStr">
         <is>
-          <t>クエリパラメータの検証：</t>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="D64" s="41" t="inlineStr">
-        <is>
-          <t>q：最大100文字（部分一致用）</t>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="D65" s="41" t="inlineStr">
-        <is>
-          <t>page：1以上の整数</t>
+      <c r="C65" s="41" t="inlineStr">
+        <is>
+          <t>管理者区分によりカスケード条件を切り替える。</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="D66" s="41" t="inlineStr">
         <is>
-          <t>per_page：1〜100の整数</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
+          <t>role_id = 3（中央会）の場合：`chuokai_flg = true` のJAを取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1">
       <c r="D67" s="41" t="inlineStr">
         <is>
-          <t>include_id：1以上の整数</t>
+          <t>role_id = 4（JA本店）または 5（JA管理支店）の場合：`chuokai_flg = false` のJAを取得</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="D68" s="41" t="inlineStr">
         <is>
-          <t>todofuken_code：2桁の文字列（01〜47）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="D69" s="41" t="inlineStr">
-        <is>
-          <t>role_id：1以上の整数</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="C70" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="D71" s="41" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request を返却する（`VALIDATION_ERROR`）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="B72" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="C73" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="C74" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="C75" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：呼び出し元画面のビュー権限（`ja.view`）が必要。</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="C76" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="36" customHeight="1">
-      <c r="C77" s="41" t="inlineStr">
-        <is>
-          <t>DataScope 適用：非 NICHINO_ADMIN/STAFF は自組織配下の JA のみ取得可能。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="B78" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
-        <is>
-          <t>フィルタ適用順：</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
-        <is>
-          <t>ソート：`ja_code ASC` 固定</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
-        <is>
-          <t>ページング：`LIMIT :per_page OFFSET (page-1)*per_page`</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
-        <is>
-          <t>`meta.total` は LIMIT 適用前の総件数（DataScope + 絞込み適用後）</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="C83" s="41" t="inlineStr">
-        <is>
-          <t>`meta.has_more = page * per_page &lt; total`</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="36" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
-        <is>
-          <t>`include_id` 指定時：上記ページ範囲に含まれていなければ、別途同一条件で SELECT して先頭に prepend。DataScope 範囲外なら silently 無視。</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="342" customHeight="1">
-      <c r="C85" s="42" t="inlineStr">
+          <t>role_id 未指定またはその他の場合：全てのJAを取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="216" customHeight="1">
+      <c r="C69" s="42" t="inlineStr">
         <is>
           <t>SELECT ja_id, ja_code, ja_name, todofuken_code, chuokai_flg
 FROM m_ja
 WHERE deleted_at IS NULL
-  -- DataScope (auto-applied per session role)
-  AND (:scope_ja_id IS NULL OR ja_id = :scope_ja_id)
-  -- q: free-text partial match
-  AND (:q IS NULL OR ja_code ILIKE :q_like OR ja_name ILIKE :q_like)
-  -- todofuken cascade
   AND (:todofuken_code IS NULL OR todofuken_code = :todofuken_code)
-  -- role_id cascade
   AND (
     CASE
-      WHEN :role_id = 3 THEN chuokai_flg = TRUE
-      WHEN :role_id IN (4, 5) THEN chuokai_flg = FALSE
-      ELSE TRUE
+      WHEN :role_id = 3 THEN chuokai_flg = true
+      WHEN :role_id IN (4, 5) THEN chuokai_flg = false
+      ELSE true
     END
   )
-ORDER BY ja_code ASC
-LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="10" t="n"/>
-      <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="n"/>
-      <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
-      <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
-      <c r="U85" s="10" t="n"/>
-      <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-      <c r="AA85" s="10" t="n"/>
-      <c r="AB85" s="10" t="n"/>
-      <c r="AC85" s="10" t="n"/>
-      <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
-      <c r="AG85" s="10" t="n"/>
-      <c r="AH85" s="10" t="n"/>
-      <c r="AI85" s="10" t="n"/>
-      <c r="AJ85" s="10" t="n"/>
-      <c r="AK85" s="11" t="n"/>
-    </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="B86" s="27" t="inlineStr">
+ORDER BY ja_code ASC</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="10" t="n"/>
+      <c r="X69" s="10" t="n"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="10" t="n"/>
+      <c r="AE69" s="10" t="n"/>
+      <c r="AF69" s="10" t="n"/>
+      <c r="AG69" s="10" t="n"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="10" t="n"/>
+      <c r="AJ69" s="10" t="n"/>
+      <c r="AK69" s="11" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="B70" s="27" t="inlineStr">
         <is>
           <t>4.4 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="C87" s="41" t="inlineStr">
+    <row r="71" ht="18" customHeight="1">
+      <c r="C71" s="41" t="inlineStr">
         <is>
           <t>取得結果を data 配列として返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="B88" s="27" t="inlineStr">
+    <row r="72" ht="18" customHeight="1">
+      <c r="B72" s="27" t="inlineStr">
         <is>
           <t>4.5 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="C89" s="41" t="inlineStr">
+    <row r="73" ht="18" customHeight="1">
+      <c r="C73" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="204">
+  <mergeCells count="137">
     <mergeCell ref="J11:AK11"/>
-    <mergeCell ref="Y28:AB28"/>
+    <mergeCell ref="Q29:S29"/>
+    <mergeCell ref="Y27:AE27"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="Y36:AE36"/>
-    <mergeCell ref="T24:X24"/>
-    <mergeCell ref="B54:I54"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="D71:AK71"/>
+    <mergeCell ref="C53:AK53"/>
+    <mergeCell ref="Q31:S31"/>
     <mergeCell ref="M32:P32"/>
-    <mergeCell ref="C77:AK77"/>
-    <mergeCell ref="N18:AK18"/>
-    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="M29:P29"/>
     <mergeCell ref="M23:P23"/>
+    <mergeCell ref="AF21:AK21"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="B48:I48"/>
-    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
-    <mergeCell ref="D64:AK64"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="M43:P43"/>
+    <mergeCell ref="C45:AK45"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C40:C43"/>
-    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="Q41:S41"/>
-    <mergeCell ref="D42:L42"/>
-    <mergeCell ref="C75:AK75"/>
+    <mergeCell ref="C65:AK65"/>
+    <mergeCell ref="D33:L33"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="M35:P35"/>
+    <mergeCell ref="Y21:AB21"/>
     <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="C80:AK80"/>
-    <mergeCell ref="AF36:AK36"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="Q43:S43"/>
-    <mergeCell ref="C46:AK46"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="D34:L34"/>
+    <mergeCell ref="T31:X31"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="Q42:S42"/>
-    <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="Y40:AE40"/>
-    <mergeCell ref="C70:AK70"/>
-    <mergeCell ref="T37:X37"/>
-    <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="B45:I45"/>
-    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="C48:AK48"/>
     <mergeCell ref="M33:P33"/>
-    <mergeCell ref="C39:L39"/>
-    <mergeCell ref="T38:X38"/>
-    <mergeCell ref="C49:AK49"/>
-    <mergeCell ref="B86:AK86"/>
-    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="T30:X30"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="T29:X29"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="D37:L37"/>
-    <mergeCell ref="C74:AK74"/>
+    <mergeCell ref="C42:AK42"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="AF32:AK32"/>
-    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="Z2:AC3"/>
-    <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="AF41:AK41"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="AF35:AK35"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="C33:L33"/>
-    <mergeCell ref="B14:I18"/>
+    <mergeCell ref="AC21:AE21"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="C55:AK55"/>
+    <mergeCell ref="D29:L29"/>
     <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D38:L38"/>
-    <mergeCell ref="T40:X40"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="Y39:AE39"/>
+    <mergeCell ref="Y30:AE30"/>
+    <mergeCell ref="B64:AK64"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="D65:AK65"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="AF37:AK37"/>
+    <mergeCell ref="Y29:AE29"/>
+    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="AF24:AK24"/>
-    <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
-    <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="B51:I51"/>
-    <mergeCell ref="C52:AK52"/>
+    <mergeCell ref="A25:AK25"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="Y31:AE31"/>
+    <mergeCell ref="C39:AK39"/>
+    <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B35:I35"/>
     <mergeCell ref="D66:AK66"/>
+    <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="M36:P36"/>
-    <mergeCell ref="Y37:AE37"/>
-    <mergeCell ref="T39:X39"/>
-    <mergeCell ref="C81:AK81"/>
-    <mergeCell ref="Y27:AB27"/>
-    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="B58:AK58"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="B52:AK52"/>
     <mergeCell ref="T32:X32"/>
-    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="T42:X42"/>
+    <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="Y41:AE41"/>
-    <mergeCell ref="C82:AK82"/>
-    <mergeCell ref="A20:AK20"/>
-    <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
-    <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
-    <mergeCell ref="C89:AK89"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="C79:AK79"/>
-    <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="D54:AK54"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="AF40:AK40"/>
+    <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="D30:L30"/>
     <mergeCell ref="C63:AK63"/>
-    <mergeCell ref="M39:P39"/>
-    <mergeCell ref="C34:C38"/>
-    <mergeCell ref="T26:X26"/>
+    <mergeCell ref="T21:X21"/>
     <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="A51:AK51"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="T41:X41"/>
-    <mergeCell ref="Y35:AE35"/>
+    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="J9:AK9"/>
-    <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="M40:P40"/>
-    <mergeCell ref="T43:X43"/>
-    <mergeCell ref="D40:L40"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="C36:AK36"/>
+    <mergeCell ref="D57:AK57"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
     <mergeCell ref="B72:AK72"/>
-    <mergeCell ref="T36:X36"/>
+    <mergeCell ref="B14:I17"/>
     <mergeCell ref="C27:L27"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="M26:P26"/>
-    <mergeCell ref="M41:P41"/>
-    <mergeCell ref="Q26:S26"/>
-    <mergeCell ref="D41:L41"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="M38:P38"/>
-    <mergeCell ref="C83:AK83"/>
-    <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="B70:AK70"/>
+    <mergeCell ref="D32:L32"/>
+    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="Y32:AE32"/>
-    <mergeCell ref="D43:L43"/>
     <mergeCell ref="D68:AK68"/>
-    <mergeCell ref="T25:X25"/>
-    <mergeCell ref="B88:AK88"/>
-    <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="D55:AK55"/>
+    <mergeCell ref="A19:AK19"/>
     <mergeCell ref="D67:AK67"/>
-    <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B57:I57"/>
-    <mergeCell ref="A30:AK30"/>
-    <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="D69:AK69"/>
+    <mergeCell ref="B44:I44"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="A61:AK61"/>
-    <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="C71:AK71"/>
     <mergeCell ref="M22:P22"/>
-    <mergeCell ref="AC28:AE28"/>
-    <mergeCell ref="C76:AK76"/>
+    <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
-    <mergeCell ref="B62:AK62"/>
-    <mergeCell ref="Y34:AE34"/>
-    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="C21:L21"/>
+    <mergeCell ref="D31:L31"/>
     <mergeCell ref="M28:P28"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/design/ACSMS-SCR-024/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_アカウントマスタ明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-024/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_アカウントマスタ明細検索画面_V1.0.xlsx
@@ -1355,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK66"/>
+  <dimension ref="A1:AK89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1516,7 +1516,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1524,7 +1524,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -1870,7 +1870,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -2208,24 +2208,193 @@
       <c r="AJ22" s="10" t="n"/>
       <c r="AK22" s="11" t="n"/>
     </row>
-    <row r="23" ht="19.5" customHeight="1"/>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>3.レスポンスデータ</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="19.5" customHeight="1"/>
-    <row r="26" ht="19.5" customHeight="1">
-      <c r="B26" s="30" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>項目ID</t>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>q</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="n"/>
+      <c r="O23" s="10" t="n"/>
+      <c r="P23" s="11" t="n"/>
+      <c r="Q23" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R23" s="10" t="n"/>
+      <c r="S23" s="11" t="n"/>
+      <c r="T23" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U23" s="10" t="n"/>
+      <c r="V23" s="10" t="n"/>
+      <c r="W23" s="10" t="n"/>
+      <c r="X23" s="11" t="n"/>
+      <c r="Y23" s="17" t="inlineStr"/>
+      <c r="Z23" s="10" t="n"/>
+      <c r="AA23" s="10" t="n"/>
+      <c r="AB23" s="11" t="n"/>
+      <c r="AC23" s="17" t="inlineStr"/>
+      <c r="AD23" s="10" t="n"/>
+      <c r="AE23" s="11" t="n"/>
+      <c r="AF23" s="19" t="inlineStr">
+        <is>
+          <t>部分一致検索（管理支店コード OR 名称）</t>
+        </is>
+      </c>
+      <c r="AG23" s="10" t="n"/>
+      <c r="AH23" s="10" t="n"/>
+      <c r="AI23" s="10" t="n"/>
+      <c r="AJ23" s="10" t="n"/>
+      <c r="AK23" s="11" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>match_field</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="n"/>
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="11" t="n"/>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="11" t="n"/>
+      <c r="T24" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="10" t="n"/>
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="11" t="n"/>
+      <c r="Y24" s="17" t="inlineStr"/>
+      <c r="Z24" s="10" t="n"/>
+      <c r="AA24" s="10" t="n"/>
+      <c r="AB24" s="11" t="n"/>
+      <c r="AC24" s="17" t="inlineStr"/>
+      <c r="AD24" s="10" t="n"/>
+      <c r="AE24" s="11" t="n"/>
+      <c r="AF24" s="19" t="inlineStr">
+        <is>
+          <t>検索対象フィールド。`both`（既定）=コードOR名称、`name`=名称のみ</t>
+        </is>
+      </c>
+      <c r="AG24" s="10" t="n"/>
+      <c r="AH24" s="10" t="n"/>
+      <c r="AI24" s="10" t="n"/>
+      <c r="AJ24" s="10" t="n"/>
+      <c r="AK24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="n"/>
+      <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="n"/>
+      <c r="S25" s="11" t="n"/>
+      <c r="T25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U25" s="10" t="n"/>
+      <c r="V25" s="10" t="n"/>
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="11" t="n"/>
+      <c r="Y25" s="17" t="inlineStr"/>
+      <c r="Z25" s="10" t="n"/>
+      <c r="AA25" s="10" t="n"/>
+      <c r="AB25" s="11" t="n"/>
+      <c r="AC25" s="17" t="inlineStr"/>
+      <c r="AD25" s="10" t="n"/>
+      <c r="AE25" s="11" t="n"/>
+      <c r="AF25" s="19" t="inlineStr">
+        <is>
+          <t>ページ番号（1始まり）。未指定時はページングなし＝全件返却</t>
+        </is>
+      </c>
+      <c r="AG25" s="10" t="n"/>
+      <c r="AH25" s="10" t="n"/>
+      <c r="AI25" s="10" t="n"/>
+      <c r="AJ25" s="10" t="n"/>
+      <c r="AK25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="B26" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -2237,44 +2406,42 @@
       <c r="J26" s="10" t="n"/>
       <c r="K26" s="10" t="n"/>
       <c r="L26" s="11" t="n"/>
-      <c r="M26" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M26" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
         </is>
       </c>
       <c r="N26" s="10" t="n"/>
       <c r="O26" s="10" t="n"/>
       <c r="P26" s="11" t="n"/>
-      <c r="Q26" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R26" s="10" t="n"/>
       <c r="S26" s="11" t="n"/>
-      <c r="T26" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
+      <c r="T26" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="U26" s="10" t="n"/>
       <c r="V26" s="10" t="n"/>
       <c r="W26" s="10" t="n"/>
       <c r="X26" s="11" t="n"/>
-      <c r="Y26" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
+      <c r="Y26" s="17" t="inlineStr"/>
       <c r="Z26" s="10" t="n"/>
       <c r="AA26" s="10" t="n"/>
-      <c r="AB26" s="10" t="n"/>
-      <c r="AC26" s="10" t="n"/>
+      <c r="AB26" s="11" t="n"/>
+      <c r="AC26" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AD26" s="10" t="n"/>
       <c r="AE26" s="11" t="n"/>
-      <c r="AF26" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF26" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数（1〜100、未指定時50）。`page`指定時のみ有効</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -2285,11 +2452,11 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>include_id</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -2303,7 +2470,7 @@
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="17" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N27" s="10" t="n"/>
@@ -2311,30 +2478,30 @@
       <c r="P27" s="11" t="n"/>
       <c r="Q27" s="17" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R27" s="10" t="n"/>
       <c r="S27" s="11" t="n"/>
-      <c r="T27" s="17" t="inlineStr"/>
+      <c r="T27" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n"/>
-      <c r="Y27" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y27" s="17" t="inlineStr"/>
       <c r="Z27" s="10" t="n"/>
       <c r="AA27" s="10" t="n"/>
-      <c r="AB27" s="10" t="n"/>
-      <c r="AC27" s="10" t="n"/>
+      <c r="AB27" s="11" t="n"/>
+      <c r="AC27" s="17" t="inlineStr"/>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>管理支店一覧</t>
+          <t>編集時の選択中ID。現ページ範囲外ならレスポンス先頭に追加</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -2343,201 +2510,151 @@
       <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="11" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="31" t="n">
+    <row r="28" ht="19.5" customHeight="1"/>
+    <row r="29" ht="19.5" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="19.5" customHeight="1"/>
+    <row r="31" ht="19.5" customHeight="1">
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
+      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="10" t="n"/>
+      <c r="X31" s="11" t="n"/>
+      <c r="Y31" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="Z31" s="10" t="n"/>
+      <c r="AA31" s="10" t="n"/>
+      <c r="AB31" s="10" t="n"/>
+      <c r="AC31" s="10" t="n"/>
+      <c r="AD31" s="10" t="n"/>
+      <c r="AE31" s="11" t="n"/>
+      <c r="AF31" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG31" s="10" t="n"/>
+      <c r="AH31" s="10" t="n"/>
+      <c r="AI31" s="10" t="n"/>
+      <c r="AJ31" s="10" t="n"/>
+      <c r="AK31" s="11" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="11" t="n"/>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="17" t="inlineStr"/>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="11" t="n"/>
+      <c r="Y32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="10" t="n"/>
+      <c r="AC32" s="10" t="n"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="11" t="n"/>
+      <c r="AF32" s="19" t="inlineStr">
+        <is>
+          <t>管理支店一覧</t>
+        </is>
+      </c>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="37" t="n"/>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="C33" s="37" t="n"/>
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>kanri_shiten_id</t>
         </is>
       </c>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="10" t="n"/>
-      <c r="K28" s="10" t="n"/>
-      <c r="L28" s="11" t="n"/>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N28" s="10" t="n"/>
-      <c r="O28" s="10" t="n"/>
-      <c r="P28" s="11" t="n"/>
-      <c r="Q28" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R28" s="10" t="n"/>
-      <c r="S28" s="11" t="n"/>
-      <c r="T28" s="17" t="inlineStr"/>
-      <c r="U28" s="10" t="n"/>
-      <c r="V28" s="10" t="n"/>
-      <c r="W28" s="10" t="n"/>
-      <c r="X28" s="11" t="n"/>
-      <c r="Y28" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z28" s="10" t="n"/>
-      <c r="AA28" s="10" t="n"/>
-      <c r="AB28" s="10" t="n"/>
-      <c r="AC28" s="10" t="n"/>
-      <c r="AD28" s="10" t="n"/>
-      <c r="AE28" s="11" t="n"/>
-      <c r="AF28" s="19" t="inlineStr">
-        <is>
-          <t>管理支店ID</t>
-        </is>
-      </c>
-      <c r="AG28" s="10" t="n"/>
-      <c r="AH28" s="10" t="n"/>
-      <c r="AI28" s="10" t="n"/>
-      <c r="AJ28" s="10" t="n"/>
-      <c r="AK28" s="11" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" s="38" t="n"/>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>kanri_shiten_code</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="10" t="n"/>
-      <c r="K29" s="10" t="n"/>
-      <c r="L29" s="11" t="n"/>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N29" s="10" t="n"/>
-      <c r="O29" s="10" t="n"/>
-      <c r="P29" s="11" t="n"/>
-      <c r="Q29" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R29" s="10" t="n"/>
-      <c r="S29" s="11" t="n"/>
-      <c r="T29" s="17" t="inlineStr"/>
-      <c r="U29" s="10" t="n"/>
-      <c r="V29" s="10" t="n"/>
-      <c r="W29" s="10" t="n"/>
-      <c r="X29" s="11" t="n"/>
-      <c r="Y29" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z29" s="10" t="n"/>
-      <c r="AA29" s="10" t="n"/>
-      <c r="AB29" s="10" t="n"/>
-      <c r="AC29" s="10" t="n"/>
-      <c r="AD29" s="10" t="n"/>
-      <c r="AE29" s="11" t="n"/>
-      <c r="AF29" s="19" t="inlineStr">
-        <is>
-          <t>管理支店コード</t>
-        </is>
-      </c>
-      <c r="AG29" s="10" t="n"/>
-      <c r="AH29" s="10" t="n"/>
-      <c r="AI29" s="10" t="n"/>
-      <c r="AJ29" s="10" t="n"/>
-      <c r="AK29" s="11" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C30" s="39" t="n"/>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>kanri_shiten_name</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
-      <c r="J30" s="10" t="n"/>
-      <c r="K30" s="10" t="n"/>
-      <c r="L30" s="11" t="n"/>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N30" s="10" t="n"/>
-      <c r="O30" s="10" t="n"/>
-      <c r="P30" s="11" t="n"/>
-      <c r="Q30" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R30" s="10" t="n"/>
-      <c r="S30" s="11" t="n"/>
-      <c r="T30" s="17" t="inlineStr"/>
-      <c r="U30" s="10" t="n"/>
-      <c r="V30" s="10" t="n"/>
-      <c r="W30" s="10" t="n"/>
-      <c r="X30" s="11" t="n"/>
-      <c r="Y30" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z30" s="10" t="n"/>
-      <c r="AA30" s="10" t="n"/>
-      <c r="AB30" s="10" t="n"/>
-      <c r="AC30" s="10" t="n"/>
-      <c r="AD30" s="10" t="n"/>
-      <c r="AE30" s="11" t="n"/>
-      <c r="AF30" s="19" t="inlineStr">
-        <is>
-          <t>管理支店名称</t>
-        </is>
-      </c>
-      <c r="AG30" s="10" t="n"/>
-      <c r="AH30" s="10" t="n"/>
-      <c r="AI30" s="10" t="n"/>
-      <c r="AJ30" s="10" t="n"/>
-      <c r="AK30" s="11" t="n"/>
-    </row>
-    <row r="31" ht="19.5" customHeight="1"/>
-    <row r="32" ht="19.5" customHeight="1">
-      <c r="B32" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="C33" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/kanri-shiten/dropdown?ja_id=10</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="n"/>
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
@@ -2545,60 +2662,179 @@
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="10" t="n"/>
       <c r="K33" s="10" t="n"/>
-      <c r="L33" s="10" t="n"/>
-      <c r="M33" s="10" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
       <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="n"/>
-      <c r="P33" s="10" t="n"/>
-      <c r="Q33" s="10" t="n"/>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R33" s="10" t="n"/>
-      <c r="S33" s="10" t="n"/>
-      <c r="T33" s="10" t="n"/>
+      <c r="S33" s="11" t="n"/>
+      <c r="T33" s="17" t="inlineStr"/>
       <c r="U33" s="10" t="n"/>
       <c r="V33" s="10" t="n"/>
       <c r="W33" s="10" t="n"/>
-      <c r="X33" s="10" t="n"/>
-      <c r="Y33" s="10" t="n"/>
+      <c r="X33" s="11" t="n"/>
+      <c r="Y33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z33" s="10" t="n"/>
       <c r="AA33" s="10" t="n"/>
       <c r="AB33" s="10" t="n"/>
       <c r="AC33" s="10" t="n"/>
       <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="10" t="n"/>
-      <c r="AF33" s="10" t="n"/>
+      <c r="AE33" s="11" t="n"/>
+      <c r="AF33" s="19" t="inlineStr">
+        <is>
+          <t>管理支店ID</t>
+        </is>
+      </c>
       <c r="AG33" s="10" t="n"/>
       <c r="AH33" s="10" t="n"/>
       <c r="AI33" s="10" t="n"/>
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="11" t="n"/>
     </row>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="B35" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（成功）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="252" customHeight="1">
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "data": [
-    {
-      "kanri_shiten_id": 20,
-      "kanri_shiten_code": "113-5001-001",
-      "kanri_shiten_name": "JA東京中央 本店管理支店"
-    },
-    {
-      "kanri_shiten_id": 21,
-      "kanri_shiten_code": "113-5001-002",
-      "kanri_shiten_name": "JA東京中央 渋谷管理支店"
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="n"/>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="38" t="n"/>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>kanri_shiten_code</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="10" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="11" t="n"/>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="11" t="n"/>
+      <c r="T34" s="17" t="inlineStr"/>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n"/>
+      <c r="W34" s="10" t="n"/>
+      <c r="X34" s="11" t="n"/>
+      <c r="Y34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z34" s="10" t="n"/>
+      <c r="AA34" s="10" t="n"/>
+      <c r="AB34" s="10" t="n"/>
+      <c r="AC34" s="10" t="n"/>
+      <c r="AD34" s="10" t="n"/>
+      <c r="AE34" s="11" t="n"/>
+      <c r="AF34" s="19" t="inlineStr">
+        <is>
+          <t>管理支店コード</t>
+        </is>
+      </c>
+      <c r="AG34" s="10" t="n"/>
+      <c r="AH34" s="10" t="n"/>
+      <c r="AI34" s="10" t="n"/>
+      <c r="AJ34" s="10" t="n"/>
+      <c r="AK34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>kanri_shiten_name</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="11" t="n"/>
+      <c r="Q35" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="11" t="n"/>
+      <c r="T35" s="17" t="inlineStr"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="11" t="n"/>
+      <c r="Y35" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n"/>
+      <c r="AB35" s="10" t="n"/>
+      <c r="AC35" s="10" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="11" t="n"/>
+      <c r="AF35" s="19" t="inlineStr">
+        <is>
+          <t>管理支店名称</t>
+        </is>
+      </c>
+      <c r="AG35" s="10" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="10" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="B36" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>paper_flg</t>
+        </is>
+      </c>
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
@@ -2606,50 +2842,179 @@
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="10" t="n"/>
       <c r="K36" s="10" t="n"/>
-      <c r="L36" s="10" t="n"/>
-      <c r="M36" s="10" t="n"/>
+      <c r="L36" s="11" t="n"/>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
       <c r="N36" s="10" t="n"/>
       <c r="O36" s="10" t="n"/>
-      <c r="P36" s="10" t="n"/>
-      <c r="Q36" s="10" t="n"/>
+      <c r="P36" s="11" t="n"/>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R36" s="10" t="n"/>
-      <c r="S36" s="10" t="n"/>
-      <c r="T36" s="10" t="n"/>
+      <c r="S36" s="11" t="n"/>
+      <c r="T36" s="17" t="inlineStr"/>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
       <c r="W36" s="10" t="n"/>
-      <c r="X36" s="10" t="n"/>
-      <c r="Y36" s="10" t="n"/>
+      <c r="X36" s="11" t="n"/>
+      <c r="Y36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z36" s="10" t="n"/>
       <c r="AA36" s="10" t="n"/>
       <c r="AB36" s="10" t="n"/>
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
-      <c r="AE36" s="10" t="n"/>
-      <c r="AF36" s="10" t="n"/>
+      <c r="AE36" s="11" t="n"/>
+      <c r="AF36" s="19" t="inlineStr">
+        <is>
+          <t>紙版取扱フラグ（SCR-011 の購読種別による絞り込み用・顧客要件2026-07）</t>
+        </is>
+      </c>
       <c r="AG36" s="10" t="n"/>
       <c r="AH36" s="10" t="n"/>
       <c r="AI36" s="10" t="n"/>
       <c r="AJ36" s="10" t="n"/>
       <c r="AK36" s="11" t="n"/>
     </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="B38" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 401 Unauthorized）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="72" customHeight="1">
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください"
-}</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="n"/>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" s="39" t="n"/>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>denshi_flg</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="10" t="n"/>
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="11" t="n"/>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="11" t="n"/>
+      <c r="T37" s="17" t="inlineStr"/>
+      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="10" t="n"/>
+      <c r="W37" s="10" t="n"/>
+      <c r="X37" s="11" t="n"/>
+      <c r="Y37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z37" s="10" t="n"/>
+      <c r="AA37" s="10" t="n"/>
+      <c r="AB37" s="10" t="n"/>
+      <c r="AC37" s="10" t="n"/>
+      <c r="AD37" s="10" t="n"/>
+      <c r="AE37" s="11" t="n"/>
+      <c r="AF37" s="19" t="inlineStr">
+        <is>
+          <t>電子版取扱フラグ（同上）</t>
+        </is>
+      </c>
+      <c r="AG37" s="10" t="n"/>
+      <c r="AH37" s="10" t="n"/>
+      <c r="AI37" s="10" t="n"/>
+      <c r="AJ37" s="10" t="n"/>
+      <c r="AK37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="17" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="11" t="n"/>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="11" t="n"/>
+      <c r="T38" s="17" t="inlineStr"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="11" t="n"/>
+      <c r="Y38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="10" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="11" t="n"/>
+      <c r="AF38" s="19" t="inlineStr">
+        <is>
+          <t>ページングメタ</t>
+        </is>
+      </c>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="B39" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" s="37" t="n"/>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
@@ -2657,50 +3022,179 @@
       <c r="I39" s="10" t="n"/>
       <c r="J39" s="10" t="n"/>
       <c r="K39" s="10" t="n"/>
-      <c r="L39" s="10" t="n"/>
-      <c r="M39" s="10" t="n"/>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
       <c r="N39" s="10" t="n"/>
       <c r="O39" s="10" t="n"/>
-      <c r="P39" s="10" t="n"/>
-      <c r="Q39" s="10" t="n"/>
+      <c r="P39" s="11" t="n"/>
+      <c r="Q39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R39" s="10" t="n"/>
-      <c r="S39" s="10" t="n"/>
-      <c r="T39" s="10" t="n"/>
+      <c r="S39" s="11" t="n"/>
+      <c r="T39" s="17" t="inlineStr"/>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
       <c r="W39" s="10" t="n"/>
-      <c r="X39" s="10" t="n"/>
-      <c r="Y39" s="10" t="n"/>
+      <c r="X39" s="11" t="n"/>
+      <c r="Y39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z39" s="10" t="n"/>
       <c r="AA39" s="10" t="n"/>
       <c r="AB39" s="10" t="n"/>
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
-      <c r="AE39" s="10" t="n"/>
-      <c r="AF39" s="10" t="n"/>
+      <c r="AE39" s="11" t="n"/>
+      <c r="AF39" s="19" t="inlineStr">
+        <is>
+          <t>`page` 未指定時は全件、指定時は当該レスポンスの件数（`data.length`。DB全体の総件数ではない）</t>
+        </is>
+      </c>
       <c r="AG39" s="10" t="n"/>
       <c r="AH39" s="10" t="n"/>
       <c r="AI39" s="10" t="n"/>
       <c r="AJ39" s="10" t="n"/>
       <c r="AK39" s="11" t="n"/>
     </row>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="B41" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="72" customHeight="1">
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
-}</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="n"/>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="11" t="n"/>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="11" t="n"/>
+      <c r="T40" s="17" t="inlineStr"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="10" t="n"/>
+      <c r="X40" s="11" t="n"/>
+      <c r="Y40" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="10" t="n"/>
+      <c r="AB40" s="10" t="n"/>
+      <c r="AC40" s="10" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="19" t="inlineStr">
+        <is>
+          <t>現在のページ番号（`page` 未指定時は1固定）</t>
+        </is>
+      </c>
+      <c r="AG40" s="10" t="n"/>
+      <c r="AH40" s="10" t="n"/>
+      <c r="AI40" s="10" t="n"/>
+      <c r="AJ40" s="10" t="n"/>
+      <c r="AK40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="B41" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="11" t="n"/>
+      <c r="Q41" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="11" t="n"/>
+      <c r="T41" s="17" t="inlineStr"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="10" t="n"/>
+      <c r="W41" s="10" t="n"/>
+      <c r="X41" s="11" t="n"/>
+      <c r="Y41" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z41" s="10" t="n"/>
+      <c r="AA41" s="10" t="n"/>
+      <c r="AB41" s="10" t="n"/>
+      <c r="AC41" s="10" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="11" t="n"/>
+      <c r="AF41" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数（`per_page` 未指定時は `data.length`）</t>
+        </is>
+      </c>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="10" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41" s="10" t="n"/>
+      <c r="AK41" s="11" t="n"/>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="B42" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C42" s="39" t="n"/>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>has_more</t>
+        </is>
+      </c>
       <c r="E42" s="10" t="n"/>
       <c r="F42" s="10" t="n"/>
       <c r="G42" s="10" t="n"/>
@@ -2708,47 +3202,61 @@
       <c r="I42" s="10" t="n"/>
       <c r="J42" s="10" t="n"/>
       <c r="K42" s="10" t="n"/>
-      <c r="L42" s="10" t="n"/>
-      <c r="M42" s="10" t="n"/>
+      <c r="L42" s="11" t="n"/>
+      <c r="M42" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
       <c r="N42" s="10" t="n"/>
       <c r="O42" s="10" t="n"/>
-      <c r="P42" s="10" t="n"/>
-      <c r="Q42" s="10" t="n"/>
+      <c r="P42" s="11" t="n"/>
+      <c r="Q42" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R42" s="10" t="n"/>
-      <c r="S42" s="10" t="n"/>
-      <c r="T42" s="10" t="n"/>
+      <c r="S42" s="11" t="n"/>
+      <c r="T42" s="17" t="inlineStr"/>
       <c r="U42" s="10" t="n"/>
       <c r="V42" s="10" t="n"/>
       <c r="W42" s="10" t="n"/>
-      <c r="X42" s="10" t="n"/>
-      <c r="Y42" s="10" t="n"/>
+      <c r="X42" s="11" t="n"/>
+      <c r="Y42" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z42" s="10" t="n"/>
       <c r="AA42" s="10" t="n"/>
       <c r="AB42" s="10" t="n"/>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
-      <c r="AE42" s="10" t="n"/>
-      <c r="AF42" s="10" t="n"/>
+      <c r="AE42" s="11" t="n"/>
+      <c r="AF42" s="19" t="inlineStr">
+        <is>
+          <t>次ページが存在するか（`page` 未指定時は常にfalse）</t>
+        </is>
+      </c>
       <c r="AG42" s="10" t="n"/>
       <c r="AH42" s="10" t="n"/>
       <c r="AI42" s="10" t="n"/>
       <c r="AJ42" s="10" t="n"/>
       <c r="AK42" s="11" t="n"/>
     </row>
+    <row r="43" ht="19.5" customHeight="1"/>
     <row r="44" ht="19.5" customHeight="1">
       <c r="B44" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="72" customHeight="1">
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
       <c r="C45" s="19" t="inlineStr">
         <is>
-          <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
-}</t>
+          <t>GET /api/v1/kanri-shiten/dropdown?ja_id=10</t>
         </is>
       </c>
       <c r="D45" s="10" t="n"/>
@@ -2786,294 +3294,689 @@
       <c r="AJ45" s="10" t="n"/>
       <c r="AK45" s="11" t="n"/>
     </row>
-    <row r="47" ht="19.5" customHeight="1"/>
-    <row r="48" ht="19.5" customHeight="1">
-      <c r="A48" s="27" t="inlineStr">
+    <row r="47" ht="19.5" customHeight="1">
+      <c r="B47" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（成功）</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="409" customHeight="1">
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "data": [
+    {
+      "kanri_shiten_id": 20,
+      "kanri_shiten_code": "113-5001-001",
+      "kanri_shiten_name": "JA東京中央 本店管理支店",
+      "paper_flg": true,
+      "denshi_flg": true
+    },
+    {
+      "kanri_shiten_id": 21,
+      "kanri_shiten_code": "113-5001-002",
+      "kanri_shiten_name": "JA東京中央 渋谷管理支店",
+      "paper_flg": true,
+      "denshi_flg": false
+    }
+  ],
+  "meta": {
+    "total": 2,
+    "page": 1,
+    "per_page": 2,
+    "has_more": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="10" t="n"/>
+      <c r="K48" s="10" t="n"/>
+      <c r="L48" s="10" t="n"/>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="10" t="n"/>
+      <c r="O48" s="10" t="n"/>
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="10" t="n"/>
+      <c r="R48" s="10" t="n"/>
+      <c r="S48" s="10" t="n"/>
+      <c r="T48" s="10" t="n"/>
+      <c r="U48" s="10" t="n"/>
+      <c r="V48" s="10" t="n"/>
+      <c r="W48" s="10" t="n"/>
+      <c r="X48" s="10" t="n"/>
+      <c r="Y48" s="10" t="n"/>
+      <c r="Z48" s="10" t="n"/>
+      <c r="AA48" s="10" t="n"/>
+      <c r="AB48" s="10" t="n"/>
+      <c r="AC48" s="10" t="n"/>
+      <c r="AD48" s="10" t="n"/>
+      <c r="AE48" s="10" t="n"/>
+      <c r="AF48" s="10" t="n"/>
+      <c r="AG48" s="10" t="n"/>
+      <c r="AH48" s="10" t="n"/>
+      <c r="AI48" s="10" t="n"/>
+      <c r="AJ48" s="10" t="n"/>
+      <c r="AK48" s="11" t="n"/>
+    </row>
+    <row r="50" ht="19.5" customHeight="1">
+      <c r="B50" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 401 Unauthorized）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="72" customHeight="1">
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "UNAUTHORIZED",
+  "message": "セッションが切れました。再度ログインしてください"
+}</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="10" t="n"/>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="10" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="10" t="n"/>
+      <c r="Q51" s="10" t="n"/>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="10" t="n"/>
+      <c r="Y51" s="10" t="n"/>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+      <c r="AC51" s="10" t="n"/>
+      <c r="AD51" s="10" t="n"/>
+      <c r="AE51" s="10" t="n"/>
+      <c r="AF51" s="10" t="n"/>
+      <c r="AG51" s="10" t="n"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="10" t="n"/>
+      <c r="AJ51" s="10" t="n"/>
+      <c r="AK51" s="11" t="n"/>
+    </row>
+    <row r="53" ht="19.5" customHeight="1">
+      <c r="B53" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 403 Forbidden）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="72" customHeight="1">
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません"
+}</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="10" t="n"/>
+      <c r="AF54" s="10" t="n"/>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="11" t="n"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="B56" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="72" customHeight="1">
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+}</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="11" t="n"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1"/>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="B49" s="27" t="inlineStr">
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="C50" s="41" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="C62" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="D51" s="41" t="inlineStr">
+    <row r="63" ht="18" customHeight="1">
+      <c r="D63" s="41" t="inlineStr">
         <is>
           <t>ja_id：数値型チェック、必須チェック</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="C52" s="41" t="inlineStr">
+    <row r="64" ht="18" customHeight="1">
+      <c r="D64" s="41" t="inlineStr">
+        <is>
+          <t>q：文字列（任意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="D65" s="41" t="inlineStr">
+        <is>
+          <t>match_field：`both` / `name` のいずれか（任意、既定 `both`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="D66" s="41" t="inlineStr">
+        <is>
+          <t>page：1以上の整数（任意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="D67" s="41" t="inlineStr">
+        <is>
+          <t>per_page：1〜100の整数（任意、既定50。`page`指定時のみ有効）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="D68" s="41" t="inlineStr">
+        <is>
+          <t>include_id：1以上の整数（任意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="C69" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="D53" s="41" t="inlineStr">
+    <row r="70" ht="18" customHeight="1">
+      <c r="D70" s="41" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="B54" s="27" t="inlineStr">
+    <row r="71" ht="18" customHeight="1">
+      <c r="B71" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="C55" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="C56" s="41" t="inlineStr">
+    <row r="72" ht="18" customHeight="1">
+      <c r="C72" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="C73" s="41" t="inlineStr">
         <is>
           <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="C57" s="41" t="inlineStr">
+    <row r="74" ht="18" customHeight="1">
+      <c r="C74" s="41" t="inlineStr">
         <is>
           <t>権限チェック：認証済みユーザーであればアクセス可能。</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="D58" s="41" t="inlineStr">
+    <row r="75" ht="18" customHeight="1">
+      <c r="D75" s="41" t="inlineStr">
         <is>
           <t>※ 呼び出し元画面の権限に依存する。</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="C59" s="41" t="inlineStr">
+    <row r="76" ht="18" customHeight="1">
+      <c r="C76" s="41" t="inlineStr">
         <is>
           <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="B60" s="27" t="inlineStr">
+    <row r="77" ht="54" customHeight="1">
+      <c r="C77" s="41" t="inlineStr">
+        <is>
+          <t>DataScope 適用：非 NICHINO_ADMIN/STAFF は自組織配下（CHUOKAI/JA_HONTEN は自JA、JA_KANRI_SHITEN は自管理支店）の管理支店のみ取得可能（`applyBranchScope`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="27" t="inlineStr">
         <is>
           <t>4.3 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="90" customHeight="1">
-      <c r="C61" s="42" t="inlineStr">
-        <is>
-          <t>SELECT kanri_shiten_id, kanri_shiten_code, kanri_shiten_name
+    <row r="79" ht="18" customHeight="1">
+      <c r="C79" s="41" t="inlineStr">
+        <is>
+          <t>フィルタ適用順：</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>ソート：`kanri_shiten_code ASC` 固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="54" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
+        <is>
+          <t>ページング：`page` 未指定時は全件取得（`has_more=false`）。指定時は `LIMIT :per_page OFFSET (page-1)*per_page` し、`per_page+1`件取得して余剰有無で `has_more` を判定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="C82" s="41" t="inlineStr">
+        <is>
+          <t>`include_id` 指定時：ページ1の範囲に含まれていなければ、同一条件で該当行を SELECT して先頭に prepend。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="180" customHeight="1">
+      <c r="C83" s="42" t="inlineStr">
+        <is>
+          <t>SELECT kanri_shiten_id, kanri_shiten_code, kanri_shiten_name, paper_flg, denshi_flg
 FROM m_kanri_shiten
 WHERE ja_id = :ja_id
   AND deleted_at IS NULL
+  -- DataScope (applyBranchScope, auto-applied per session role)
+  AND (:q IS NULL OR
+       CASE WHEN :match_field = 'name' THEN kanri_shiten_name ILIKE :q_like
+            ELSE (kanri_shiten_code ILIKE :q_like OR kanri_shiten_name ILIKE :q_like)
+       END)
 ORDER BY kanri_shiten_code ASC</t>
         </is>
       </c>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="n"/>
-      <c r="L61" s="10" t="n"/>
-      <c r="M61" s="10" t="n"/>
-      <c r="N61" s="10" t="n"/>
-      <c r="O61" s="10" t="n"/>
-      <c r="P61" s="10" t="n"/>
-      <c r="Q61" s="10" t="n"/>
-      <c r="R61" s="10" t="n"/>
-      <c r="S61" s="10" t="n"/>
-      <c r="T61" s="10" t="n"/>
-      <c r="U61" s="10" t="n"/>
-      <c r="V61" s="10" t="n"/>
-      <c r="W61" s="10" t="n"/>
-      <c r="X61" s="10" t="n"/>
-      <c r="Y61" s="10" t="n"/>
-      <c r="Z61" s="10" t="n"/>
-      <c r="AA61" s="10" t="n"/>
-      <c r="AB61" s="10" t="n"/>
-      <c r="AC61" s="10" t="n"/>
-      <c r="AD61" s="10" t="n"/>
-      <c r="AE61" s="10" t="n"/>
-      <c r="AF61" s="10" t="n"/>
-      <c r="AG61" s="10" t="n"/>
-      <c r="AH61" s="10" t="n"/>
-      <c r="AI61" s="10" t="n"/>
-      <c r="AJ61" s="10" t="n"/>
-      <c r="AK61" s="11" t="n"/>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="B62" s="27" t="inlineStr">
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="10" t="n"/>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
+      <c r="T83" s="10" t="n"/>
+      <c r="U83" s="10" t="n"/>
+      <c r="V83" s="10" t="n"/>
+      <c r="W83" s="10" t="n"/>
+      <c r="X83" s="10" t="n"/>
+      <c r="Y83" s="10" t="n"/>
+      <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
+      <c r="AB83" s="10" t="n"/>
+      <c r="AC83" s="10" t="n"/>
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="10" t="n"/>
+      <c r="AF83" s="10" t="n"/>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="10" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="B84" s="27" t="inlineStr">
         <is>
           <t>4.4 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="C63" s="41" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
         <is>
           <t>取得結果を data 配列として返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1">
-      <c r="C64" s="41" t="inlineStr">
+    <row r="86" ht="18" customHeight="1">
+      <c r="C86" s="41" t="inlineStr">
         <is>
           <t>該当データが0件の場合：data は空配列 `[]` で返却。</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="B65" s="27" t="inlineStr">
+    <row r="87" ht="54" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>meta を付与する：`total`（`page`未指定時は全件数、指定時は`data.length`）、`page`（未指定時1）、`per_page`（未指定時`data.length`）、`has_more`。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="B88" s="27" t="inlineStr">
         <is>
           <t>4.5 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1">
-      <c r="C66" s="41" t="inlineStr">
+    <row r="89" ht="18" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="114">
+  <mergeCells count="203">
     <mergeCell ref="J11:AK11"/>
-    <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Y27:AE27"/>
     <mergeCell ref="C57:AK57"/>
-    <mergeCell ref="C66:AK66"/>
-    <mergeCell ref="M29:P29"/>
-    <mergeCell ref="D58:AK58"/>
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="Y36:AE36"/>
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="T33:X33"/>
+    <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="C77:AK77"/>
+    <mergeCell ref="C86:AK86"/>
+    <mergeCell ref="M23:P23"/>
     <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="D64:AK64"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D51:AK51"/>
     <mergeCell ref="C45:AK45"/>
+    <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="B49:AK49"/>
+    <mergeCell ref="Y24:AB24"/>
+    <mergeCell ref="D33:L33"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="D42:L42"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="B65:AK65"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="Y21:AB21"/>
     <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="M35:P35"/>
+    <mergeCell ref="C80:AK80"/>
+    <mergeCell ref="AF36:AK36"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="D35:L35"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="B9:I9"/>
+    <mergeCell ref="T31:X31"/>
+    <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="C51:AK51"/>
+    <mergeCell ref="D34:L34"/>
     <mergeCell ref="C22:L22"/>
-    <mergeCell ref="Y26:AE26"/>
-    <mergeCell ref="T28:X28"/>
-    <mergeCell ref="T30:X30"/>
-    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="Q42:S42"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="C48:AK48"/>
+    <mergeCell ref="T37:X37"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="D75:AK75"/>
+    <mergeCell ref="M33:P33"/>
+    <mergeCell ref="B47:I47"/>
+    <mergeCell ref="T38:X38"/>
+    <mergeCell ref="C32:L32"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="C38:L38"/>
     <mergeCell ref="N14:AK14"/>
+    <mergeCell ref="Y33:AE33"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="C33:AK33"/>
+    <mergeCell ref="B61:AK61"/>
     <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="C42:AK42"/>
+    <mergeCell ref="D37:L37"/>
+    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="AF41:AK41"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="AF35:AK35"/>
+    <mergeCell ref="D39:L39"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="AC21:AE21"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="C55:AK55"/>
+    <mergeCell ref="AF38:AK38"/>
+    <mergeCell ref="D63:AK63"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="T40:X40"/>
     <mergeCell ref="C26:L26"/>
-    <mergeCell ref="Y30:AE30"/>
+    <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="Y29:AE29"/>
-    <mergeCell ref="C59:AK59"/>
+    <mergeCell ref="D65:AK65"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="C52:AK52"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="AF33:AK33"/>
+    <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="M21:P21"/>
-    <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="C39:AK39"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B35:I35"/>
-    <mergeCell ref="Y28:AE28"/>
+    <mergeCell ref="Y31:AE31"/>
+    <mergeCell ref="B50:I50"/>
+    <mergeCell ref="D66:AK66"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="D53:AK53"/>
+    <mergeCell ref="C72:AK72"/>
+    <mergeCell ref="B71:AK71"/>
+    <mergeCell ref="M36:P36"/>
+    <mergeCell ref="Y37:AE37"/>
+    <mergeCell ref="T39:X39"/>
+    <mergeCell ref="C81:AK81"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="T32:X32"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="AF30:AK30"/>
-    <mergeCell ref="B60:AK60"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="T42:X42"/>
+    <mergeCell ref="C62:AK62"/>
+    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="C82:AK82"/>
+    <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="A29:AK29"/>
     <mergeCell ref="B11:I11"/>
+    <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
-    <mergeCell ref="D28:L28"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C64:AK64"/>
-    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="C89:AK89"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="M34:P34"/>
+    <mergeCell ref="C79:AK79"/>
+    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="D30:L30"/>
-    <mergeCell ref="C63:AK63"/>
+    <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="C54:AK54"/>
+    <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="T21:X21"/>
-    <mergeCell ref="C50:AK50"/>
+    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="B84:AK84"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="A24:AK24"/>
-    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="C39:C42"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="C56:AK56"/>
+    <mergeCell ref="A60:AK60"/>
+    <mergeCell ref="T41:X41"/>
+    <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="T23:X23"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="C36:AK36"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="M40:P40"/>
+    <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="B54:AK54"/>
+    <mergeCell ref="T36:X36"/>
     <mergeCell ref="B14:I17"/>
-    <mergeCell ref="B32:I32"/>
     <mergeCell ref="C27:L27"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="M26:P26"/>
+    <mergeCell ref="M41:P41"/>
     <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="D41:L41"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="C69:AK69"/>
+    <mergeCell ref="M38:P38"/>
+    <mergeCell ref="C83:AK83"/>
+    <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="Y23:AB23"/>
+    <mergeCell ref="Y32:AE32"/>
+    <mergeCell ref="D68:AK68"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="B88:AK88"/>
+    <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="A19:AK19"/>
+    <mergeCell ref="D67:AK67"/>
+    <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="A48:AK48"/>
     <mergeCell ref="B44:I44"/>
-    <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="C33:C37"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
-    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="C76:AK76"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="C21:L21"/>
-    <mergeCell ref="B62:AK62"/>
-    <mergeCell ref="M28:P28"/>
-    <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="Y34:AE34"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="D70:AK70"/>
+    <mergeCell ref="M42:P42"/>
+    <mergeCell ref="M37:P37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3085,7 +3988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3245,22 +4148,154 @@
       <c r="AF2" s="10" t="n"/>
       <c r="AG2" s="11" t="n"/>
     </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/14</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="11" t="n"/>
+      <c r="R3" s="19" t="inlineStr">
+        <is>
+          <t>検索条件に shiten_id、レスポンス一覧に shiten_id / shiten_name を追加（顧客要件2026-07）</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="11" t="n"/>
+      <c r="AB3" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>実装コードとの差異を修正：検索条件に todofuken_code を追加、sort_by 許可リスト・レスポンス項目（email/sub_email_1-3/account_lock_flg）・DataScope 記述・削除時のCONFLICTメッセージ・before_value例を実装に合わせて修正。共用API（ACSMS-API-COMMON-003/004）に match_field・scope 等の未記載パラメータおよびCOMMON-004のmetaオブジェクトを追加、COMMON-003の権限チェック記述（`@Permissions`なし）を実装に合わせて修正</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="11" t="n"/>
+      <c r="AB4" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="H1:J1"/>
+  <mergeCells count="28">
     <mergeCell ref="R1:V1"/>
-    <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="W1:AA1"/>
-    <mergeCell ref="R2:V2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="R4:V4"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="W4:AA4"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="W3:AA3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3433,7 +4468,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3441,7 +4476,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -3859,7 +4894,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3867,7 +4902,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -4427,7 +5462,7 @@
       <c r="U14" s="11" t="n"/>
       <c r="V14" s="19" t="inlineStr">
         <is>
-          <t>このレコードは現在使用中のため、削除できません。</t>
+          <t>関連データが存在するため処理を実行できません。</t>
         </is>
       </c>
       <c r="W14" s="10" t="n"/>
@@ -4674,7 +5709,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4682,7 +5717,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -4990,7 +6025,7 @@
       <c r="R9" s="11" t="n"/>
       <c r="S9" s="19" t="inlineStr">
         <is>
-          <t>JAプルダウンリストを取得する（都道府県・管理者区分によるカスケード絞込み。共用API：アカウント検索・登録等で使用）</t>
+          <t>JAプルダウンリストを取得する（共用API）。2つのユースケースを1つのエンドポイントで提供：（A）ページング+フリーテキスト検索（SCR-009 等のフォーム用）、（B）都道府県・管理者区分によるカスケード絞込み（SCR-024 アカウント検索／SCR-025 登録用）。両方のレスポンス形状は同一（`{data, meta}`）。</t>
         </is>
       </c>
       <c r="T9" s="10" t="n"/>
@@ -5137,7 +6172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK112"/>
+  <dimension ref="A1:AK126"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -5298,7 +6333,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -5306,7 +6341,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -5652,7 +6687,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -6054,11 +7089,11 @@
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="B24" s="31" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="D24" s="10" t="n"/>
@@ -6072,7 +7107,7 @@
       <c r="L24" s="11" t="n"/>
       <c r="M24" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N24" s="10" t="n"/>
@@ -6098,12 +7133,14 @@
       <c r="Z24" s="10" t="n"/>
       <c r="AA24" s="10" t="n"/>
       <c r="AB24" s="11" t="n"/>
-      <c r="AC24" s="17" t="inlineStr"/>
+      <c r="AC24" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="AD24" s="10" t="n"/>
       <c r="AE24" s="11" t="n"/>
       <c r="AF24" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>都道府県コード（完全一致）</t>
         </is>
       </c>
       <c r="AG24" s="10" t="n"/>
@@ -6114,11 +7151,11 @@
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="B25" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_id</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="D25" s="10" t="n"/>
@@ -6163,7 +7200,7 @@
       <c r="AE25" s="11" t="n"/>
       <c r="AF25" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG25" s="10" t="n"/>
@@ -6174,11 +7211,11 @@
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="B26" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="D26" s="10" t="n"/>
@@ -6223,7 +7260,7 @@
       <c r="AE26" s="11" t="n"/>
       <c r="AF26" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（デフォルト: 1）</t>
+          <t>管理支店ID</t>
         </is>
       </c>
       <c r="AG26" s="10" t="n"/>
@@ -6234,11 +7271,11 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="B27" s="31" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>shiten_id</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -6283,7 +7320,7 @@
       <c r="AE27" s="11" t="n"/>
       <c r="AF27" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数（デフォルト: 20、最大: 100）</t>
+          <t>所属支店ID（顧客要件2026-07）</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -6294,11 +7331,11 @@
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>page</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -6312,7 +7349,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -6343,7 +7380,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>ソート項目（デフォルト: created_at）</t>
+          <t>ページ番号（デフォルト: 1）</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -6354,11 +7391,11 @@
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -6372,7 +7409,7 @@
       <c r="L29" s="11" t="n"/>
       <c r="M29" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N29" s="10" t="n"/>
@@ -6403,7 +7440,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>ソート順（asc / desc、デフォルト: desc）</t>
+          <t>1ページあたりの件数（デフォルト: 20、最大: 100）</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -6412,151 +7449,147 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="19.5" customHeight="1"/>
-    <row r="31" ht="19.5" customHeight="1">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>3.レスポンスデータ</t>
-        </is>
-      </c>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>sort_by</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="11" t="n"/>
+      <c r="Q30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="11" t="n"/>
+      <c r="T30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U30" s="10" t="n"/>
+      <c r="V30" s="10" t="n"/>
+      <c r="W30" s="10" t="n"/>
+      <c r="X30" s="11" t="n"/>
+      <c r="Y30" s="17" t="inlineStr"/>
+      <c r="Z30" s="10" t="n"/>
+      <c r="AA30" s="10" t="n"/>
+      <c r="AB30" s="11" t="n"/>
+      <c r="AC30" s="17" t="inlineStr"/>
+      <c r="AD30" s="10" t="n"/>
+      <c r="AE30" s="11" t="n"/>
+      <c r="AF30" s="19" t="inlineStr">
+        <is>
+          <t>ソート項目（デフォルト: created_at）</t>
+        </is>
+      </c>
+      <c r="AG30" s="10" t="n"/>
+      <c r="AH30" s="10" t="n"/>
+      <c r="AI30" s="10" t="n"/>
+      <c r="AJ30" s="10" t="n"/>
+      <c r="AK30" s="11" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="B31" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="10" t="n"/>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="10" t="n"/>
+      <c r="X31" s="11" t="n"/>
+      <c r="Y31" s="17" t="inlineStr"/>
+      <c r="Z31" s="10" t="n"/>
+      <c r="AA31" s="10" t="n"/>
+      <c r="AB31" s="11" t="n"/>
+      <c r="AC31" s="17" t="inlineStr"/>
+      <c r="AD31" s="10" t="n"/>
+      <c r="AE31" s="11" t="n"/>
+      <c r="AF31" s="19" t="inlineStr">
+        <is>
+          <t>ソート順（asc / desc、デフォルト: desc）</t>
+        </is>
+      </c>
+      <c r="AG31" s="10" t="n"/>
+      <c r="AH31" s="10" t="n"/>
+      <c r="AI31" s="10" t="n"/>
+      <c r="AJ31" s="10" t="n"/>
+      <c r="AK31" s="11" t="n"/>
     </row>
     <row r="32" ht="19.5" customHeight="1"/>
     <row r="33" ht="19.5" customHeight="1">
-      <c r="B33" s="30" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19.5" customHeight="1"/>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
         </is>
       </c>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N33" s="10" t="n"/>
-      <c r="O33" s="10" t="n"/>
-      <c r="P33" s="11" t="n"/>
-      <c r="Q33" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R33" s="10" t="n"/>
-      <c r="S33" s="11" t="n"/>
-      <c r="T33" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U33" s="10" t="n"/>
-      <c r="V33" s="10" t="n"/>
-      <c r="W33" s="10" t="n"/>
-      <c r="X33" s="11" t="n"/>
-      <c r="Y33" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z33" s="10" t="n"/>
-      <c r="AA33" s="10" t="n"/>
-      <c r="AB33" s="10" t="n"/>
-      <c r="AC33" s="10" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="11" t="n"/>
-      <c r="AF33" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG33" s="10" t="n"/>
-      <c r="AH33" s="10" t="n"/>
-      <c r="AI33" s="10" t="n"/>
-      <c r="AJ33" s="10" t="n"/>
-      <c r="AK33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="B34" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="10" t="n"/>
-      <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="11" t="n"/>
-      <c r="M34" s="17" t="inlineStr">
-        <is>
-          <t>Array</t>
-        </is>
-      </c>
-      <c r="N34" s="10" t="n"/>
-      <c r="O34" s="10" t="n"/>
-      <c r="P34" s="11" t="n"/>
-      <c r="Q34" s="17" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="R34" s="10" t="n"/>
-      <c r="S34" s="11" t="n"/>
-      <c r="T34" s="17" t="inlineStr"/>
-      <c r="U34" s="10" t="n"/>
-      <c r="V34" s="10" t="n"/>
-      <c r="W34" s="10" t="n"/>
-      <c r="X34" s="11" t="n"/>
-      <c r="Y34" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z34" s="10" t="n"/>
-      <c r="AA34" s="10" t="n"/>
-      <c r="AB34" s="10" t="n"/>
-      <c r="AC34" s="10" t="n"/>
-      <c r="AD34" s="10" t="n"/>
-      <c r="AE34" s="11" t="n"/>
-      <c r="AF34" s="19" t="inlineStr">
-        <is>
-          <t>アカウント一覧</t>
-        </is>
-      </c>
-      <c r="AG34" s="10" t="n"/>
-      <c r="AH34" s="10" t="n"/>
-      <c r="AI34" s="10" t="n"/>
-      <c r="AJ34" s="10" t="n"/>
-      <c r="AK34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="B35" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" s="37" t="n"/>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>account_id</t>
-        </is>
-      </c>
+      <c r="D35" s="10" t="n"/>
       <c r="E35" s="10" t="n"/>
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
@@ -6565,29 +7598,33 @@
       <c r="J35" s="10" t="n"/>
       <c r="K35" s="10" t="n"/>
       <c r="L35" s="11" t="n"/>
-      <c r="M35" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N35" s="10" t="n"/>
       <c r="O35" s="10" t="n"/>
       <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q35" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R35" s="10" t="n"/>
       <c r="S35" s="11" t="n"/>
-      <c r="T35" s="17" t="inlineStr"/>
+      <c r="T35" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U35" s="10" t="n"/>
       <c r="V35" s="10" t="n"/>
       <c r="W35" s="10" t="n"/>
       <c r="X35" s="11" t="n"/>
-      <c r="Y35" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y35" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z35" s="10" t="n"/>
@@ -6596,9 +7633,9 @@
       <c r="AC35" s="10" t="n"/>
       <c r="AD35" s="10" t="n"/>
       <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="19" t="inlineStr">
-        <is>
-          <t>アカウントID</t>
+      <c r="AF35" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG35" s="10" t="n"/>
@@ -6609,14 +7646,14 @@
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>login_id</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="n"/>
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
@@ -6627,7 +7664,7 @@
       <c r="L36" s="11" t="n"/>
       <c r="M36" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N36" s="10" t="n"/>
@@ -6635,7 +7672,7 @@
       <c r="P36" s="11" t="n"/>
       <c r="Q36" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>○</t>
         </is>
       </c>
       <c r="R36" s="10" t="n"/>
@@ -6658,7 +7695,7 @@
       <c r="AE36" s="11" t="n"/>
       <c r="AF36" s="19" t="inlineStr">
         <is>
-          <t>ログインID</t>
+          <t>アカウント一覧</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -6669,12 +7706,12 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C37" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C37" s="37" t="n"/>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>account_name</t>
+          <t>account_id</t>
         </is>
       </c>
       <c r="E37" s="10" t="n"/>
@@ -6687,7 +7724,7 @@
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N37" s="10" t="n"/>
@@ -6718,7 +7755,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>アカウント名</t>
+          <t>アカウントID</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -6729,12 +7766,12 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>login_id</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -6747,7 +7784,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -6778,7 +7815,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>管理者区分ID</t>
+          <t>ログインID</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -6789,12 +7826,12 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>role_name</t>
+          <t>account_name</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -6838,7 +7875,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>管理者区分名称</t>
+          <t>アカウント名</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -6849,12 +7886,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>todofuken_code</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -6867,7 +7904,7 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N40" s="10" t="n"/>
@@ -6887,7 +7924,7 @@
       <c r="X40" s="11" t="n"/>
       <c r="Y40" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z40" s="10" t="n"/>
@@ -6898,7 +7935,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード</t>
+          <t>管理者区分ID</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -6909,12 +7946,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>todofuken_name</t>
+          <t>role_name</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -6947,7 +7984,7 @@
       <c r="X41" s="11" t="n"/>
       <c r="Y41" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z41" s="10" t="n"/>
@@ -6958,7 +7995,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>都道府県名</t>
+          <t>管理者区分名称</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -6969,12 +8006,12 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -6987,7 +8024,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N42" s="10" t="n"/>
@@ -7018,7 +8055,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>都道府県コード</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -7029,12 +8066,12 @@
     </row>
     <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>ja_name</t>
+          <t>todofuken_name</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -7078,7 +8115,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>JA名称</t>
+          <t>都道府県名</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -7089,12 +8126,12 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_id</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -7138,7 +8175,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>管理支店ID</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -7149,12 +8186,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>kanri_shiten_name</t>
+          <t>ja_name</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -7198,7 +8235,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>管理支店名称</t>
+          <t>JA名称</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -7209,12 +8246,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>paper_flg</t>
+          <t>kanri_shiten_id</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -7227,7 +8264,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -7247,7 +8284,7 @@
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z46" s="10" t="n"/>
@@ -7258,7 +8295,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>紙版取扱フラグ</t>
+          <t>管理支店ID</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -7269,12 +8306,12 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>denshi_flg</t>
+          <t>kanri_shiten_name</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -7287,7 +8324,7 @@
       <c r="L47" s="11" t="n"/>
       <c r="M47" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N47" s="10" t="n"/>
@@ -7307,7 +8344,7 @@
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z47" s="10" t="n"/>
@@ -7318,7 +8355,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>電子版取扱フラグ</t>
+          <t>管理支店名称</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -7329,12 +8366,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>15</v>
+        <v>12.1</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>shiten_id</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -7347,7 +8384,7 @@
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N48" s="10" t="n"/>
@@ -7360,18 +8397,14 @@
       </c>
       <c r="R48" s="10" t="n"/>
       <c r="S48" s="11" t="n"/>
-      <c r="T48" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T48" s="17" t="inlineStr"/>
       <c r="U48" s="10" t="n"/>
       <c r="V48" s="10" t="n"/>
       <c r="W48" s="10" t="n"/>
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z48" s="10" t="n"/>
@@ -7382,7 +8415,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>所属支店ID（顧客要件2026-07）</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -7393,12 +8426,12 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>16</v>
-      </c>
-      <c r="C49" s="39" t="n"/>
+        <v>12.2</v>
+      </c>
+      <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>shiten_name</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -7424,11 +8457,7 @@
       </c>
       <c r="R49" s="10" t="n"/>
       <c r="S49" s="11" t="n"/>
-      <c r="T49" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T49" s="17" t="inlineStr"/>
       <c r="U49" s="10" t="n"/>
       <c r="V49" s="10" t="n"/>
       <c r="W49" s="10" t="n"/>
@@ -7446,7 +8475,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>所属支店名称</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -7457,14 +8486,14 @@
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
       <c r="E50" s="10" t="n"/>
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
@@ -7475,7 +8504,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -7506,7 +8535,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>メールアドレス（NOT NULL列、未設定時は空文字）</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -7517,12 +8546,12 @@
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="C51" s="37" t="n"/>
+        <v>13.1</v>
+      </c>
+      <c r="C51" s="38" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>sub_email_1</t>
         </is>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -7535,7 +8564,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N51" s="10" t="n"/>
@@ -7566,7 +8595,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>サブメールアドレス1（NOT NULL列、未設定時は空文字）</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -7577,12 +8606,12 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>19</v>
+        <v>13.2</v>
       </c>
       <c r="C52" s="38" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>sub_email_2</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -7595,7 +8624,7 @@
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N52" s="10" t="n"/>
@@ -7626,7 +8655,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>現在ページ</t>
+          <t>サブメールアドレス2（NOT NULL列、未設定時は空文字）</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -7637,12 +8666,12 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>sub_email_3</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -7655,7 +8684,7 @@
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N53" s="10" t="n"/>
@@ -7686,7 +8715,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数</t>
+          <t>サブメールアドレス3（NOT NULL列、未設定時は空文字）</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -7697,12 +8726,12 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>21</v>
-      </c>
-      <c r="C54" s="39" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="C54" s="38" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>total_pages</t>
+          <t>paper_flg</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
@@ -7715,7 +8744,7 @@
       <c r="L54" s="11" t="n"/>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N54" s="10" t="n"/>
@@ -7746,7 +8775,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>紙版取扱フラグ</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -7755,21 +8784,136 @@
       <c r="AJ54" s="10" t="n"/>
       <c r="AK54" s="11" t="n"/>
     </row>
-    <row r="55" ht="19.5" customHeight="1"/>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="B56" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="C55" s="38" t="n"/>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>denshi_flg</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="10" t="n"/>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="11" t="n"/>
+      <c r="M55" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="n"/>
+      <c r="P55" s="11" t="n"/>
+      <c r="Q55" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="11" t="n"/>
+      <c r="T55" s="17" t="inlineStr"/>
+      <c r="U55" s="10" t="n"/>
+      <c r="V55" s="10" t="n"/>
+      <c r="W55" s="10" t="n"/>
+      <c r="X55" s="11" t="n"/>
+      <c r="Y55" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z55" s="10" t="n"/>
+      <c r="AA55" s="10" t="n"/>
+      <c r="AB55" s="10" t="n"/>
+      <c r="AC55" s="10" t="n"/>
+      <c r="AD55" s="10" t="n"/>
+      <c r="AE55" s="11" t="n"/>
+      <c r="AF55" s="19" t="inlineStr">
+        <is>
+          <t>電子版取扱フラグ</t>
+        </is>
+      </c>
+      <c r="AG55" s="10" t="n"/>
+      <c r="AH55" s="10" t="n"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
+      <c r="AK55" s="11" t="n"/>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="B56" s="31" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>account_lock_flg</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="10" t="n"/>
+      <c r="J56" s="10" t="n"/>
+      <c r="K56" s="10" t="n"/>
+      <c r="L56" s="11" t="n"/>
+      <c r="M56" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="11" t="n"/>
+      <c r="Q56" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="11" t="n"/>
+      <c r="T56" s="17" t="inlineStr"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
+      <c r="W56" s="10" t="n"/>
+      <c r="X56" s="11" t="n"/>
+      <c r="Y56" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z56" s="10" t="n"/>
+      <c r="AA56" s="10" t="n"/>
+      <c r="AB56" s="10" t="n"/>
+      <c r="AC56" s="10" t="n"/>
+      <c r="AD56" s="10" t="n"/>
+      <c r="AE56" s="11" t="n"/>
+      <c r="AF56" s="19" t="inlineStr">
+        <is>
+          <t>アカウントロックフラグ（ログイン失敗回数が閾値到達時true。ACSMS-SCR-025編集画面で管理者が解除可）</t>
+        </is>
+      </c>
+      <c r="AG56" s="10" t="n"/>
+      <c r="AH56" s="10" t="n"/>
+      <c r="AI56" s="10" t="n"/>
+      <c r="AJ56" s="10" t="n"/>
+      <c r="AK56" s="11" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1">
-      <c r="C57" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/accounts?login_id=admin&amp;role_id=1&amp;page=1&amp;per_page=20&amp;sort_by=created_at&amp;sort_order=desc</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="n"/>
+      <c r="B57" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C57" s="38" t="n"/>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
       <c r="E57" s="10" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
@@ -7777,90 +8921,187 @@
       <c r="I57" s="10" t="n"/>
       <c r="J57" s="10" t="n"/>
       <c r="K57" s="10" t="n"/>
-      <c r="L57" s="10" t="n"/>
-      <c r="M57" s="10" t="n"/>
+      <c r="L57" s="11" t="n"/>
+      <c r="M57" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
       <c r="N57" s="10" t="n"/>
       <c r="O57" s="10" t="n"/>
-      <c r="P57" s="10" t="n"/>
-      <c r="Q57" s="10" t="n"/>
+      <c r="P57" s="11" t="n"/>
+      <c r="Q57" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R57" s="10" t="n"/>
-      <c r="S57" s="10" t="n"/>
-      <c r="T57" s="10" t="n"/>
+      <c r="S57" s="11" t="n"/>
+      <c r="T57" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U57" s="10" t="n"/>
       <c r="V57" s="10" t="n"/>
       <c r="W57" s="10" t="n"/>
-      <c r="X57" s="10" t="n"/>
-      <c r="Y57" s="10" t="n"/>
+      <c r="X57" s="11" t="n"/>
+      <c r="Y57" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z57" s="10" t="n"/>
       <c r="AA57" s="10" t="n"/>
       <c r="AB57" s="10" t="n"/>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
-      <c r="AE57" s="10" t="n"/>
-      <c r="AF57" s="10" t="n"/>
+      <c r="AE57" s="11" t="n"/>
+      <c r="AF57" s="19" t="inlineStr">
+        <is>
+          <t>作成日時</t>
+        </is>
+      </c>
       <c r="AG57" s="10" t="n"/>
       <c r="AH57" s="10" t="n"/>
       <c r="AI57" s="10" t="n"/>
       <c r="AJ57" s="10" t="n"/>
       <c r="AK57" s="11" t="n"/>
     </row>
-    <row r="59" ht="19.5" customHeight="1">
-      <c r="B59" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（成功）</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="409" customHeight="1">
-      <c r="C60" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "data": [
-    {
-      "account_id": 1,
-      "login_id": "admin001",
-      "account_name": "管理者 太郎",
-      "role_id": 1,
-      "role_name": "日農（管理者）",
-      "todofuken_code": null,
-      "todofuken_name": null,
-      "ja_id": null,
-      "ja_name": null,
-      "kanri_shiten_id": null,
-      "kanri_shiten_name": null,
-      "paper_flg": true,
-      "denshi_flg": false,
-      "created_at": "2026-01-15T10:00:00Z",
-      "updated_at": "2026-03-10T14:30:00Z"
-    },
-    {
-      "account_id": 2,
-      "login_id": "ja_honten001",
-      "account_name": "JA本店 花子",
-      "role_id": 4,
-      "role_name": "JA本店",
-      "todofuken_code": "13",
-      "todofuken_name": "東京都",
-      "ja_id": 10,
-      "ja_name": "JA東京中央",
-      "kanri_shiten_id": null,
-      "kanri_shiten_name": null,
-      "paper_flg": true,
-      "denshi_flg": true,
-      "created_at": "2026-02-01T09:00:00Z",
-      "updated_at": "2026-03-15T11:00:00Z"
-    }
-  ],
-  "meta": {
-    "total": 50,
-    "page": 1,
-    "per_page": 20,
-    "total_pages": 3
-  }
-}</t>
-        </is>
-      </c>
-      <c r="D60" s="10" t="n"/>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="C58" s="39" t="n"/>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="10" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="11" t="n"/>
+      <c r="M58" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N58" s="10" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="11" t="n"/>
+      <c r="Q58" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R58" s="10" t="n"/>
+      <c r="S58" s="11" t="n"/>
+      <c r="T58" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
+      <c r="U58" s="10" t="n"/>
+      <c r="V58" s="10" t="n"/>
+      <c r="W58" s="10" t="n"/>
+      <c r="X58" s="11" t="n"/>
+      <c r="Y58" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="Z58" s="10" t="n"/>
+      <c r="AA58" s="10" t="n"/>
+      <c r="AB58" s="10" t="n"/>
+      <c r="AC58" s="10" t="n"/>
+      <c r="AD58" s="10" t="n"/>
+      <c r="AE58" s="11" t="n"/>
+      <c r="AF58" s="19" t="inlineStr">
+        <is>
+          <t>更新日時</t>
+        </is>
+      </c>
+      <c r="AG58" s="10" t="n"/>
+      <c r="AH58" s="10" t="n"/>
+      <c r="AI58" s="10" t="n"/>
+      <c r="AJ58" s="10" t="n"/>
+      <c r="AK58" s="11" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="31" t="n">
+        <v>18</v>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="10" t="n"/>
+      <c r="J59" s="10" t="n"/>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="11" t="n"/>
+      <c r="M59" s="17" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="11" t="n"/>
+      <c r="T59" s="17" t="inlineStr"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="10" t="n"/>
+      <c r="X59" s="11" t="n"/>
+      <c r="Y59" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="10" t="n"/>
+      <c r="AE59" s="11" t="n"/>
+      <c r="AF59" s="19" t="inlineStr">
+        <is>
+          <t>ページネーション情報</t>
+        </is>
+      </c>
+      <c r="AG59" s="10" t="n"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="10" t="n"/>
+      <c r="AJ59" s="10" t="n"/>
+      <c r="AK59" s="11" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="C60" s="37" t="n"/>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
       <c r="E60" s="10" t="n"/>
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="10" t="n"/>
@@ -7868,50 +9109,179 @@
       <c r="I60" s="10" t="n"/>
       <c r="J60" s="10" t="n"/>
       <c r="K60" s="10" t="n"/>
-      <c r="L60" s="10" t="n"/>
-      <c r="M60" s="10" t="n"/>
+      <c r="L60" s="11" t="n"/>
+      <c r="M60" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
       <c r="N60" s="10" t="n"/>
       <c r="O60" s="10" t="n"/>
-      <c r="P60" s="10" t="n"/>
-      <c r="Q60" s="10" t="n"/>
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R60" s="10" t="n"/>
-      <c r="S60" s="10" t="n"/>
-      <c r="T60" s="10" t="n"/>
+      <c r="S60" s="11" t="n"/>
+      <c r="T60" s="17" t="inlineStr"/>
       <c r="U60" s="10" t="n"/>
       <c r="V60" s="10" t="n"/>
       <c r="W60" s="10" t="n"/>
-      <c r="X60" s="10" t="n"/>
-      <c r="Y60" s="10" t="n"/>
+      <c r="X60" s="11" t="n"/>
+      <c r="Y60" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z60" s="10" t="n"/>
       <c r="AA60" s="10" t="n"/>
       <c r="AB60" s="10" t="n"/>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
-      <c r="AE60" s="10" t="n"/>
-      <c r="AF60" s="10" t="n"/>
+      <c r="AE60" s="11" t="n"/>
+      <c r="AF60" s="19" t="inlineStr">
+        <is>
+          <t>総件数</t>
+        </is>
+      </c>
       <c r="AG60" s="10" t="n"/>
       <c r="AH60" s="10" t="n"/>
       <c r="AI60" s="10" t="n"/>
       <c r="AJ60" s="10" t="n"/>
       <c r="AK60" s="11" t="n"/>
     </row>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="B62" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 401 Unauthorized）</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="72" customHeight="1">
-      <c r="C63" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください"
-}</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="n"/>
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="C61" s="38" t="n"/>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="10" t="n"/>
+      <c r="J61" s="10" t="n"/>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="11" t="n"/>
+      <c r="M61" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="11" t="n"/>
+      <c r="T61" s="17" t="inlineStr"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="10" t="n"/>
+      <c r="X61" s="11" t="n"/>
+      <c r="Y61" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="10" t="n"/>
+      <c r="AE61" s="11" t="n"/>
+      <c r="AF61" s="19" t="inlineStr">
+        <is>
+          <t>現在ページ</t>
+        </is>
+      </c>
+      <c r="AG61" s="10" t="n"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="10" t="n"/>
+      <c r="AJ61" s="10" t="n"/>
+      <c r="AK61" s="11" t="n"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="31" t="n">
+        <v>21</v>
+      </c>
+      <c r="C62" s="38" t="n"/>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="10" t="n"/>
+      <c r="J62" s="10" t="n"/>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="11" t="n"/>
+      <c r="M62" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="11" t="n"/>
+      <c r="Q62" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="11" t="n"/>
+      <c r="T62" s="17" t="inlineStr"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="10" t="n"/>
+      <c r="X62" s="11" t="n"/>
+      <c r="Y62" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="10" t="n"/>
+      <c r="AE62" s="11" t="n"/>
+      <c r="AF62" s="19" t="inlineStr">
+        <is>
+          <t>1ページあたりの件数</t>
+        </is>
+      </c>
+      <c r="AG62" s="10" t="n"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="10" t="n"/>
+      <c r="AJ62" s="10" t="n"/>
+      <c r="AK62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="B63" s="31" t="n">
+        <v>22</v>
+      </c>
+      <c r="C63" s="39" t="n"/>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
       <c r="E63" s="10" t="n"/>
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
@@ -7919,47 +9289,61 @@
       <c r="I63" s="10" t="n"/>
       <c r="J63" s="10" t="n"/>
       <c r="K63" s="10" t="n"/>
-      <c r="L63" s="10" t="n"/>
-      <c r="M63" s="10" t="n"/>
+      <c r="L63" s="11" t="n"/>
+      <c r="M63" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
       <c r="N63" s="10" t="n"/>
       <c r="O63" s="10" t="n"/>
-      <c r="P63" s="10" t="n"/>
-      <c r="Q63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R63" s="10" t="n"/>
-      <c r="S63" s="10" t="n"/>
-      <c r="T63" s="10" t="n"/>
+      <c r="S63" s="11" t="n"/>
+      <c r="T63" s="17" t="inlineStr"/>
       <c r="U63" s="10" t="n"/>
       <c r="V63" s="10" t="n"/>
       <c r="W63" s="10" t="n"/>
-      <c r="X63" s="10" t="n"/>
-      <c r="Y63" s="10" t="n"/>
+      <c r="X63" s="11" t="n"/>
+      <c r="Y63" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z63" s="10" t="n"/>
       <c r="AA63" s="10" t="n"/>
       <c r="AB63" s="10" t="n"/>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
-      <c r="AE63" s="10" t="n"/>
-      <c r="AF63" s="10" t="n"/>
+      <c r="AE63" s="11" t="n"/>
+      <c r="AF63" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
       <c r="AG63" s="10" t="n"/>
       <c r="AH63" s="10" t="n"/>
       <c r="AI63" s="10" t="n"/>
       <c r="AJ63" s="10" t="n"/>
       <c r="AK63" s="11" t="n"/>
     </row>
+    <row r="64" ht="19.5" customHeight="1"/>
     <row r="65" ht="19.5" customHeight="1">
       <c r="B65" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="72" customHeight="1">
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
       <c r="C66" s="19" t="inlineStr">
         <is>
-          <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
-}</t>
+          <t>GET /api/v1/accounts?login_id=admin&amp;role_id=1&amp;page=1&amp;per_page=20&amp;sort_by=created_at&amp;sort_order=desc</t>
         </is>
       </c>
       <c r="D66" s="10" t="n"/>
@@ -8000,16 +9384,70 @@
     <row r="68" ht="19.5" customHeight="1">
       <c r="B68" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="72" customHeight="1">
+          <t>レスポンス（成功）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="409" customHeight="1">
       <c r="C69" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+  "data": [
+    {
+      "account_id": 1,
+      "login_id": "admin001",
+      "account_name": "管理者 太郎",
+      "role_id": 1,
+      "role_name": "日農（管理者）",
+      "todofuken_code": null,
+      "todofuken_name": null,
+      "ja_id": null,
+      "ja_name": null,
+      "kanri_shiten_id": null,
+      "kanri_shiten_name": null,
+      "shiten_id": null,
+      "shiten_name": null,
+      "email": "admin001@example.com",
+      "sub_email_1": "",
+      "sub_email_2": "",
+      "sub_email_3": "",
+      "paper_flg": true,
+      "denshi_flg": false,
+      "account_lock_flg": false,
+      "created_at": "2026-01-15T10:00:00Z",
+      "updated_at": "2026-03-10T14:30:00Z"
+    },
+    {
+      "account_id": 2,
+      "login_id": "ja_honten001",
+      "account_name": "JA本店 花子",
+      "role_id": 4,
+      "role_name": "JA本店",
+      "todofuken_code": "13",
+      "todofuken_name": "東京都",
+      "ja_id": 10,
+      "ja_name": "JA東京中央",
+      "kanri_shiten_id": null,
+      "kanri_shiten_name": null,
+      "shiten_id": null,
+      "shiten_name": null,
+      "email": "ja_honten001@example.com",
+      "sub_email_1": "",
+      "sub_email_2": "",
+      "sub_email_3": "",
+      "paper_flg": true,
+      "denshi_flg": true,
+      "account_lock_flg": false,
+      "created_at": "2026-02-01T09:00:00Z",
+      "updated_at": "2026-03-15T11:00:00Z"
+    }
+  ],
+  "meta": {
+    "total": 50,
+    "page": 1,
+    "per_page": 20,
+    "total_pages": 3
+  }
 }</t>
         </is>
       </c>
@@ -8048,677 +9486,936 @@
       <c r="AJ69" s="10" t="n"/>
       <c r="AK69" s="11" t="n"/>
     </row>
-    <row r="71" ht="19.5" customHeight="1"/>
-    <row r="72" ht="19.5" customHeight="1">
-      <c r="A72" s="27" t="inlineStr">
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="B71" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 401 Unauthorized）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="72" customHeight="1">
+      <c r="C72" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "UNAUTHORIZED",
+  "message": "セッションが切れました。再度ログインしてください"
+}</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
+      <c r="AF72" s="10" t="n"/>
+      <c r="AG72" s="10" t="n"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="n"/>
+      <c r="AK72" s="11" t="n"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="B74" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 403 Forbidden）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="72" customHeight="1">
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません"
+}</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="10" t="n"/>
+      <c r="J75" s="10" t="n"/>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="10" t="n"/>
+      <c r="X75" s="10" t="n"/>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="10" t="n"/>
+      <c r="AE75" s="10" t="n"/>
+      <c r="AF75" s="10" t="n"/>
+      <c r="AG75" s="10" t="n"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="10" t="n"/>
+      <c r="AJ75" s="10" t="n"/>
+      <c r="AK75" s="11" t="n"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="1">
+      <c r="B77" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="72" customHeight="1">
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+}</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="10" t="n"/>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="10" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="10" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="10" t="n"/>
+      <c r="R78" s="10" t="n"/>
+      <c r="S78" s="10" t="n"/>
+      <c r="T78" s="10" t="n"/>
+      <c r="U78" s="10" t="n"/>
+      <c r="V78" s="10" t="n"/>
+      <c r="W78" s="10" t="n"/>
+      <c r="X78" s="10" t="n"/>
+      <c r="Y78" s="10" t="n"/>
+      <c r="Z78" s="10" t="n"/>
+      <c r="AA78" s="10" t="n"/>
+      <c r="AB78" s="10" t="n"/>
+      <c r="AC78" s="10" t="n"/>
+      <c r="AD78" s="10" t="n"/>
+      <c r="AE78" s="10" t="n"/>
+      <c r="AF78" s="10" t="n"/>
+      <c r="AG78" s="10" t="n"/>
+      <c r="AH78" s="10" t="n"/>
+      <c r="AI78" s="10" t="n"/>
+      <c r="AJ78" s="10" t="n"/>
+      <c r="AK78" s="11" t="n"/>
+    </row>
+    <row r="80" ht="19.5" customHeight="1"/>
+    <row r="81" ht="19.5" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="B73" s="27" t="inlineStr">
+    <row r="82" ht="18" customHeight="1">
+      <c r="B82" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="18" customHeight="1">
-      <c r="C74" s="41" t="inlineStr">
-        <is>
-          <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="D75" s="41" t="inlineStr">
-        <is>
-          <t>login_id：最大20桁、文字列</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="D76" s="41" t="inlineStr">
-        <is>
-          <t>role_id：1〜5の整数</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="D77" s="41" t="inlineStr">
-        <is>
-          <t>ja_id：数値型チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="D78" s="41" t="inlineStr">
-        <is>
-          <t>kanri_shiten_id：数値型チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="D79" s="41" t="inlineStr">
-        <is>
-          <t>page：正の整数（デフォルト: 1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="D80" s="41" t="inlineStr">
-        <is>
-          <t>per_page：1〜100の整数（デフォルト: 20）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="D81" s="41" t="inlineStr">
-        <is>
-          <t>sort_by：許可されたカラム名（login_id, role_id, created_at）</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="D82" s="41" t="inlineStr">
-        <is>
-          <t>sort_order：asc または desc（デフォルト: desc）</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="C83" s="41" t="inlineStr">
         <is>
-          <t>不正なパラメータが存在する場合：</t>
+          <t>クエリパラメータの検証：</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="D84" s="41" t="inlineStr">
         <is>
-          <t>HTTP 400 Bad Request を返却する。</t>
+          <t>login_id：最大20桁、文字列</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
-      <c r="B85" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="D85" s="41" t="inlineStr">
+        <is>
+          <t>role_id：1〜5の整数</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+      <c r="D86" s="41" t="inlineStr">
+        <is>
+          <t>todofuken_code：最大2桁、文字列</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="C87" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+      <c r="D87" s="41" t="inlineStr">
+        <is>
+          <t>ja_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="C88" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`account.view` を保持しているか確認する。</t>
+      <c r="D88" s="41" t="inlineStr">
+        <is>
+          <t>kanri_shiten_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="D89" s="41" t="inlineStr">
         <is>
-          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
+          <t>shiten_id：数値型チェック</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+      <c r="D90" s="41" t="inlineStr">
+        <is>
+          <t>page：正の整数（デフォルト: 1）</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="B91" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
-      <c r="C92" s="41" t="inlineStr">
-        <is>
-          <t>検索条件を構築する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="36" customHeight="1">
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>per_page：1〜100の整数（デフォルト: 20）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="54" customHeight="1">
+      <c r="D92" s="41" t="inlineStr">
+        <is>
+          <t>sort_by：許可されたカラム名（login_id, account_name, role_id, role_name, todofuken_code, created_at, updated_at。デフォルト: created_at）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
       <c r="D93" s="41" t="inlineStr">
         <is>
-          <t>login_id が指定されている場合：`LIKE '%' || :login_id || '%'`（部分一致）</t>
+          <t>sort_order：asc または desc（デフォルト: desc）</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="D94" s="41" t="inlineStr">
-        <is>
-          <t>role_id が指定されている場合：`= :role_id`（完全一致）</t>
+      <c r="C94" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="D95" s="41" t="inlineStr">
         <is>
-          <t>ja_id が指定されている場合：`= :ja_id`（完全一致）</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="36" customHeight="1">
-      <c r="D96" s="41" t="inlineStr">
-        <is>
-          <t>kanri_shiten_id が指定されている場合：`= :kanri_shiten_id`（完全一致）</t>
+          <t>HTTP 400 Bad Request を返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="C97" s="41" t="inlineStr">
         <is>
-          <t>常に `deleted_at IS NULL` でフィルタリングする。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="C98" s="41" t="inlineStr">
         <is>
-          <t>NICHINO_ADMINは全アカウントを参照可能（DataScope制限なし）。</t>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
-      <c r="B99" s="27" t="inlineStr">
+      <c r="C99" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：`account.view` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="D100" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_ADMIN（日農管理者）のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="C101" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="B102" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="C103" s="41" t="inlineStr">
+        <is>
+          <t>検索条件を構築する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="D104" s="41" t="inlineStr">
+        <is>
+          <t>login_id が指定されている場合：`LIKE '%' || :login_id || '%'`（部分一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="D105" s="41" t="inlineStr">
+        <is>
+          <t>role_id が指定されている場合：`= :role_id`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="36" customHeight="1">
+      <c r="D106" s="41" t="inlineStr">
+        <is>
+          <t>todofuken_code が指定されている場合：`= :todofuken_code`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="D107" s="41" t="inlineStr">
+        <is>
+          <t>ja_id が指定されている場合：`= :ja_id`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="36" customHeight="1">
+      <c r="D108" s="41" t="inlineStr">
+        <is>
+          <t>kanri_shiten_id が指定されている場合：`= :kanri_shiten_id`（完全一致）</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="36" customHeight="1">
+      <c r="D109" s="41" t="inlineStr">
+        <is>
+          <t>shiten_id が指定されている場合：`= :shiten_id`（完全一致、顧客要件2026-07）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="C110" s="41" t="inlineStr">
+        <is>
+          <t>常に `deleted_at IS NULL` でフィルタリングする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="72" customHeight="1">
+      <c r="C111" s="41" t="inlineStr">
+        <is>
+          <t>DataScope（`applyBranchScope`）を適用する：CHUOKAI / JA_HONTEN は自JAのアカウントのみ、JA_KANRI_SHITEN は自管理支店のアカウントのみを参照可能。NICHINO_ADMIN / NICHINO_STAFF はDataScope制限なし（全アカウント参照可）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="54" customHeight="1">
+      <c r="D112" s="41" t="inlineStr">
+        <is>
+          <t>ただし本APIの `account.view` 権限は現状 NICHINO_ADMIN のみに付与されているため（seeder.md §3）、実際に呼び出せるのは NICHINO_ADMIN のみ。上記スコープ制限は将来他ロールへ権限が付与された場合に備えた多層防御。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="B113" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="126" customHeight="1">
-      <c r="C100" s="42" t="inlineStr">
+    <row r="114" ht="180" customHeight="1">
+      <c r="C114" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS total
 FROM m_account a
 WHERE a.deleted_at IS NULL
+  -- DataScope (applyBranchScope, auto-applied per session role)
   AND (:login_id IS NULL OR a.login_id LIKE '%' || :login_id || '%')
   AND (:role_id IS NULL OR a.role_id = :role_id)
+  AND (:todofuken_code IS NULL OR a.todofuken_code = :todofuken_code)
   AND (:ja_id IS NULL OR a.ja_id = :ja_id)
-  AND (:kanri_shiten_id IS NULL OR a.kanri_shiten_id = :kanri_shiten_id)</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="n"/>
-      <c r="E100" s="10" t="n"/>
-      <c r="F100" s="10" t="n"/>
-      <c r="G100" s="10" t="n"/>
-      <c r="H100" s="10" t="n"/>
-      <c r="I100" s="10" t="n"/>
-      <c r="J100" s="10" t="n"/>
-      <c r="K100" s="10" t="n"/>
-      <c r="L100" s="10" t="n"/>
-      <c r="M100" s="10" t="n"/>
-      <c r="N100" s="10" t="n"/>
-      <c r="O100" s="10" t="n"/>
-      <c r="P100" s="10" t="n"/>
-      <c r="Q100" s="10" t="n"/>
-      <c r="R100" s="10" t="n"/>
-      <c r="S100" s="10" t="n"/>
-      <c r="T100" s="10" t="n"/>
-      <c r="U100" s="10" t="n"/>
-      <c r="V100" s="10" t="n"/>
-      <c r="W100" s="10" t="n"/>
-      <c r="X100" s="10" t="n"/>
-      <c r="Y100" s="10" t="n"/>
-      <c r="Z100" s="10" t="n"/>
-      <c r="AA100" s="10" t="n"/>
-      <c r="AB100" s="10" t="n"/>
-      <c r="AC100" s="10" t="n"/>
-      <c r="AD100" s="10" t="n"/>
-      <c r="AE100" s="10" t="n"/>
-      <c r="AF100" s="10" t="n"/>
-      <c r="AG100" s="10" t="n"/>
-      <c r="AH100" s="10" t="n"/>
-      <c r="AI100" s="10" t="n"/>
-      <c r="AJ100" s="10" t="n"/>
-      <c r="AK100" s="11" t="n"/>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="B101" s="27" t="inlineStr">
+  AND (:kanri_shiten_id IS NULL OR a.kanri_shiten_id = :kanri_shiten_id)
+  AND (:shiten_id IS NULL OR a.shiten_id = :shiten_id)</t>
+        </is>
+      </c>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="10" t="n"/>
+      <c r="J114" s="10" t="n"/>
+      <c r="K114" s="10" t="n"/>
+      <c r="L114" s="10" t="n"/>
+      <c r="M114" s="10" t="n"/>
+      <c r="N114" s="10" t="n"/>
+      <c r="O114" s="10" t="n"/>
+      <c r="P114" s="10" t="n"/>
+      <c r="Q114" s="10" t="n"/>
+      <c r="R114" s="10" t="n"/>
+      <c r="S114" s="10" t="n"/>
+      <c r="T114" s="10" t="n"/>
+      <c r="U114" s="10" t="n"/>
+      <c r="V114" s="10" t="n"/>
+      <c r="W114" s="10" t="n"/>
+      <c r="X114" s="10" t="n"/>
+      <c r="Y114" s="10" t="n"/>
+      <c r="Z114" s="10" t="n"/>
+      <c r="AA114" s="10" t="n"/>
+      <c r="AB114" s="10" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="10" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="10" t="n"/>
+      <c r="AK114" s="11" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="B115" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="360" customHeight="1">
-      <c r="C102" s="42" t="inlineStr">
+    <row r="116" ht="409" customHeight="1">
+      <c r="C116" s="42" t="inlineStr">
         <is>
           <t>SELECT a.account_id, a.login_id, a.account_name,
        a.role_id, r.role_name,
        a.todofuken_code, t.todofuken_name,
        a.ja_id, j.ja_name,
        a.kanri_shiten_id, ks.kanri_shiten_name,
-       a.paper_flg, a.denshi_flg,
+       a.shiten_id, s.shiten_name,
+       a.email, a.sub_email_1, a.sub_email_2, a.sub_email_3,
+       a.paper_flg, a.denshi_flg, a.account_lock_flg,
        a.created_at, a.updated_at
 FROM m_account a
   LEFT JOIN m_roles r ON a.role_id = r.role_id AND r.deleted_at IS NULL
   LEFT JOIN m_todofuken t ON a.todofuken_code = t.todofuken_code
   LEFT JOIN m_ja j ON a.ja_id = j.ja_id AND j.deleted_at IS NULL
   LEFT JOIN m_kanri_shiten ks ON a.kanri_shiten_id = ks.kanri_shiten_id AND ks.deleted_at IS NULL
+  LEFT JOIN m_shiten s ON a.shiten_id = s.shiten_id AND s.deleted_at IS NULL
 WHERE a.deleted_at IS NULL
+  -- DataScope (applyBranchScope, auto-applied per session role)
   AND (:login_id IS NULL OR a.login_id LIKE '%' || :login_id || '%')
   AND (:role_id IS NULL OR a.role_id = :role_id)
+  AND (:todofuken_code IS NULL OR a.todofuken_code = :todofuken_code)
   AND (:ja_id IS NULL OR a.ja_id = :ja_id)
   AND (:kanri_shiten_id IS NULL OR a.kanri_shiten_id = :kanri_shiten_id)
-ORDER BY a.:sort_by :sort_order
+  AND (:shiten_id IS NULL OR a.shiten_id = :shiten_id)
+-- sort_by=role_name は r.role_name、それ以外は a.&lt;sort_by&gt;（許可リスト外は a.created_at にフォールバック）
+ORDER BY :sort_column :sort_order
 LIMIT :per_page
 OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n"/>
-      <c r="E102" s="10" t="n"/>
-      <c r="F102" s="10" t="n"/>
-      <c r="G102" s="10" t="n"/>
-      <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="n"/>
-      <c r="J102" s="10" t="n"/>
-      <c r="K102" s="10" t="n"/>
-      <c r="L102" s="10" t="n"/>
-      <c r="M102" s="10" t="n"/>
-      <c r="N102" s="10" t="n"/>
-      <c r="O102" s="10" t="n"/>
-      <c r="P102" s="10" t="n"/>
-      <c r="Q102" s="10" t="n"/>
-      <c r="R102" s="10" t="n"/>
-      <c r="S102" s="10" t="n"/>
-      <c r="T102" s="10" t="n"/>
-      <c r="U102" s="10" t="n"/>
-      <c r="V102" s="10" t="n"/>
-      <c r="W102" s="10" t="n"/>
-      <c r="X102" s="10" t="n"/>
-      <c r="Y102" s="10" t="n"/>
-      <c r="Z102" s="10" t="n"/>
-      <c r="AA102" s="10" t="n"/>
-      <c r="AB102" s="10" t="n"/>
-      <c r="AC102" s="10" t="n"/>
-      <c r="AD102" s="10" t="n"/>
-      <c r="AE102" s="10" t="n"/>
-      <c r="AF102" s="10" t="n"/>
-      <c r="AG102" s="10" t="n"/>
-      <c r="AH102" s="10" t="n"/>
-      <c r="AI102" s="10" t="n"/>
-      <c r="AJ102" s="10" t="n"/>
-      <c r="AK102" s="11" t="n"/>
-    </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="B103" s="27" t="inlineStr">
+      <c r="D116" s="10" t="n"/>
+      <c r="E116" s="10" t="n"/>
+      <c r="F116" s="10" t="n"/>
+      <c r="G116" s="10" t="n"/>
+      <c r="H116" s="10" t="n"/>
+      <c r="I116" s="10" t="n"/>
+      <c r="J116" s="10" t="n"/>
+      <c r="K116" s="10" t="n"/>
+      <c r="L116" s="10" t="n"/>
+      <c r="M116" s="10" t="n"/>
+      <c r="N116" s="10" t="n"/>
+      <c r="O116" s="10" t="n"/>
+      <c r="P116" s="10" t="n"/>
+      <c r="Q116" s="10" t="n"/>
+      <c r="R116" s="10" t="n"/>
+      <c r="S116" s="10" t="n"/>
+      <c r="T116" s="10" t="n"/>
+      <c r="U116" s="10" t="n"/>
+      <c r="V116" s="10" t="n"/>
+      <c r="W116" s="10" t="n"/>
+      <c r="X116" s="10" t="n"/>
+      <c r="Y116" s="10" t="n"/>
+      <c r="Z116" s="10" t="n"/>
+      <c r="AA116" s="10" t="n"/>
+      <c r="AB116" s="10" t="n"/>
+      <c r="AC116" s="10" t="n"/>
+      <c r="AD116" s="10" t="n"/>
+      <c r="AE116" s="10" t="n"/>
+      <c r="AF116" s="10" t="n"/>
+      <c r="AG116" s="10" t="n"/>
+      <c r="AH116" s="10" t="n"/>
+      <c r="AI116" s="10" t="n"/>
+      <c r="AJ116" s="10" t="n"/>
+      <c r="AK116" s="11" t="n"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="B117" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="C104" s="41" t="inlineStr">
+    <row r="118" ht="18" customHeight="1">
+      <c r="C118" s="41" t="inlineStr">
         <is>
           <t>取得結果を data 配列として返却する。</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="C105" s="41" t="inlineStr">
+    <row r="119" ht="18" customHeight="1">
+      <c r="C119" s="41" t="inlineStr">
         <is>
           <t>ページネーション情報を meta オブジェクトとして返却する。</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="18" customHeight="1">
-      <c r="D106" s="41" t="inlineStr">
+    <row r="120" ht="18" customHeight="1">
+      <c r="D120" s="41" t="inlineStr">
         <is>
           <t>total：4.4 で取得した総件数</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="D107" s="41" t="inlineStr">
+    <row r="121" ht="18" customHeight="1">
+      <c r="D121" s="41" t="inlineStr">
         <is>
           <t>page：リクエストの page</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="D108" s="41" t="inlineStr">
+    <row r="122" ht="18" customHeight="1">
+      <c r="D122" s="41" t="inlineStr">
         <is>
           <t>per_page：リクエストの per_page</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="D109" s="41" t="inlineStr">
+    <row r="123" ht="18" customHeight="1">
+      <c r="D123" s="41" t="inlineStr">
         <is>
           <t>total_pages：CEIL(total / per_page)</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="36" customHeight="1">
-      <c r="C110" s="41" t="inlineStr">
+    <row r="124" ht="36" customHeight="1">
+      <c r="C124" s="41" t="inlineStr">
         <is>
           <t>検索結果が0件の場合：data は空配列 `[]`、meta.total = 0 で返却（HTTP 200）。</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="B111" s="27" t="inlineStr">
+    <row r="125" ht="18" customHeight="1">
+      <c r="B125" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="C112" s="41" t="inlineStr">
+    <row r="126" ht="18" customHeight="1">
+      <c r="C126" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="288">
+  <mergeCells count="349">
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="Y45:AE45"/>
+    <mergeCell ref="D61:L61"/>
+    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="T53:X53"/>
+    <mergeCell ref="D62:L62"/>
+    <mergeCell ref="D56:L56"/>
+    <mergeCell ref="T55:X55"/>
+    <mergeCell ref="M59:P59"/>
+    <mergeCell ref="B8:I8"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="D51:L51"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="C22:L22"/>
+    <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="B113:AK113"/>
+    <mergeCell ref="T37:X37"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="B115:AK115"/>
+    <mergeCell ref="T38:X38"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="Q59:S59"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="C126:AK126"/>
+    <mergeCell ref="Y53:AE53"/>
+    <mergeCell ref="AF41:AK41"/>
+    <mergeCell ref="Q61:S61"/>
+    <mergeCell ref="D39:L39"/>
+    <mergeCell ref="AF35:AK35"/>
+    <mergeCell ref="Q48:S48"/>
+    <mergeCell ref="Y55:AE55"/>
+    <mergeCell ref="T40:X40"/>
+    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="M27:P27"/>
+    <mergeCell ref="Y37:AE37"/>
+    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="T45:X45"/>
+    <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="C28:L28"/>
+    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="D92:AK92"/>
+    <mergeCell ref="AC25:AE25"/>
+    <mergeCell ref="B77:I77"/>
+    <mergeCell ref="B11:I11"/>
+    <mergeCell ref="Q49:S49"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="Y56:AE56"/>
+    <mergeCell ref="T59:X59"/>
+    <mergeCell ref="C30:L30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="T51:X51"/>
+    <mergeCell ref="T26:X26"/>
+    <mergeCell ref="AF56:AK56"/>
+    <mergeCell ref="AF43:AK43"/>
+    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="D105:AK105"/>
+    <mergeCell ref="M40:P40"/>
+    <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="C119:AK119"/>
+    <mergeCell ref="D120:AK120"/>
+    <mergeCell ref="Q54:S54"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="AF57:AK57"/>
+    <mergeCell ref="B96:AK96"/>
+    <mergeCell ref="M41:P41"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="Y23:AB23"/>
+    <mergeCell ref="D58:L58"/>
+    <mergeCell ref="Y38:AE38"/>
+    <mergeCell ref="D100:AK100"/>
+    <mergeCell ref="Q57:S57"/>
+    <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="T61:X61"/>
+    <mergeCell ref="Y51:AE51"/>
+    <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="D108:AK108"/>
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="D95:AK95"/>
+    <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="M30:P30"/>
+    <mergeCell ref="Y22:AB22"/>
+    <mergeCell ref="Q52:S52"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="M46:P46"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="M61:P61"/>
+    <mergeCell ref="C66:AK66"/>
+    <mergeCell ref="AC23:AE23"/>
+    <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="D121:AK121"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="M56:P56"/>
+    <mergeCell ref="M43:P43"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="AF50:AK50"/>
+    <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="C60:C63"/>
+    <mergeCell ref="T22:X22"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="AF49:AK49"/>
+    <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="B117:AK117"/>
+    <mergeCell ref="M62:P62"/>
+    <mergeCell ref="AC29:AE29"/>
+    <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="C103:AK103"/>
+    <mergeCell ref="C118:AK118"/>
+    <mergeCell ref="M51:P51"/>
+    <mergeCell ref="C37:C58"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="AF37:AK37"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="T46:X46"/>
+    <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="D49:L49"/>
+    <mergeCell ref="T48:X48"/>
+    <mergeCell ref="C98:AK98"/>
+    <mergeCell ref="AF42:AK42"/>
+    <mergeCell ref="C116:AK116"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="D54:L54"/>
+    <mergeCell ref="T41:X41"/>
+    <mergeCell ref="Y35:AE35"/>
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="T56:X56"/>
+    <mergeCell ref="T43:X43"/>
+    <mergeCell ref="Y31:AB31"/>
+    <mergeCell ref="T36:X36"/>
+    <mergeCell ref="Y46:AE46"/>
+    <mergeCell ref="D57:L57"/>
+    <mergeCell ref="AF63:AK63"/>
+    <mergeCell ref="C111:AK111"/>
+    <mergeCell ref="A33:AK33"/>
+    <mergeCell ref="Y61:AE61"/>
+    <mergeCell ref="C83:AK83"/>
+    <mergeCell ref="Y48:AE48"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="M58:P58"/>
+    <mergeCell ref="B82:AK82"/>
+    <mergeCell ref="T62:X62"/>
+    <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="C124:AK124"/>
+    <mergeCell ref="D50:L50"/>
+    <mergeCell ref="D44:L44"/>
+    <mergeCell ref="D60:L60"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="Y59:AE59"/>
+    <mergeCell ref="C21:L21"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="M42:P42"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="Y36:AE36"/>
-    <mergeCell ref="T24:X24"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="C66:AK66"/>
-    <mergeCell ref="Y45:AE45"/>
-    <mergeCell ref="T33:X33"/>
-    <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C102:AK102"/>
-    <mergeCell ref="D48:L48"/>
+    <mergeCell ref="D87:AK87"/>
+    <mergeCell ref="D122:AK122"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="J12:AK12"/>
+    <mergeCell ref="Y62:AE62"/>
+    <mergeCell ref="Y54:AE54"/>
+    <mergeCell ref="Y21:AB21"/>
+    <mergeCell ref="M35:P35"/>
+    <mergeCell ref="C114:AK114"/>
+    <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="Q42:S42"/>
+    <mergeCell ref="T28:X28"/>
+    <mergeCell ref="T30:X30"/>
+    <mergeCell ref="T57:X57"/>
+    <mergeCell ref="T29:X29"/>
+    <mergeCell ref="D53:L53"/>
+    <mergeCell ref="D47:L47"/>
+    <mergeCell ref="AF59:AK59"/>
+    <mergeCell ref="B12:I12"/>
+    <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="T58:X58"/>
+    <mergeCell ref="T54:X54"/>
+    <mergeCell ref="D89:AK89"/>
+    <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="AD2:AG3"/>
+    <mergeCell ref="D88:AK88"/>
+    <mergeCell ref="AC21:AE21"/>
+    <mergeCell ref="B13:I13"/>
+    <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="C99:AK99"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="Y39:AE39"/>
+    <mergeCell ref="D90:AK90"/>
+    <mergeCell ref="J13:AK13"/>
+    <mergeCell ref="AF27:AK27"/>
+    <mergeCell ref="Q47:S47"/>
+    <mergeCell ref="T60:X60"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C72:AK72"/>
+    <mergeCell ref="M36:P36"/>
+    <mergeCell ref="Q63:S63"/>
+    <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="Y57:AE57"/>
+    <mergeCell ref="T42:X42"/>
+    <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="A81:AK81"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="T50:X50"/>
+    <mergeCell ref="T44:X44"/>
+    <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="D55:L55"/>
+    <mergeCell ref="AF40:AK40"/>
+    <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="Y60:AE60"/>
+    <mergeCell ref="N16:AK16"/>
+    <mergeCell ref="B125:AK125"/>
+    <mergeCell ref="Q55:S55"/>
+    <mergeCell ref="B14:I17"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="D91:AK91"/>
+    <mergeCell ref="AC24:AE24"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="D106:AK106"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="C69:AK69"/>
+    <mergeCell ref="D93:AK93"/>
+    <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="AF47:AK47"/>
+    <mergeCell ref="M52:P52"/>
+    <mergeCell ref="Y58:AE58"/>
+    <mergeCell ref="D109:AK109"/>
+    <mergeCell ref="AF46:AK46"/>
+    <mergeCell ref="D84:AK84"/>
+    <mergeCell ref="Q53:S53"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="AF61:AK61"/>
+    <mergeCell ref="AF48:AK48"/>
+    <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="D104:AK104"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="B102:AK102"/>
+    <mergeCell ref="M57:P57"/>
     <mergeCell ref="M29:P29"/>
-    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="AF21:AK21"/>
-    <mergeCell ref="T53:X53"/>
-    <mergeCell ref="B56:I56"/>
-    <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="M46:P46"/>
     <mergeCell ref="N17:AK17"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="D82:AK82"/>
-    <mergeCell ref="M43:P43"/>
-    <mergeCell ref="B73:AK73"/>
-    <mergeCell ref="Y52:AE52"/>
-    <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="C34:L34"/>
-    <mergeCell ref="AF50:AK50"/>
-    <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C100:AK100"/>
-    <mergeCell ref="C112:AK112"/>
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="T63:X63"/>
+    <mergeCell ref="AF29:AK29"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
-    <mergeCell ref="D51:L51"/>
-    <mergeCell ref="AF52:AK52"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="D106:AK106"/>
-    <mergeCell ref="Y54:AE54"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="Y21:AB21"/>
-    <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF36:AK36"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="M54:P54"/>
+    <mergeCell ref="Q56:S56"/>
     <mergeCell ref="Q43:S43"/>
-    <mergeCell ref="J2:P3"/>
-    <mergeCell ref="T22:X22"/>
-    <mergeCell ref="B65:I65"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="AF34:AK34"/>
-    <mergeCell ref="B68:I68"/>
-    <mergeCell ref="C22:L22"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="D77:AK77"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="Q42:S42"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="T28:X28"/>
-    <mergeCell ref="Y40:AE40"/>
-    <mergeCell ref="AF49:AK49"/>
-    <mergeCell ref="B91:AK91"/>
-    <mergeCell ref="T37:X37"/>
-    <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="D75:AK75"/>
-    <mergeCell ref="M33:P33"/>
+    <mergeCell ref="T31:X31"/>
+    <mergeCell ref="C59:L59"/>
     <mergeCell ref="M45:P45"/>
-    <mergeCell ref="T29:X29"/>
-    <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="B59:I59"/>
-    <mergeCell ref="T38:X38"/>
+    <mergeCell ref="AF62:AK62"/>
+    <mergeCell ref="D112:AK112"/>
     <mergeCell ref="M47:P47"/>
-    <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="D53:L53"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D47:L47"/>
-    <mergeCell ref="AC29:AE29"/>
-    <mergeCell ref="Y33:AE33"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B101:AK101"/>
-    <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="C104:AK104"/>
-    <mergeCell ref="Q22:S22"/>
     <mergeCell ref="D37:L37"/>
-    <mergeCell ref="Q46:S46"/>
     <mergeCell ref="AF51:AK51"/>
-    <mergeCell ref="T54:X54"/>
-    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="C88:AK88"/>
-    <mergeCell ref="Y53:AE53"/>
-    <mergeCell ref="D89:AK89"/>
-    <mergeCell ref="B103:AK103"/>
-    <mergeCell ref="Z2:AC3"/>
-    <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="AF41:AK41"/>
-    <mergeCell ref="C24:L24"/>
-    <mergeCell ref="AF35:AK35"/>
-    <mergeCell ref="D39:L39"/>
-    <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="C33:L33"/>
+    <mergeCell ref="Y63:AE63"/>
     <mergeCell ref="M44:P44"/>
-    <mergeCell ref="AC21:AE21"/>
-    <mergeCell ref="Q48:S48"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="D79:AK79"/>
-    <mergeCell ref="Q45:S45"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="D38:L38"/>
-    <mergeCell ref="T40:X40"/>
-    <mergeCell ref="C26:L26"/>
-    <mergeCell ref="D81:AK81"/>
-    <mergeCell ref="Y39:AE39"/>
-    <mergeCell ref="M51:P51"/>
-    <mergeCell ref="J13:AK13"/>
-    <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="C50:L50"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="AF37:AK37"/>
+    <mergeCell ref="M60:P60"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="D63:L63"/>
     <mergeCell ref="Y26:AB26"/>
-    <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="M21:P21"/>
-    <mergeCell ref="D76:AK76"/>
     <mergeCell ref="D107:AK107"/>
-    <mergeCell ref="T46:X46"/>
-    <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
-    <mergeCell ref="M27:P27"/>
     <mergeCell ref="D52:L52"/>
-    <mergeCell ref="M37:P37"/>
-    <mergeCell ref="M36:P36"/>
-    <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="T39:X39"/>
-    <mergeCell ref="D49:L49"/>
     <mergeCell ref="Y27:AB27"/>
-    <mergeCell ref="T48:X48"/>
-    <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="Q35:S35"/>
-    <mergeCell ref="Q50:S50"/>
-    <mergeCell ref="C87:AK87"/>
-    <mergeCell ref="T45:X45"/>
-    <mergeCell ref="A5:AK5"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="T42:X42"/>
-    <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="C28:L28"/>
-    <mergeCell ref="D78:AK78"/>
-    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="M63:P63"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
-    <mergeCell ref="AC25:AE25"/>
-    <mergeCell ref="C98:AK98"/>
     <mergeCell ref="M50:P50"/>
-    <mergeCell ref="A72:AK72"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="AF42:AK42"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="Q2:U3"/>
-    <mergeCell ref="Q49:S49"/>
-    <mergeCell ref="T50:X50"/>
-    <mergeCell ref="Q36:S36"/>
-    <mergeCell ref="T44:X44"/>
-    <mergeCell ref="M34:P34"/>
-    <mergeCell ref="Y43:AE43"/>
-    <mergeCell ref="D94:AK94"/>
-    <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="A31:AK31"/>
-    <mergeCell ref="AF40:AK40"/>
-    <mergeCell ref="M49:P49"/>
-    <mergeCell ref="C63:AK63"/>
+    <mergeCell ref="M55:P55"/>
     <mergeCell ref="T21:X21"/>
-    <mergeCell ref="M39:P39"/>
     <mergeCell ref="M48:P48"/>
-    <mergeCell ref="T51:X51"/>
-    <mergeCell ref="T26:X26"/>
-    <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="D54:L54"/>
-    <mergeCell ref="T41:X41"/>
-    <mergeCell ref="Y35:AE35"/>
-    <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="D80:AK80"/>
-    <mergeCell ref="J9:AK9"/>
-    <mergeCell ref="AF43:AK43"/>
-    <mergeCell ref="C105:AK105"/>
-    <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="D96:AK96"/>
-    <mergeCell ref="M40:P40"/>
-    <mergeCell ref="T43:X43"/>
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
-    <mergeCell ref="N16:AK16"/>
-    <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="Q54:S54"/>
-    <mergeCell ref="T36:X36"/>
-    <mergeCell ref="B14:I17"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="Y46:AE46"/>
-    <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="M26:P26"/>
-    <mergeCell ref="M41:P41"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="T49:X49"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="M38:P38"/>
-    <mergeCell ref="Y48:AE48"/>
-    <mergeCell ref="C83:AK83"/>
-    <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="T35:X35"/>
-    <mergeCell ref="C92:AK92"/>
-    <mergeCell ref="D93:AK93"/>
-    <mergeCell ref="B111:AK111"/>
-    <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="C35:C49"/>
+    <mergeCell ref="B71:I71"/>
+    <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="D43:L43"/>
-    <mergeCell ref="T25:X25"/>
-    <mergeCell ref="Y42:AE42"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="A19:AK19"/>
-    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="Y38:AE38"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B99:AK99"/>
-    <mergeCell ref="AF47:AK47"/>
-    <mergeCell ref="M52:P52"/>
-    <mergeCell ref="AC27:AE27"/>
-    <mergeCell ref="D109:AK109"/>
-    <mergeCell ref="AF46:AK46"/>
-    <mergeCell ref="AF28:AK28"/>
-    <mergeCell ref="C29:L29"/>
-    <mergeCell ref="D84:AK84"/>
-    <mergeCell ref="D44:L44"/>
-    <mergeCell ref="Q53:S53"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="Y51:AE51"/>
-    <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C90:AK90"/>
-    <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="C60:AK60"/>
-    <mergeCell ref="B85:AK85"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="AF48:AK48"/>
-    <mergeCell ref="D108:AK108"/>
+    <mergeCell ref="D123:AK123"/>
+    <mergeCell ref="AF60:AK60"/>
+    <mergeCell ref="D85:AK85"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="M22:P22"/>
     <mergeCell ref="Y50:AE50"/>
-    <mergeCell ref="D95:AK95"/>
-    <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="C110:AK110"/>
-    <mergeCell ref="Y22:AB22"/>
-    <mergeCell ref="Q52:S52"/>
-    <mergeCell ref="C21:L21"/>
-    <mergeCell ref="Y34:AE34"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="D45:L45"/>
-    <mergeCell ref="M28:P28"/>
-    <mergeCell ref="M42:P42"/>
-    <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="Y52:AE52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8730,7 +10427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK85"/>
+  <dimension ref="A1:AK84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -8891,7 +10588,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8899,7 +10596,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -9245,7 +10942,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -9297,7 +10994,7 @@
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>正常にアカウントを削除しました</t>
+          <t>削除しました</t>
         </is>
       </c>
       <c r="O14" s="10" t="n"/>
@@ -9449,7 +11146,7 @@
       <c r="M18" s="11" t="n"/>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>このレコードは現在使用中のため、削除できません。</t>
+          <t>関連データが存在するため処理を実行できません。</t>
         </is>
       </c>
       <c r="O18" s="10" t="n"/>
@@ -9854,7 +11551,7 @@
       <c r="C35" s="19" t="inlineStr">
         <is>
           <t>{
-  "message": "正常に削除しました"
+  "message": "削除しました。"
 }</t>
         </is>
       </c>
@@ -10058,7 +11755,7 @@
         <is>
           <t>{
   "error_code": "CONFLICT",
-  "message": "このレコードは現在使用中のため、削除できません。"
+  "message": "関連データが存在するため処理を実行できません。"
 }</t>
         </is>
       </c>
@@ -10156,59 +11853,96 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="B54" s="27" t="inlineStr">
+    <row r="54" ht="54" customHeight="1">
+      <c r="B54" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="10" t="n"/>
+      <c r="AF54" s="10" t="n"/>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="11" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="C55" s="41" t="inlineStr">
+    <row r="56" ht="18" customHeight="1">
+      <c r="C56" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="D56" s="41" t="inlineStr">
+    <row r="57" ht="18" customHeight="1">
+      <c r="D57" s="41" t="inlineStr">
         <is>
           <t>account_id：数値型チェック、必須チェック</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="C57" s="41" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="C58" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="D58" s="41" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="D59" s="41" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="B59" s="27" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="C60" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="C61" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -10234,28 +11968,21 @@
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>自分自身のアカウントは削除不可とする。</t>
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定（存在確認・関連データチェック）</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
-      <c r="B66" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定（存在確認・関連データチェック）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="C67" s="41" t="inlineStr">
+      <c r="C66" s="41" t="inlineStr">
         <is>
           <t>対象アカウントの存在を確認する。</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="126" customHeight="1">
-      <c r="C68" s="42" t="inlineStr">
+    <row r="67" ht="126" customHeight="1">
+      <c r="C67" s="42" t="inlineStr">
         <is>
           <t>SELECT a.account_id, a.login_id, a.account_name, a.role_id,
        a.ja_id, a.kanri_shiten_id, a.todofuken_code,
@@ -10266,57 +11993,57 @@
   AND a.deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D68" s="10" t="n"/>
-      <c r="E68" s="10" t="n"/>
-      <c r="F68" s="10" t="n"/>
-      <c r="G68" s="10" t="n"/>
-      <c r="H68" s="10" t="n"/>
-      <c r="I68" s="10" t="n"/>
-      <c r="J68" s="10" t="n"/>
-      <c r="K68" s="10" t="n"/>
-      <c r="L68" s="10" t="n"/>
-      <c r="M68" s="10" t="n"/>
-      <c r="N68" s="10" t="n"/>
-      <c r="O68" s="10" t="n"/>
-      <c r="P68" s="10" t="n"/>
-      <c r="Q68" s="10" t="n"/>
-      <c r="R68" s="10" t="n"/>
-      <c r="S68" s="10" t="n"/>
-      <c r="T68" s="10" t="n"/>
-      <c r="U68" s="10" t="n"/>
-      <c r="V68" s="10" t="n"/>
-      <c r="W68" s="10" t="n"/>
-      <c r="X68" s="10" t="n"/>
-      <c r="Y68" s="10" t="n"/>
-      <c r="Z68" s="10" t="n"/>
-      <c r="AA68" s="10" t="n"/>
-      <c r="AB68" s="10" t="n"/>
-      <c r="AC68" s="10" t="n"/>
-      <c r="AD68" s="10" t="n"/>
-      <c r="AE68" s="10" t="n"/>
-      <c r="AF68" s="10" t="n"/>
-      <c r="AG68" s="10" t="n"/>
-      <c r="AH68" s="10" t="n"/>
-      <c r="AI68" s="10" t="n"/>
-      <c r="AJ68" s="10" t="n"/>
-      <c r="AK68" s="11" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="n"/>
+      <c r="J67" s="10" t="n"/>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="10" t="n"/>
+      <c r="Q67" s="10" t="n"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="10" t="n"/>
+      <c r="X67" s="10" t="n"/>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="10" t="n"/>
+      <c r="AE67" s="10" t="n"/>
+      <c r="AF67" s="10" t="n"/>
+      <c r="AG67" s="10" t="n"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="10" t="n"/>
+      <c r="AJ67" s="10" t="n"/>
+      <c r="AK67" s="11" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="C68" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="18" customHeight="1">
       <c r="C69" s="41" t="inlineStr">
         <is>
-          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="C70" s="41" t="inlineStr">
-        <is>
           <t>関連テーブルに紐づくデータが存在するか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="72" customHeight="1">
-      <c r="C71" s="42" t="inlineStr">
+    <row r="70" ht="72" customHeight="1">
+      <c r="C70" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS related_count
 FROM (
@@ -10324,57 +12051,57 @@
 ) AS related_data</t>
         </is>
       </c>
-      <c r="D71" s="10" t="n"/>
-      <c r="E71" s="10" t="n"/>
-      <c r="F71" s="10" t="n"/>
-      <c r="G71" s="10" t="n"/>
-      <c r="H71" s="10" t="n"/>
-      <c r="I71" s="10" t="n"/>
-      <c r="J71" s="10" t="n"/>
-      <c r="K71" s="10" t="n"/>
-      <c r="L71" s="10" t="n"/>
-      <c r="M71" s="10" t="n"/>
-      <c r="N71" s="10" t="n"/>
-      <c r="O71" s="10" t="n"/>
-      <c r="P71" s="10" t="n"/>
-      <c r="Q71" s="10" t="n"/>
-      <c r="R71" s="10" t="n"/>
-      <c r="S71" s="10" t="n"/>
-      <c r="T71" s="10" t="n"/>
-      <c r="U71" s="10" t="n"/>
-      <c r="V71" s="10" t="n"/>
-      <c r="W71" s="10" t="n"/>
-      <c r="X71" s="10" t="n"/>
-      <c r="Y71" s="10" t="n"/>
-      <c r="Z71" s="10" t="n"/>
-      <c r="AA71" s="10" t="n"/>
-      <c r="AB71" s="10" t="n"/>
-      <c r="AC71" s="10" t="n"/>
-      <c r="AD71" s="10" t="n"/>
-      <c r="AE71" s="10" t="n"/>
-      <c r="AF71" s="10" t="n"/>
-      <c r="AG71" s="10" t="n"/>
-      <c r="AH71" s="10" t="n"/>
-      <c r="AI71" s="10" t="n"/>
-      <c r="AJ71" s="10" t="n"/>
-      <c r="AK71" s="11" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="n"/>
+      <c r="J70" s="10" t="n"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="10" t="n"/>
+      <c r="X70" s="10" t="n"/>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="10" t="n"/>
+      <c r="AE70" s="10" t="n"/>
+      <c r="AF70" s="10" t="n"/>
+      <c r="AG70" s="10" t="n"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="10" t="n"/>
+      <c r="AJ70" s="10" t="n"/>
+      <c r="AK70" s="11" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="C71" s="41" t="inlineStr">
+        <is>
+          <t>関連データが存在する場合：HTTP 409 (`CONFLICT`)</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="18" customHeight="1">
-      <c r="C72" s="41" t="inlineStr">
-        <is>
-          <t>関連データが存在する場合：HTTP 409 (`CONFLICT`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="B73" s="27" t="inlineStr">
+      <c r="B72" s="27" t="inlineStr">
         <is>
           <t>4.4 論理削除の実行</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="108" customHeight="1">
-      <c r="C74" s="42" t="inlineStr">
+    <row r="73" ht="108" customHeight="1">
+      <c r="C73" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_account
 SET deleted_at = NOW(),
@@ -10384,57 +12111,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D74" s="10" t="n"/>
-      <c r="E74" s="10" t="n"/>
-      <c r="F74" s="10" t="n"/>
-      <c r="G74" s="10" t="n"/>
-      <c r="H74" s="10" t="n"/>
-      <c r="I74" s="10" t="n"/>
-      <c r="J74" s="10" t="n"/>
-      <c r="K74" s="10" t="n"/>
-      <c r="L74" s="10" t="n"/>
-      <c r="M74" s="10" t="n"/>
-      <c r="N74" s="10" t="n"/>
-      <c r="O74" s="10" t="n"/>
-      <c r="P74" s="10" t="n"/>
-      <c r="Q74" s="10" t="n"/>
-      <c r="R74" s="10" t="n"/>
-      <c r="S74" s="10" t="n"/>
-      <c r="T74" s="10" t="n"/>
-      <c r="U74" s="10" t="n"/>
-      <c r="V74" s="10" t="n"/>
-      <c r="W74" s="10" t="n"/>
-      <c r="X74" s="10" t="n"/>
-      <c r="Y74" s="10" t="n"/>
-      <c r="Z74" s="10" t="n"/>
-      <c r="AA74" s="10" t="n"/>
-      <c r="AB74" s="10" t="n"/>
-      <c r="AC74" s="10" t="n"/>
-      <c r="AD74" s="10" t="n"/>
-      <c r="AE74" s="10" t="n"/>
-      <c r="AF74" s="10" t="n"/>
-      <c r="AG74" s="10" t="n"/>
-      <c r="AH74" s="10" t="n"/>
-      <c r="AI74" s="10" t="n"/>
-      <c r="AJ74" s="10" t="n"/>
-      <c r="AK74" s="11" t="n"/>
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="10" t="n"/>
+      <c r="J73" s="10" t="n"/>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="10" t="n"/>
+      <c r="X73" s="10" t="n"/>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="10" t="n"/>
+      <c r="AE73" s="10" t="n"/>
+      <c r="AF73" s="10" t="n"/>
+      <c r="AG73" s="10" t="n"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="10" t="n"/>
+      <c r="AJ73" s="10" t="n"/>
+      <c r="AK73" s="11" t="n"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="B74" s="27" t="inlineStr">
+        <is>
+          <t>4.5 操作ログ記録</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="B75" s="27" t="inlineStr">
-        <is>
-          <t>4.5 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="C76" s="41" t="inlineStr">
+      <c r="C75" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="216" customHeight="1">
-      <c r="C77" s="42" t="inlineStr">
+    <row r="76" ht="216" customHeight="1">
+      <c r="C76" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -10448,6 +12175,60 @@
         :before_value_json, '',
         '', '',
         :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="10" t="n"/>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="10" t="n"/>
+      <c r="X76" s="10" t="n"/>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="10" t="n"/>
+      <c r="AE76" s="10" t="n"/>
+      <c r="AF76" s="10" t="n"/>
+      <c r="AG76" s="10" t="n"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="10" t="n"/>
+      <c r="AJ76" s="10" t="n"/>
+      <c r="AK76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="252" customHeight="1">
+      <c r="C77" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+`after_value`：DELETE のため空文字列を設定する。
+{
+  "account_id": 5,
+  "login_id": "ja_shiten001",
+  "account_name": "JA管理支店 次郎",
+  "role_id": 5,
+  "ja_id": 10,
+  "kanri_shiten_id": 20,
+  "todofuken_code": "13",
+  "paper_flg": true,
+  "denshi_flg": false,
+  "email": "shiten001@example.com"
+}</t>
         </is>
       </c>
       <c r="D77" s="10" t="n"/>
@@ -10485,140 +12266,86 @@
       <c r="AJ77" s="10" t="n"/>
       <c r="AK77" s="11" t="n"/>
     </row>
-    <row r="78" ht="252" customHeight="1">
-      <c r="C78" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-`after_value`：DELETE のため空文字列を設定する。
-{
-  "account_id": 5,
-  "login_id": "ja_shiten001",
-  "account_name": "JA管理支店 次郎",
-  "role_id": 5,
-  "ja_id": 10,
-  "kanri_shiten_id": 20,
-  "todofuken_code": "13",
-  "paper_flg": true,
-  "denshi_flg": false,
-  "email": "shiten001@example.com"
+    <row r="78" ht="18" customHeight="1">
+      <c r="B78" s="27" t="inlineStr">
+        <is>
+          <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="C79" s="41" t="inlineStr">
+        <is>
+          <t>削除成功メッセージを返却する。HTTP 200。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="54" customHeight="1">
+      <c r="C80" s="42" t="inlineStr">
+        <is>
+          <t>{
+  "message": "削除しました。"
 }</t>
         </is>
       </c>
-      <c r="D78" s="10" t="n"/>
-      <c r="E78" s="10" t="n"/>
-      <c r="F78" s="10" t="n"/>
-      <c r="G78" s="10" t="n"/>
-      <c r="H78" s="10" t="n"/>
-      <c r="I78" s="10" t="n"/>
-      <c r="J78" s="10" t="n"/>
-      <c r="K78" s="10" t="n"/>
-      <c r="L78" s="10" t="n"/>
-      <c r="M78" s="10" t="n"/>
-      <c r="N78" s="10" t="n"/>
-      <c r="O78" s="10" t="n"/>
-      <c r="P78" s="10" t="n"/>
-      <c r="Q78" s="10" t="n"/>
-      <c r="R78" s="10" t="n"/>
-      <c r="S78" s="10" t="n"/>
-      <c r="T78" s="10" t="n"/>
-      <c r="U78" s="10" t="n"/>
-      <c r="V78" s="10" t="n"/>
-      <c r="W78" s="10" t="n"/>
-      <c r="X78" s="10" t="n"/>
-      <c r="Y78" s="10" t="n"/>
-      <c r="Z78" s="10" t="n"/>
-      <c r="AA78" s="10" t="n"/>
-      <c r="AB78" s="10" t="n"/>
-      <c r="AC78" s="10" t="n"/>
-      <c r="AD78" s="10" t="n"/>
-      <c r="AE78" s="10" t="n"/>
-      <c r="AF78" s="10" t="n"/>
-      <c r="AG78" s="10" t="n"/>
-      <c r="AH78" s="10" t="n"/>
-      <c r="AI78" s="10" t="n"/>
-      <c r="AJ78" s="10" t="n"/>
-      <c r="AK78" s="11" t="n"/>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="B79" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
-        <is>
-          <t>削除成功メッセージを返却する。HTTP 200。</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="54" customHeight="1">
-      <c r="C81" s="42" t="inlineStr">
-        <is>
-          <t>{
-  "message": "正常に削除しました"
-}</t>
-        </is>
-      </c>
-      <c r="D81" s="10" t="n"/>
-      <c r="E81" s="10" t="n"/>
-      <c r="F81" s="10" t="n"/>
-      <c r="G81" s="10" t="n"/>
-      <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="n"/>
-      <c r="J81" s="10" t="n"/>
-      <c r="K81" s="10" t="n"/>
-      <c r="L81" s="10" t="n"/>
-      <c r="M81" s="10" t="n"/>
-      <c r="N81" s="10" t="n"/>
-      <c r="O81" s="10" t="n"/>
-      <c r="P81" s="10" t="n"/>
-      <c r="Q81" s="10" t="n"/>
-      <c r="R81" s="10" t="n"/>
-      <c r="S81" s="10" t="n"/>
-      <c r="T81" s="10" t="n"/>
-      <c r="U81" s="10" t="n"/>
-      <c r="V81" s="10" t="n"/>
-      <c r="W81" s="10" t="n"/>
-      <c r="X81" s="10" t="n"/>
-      <c r="Y81" s="10" t="n"/>
-      <c r="Z81" s="10" t="n"/>
-      <c r="AA81" s="10" t="n"/>
-      <c r="AB81" s="10" t="n"/>
-      <c r="AC81" s="10" t="n"/>
-      <c r="AD81" s="10" t="n"/>
-      <c r="AE81" s="10" t="n"/>
-      <c r="AF81" s="10" t="n"/>
-      <c r="AG81" s="10" t="n"/>
-      <c r="AH81" s="10" t="n"/>
-      <c r="AI81" s="10" t="n"/>
-      <c r="AJ81" s="10" t="n"/>
-      <c r="AK81" s="11" t="n"/>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="10" t="n"/>
+      <c r="J80" s="10" t="n"/>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="10" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="10" t="n"/>
+      <c r="Q80" s="10" t="n"/>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="10" t="n"/>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="10" t="n"/>
+      <c r="X80" s="10" t="n"/>
+      <c r="Y80" s="10" t="n"/>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="10" t="n"/>
+      <c r="AC80" s="10" t="n"/>
+      <c r="AD80" s="10" t="n"/>
+      <c r="AE80" s="10" t="n"/>
+      <c r="AF80" s="10" t="n"/>
+      <c r="AG80" s="10" t="n"/>
+      <c r="AH80" s="10" t="n"/>
+      <c r="AI80" s="10" t="n"/>
+      <c r="AJ80" s="10" t="n"/>
+      <c r="AK80" s="11" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="B81" s="27" t="inlineStr">
+        <is>
+          <t>4.7 例外処理</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="B82" s="27" t="inlineStr">
-        <is>
-          <t>4.7 例外処理</t>
+      <c r="C82" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="C83" s="41" t="inlineStr">
         <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="C84" s="41" t="inlineStr">
-        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="216" customHeight="1">
-      <c r="C85" s="42" t="inlineStr">
+    <row r="84" ht="216" customHeight="1">
+      <c r="C84" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -10634,49 +12361,49 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="10" t="n"/>
-      <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="n"/>
-      <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
-      <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
-      <c r="U85" s="10" t="n"/>
-      <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-      <c r="AA85" s="10" t="n"/>
-      <c r="AB85" s="10" t="n"/>
-      <c r="AC85" s="10" t="n"/>
-      <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
-      <c r="AG85" s="10" t="n"/>
-      <c r="AH85" s="10" t="n"/>
-      <c r="AI85" s="10" t="n"/>
-      <c r="AJ85" s="10" t="n"/>
-      <c r="AK85" s="11" t="n"/>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="10" t="n"/>
+      <c r="K84" s="10" t="n"/>
+      <c r="L84" s="10" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="10" t="n"/>
+      <c r="S84" s="10" t="n"/>
+      <c r="T84" s="10" t="n"/>
+      <c r="U84" s="10" t="n"/>
+      <c r="V84" s="10" t="n"/>
+      <c r="W84" s="10" t="n"/>
+      <c r="X84" s="10" t="n"/>
+      <c r="Y84" s="10" t="n"/>
+      <c r="Z84" s="10" t="n"/>
+      <c r="AA84" s="10" t="n"/>
+      <c r="AB84" s="10" t="n"/>
+      <c r="AC84" s="10" t="n"/>
+      <c r="AD84" s="10" t="n"/>
+      <c r="AE84" s="10" t="n"/>
+      <c r="AF84" s="10" t="n"/>
+      <c r="AG84" s="10" t="n"/>
+      <c r="AH84" s="10" t="n"/>
+      <c r="AI84" s="10" t="n"/>
+      <c r="AJ84" s="10" t="n"/>
+      <c r="AK84" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="117">
+  <mergeCells count="116">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="A26:AK26"/>
-    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="C66:AK66"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="C77:AK77"/>
@@ -10684,24 +12411,23 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="D58:AK58"/>
     <mergeCell ref="C68:AK68"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="A53:AK53"/>
     <mergeCell ref="N17:AK17"/>
+    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="B73:AK73"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
-    <mergeCell ref="C65:AK65"/>
     <mergeCell ref="C44:AK44"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="B65:AK65"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="C80:AK80"/>
@@ -10709,7 +12435,6 @@
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="B66:AK66"/>
     <mergeCell ref="C38:AK38"/>
     <mergeCell ref="A21:AK21"/>
     <mergeCell ref="T29:X29"/>
@@ -10717,51 +12442,54 @@
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D56:AK56"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="B78:AK78"/>
     <mergeCell ref="C24:L24"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="C55:AK55"/>
     <mergeCell ref="D63:AK63"/>
+    <mergeCell ref="B55:AK55"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="B49:I49"/>
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="Y28:AE28"/>
-    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="C32:AK32"/>
-    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="B60:AK60"/>
     <mergeCell ref="C62:AK62"/>
     <mergeCell ref="C28:L28"/>
+    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C64:AK64"/>
+    <mergeCell ref="C79:AK79"/>
+    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
     <mergeCell ref="C41:AK41"/>
     <mergeCell ref="C50:AK50"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="C56:AK56"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="D57:AK57"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="B54:AK54"/>
+    <mergeCell ref="B72:AK72"/>
     <mergeCell ref="C67:AK67"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
@@ -10771,22 +12499,20 @@
     <mergeCell ref="C83:AK83"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="J14:M14"/>
+    <mergeCell ref="D59:AK59"/>
     <mergeCell ref="C47:AK47"/>
+    <mergeCell ref="B74:AK74"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="C76:AK76"/>
-    <mergeCell ref="B75:AK75"/>
     <mergeCell ref="M28:P28"/>
-    <mergeCell ref="B59:AK59"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10960,7 +12686,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -10968,7 +12694,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -11314,7 +13040,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -12197,7 +13923,7 @@
     <row r="51" ht="18" customHeight="1">
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -12424,7 +14150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK73"/>
+  <dimension ref="A1:AK94"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -12585,7 +14311,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -12593,7 +14319,7 @@
       <c r="AG2" s="22" t="n"/>
       <c r="AH2" s="20" t="inlineStr">
         <is>
-          <t>Nguyen Duyen Manh</t>
+          <t>Tran Duc Tuyen</t>
         </is>
       </c>
       <c r="AI2" s="21" t="n"/>
@@ -12694,7 +14420,7 @@
       <c r="AJ7" s="10" t="n"/>
       <c r="AK7" s="11" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="B8" s="33" t="inlineStr">
         <is>
           <t>概要</t>
@@ -12709,7 +14435,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="19" t="inlineStr">
         <is>
-          <t>JAプルダウンリストを取得する（都道府県・管理者区分によるカスケード絞込み。共用API：アカウント検索・登録等で使用）</t>
+          <t>JAプルダウンリストを取得する（共用API）。2つのユースケースを1つのエンドポイントで提供：（A）ページング+フリーテキスト検索（SCR-009 等のフォーム用）、（B）都道府県・管理者区分によるカスケード絞込み（SCR-024 アカウント検索／SCR-025 登録用）。両方のレスポンス形状は同一（`{data, meta}`）。</t>
         </is>
       </c>
       <c r="K8" s="10" t="n"/>
@@ -12939,7 +14665,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -13022,14 +14748,14 @@
       <c r="B15" s="35" t="n"/>
       <c r="I15" s="36" t="n"/>
       <c r="J15" s="17" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K15" s="10" t="n"/>
       <c r="L15" s="10" t="n"/>
       <c r="M15" s="11" t="n"/>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>セッションが切れました。再度ログインしてください</t>
+          <t>リクエストパラメータが不正です</t>
         </is>
       </c>
       <c r="O15" s="10" t="n"/>
@@ -13060,14 +14786,14 @@
       <c r="B16" s="35" t="n"/>
       <c r="I16" s="36" t="n"/>
       <c r="J16" s="17" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K16" s="10" t="n"/>
       <c r="L16" s="10" t="n"/>
       <c r="M16" s="11" t="n"/>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>この画面へのアクセス権限がありません</t>
+          <t>セッションが切れました。再度ログインしてください</t>
         </is>
       </c>
       <c r="O16" s="10" t="n"/>
@@ -13095,23 +14821,17 @@
       <c r="AK16" s="11" t="n"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="25" t="n"/>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="26" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="I17" s="36" t="n"/>
       <c r="J17" s="17" t="n">
-        <v>500</v>
+        <v>403</v>
       </c>
       <c r="K17" s="10" t="n"/>
       <c r="L17" s="10" t="n"/>
       <c r="M17" s="11" t="n"/>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>システムエラーが発生しました</t>
+          <t>この画面へのアクセス権限がありません</t>
         </is>
       </c>
       <c r="O17" s="10" t="n"/>
@@ -13138,92 +14858,68 @@
       <c r="AJ17" s="10" t="n"/>
       <c r="AK17" s="11" t="n"/>
     </row>
-    <row r="18" ht="19.5" customHeight="1"/>
-    <row r="19" ht="19.5" customHeight="1">
-      <c r="A19" s="27" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="26" t="n"/>
+      <c r="J18" s="17" t="n">
+        <v>500</v>
+      </c>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="11" t="n"/>
+      <c r="N18" s="19" t="inlineStr">
+        <is>
+          <t>システムエラーが発生しました</t>
+        </is>
+      </c>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n"/>
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="10" t="n"/>
+      <c r="Y18" s="10" t="n"/>
+      <c r="Z18" s="10" t="n"/>
+      <c r="AA18" s="10" t="n"/>
+      <c r="AB18" s="10" t="n"/>
+      <c r="AC18" s="10" t="n"/>
+      <c r="AD18" s="10" t="n"/>
+      <c r="AE18" s="10" t="n"/>
+      <c r="AF18" s="10" t="n"/>
+      <c r="AG18" s="10" t="n"/>
+      <c r="AH18" s="10" t="n"/>
+      <c r="AI18" s="10" t="n"/>
+      <c r="AJ18" s="10" t="n"/>
+      <c r="AK18" s="11" t="n"/>
+    </row>
+    <row r="19" ht="19.5" customHeight="1"/>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>2. リクエストパラメータ</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="19.5" customHeight="1"/>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="B21" s="30" t="inlineStr">
+    <row r="21" ht="19.5" customHeight="1"/>
+    <row r="22" ht="19.5" customHeight="1">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr">
         <is>
           <t>パラメーターID</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="11" t="n"/>
-      <c r="M21" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="n"/>
-      <c r="O21" s="10" t="n"/>
-      <c r="P21" s="11" t="n"/>
-      <c r="Q21" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R21" s="10" t="n"/>
-      <c r="S21" s="11" t="n"/>
-      <c r="T21" s="16" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="U21" s="10" t="n"/>
-      <c r="V21" s="10" t="n"/>
-      <c r="W21" s="10" t="n"/>
-      <c r="X21" s="11" t="n"/>
-      <c r="Y21" s="16" t="inlineStr">
-        <is>
-          <t>最小長</t>
-        </is>
-      </c>
-      <c r="Z21" s="10" t="n"/>
-      <c r="AA21" s="10" t="n"/>
-      <c r="AB21" s="11" t="n"/>
-      <c r="AC21" s="16" t="inlineStr">
-        <is>
-          <t>最大長</t>
-        </is>
-      </c>
-      <c r="AD21" s="10" t="n"/>
-      <c r="AE21" s="11" t="n"/>
-      <c r="AF21" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG21" s="10" t="n"/>
-      <c r="AH21" s="10" t="n"/>
-      <c r="AI21" s="10" t="n"/>
-      <c r="AJ21" s="10" t="n"/>
-      <c r="AK21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>todofuken_code</t>
         </is>
       </c>
       <c r="D22" s="10" t="n"/>
@@ -13235,44 +14931,48 @@
       <c r="J22" s="10" t="n"/>
       <c r="K22" s="10" t="n"/>
       <c r="L22" s="11" t="n"/>
-      <c r="M22" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
+      <c r="M22" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N22" s="10" t="n"/>
       <c r="O22" s="10" t="n"/>
       <c r="P22" s="11" t="n"/>
-      <c r="Q22" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q22" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R22" s="10" t="n"/>
       <c r="S22" s="11" t="n"/>
-      <c r="T22" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="T22" s="16" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
       <c r="U22" s="10" t="n"/>
       <c r="V22" s="10" t="n"/>
       <c r="W22" s="10" t="n"/>
       <c r="X22" s="11" t="n"/>
-      <c r="Y22" s="17" t="n">
-        <v>2</v>
+      <c r="Y22" s="16" t="inlineStr">
+        <is>
+          <t>最小長</t>
+        </is>
       </c>
       <c r="Z22" s="10" t="n"/>
       <c r="AA22" s="10" t="n"/>
       <c r="AB22" s="11" t="n"/>
-      <c r="AC22" s="17" t="n">
-        <v>2</v>
+      <c r="AC22" s="16" t="inlineStr">
+        <is>
+          <t>最大長</t>
+        </is>
       </c>
       <c r="AD22" s="10" t="n"/>
       <c r="AE22" s="11" t="n"/>
-      <c r="AF22" s="19" t="inlineStr">
-        <is>
-          <t>都道府県コード（01〜47）</t>
+      <c r="AF22" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG22" s="10" t="n"/>
@@ -13283,11 +14983,11 @@
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="B23" s="31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>role_id</t>
+          <t>q</t>
         </is>
       </c>
       <c r="D23" s="10" t="n"/>
@@ -13301,7 +15001,7 @@
       <c r="L23" s="11" t="n"/>
       <c r="M23" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N23" s="10" t="n"/>
@@ -13323,16 +15023,22 @@
       <c r="V23" s="10" t="n"/>
       <c r="W23" s="10" t="n"/>
       <c r="X23" s="11" t="n"/>
-      <c r="Y23" s="17" t="inlineStr"/>
+      <c r="Y23" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z23" s="10" t="n"/>
       <c r="AA23" s="10" t="n"/>
       <c r="AB23" s="11" t="n"/>
-      <c r="AC23" s="17" t="inlineStr"/>
+      <c r="AC23" s="17" t="n">
+        <v>100</v>
+      </c>
       <c r="AD23" s="10" t="n"/>
       <c r="AE23" s="11" t="n"/>
       <c r="AF23" s="19" t="inlineStr">
         <is>
-          <t>管理者区分（3:中央会→chuokai_flg=true、4,5:JA→chuokai_flg=false）</t>
+          <t>フリーテキスト検索。`ja_code` または `ja_name` に対する部分一致（ILIKE `%q%`）</t>
         </is>
       </c>
       <c r="AG23" s="10" t="n"/>
@@ -13341,24 +15047,193 @@
       <c r="AJ23" s="10" t="n"/>
       <c r="AK23" s="11" t="n"/>
     </row>
-    <row r="24" ht="19.5" customHeight="1"/>
-    <row r="25" ht="19.5" customHeight="1">
-      <c r="A25" s="27" t="inlineStr">
-        <is>
-          <t>3.レスポンスデータ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="19.5" customHeight="1"/>
-    <row r="27" ht="19.5" customHeight="1">
-      <c r="B27" s="30" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>項目ID</t>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="n"/>
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="11" t="n"/>
+      <c r="Q24" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="11" t="n"/>
+      <c r="T24" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U24" s="10" t="n"/>
+      <c r="V24" s="10" t="n"/>
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="11" t="n"/>
+      <c r="Y24" s="17" t="inlineStr"/>
+      <c r="Z24" s="10" t="n"/>
+      <c r="AA24" s="10" t="n"/>
+      <c r="AB24" s="11" t="n"/>
+      <c r="AC24" s="17" t="inlineStr"/>
+      <c r="AD24" s="10" t="n"/>
+      <c r="AE24" s="11" t="n"/>
+      <c r="AF24" s="19" t="inlineStr">
+        <is>
+          <t>ページ番号（1以上、デフォルト=1）</t>
+        </is>
+      </c>
+      <c r="AG24" s="10" t="n"/>
+      <c r="AH24" s="10" t="n"/>
+      <c r="AI24" s="10" t="n"/>
+      <c r="AJ24" s="10" t="n"/>
+      <c r="AK24" s="11" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="n"/>
+      <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="n"/>
+      <c r="S25" s="11" t="n"/>
+      <c r="T25" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U25" s="10" t="n"/>
+      <c r="V25" s="10" t="n"/>
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="11" t="n"/>
+      <c r="Y25" s="17" t="inlineStr"/>
+      <c r="Z25" s="10" t="n"/>
+      <c r="AA25" s="10" t="n"/>
+      <c r="AB25" s="11" t="n"/>
+      <c r="AC25" s="17" t="inlineStr"/>
+      <c r="AD25" s="10" t="n"/>
+      <c r="AE25" s="11" t="n"/>
+      <c r="AF25" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数（1〜100、デフォルト=50）</t>
+        </is>
+      </c>
+      <c r="AG25" s="10" t="n"/>
+      <c r="AH25" s="10" t="n"/>
+      <c r="AI25" s="10" t="n"/>
+      <c r="AJ25" s="10" t="n"/>
+      <c r="AK25" s="11" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="B26" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>include_id</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="10" t="n"/>
+      <c r="J26" s="10" t="n"/>
+      <c r="K26" s="10" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="n"/>
+      <c r="O26" s="10" t="n"/>
+      <c r="P26" s="11" t="n"/>
+      <c r="Q26" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R26" s="10" t="n"/>
+      <c r="S26" s="11" t="n"/>
+      <c r="T26" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U26" s="10" t="n"/>
+      <c r="V26" s="10" t="n"/>
+      <c r="W26" s="10" t="n"/>
+      <c r="X26" s="11" t="n"/>
+      <c r="Y26" s="17" t="inlineStr"/>
+      <c r="Z26" s="10" t="n"/>
+      <c r="AA26" s="10" t="n"/>
+      <c r="AB26" s="11" t="n"/>
+      <c r="AC26" s="17" t="inlineStr"/>
+      <c r="AD26" s="10" t="n"/>
+      <c r="AE26" s="11" t="n"/>
+      <c r="AF26" s="19" t="inlineStr">
+        <is>
+          <t>編集フォーム用エスケープハッチ。指定された ja_id がページ範囲に含まれない場合、レスポンス先頭に追加して返す。DataScope 制限により範囲外のIDは無視（silently dropped）</t>
+        </is>
+      </c>
+      <c r="AG26" s="10" t="n"/>
+      <c r="AH26" s="10" t="n"/>
+      <c r="AI26" s="10" t="n"/>
+      <c r="AJ26" s="10" t="n"/>
+      <c r="AK26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="B27" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="D27" s="10" t="n"/>
@@ -13370,44 +15245,44 @@
       <c r="J27" s="10" t="n"/>
       <c r="K27" s="10" t="n"/>
       <c r="L27" s="11" t="n"/>
-      <c r="M27" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M27" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
         </is>
       </c>
       <c r="N27" s="10" t="n"/>
       <c r="O27" s="10" t="n"/>
       <c r="P27" s="11" t="n"/>
-      <c r="Q27" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q27" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="R27" s="10" t="n"/>
       <c r="S27" s="11" t="n"/>
-      <c r="T27" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
+      <c r="T27" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="U27" s="10" t="n"/>
       <c r="V27" s="10" t="n"/>
       <c r="W27" s="10" t="n"/>
       <c r="X27" s="11" t="n"/>
-      <c r="Y27" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
+      <c r="Y27" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="Z27" s="10" t="n"/>
       <c r="AA27" s="10" t="n"/>
-      <c r="AB27" s="10" t="n"/>
-      <c r="AC27" s="10" t="n"/>
+      <c r="AB27" s="11" t="n"/>
+      <c r="AC27" s="17" t="n">
+        <v>2</v>
+      </c>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="11" t="n"/>
-      <c r="AF27" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF27" s="19" t="inlineStr">
+        <is>
+          <t>都道府県コード（01〜47）。完全一致でカスケード絞込み</t>
         </is>
       </c>
       <c r="AG27" s="10" t="n"/>
@@ -13416,13 +15291,13 @@
       <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="11" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
+    <row r="28" ht="36" customHeight="1">
       <c r="B28" s="31" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>role_id</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -13436,7 +15311,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -13444,30 +15319,30 @@
       <c r="P28" s="11" t="n"/>
       <c r="Q28" s="17" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R28" s="10" t="n"/>
       <c r="S28" s="11" t="n"/>
-      <c r="T28" s="17" t="inlineStr"/>
+      <c r="T28" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="U28" s="10" t="n"/>
       <c r="V28" s="10" t="n"/>
       <c r="W28" s="10" t="n"/>
       <c r="X28" s="11" t="n"/>
-      <c r="Y28" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y28" s="17" t="inlineStr"/>
       <c r="Z28" s="10" t="n"/>
       <c r="AA28" s="10" t="n"/>
-      <c r="AB28" s="10" t="n"/>
-      <c r="AC28" s="10" t="n"/>
+      <c r="AB28" s="11" t="n"/>
+      <c r="AC28" s="17" t="inlineStr"/>
       <c r="AD28" s="10" t="n"/>
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>JA一覧</t>
+          <t>管理者区分（3:中央会→`chuokai_flg=TRUE`、4,5:JA→`chuokai_flg=FALSE`、その他/未指定: 絞込みなし）</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -13476,16 +15351,16 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="54" customHeight="1">
       <c r="B29" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" s="37" t="n"/>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>ja_id</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>match_field</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n"/>
       <c r="E29" s="10" t="n"/>
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
@@ -13496,7 +15371,7 @@
       <c r="L29" s="11" t="n"/>
       <c r="M29" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N29" s="10" t="n"/>
@@ -13509,25 +15384,25 @@
       </c>
       <c r="R29" s="10" t="n"/>
       <c r="S29" s="11" t="n"/>
-      <c r="T29" s="17" t="inlineStr"/>
+      <c r="T29" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="U29" s="10" t="n"/>
       <c r="V29" s="10" t="n"/>
       <c r="W29" s="10" t="n"/>
       <c r="X29" s="11" t="n"/>
-      <c r="Y29" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y29" s="17" t="inlineStr"/>
       <c r="Z29" s="10" t="n"/>
       <c r="AA29" s="10" t="n"/>
-      <c r="AB29" s="10" t="n"/>
-      <c r="AC29" s="10" t="n"/>
+      <c r="AB29" s="11" t="n"/>
+      <c r="AC29" s="17" t="inlineStr"/>
       <c r="AD29" s="10" t="n"/>
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>検索対象フィールド。`both`（既定）=`ja_code` OR `ja_name`、`name`=`ja_name`のみ（`ja_code`非表示のACSMS-SCR-024用）</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -13536,16 +15411,16 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="36" customHeight="1">
       <c r="B30" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="19" t="inlineStr">
-        <is>
-          <t>ja_code</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n"/>
       <c r="E30" s="10" t="n"/>
       <c r="F30" s="10" t="n"/>
       <c r="G30" s="10" t="n"/>
@@ -13569,25 +15444,25 @@
       </c>
       <c r="R30" s="10" t="n"/>
       <c r="S30" s="11" t="n"/>
-      <c r="T30" s="17" t="inlineStr"/>
+      <c r="T30" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="U30" s="10" t="n"/>
       <c r="V30" s="10" t="n"/>
       <c r="W30" s="10" t="n"/>
       <c r="X30" s="11" t="n"/>
-      <c r="Y30" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="Y30" s="17" t="inlineStr"/>
       <c r="Z30" s="10" t="n"/>
       <c r="AA30" s="10" t="n"/>
-      <c r="AB30" s="10" t="n"/>
-      <c r="AC30" s="10" t="n"/>
+      <c r="AB30" s="11" t="n"/>
+      <c r="AC30" s="17" t="inlineStr"/>
       <c r="AD30" s="10" t="n"/>
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>JAコード</t>
+          <t>DataScope範囲。`own`（既定）=自組織階層のみ、`todofuken`=中央会(CHUOKAI)限定で自都道府県の全JAへ拡大（ACSMS-SCR-022専用）</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -13596,201 +15471,151 @@
       <c r="AJ30" s="10" t="n"/>
       <c r="AK30" s="11" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="B31" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="38" t="n"/>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>ja_name</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="10" t="n"/>
-      <c r="H31" s="10" t="n"/>
-      <c r="I31" s="10" t="n"/>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="10" t="n"/>
-      <c r="L31" s="11" t="n"/>
-      <c r="M31" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N31" s="10" t="n"/>
-      <c r="O31" s="10" t="n"/>
-      <c r="P31" s="11" t="n"/>
-      <c r="Q31" s="17" t="inlineStr">
+    <row r="31" ht="19.5" customHeight="1"/>
+    <row r="32" ht="19.5" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19.5" customHeight="1"/>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="10" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="11" t="n"/>
+      <c r="Q34" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="11" t="n"/>
+      <c r="T34" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n"/>
+      <c r="W34" s="10" t="n"/>
+      <c r="X34" s="11" t="n"/>
+      <c r="Y34" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="Z34" s="10" t="n"/>
+      <c r="AA34" s="10" t="n"/>
+      <c r="AB34" s="10" t="n"/>
+      <c r="AC34" s="10" t="n"/>
+      <c r="AD34" s="10" t="n"/>
+      <c r="AE34" s="11" t="n"/>
+      <c r="AF34" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG34" s="10" t="n"/>
+      <c r="AH34" s="10" t="n"/>
+      <c r="AI34" s="10" t="n"/>
+      <c r="AJ34" s="10" t="n"/>
+      <c r="AK34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="B35" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="17" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="11" t="n"/>
+      <c r="Q35" s="17" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="11" t="n"/>
+      <c r="T35" s="17" t="inlineStr"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="11" t="n"/>
+      <c r="Y35" s="17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R31" s="10" t="n"/>
-      <c r="S31" s="11" t="n"/>
-      <c r="T31" s="17" t="inlineStr"/>
-      <c r="U31" s="10" t="n"/>
-      <c r="V31" s="10" t="n"/>
-      <c r="W31" s="10" t="n"/>
-      <c r="X31" s="11" t="n"/>
-      <c r="Y31" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z31" s="10" t="n"/>
-      <c r="AA31" s="10" t="n"/>
-      <c r="AB31" s="10" t="n"/>
-      <c r="AC31" s="10" t="n"/>
-      <c r="AD31" s="10" t="n"/>
-      <c r="AE31" s="11" t="n"/>
-      <c r="AF31" s="19" t="inlineStr">
-        <is>
-          <t>JA名称</t>
-        </is>
-      </c>
-      <c r="AG31" s="10" t="n"/>
-      <c r="AH31" s="10" t="n"/>
-      <c r="AI31" s="10" t="n"/>
-      <c r="AJ31" s="10" t="n"/>
-      <c r="AK31" s="11" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>todofuken_code</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N32" s="10" t="n"/>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R32" s="10" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="17" t="inlineStr"/>
-      <c r="U32" s="10" t="n"/>
-      <c r="V32" s="10" t="n"/>
-      <c r="W32" s="10" t="n"/>
-      <c r="X32" s="11" t="n"/>
-      <c r="Y32" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z32" s="10" t="n"/>
-      <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="10" t="n"/>
-      <c r="AC32" s="10" t="n"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="11" t="n"/>
-      <c r="AF32" s="19" t="inlineStr">
-        <is>
-          <t>都道府県コード</t>
-        </is>
-      </c>
-      <c r="AG32" s="10" t="n"/>
-      <c r="AH32" s="10" t="n"/>
-      <c r="AI32" s="10" t="n"/>
-      <c r="AJ32" s="10" t="n"/>
-      <c r="AK32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="C33" s="39" t="n"/>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>chuokai_flg</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="11" t="n"/>
-      <c r="M33" s="17" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="N33" s="10" t="n"/>
-      <c r="O33" s="10" t="n"/>
-      <c r="P33" s="11" t="n"/>
-      <c r="Q33" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R33" s="10" t="n"/>
-      <c r="S33" s="11" t="n"/>
-      <c r="T33" s="17" t="inlineStr"/>
-      <c r="U33" s="10" t="n"/>
-      <c r="V33" s="10" t="n"/>
-      <c r="W33" s="10" t="n"/>
-      <c r="X33" s="11" t="n"/>
-      <c r="Y33" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z33" s="10" t="n"/>
-      <c r="AA33" s="10" t="n"/>
-      <c r="AB33" s="10" t="n"/>
-      <c r="AC33" s="10" t="n"/>
-      <c r="AD33" s="10" t="n"/>
-      <c r="AE33" s="11" t="n"/>
-      <c r="AF33" s="19" t="inlineStr">
-        <is>
-          <t>中央会フラグ</t>
-        </is>
-      </c>
-      <c r="AG33" s="10" t="n"/>
-      <c r="AH33" s="10" t="n"/>
-      <c r="AI33" s="10" t="n"/>
-      <c r="AJ33" s="10" t="n"/>
-      <c r="AK33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="19.5" customHeight="1"/>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="B35" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+      <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n"/>
+      <c r="AB35" s="10" t="n"/>
+      <c r="AC35" s="10" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="11" t="n"/>
+      <c r="AF35" s="19" t="inlineStr">
+        <is>
+          <t>JA一覧</t>
+        </is>
+      </c>
+      <c r="AG35" s="10" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="10" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="11" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/ja/dropdown?todofuken_code=13&amp;role_id=3</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="n"/>
+      <c r="B36" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="37" t="n"/>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>ja_id</t>
+        </is>
+      </c>
       <c r="E36" s="10" t="n"/>
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
@@ -13798,57 +15623,179 @@
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="10" t="n"/>
       <c r="K36" s="10" t="n"/>
-      <c r="L36" s="10" t="n"/>
-      <c r="M36" s="10" t="n"/>
+      <c r="L36" s="11" t="n"/>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
       <c r="N36" s="10" t="n"/>
       <c r="O36" s="10" t="n"/>
-      <c r="P36" s="10" t="n"/>
-      <c r="Q36" s="10" t="n"/>
+      <c r="P36" s="11" t="n"/>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R36" s="10" t="n"/>
-      <c r="S36" s="10" t="n"/>
-      <c r="T36" s="10" t="n"/>
+      <c r="S36" s="11" t="n"/>
+      <c r="T36" s="17" t="inlineStr"/>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
       <c r="W36" s="10" t="n"/>
-      <c r="X36" s="10" t="n"/>
-      <c r="Y36" s="10" t="n"/>
+      <c r="X36" s="11" t="n"/>
+      <c r="Y36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z36" s="10" t="n"/>
       <c r="AA36" s="10" t="n"/>
       <c r="AB36" s="10" t="n"/>
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
-      <c r="AE36" s="10" t="n"/>
-      <c r="AF36" s="10" t="n"/>
+      <c r="AE36" s="11" t="n"/>
+      <c r="AF36" s="19" t="inlineStr">
+        <is>
+          <t>JA ID</t>
+        </is>
+      </c>
       <c r="AG36" s="10" t="n"/>
       <c r="AH36" s="10" t="n"/>
       <c r="AI36" s="10" t="n"/>
       <c r="AJ36" s="10" t="n"/>
       <c r="AK36" s="11" t="n"/>
     </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="B38" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（成功）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="198" customHeight="1">
-      <c r="C39" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "data": [
-    {
-      "ja_id": 1,
-      "ja_code": "1300001",
-      "ja_name": "東京都中央会",
-      "todofuken_code": "13",
-      "chuokai_flg": true
-    }
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="n"/>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>ja_code</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="10" t="n"/>
+      <c r="K37" s="10" t="n"/>
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="11" t="n"/>
+      <c r="Q37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R37" s="10" t="n"/>
+      <c r="S37" s="11" t="n"/>
+      <c r="T37" s="17" t="inlineStr"/>
+      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="10" t="n"/>
+      <c r="W37" s="10" t="n"/>
+      <c r="X37" s="11" t="n"/>
+      <c r="Y37" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z37" s="10" t="n"/>
+      <c r="AA37" s="10" t="n"/>
+      <c r="AB37" s="10" t="n"/>
+      <c r="AC37" s="10" t="n"/>
+      <c r="AD37" s="10" t="n"/>
+      <c r="AE37" s="11" t="n"/>
+      <c r="AF37" s="19" t="inlineStr">
+        <is>
+          <t>JAコード</t>
+        </is>
+      </c>
+      <c r="AG37" s="10" t="n"/>
+      <c r="AH37" s="10" t="n"/>
+      <c r="AI37" s="10" t="n"/>
+      <c r="AJ37" s="10" t="n"/>
+      <c r="AK37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>ja_name</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="11" t="n"/>
+      <c r="Q38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="11" t="n"/>
+      <c r="T38" s="17" t="inlineStr"/>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="11" t="n"/>
+      <c r="Y38" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z38" s="10" t="n"/>
+      <c r="AA38" s="10" t="n"/>
+      <c r="AB38" s="10" t="n"/>
+      <c r="AC38" s="10" t="n"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="11" t="n"/>
+      <c r="AF38" s="19" t="inlineStr">
+        <is>
+          <t>JA名称</t>
+        </is>
+      </c>
+      <c r="AG38" s="10" t="n"/>
+      <c r="AH38" s="10" t="n"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
+      <c r="AK38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>todofuken_code</t>
+        </is>
+      </c>
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
@@ -13856,50 +15803,179 @@
       <c r="I39" s="10" t="n"/>
       <c r="J39" s="10" t="n"/>
       <c r="K39" s="10" t="n"/>
-      <c r="L39" s="10" t="n"/>
-      <c r="M39" s="10" t="n"/>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
       <c r="N39" s="10" t="n"/>
       <c r="O39" s="10" t="n"/>
-      <c r="P39" s="10" t="n"/>
-      <c r="Q39" s="10" t="n"/>
+      <c r="P39" s="11" t="n"/>
+      <c r="Q39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R39" s="10" t="n"/>
-      <c r="S39" s="10" t="n"/>
-      <c r="T39" s="10" t="n"/>
+      <c r="S39" s="11" t="n"/>
+      <c r="T39" s="17" t="inlineStr"/>
       <c r="U39" s="10" t="n"/>
       <c r="V39" s="10" t="n"/>
       <c r="W39" s="10" t="n"/>
-      <c r="X39" s="10" t="n"/>
-      <c r="Y39" s="10" t="n"/>
+      <c r="X39" s="11" t="n"/>
+      <c r="Y39" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z39" s="10" t="n"/>
       <c r="AA39" s="10" t="n"/>
       <c r="AB39" s="10" t="n"/>
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
-      <c r="AE39" s="10" t="n"/>
-      <c r="AF39" s="10" t="n"/>
+      <c r="AE39" s="11" t="n"/>
+      <c r="AF39" s="19" t="inlineStr">
+        <is>
+          <t>都道府県コード</t>
+        </is>
+      </c>
       <c r="AG39" s="10" t="n"/>
       <c r="AH39" s="10" t="n"/>
       <c r="AI39" s="10" t="n"/>
       <c r="AJ39" s="10" t="n"/>
       <c r="AK39" s="11" t="n"/>
     </row>
-    <row r="41" ht="19.5" customHeight="1">
-      <c r="B41" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 401 Unauthorized）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="72" customHeight="1">
-      <c r="C42" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください"
-}</t>
-        </is>
-      </c>
-      <c r="D42" s="10" t="n"/>
+    <row r="40" ht="18" customHeight="1">
+      <c r="B40" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C40" s="39" t="n"/>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>chuokai_flg</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="10" t="n"/>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="11" t="n"/>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="11" t="n"/>
+      <c r="T40" s="17" t="inlineStr"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="10" t="n"/>
+      <c r="X40" s="11" t="n"/>
+      <c r="Y40" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z40" s="10" t="n"/>
+      <c r="AA40" s="10" t="n"/>
+      <c r="AB40" s="10" t="n"/>
+      <c r="AC40" s="10" t="n"/>
+      <c r="AD40" s="10" t="n"/>
+      <c r="AE40" s="11" t="n"/>
+      <c r="AF40" s="19" t="inlineStr">
+        <is>
+          <t>中央会フラグ</t>
+        </is>
+      </c>
+      <c r="AG40" s="10" t="n"/>
+      <c r="AH40" s="10" t="n"/>
+      <c r="AI40" s="10" t="n"/>
+      <c r="AJ40" s="10" t="n"/>
+      <c r="AK40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="C41" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="10" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="11" t="n"/>
+      <c r="M41" s="17" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="11" t="n"/>
+      <c r="Q41" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="11" t="n"/>
+      <c r="T41" s="17" t="inlineStr"/>
+      <c r="U41" s="10" t="n"/>
+      <c r="V41" s="10" t="n"/>
+      <c r="W41" s="10" t="n"/>
+      <c r="X41" s="11" t="n"/>
+      <c r="Y41" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z41" s="10" t="n"/>
+      <c r="AA41" s="10" t="n"/>
+      <c r="AB41" s="10" t="n"/>
+      <c r="AC41" s="10" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="11" t="n"/>
+      <c r="AF41" s="19" t="inlineStr">
+        <is>
+          <t>ページングメタ</t>
+        </is>
+      </c>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="10" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41" s="10" t="n"/>
+      <c r="AK41" s="11" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="B42" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="37" t="n"/>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
       <c r="E42" s="10" t="n"/>
       <c r="F42" s="10" t="n"/>
       <c r="G42" s="10" t="n"/>
@@ -13907,50 +15983,179 @@
       <c r="I42" s="10" t="n"/>
       <c r="J42" s="10" t="n"/>
       <c r="K42" s="10" t="n"/>
-      <c r="L42" s="10" t="n"/>
-      <c r="M42" s="10" t="n"/>
+      <c r="L42" s="11" t="n"/>
+      <c r="M42" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
       <c r="N42" s="10" t="n"/>
       <c r="O42" s="10" t="n"/>
-      <c r="P42" s="10" t="n"/>
-      <c r="Q42" s="10" t="n"/>
+      <c r="P42" s="11" t="n"/>
+      <c r="Q42" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R42" s="10" t="n"/>
-      <c r="S42" s="10" t="n"/>
-      <c r="T42" s="10" t="n"/>
+      <c r="S42" s="11" t="n"/>
+      <c r="T42" s="17" t="inlineStr"/>
       <c r="U42" s="10" t="n"/>
       <c r="V42" s="10" t="n"/>
       <c r="W42" s="10" t="n"/>
-      <c r="X42" s="10" t="n"/>
-      <c r="Y42" s="10" t="n"/>
+      <c r="X42" s="11" t="n"/>
+      <c r="Y42" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z42" s="10" t="n"/>
       <c r="AA42" s="10" t="n"/>
       <c r="AB42" s="10" t="n"/>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
-      <c r="AE42" s="10" t="n"/>
-      <c r="AF42" s="10" t="n"/>
+      <c r="AE42" s="11" t="n"/>
+      <c r="AF42" s="19" t="inlineStr">
+        <is>
+          <t>DataScope 適用後の総件数（カスケード絞込み込み）</t>
+        </is>
+      </c>
       <c r="AG42" s="10" t="n"/>
       <c r="AH42" s="10" t="n"/>
       <c r="AI42" s="10" t="n"/>
       <c r="AJ42" s="10" t="n"/>
       <c r="AK42" s="11" t="n"/>
     </row>
-    <row r="44" ht="19.5" customHeight="1">
-      <c r="B44" s="40" t="inlineStr">
-        <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="72" customHeight="1">
-      <c r="C45" s="19" t="inlineStr">
-        <is>
-          <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
-}</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="n"/>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="10" t="n"/>
+      <c r="K43" s="10" t="n"/>
+      <c r="L43" s="11" t="n"/>
+      <c r="M43" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="n"/>
+      <c r="O43" s="10" t="n"/>
+      <c r="P43" s="11" t="n"/>
+      <c r="Q43" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="11" t="n"/>
+      <c r="T43" s="17" t="inlineStr"/>
+      <c r="U43" s="10" t="n"/>
+      <c r="V43" s="10" t="n"/>
+      <c r="W43" s="10" t="n"/>
+      <c r="X43" s="11" t="n"/>
+      <c r="Y43" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z43" s="10" t="n"/>
+      <c r="AA43" s="10" t="n"/>
+      <c r="AB43" s="10" t="n"/>
+      <c r="AC43" s="10" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="11" t="n"/>
+      <c r="AF43" s="19" t="inlineStr">
+        <is>
+          <t>現在のページ番号</t>
+        </is>
+      </c>
+      <c r="AG43" s="10" t="n"/>
+      <c r="AH43" s="10" t="n"/>
+      <c r="AI43" s="10" t="n"/>
+      <c r="AJ43" s="10" t="n"/>
+      <c r="AK43" s="11" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="11" t="n"/>
+      <c r="M44" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="n"/>
+      <c r="P44" s="11" t="n"/>
+      <c r="Q44" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="11" t="n"/>
+      <c r="T44" s="17" t="inlineStr"/>
+      <c r="U44" s="10" t="n"/>
+      <c r="V44" s="10" t="n"/>
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="11" t="n"/>
+      <c r="Y44" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z44" s="10" t="n"/>
+      <c r="AA44" s="10" t="n"/>
+      <c r="AB44" s="10" t="n"/>
+      <c r="AC44" s="10" t="n"/>
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="11" t="n"/>
+      <c r="AF44" s="19" t="inlineStr">
+        <is>
+          <t>1ページの件数</t>
+        </is>
+      </c>
+      <c r="AG44" s="10" t="n"/>
+      <c r="AH44" s="10" t="n"/>
+      <c r="AI44" s="10" t="n"/>
+      <c r="AJ44" s="10" t="n"/>
+      <c r="AK44" s="11" t="n"/>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="B45" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C45" s="39" t="n"/>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>has_more</t>
+        </is>
+      </c>
       <c r="E45" s="10" t="n"/>
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
@@ -13958,47 +16163,61 @@
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="10" t="n"/>
       <c r="K45" s="10" t="n"/>
-      <c r="L45" s="10" t="n"/>
-      <c r="M45" s="10" t="n"/>
+      <c r="L45" s="11" t="n"/>
+      <c r="M45" s="17" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
       <c r="N45" s="10" t="n"/>
       <c r="O45" s="10" t="n"/>
-      <c r="P45" s="10" t="n"/>
-      <c r="Q45" s="10" t="n"/>
+      <c r="P45" s="11" t="n"/>
+      <c r="Q45" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R45" s="10" t="n"/>
-      <c r="S45" s="10" t="n"/>
-      <c r="T45" s="10" t="n"/>
+      <c r="S45" s="11" t="n"/>
+      <c r="T45" s="17" t="inlineStr"/>
       <c r="U45" s="10" t="n"/>
       <c r="V45" s="10" t="n"/>
       <c r="W45" s="10" t="n"/>
-      <c r="X45" s="10" t="n"/>
-      <c r="Y45" s="10" t="n"/>
+      <c r="X45" s="11" t="n"/>
+      <c r="Y45" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z45" s="10" t="n"/>
       <c r="AA45" s="10" t="n"/>
       <c r="AB45" s="10" t="n"/>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
-      <c r="AE45" s="10" t="n"/>
-      <c r="AF45" s="10" t="n"/>
+      <c r="AE45" s="11" t="n"/>
+      <c r="AF45" s="19" t="inlineStr">
+        <is>
+          <t>次ページが存在するか（`page * per_page &lt; total`）</t>
+        </is>
+      </c>
       <c r="AG45" s="10" t="n"/>
       <c r="AH45" s="10" t="n"/>
       <c r="AI45" s="10" t="n"/>
       <c r="AJ45" s="10" t="n"/>
       <c r="AK45" s="11" t="n"/>
     </row>
+    <row r="46" ht="19.5" customHeight="1"/>
     <row r="47" ht="19.5" customHeight="1">
       <c r="B47" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="72" customHeight="1">
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
       <c r="C48" s="19" t="inlineStr">
         <is>
-          <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
-}</t>
+          <t>GET /api/v1/ja/dropdown?q=東京&amp;page=1&amp;per_page=50</t>
         </is>
       </c>
       <c r="D48" s="10" t="n"/>
@@ -14036,352 +16255,723 @@
       <c r="AJ48" s="10" t="n"/>
       <c r="AK48" s="11" t="n"/>
     </row>
-    <row r="50" ht="19.5" customHeight="1"/>
-    <row r="51" ht="19.5" customHeight="1">
-      <c r="A51" s="27" t="inlineStr">
+    <row r="50" ht="19.5" customHeight="1">
+      <c r="B50" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（成功）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="306" customHeight="1">
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "data": [
+    {
+      "ja_id": 1,
+      "ja_code": "1300001",
+      "ja_name": "東京都中央会",
+      "todofuken_code": "13",
+      "chuokai_flg": true
+    }
+  ],
+  "meta": {
+    "total": 1,
+    "page": 1,
+    "per_page": 50,
+    "has_more": false
+  }
+}</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="10" t="n"/>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="10" t="n"/>
+      <c r="M51" s="10" t="n"/>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="10" t="n"/>
+      <c r="Q51" s="10" t="n"/>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
+      <c r="U51" s="10" t="n"/>
+      <c r="V51" s="10" t="n"/>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="10" t="n"/>
+      <c r="Y51" s="10" t="n"/>
+      <c r="Z51" s="10" t="n"/>
+      <c r="AA51" s="10" t="n"/>
+      <c r="AB51" s="10" t="n"/>
+      <c r="AC51" s="10" t="n"/>
+      <c r="AD51" s="10" t="n"/>
+      <c r="AE51" s="10" t="n"/>
+      <c r="AF51" s="10" t="n"/>
+      <c r="AG51" s="10" t="n"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="10" t="n"/>
+      <c r="AJ51" s="10" t="n"/>
+      <c r="AK51" s="11" t="n"/>
+    </row>
+    <row r="53" ht="19.5" customHeight="1">
+      <c r="B53" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 401 Unauthorized）</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="72" customHeight="1">
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "UNAUTHORIZED",
+  "message": "セッションが切れました。再度ログインしてください"
+}</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="10" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="10" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="n"/>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="10" t="n"/>
+      <c r="Z54" s="10" t="n"/>
+      <c r="AA54" s="10" t="n"/>
+      <c r="AB54" s="10" t="n"/>
+      <c r="AC54" s="10" t="n"/>
+      <c r="AD54" s="10" t="n"/>
+      <c r="AE54" s="10" t="n"/>
+      <c r="AF54" s="10" t="n"/>
+      <c r="AG54" s="10" t="n"/>
+      <c r="AH54" s="10" t="n"/>
+      <c r="AI54" s="10" t="n"/>
+      <c r="AJ54" s="10" t="n"/>
+      <c r="AK54" s="11" t="n"/>
+    </row>
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="B56" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 403 Forbidden）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="72" customHeight="1">
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません"
+}</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="11" t="n"/>
+    </row>
+    <row r="59" ht="19.5" customHeight="1">
+      <c r="B59" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="72" customHeight="1">
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+}</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="10" t="n"/>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="10" t="n"/>
+      <c r="T60" s="10" t="n"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="10" t="n"/>
+      <c r="Y60" s="10" t="n"/>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="10" t="n"/>
+      <c r="AF60" s="10" t="n"/>
+      <c r="AG60" s="10" t="n"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
+      <c r="AK60" s="11" t="n"/>
+    </row>
+    <row r="62" ht="19.5" customHeight="1"/>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="B52" s="27" t="inlineStr">
-        <is>
-          <t>4.1 リクエストのバリデーション</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="C53" s="41" t="inlineStr">
-        <is>
-          <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="D54" s="41" t="inlineStr">
-        <is>
-          <t>todofuken_code：2桁の文字列（01〜47）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="D55" s="41" t="inlineStr">
-        <is>
-          <t>role_id：1〜5の整数</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="18" customHeight="1">
-      <c r="C56" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="D57" s="41" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request を返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="C59" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="C60" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="C61" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：認証済みユーザーであればアクセス可能。</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="D62" s="41" t="inlineStr">
-        <is>
-          <t>※ 呼び出し元画面の権限に依存する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="C63" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="B64" s="27" t="inlineStr">
         <is>
-          <t>4.3 データ取得</t>
+          <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
       <c r="C65" s="41" t="inlineStr">
         <is>
-          <t>管理者区分によりカスケード条件を切り替える。</t>
+          <t>クエリパラメータの検証：</t>
         </is>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="D66" s="41" t="inlineStr">
         <is>
-          <t>role_id = 3（中央会）の場合：`chuokai_flg = true` のJAを取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="36" customHeight="1">
+          <t>q：最大100文字（部分一致用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
       <c r="D67" s="41" t="inlineStr">
         <is>
-          <t>role_id = 4（JA本店）または 5（JA管理支店）の場合：`chuokai_flg = false` のJAを取得</t>
+          <t>page：1以上の整数</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="D68" s="41" t="inlineStr">
         <is>
-          <t>role_id 未指定またはその他の場合：全てのJAを取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="216" customHeight="1">
-      <c r="C69" s="42" t="inlineStr">
+          <t>per_page：1〜100の整数</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="D69" s="41" t="inlineStr">
+        <is>
+          <t>include_id：1以上の整数</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="D70" s="41" t="inlineStr">
+        <is>
+          <t>todofuken_code：2桁の文字列（01〜47）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="D71" s="41" t="inlineStr">
+        <is>
+          <t>role_id：1以上の整数</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="D72" s="41" t="inlineStr">
+        <is>
+          <t>match_field：`both` / `name` のいずれか（任意、既定 `both`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="D73" s="41" t="inlineStr">
+        <is>
+          <t>scope：`own` / `todofuken` のいずれか（任意、既定 `own`）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="C74" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="D75" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request を返却する（`VALIDATION_ERROR`）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="B76" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="C77" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="C78" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="72" customHeight="1">
+      <c r="C79" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：認証済みユーザーであればアクセス可能（`@Permissions` なし）。単一のCRUD権限（例 `ja.view`）で塞ぐと、その権限を持たない呼び出し元画面（例 JA_KANRI_SHITEN は `file.upload` はあるが `ja.view` なし）を締め出してしまうため。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="D80" s="41" t="inlineStr">
+        <is>
+          <t>※ 画面へのアクセス制御自体は呼び出し元画面のルートガードが担保する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)（未認証の場合を除き通常発生しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="C82" s="41" t="inlineStr">
+        <is>
+          <t>DataScope 適用：非 NICHINO_ADMIN/STAFF は自組織配下の JA のみ取得可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="B83" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="C84" s="41" t="inlineStr">
+        <is>
+          <t>フィルタ適用順：</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="C85" s="41" t="inlineStr">
+        <is>
+          <t>ソート：`ja_code ASC` 固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>ページング：`LIMIT :per_page OFFSET (page-1)*per_page`</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
+        <is>
+          <t>`meta.total` は LIMIT 適用前の総件数（DataScope + 絞込み適用後）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="C88" s="41" t="inlineStr">
+        <is>
+          <t>`meta.has_more = page * per_page &lt; total`</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
+        <is>
+          <t>`include_id` 指定時：上記ページ範囲に含まれていなければ、別途同一条件で SELECT して先頭に prepend。DataScope 範囲外なら silently 無視。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="342" customHeight="1">
+      <c r="C90" s="42" t="inlineStr">
         <is>
           <t>SELECT ja_id, ja_code, ja_name, todofuken_code, chuokai_flg
 FROM m_ja
 WHERE deleted_at IS NULL
+  -- DataScope (auto-applied per session role)
+  AND (:scope_ja_id IS NULL OR ja_id = :scope_ja_id)
+  -- q: free-text partial match
+  AND (:q IS NULL OR ja_code ILIKE :q_like OR ja_name ILIKE :q_like)
+  -- todofuken cascade
   AND (:todofuken_code IS NULL OR todofuken_code = :todofuken_code)
+  -- role_id cascade
   AND (
     CASE
-      WHEN :role_id = 3 THEN chuokai_flg = true
-      WHEN :role_id IN (4, 5) THEN chuokai_flg = false
-      ELSE true
+      WHEN :role_id = 3 THEN chuokai_flg = TRUE
+      WHEN :role_id IN (4, 5) THEN chuokai_flg = FALSE
+      ELSE TRUE
     END
   )
-ORDER BY ja_code ASC</t>
-        </is>
-      </c>
-      <c r="D69" s="10" t="n"/>
-      <c r="E69" s="10" t="n"/>
-      <c r="F69" s="10" t="n"/>
-      <c r="G69" s="10" t="n"/>
-      <c r="H69" s="10" t="n"/>
-      <c r="I69" s="10" t="n"/>
-      <c r="J69" s="10" t="n"/>
-      <c r="K69" s="10" t="n"/>
-      <c r="L69" s="10" t="n"/>
-      <c r="M69" s="10" t="n"/>
-      <c r="N69" s="10" t="n"/>
-      <c r="O69" s="10" t="n"/>
-      <c r="P69" s="10" t="n"/>
-      <c r="Q69" s="10" t="n"/>
-      <c r="R69" s="10" t="n"/>
-      <c r="S69" s="10" t="n"/>
-      <c r="T69" s="10" t="n"/>
-      <c r="U69" s="10" t="n"/>
-      <c r="V69" s="10" t="n"/>
-      <c r="W69" s="10" t="n"/>
-      <c r="X69" s="10" t="n"/>
-      <c r="Y69" s="10" t="n"/>
-      <c r="Z69" s="10" t="n"/>
-      <c r="AA69" s="10" t="n"/>
-      <c r="AB69" s="10" t="n"/>
-      <c r="AC69" s="10" t="n"/>
-      <c r="AD69" s="10" t="n"/>
-      <c r="AE69" s="10" t="n"/>
-      <c r="AF69" s="10" t="n"/>
-      <c r="AG69" s="10" t="n"/>
-      <c r="AH69" s="10" t="n"/>
-      <c r="AI69" s="10" t="n"/>
-      <c r="AJ69" s="10" t="n"/>
-      <c r="AK69" s="11" t="n"/>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="B70" s="27" t="inlineStr">
+ORDER BY ja_code ASC
+LIMIT :per_page OFFSET (:page - 1) * :per_page</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
+      <c r="AF90" s="10" t="n"/>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="B91" s="27" t="inlineStr">
         <is>
           <t>4.4 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="C71" s="41" t="inlineStr">
+    <row r="92" ht="18" customHeight="1">
+      <c r="C92" s="41" t="inlineStr">
         <is>
           <t>取得結果を data 配列として返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="B72" s="27" t="inlineStr">
+    <row r="93" ht="18" customHeight="1">
+      <c r="B93" s="27" t="inlineStr">
         <is>
           <t>4.5 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
-      <c r="C73" s="41" t="inlineStr">
+    <row r="94" ht="18" customHeight="1">
+      <c r="C94" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="137">
+  <mergeCells count="221">
     <mergeCell ref="J11:AK11"/>
+    <mergeCell ref="Y28:AB28"/>
     <mergeCell ref="Q29:S29"/>
-    <mergeCell ref="Y27:AE27"/>
+    <mergeCell ref="C57:AK57"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="T33:X33"/>
+    <mergeCell ref="Y36:AE36"/>
+    <mergeCell ref="T24:X24"/>
+    <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="AC23:AE23"/>
-    <mergeCell ref="C53:AK53"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="D71:AK71"/>
+    <mergeCell ref="C77:AK77"/>
+    <mergeCell ref="N18:AK18"/>
     <mergeCell ref="M29:P29"/>
+    <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="C86:AK86"/>
+    <mergeCell ref="B56:I56"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
-    <mergeCell ref="C45:AK45"/>
+    <mergeCell ref="D73:AK73"/>
+    <mergeCell ref="A63:AK63"/>
+    <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="C34:L34"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="C65:AK65"/>
-    <mergeCell ref="D33:L33"/>
+    <mergeCell ref="C94:AK94"/>
+    <mergeCell ref="Q41:S41"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="Y21:AB21"/>
+    <mergeCell ref="M35:P35"/>
     <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="AF36:AK36"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="Q43:S43"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="B9:I9"/>
-    <mergeCell ref="T31:X31"/>
+    <mergeCell ref="AF34:AK34"/>
+    <mergeCell ref="C51:AK51"/>
     <mergeCell ref="C22:L22"/>
-    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="Q42:S42"/>
+    <mergeCell ref="M25:P25"/>
     <mergeCell ref="T28:X28"/>
+    <mergeCell ref="Y40:AE40"/>
     <mergeCell ref="C48:AK48"/>
-    <mergeCell ref="M33:P33"/>
+    <mergeCell ref="B91:AK91"/>
+    <mergeCell ref="T37:X37"/>
+    <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="D75:AK75"/>
+    <mergeCell ref="M45:P45"/>
     <mergeCell ref="T30:X30"/>
+    <mergeCell ref="B93:AK93"/>
     <mergeCell ref="B47:I47"/>
+    <mergeCell ref="D72:AK72"/>
+    <mergeCell ref="C42:C45"/>
     <mergeCell ref="T29:X29"/>
+    <mergeCell ref="AF44:AK44"/>
+    <mergeCell ref="A32:AK32"/>
+    <mergeCell ref="T38:X38"/>
+    <mergeCell ref="C36:C40"/>
+    <mergeCell ref="B59:I59"/>
     <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="Y33:AE33"/>
+    <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="Q44:S44"/>
     <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="C42:AK42"/>
+    <mergeCell ref="D37:L37"/>
+    <mergeCell ref="C74:AK74"/>
     <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="AF32:AK32"/>
+    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="Z2:AC3"/>
+    <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="AF41:AK41"/>
+    <mergeCell ref="C24:L24"/>
+    <mergeCell ref="AF35:AK35"/>
+    <mergeCell ref="D39:L39"/>
     <mergeCell ref="AD2:AG3"/>
-    <mergeCell ref="AC21:AE21"/>
+    <mergeCell ref="M44:P44"/>
+    <mergeCell ref="B14:I18"/>
     <mergeCell ref="B13:I13"/>
-    <mergeCell ref="D29:L29"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="Y30:AE30"/>
+    <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="AF38:AK38"/>
+    <mergeCell ref="D38:L38"/>
+    <mergeCell ref="T40:X40"/>
+    <mergeCell ref="C26:L26"/>
+    <mergeCell ref="Y39:AE39"/>
+    <mergeCell ref="C35:L35"/>
     <mergeCell ref="B64:AK64"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="Y29:AE29"/>
-    <mergeCell ref="C59:AK59"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="AF33:AK33"/>
-    <mergeCell ref="A25:AK25"/>
+    <mergeCell ref="AF24:AK24"/>
+    <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="M21:P21"/>
-    <mergeCell ref="Y31:AE31"/>
-    <mergeCell ref="C39:AK39"/>
-    <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="B50:I50"/>
     <mergeCell ref="D66:AK66"/>
-    <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="B58:AK58"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="M36:P36"/>
+    <mergeCell ref="Y37:AE37"/>
+    <mergeCell ref="T39:X39"/>
+    <mergeCell ref="C81:AK81"/>
+    <mergeCell ref="Y27:AB27"/>
+    <mergeCell ref="AF25:AK25"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="B52:AK52"/>
-    <mergeCell ref="T32:X32"/>
+    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="C87:AK87"/>
+    <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="T42:X42"/>
     <mergeCell ref="C28:L28"/>
+    <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="C82:AK82"/>
+    <mergeCell ref="A20:AK20"/>
+    <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
+    <mergeCell ref="AF42:AK42"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
+    <mergeCell ref="C89:AK89"/>
+    <mergeCell ref="Q36:S36"/>
+    <mergeCell ref="T44:X44"/>
+    <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="D54:AK54"/>
-    <mergeCell ref="C73:AK73"/>
+    <mergeCell ref="M34:P34"/>
+    <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="D30:L30"/>
-    <mergeCell ref="C63:AK63"/>
-    <mergeCell ref="T21:X21"/>
+    <mergeCell ref="C54:AK54"/>
+    <mergeCell ref="AF40:AK40"/>
+    <mergeCell ref="M39:P39"/>
+    <mergeCell ref="T26:X26"/>
     <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="A51:AK51"/>
+    <mergeCell ref="Y30:AB30"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="C56:AK56"/>
+    <mergeCell ref="T41:X41"/>
+    <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
+    <mergeCell ref="Y29:AB29"/>
+    <mergeCell ref="Y44:AE44"/>
+    <mergeCell ref="D80:AK80"/>
     <mergeCell ref="J9:AK9"/>
+    <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="M31:P31"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="C36:AK36"/>
-    <mergeCell ref="D57:AK57"/>
+    <mergeCell ref="C41:L41"/>
+    <mergeCell ref="M40:P40"/>
+    <mergeCell ref="T43:X43"/>
+    <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="T27:X27"/>
-    <mergeCell ref="B72:AK72"/>
-    <mergeCell ref="B14:I17"/>
+    <mergeCell ref="T36:X36"/>
     <mergeCell ref="C27:L27"/>
+    <mergeCell ref="Q38:S38"/>
+    <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B70:AK70"/>
-    <mergeCell ref="D32:L32"/>
-    <mergeCell ref="C69:AK69"/>
+    <mergeCell ref="M26:P26"/>
+    <mergeCell ref="M41:P41"/>
+    <mergeCell ref="Q26:S26"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="M38:P38"/>
+    <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="T35:X35"/>
+    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="Y23:AB23"/>
-    <mergeCell ref="Y32:AE32"/>
     <mergeCell ref="D68:AK68"/>
-    <mergeCell ref="D55:AK55"/>
-    <mergeCell ref="A19:AK19"/>
+    <mergeCell ref="D43:L43"/>
+    <mergeCell ref="T25:X25"/>
+    <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="D67:AK67"/>
+    <mergeCell ref="Y38:AE38"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="B53:I53"/>
+    <mergeCell ref="D69:AK69"/>
+    <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="B83:AK83"/>
     <mergeCell ref="AF28:AK28"/>
+    <mergeCell ref="C29:L29"/>
+    <mergeCell ref="D44:L44"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="C90:AK90"/>
+    <mergeCell ref="B76:AK76"/>
+    <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="C60:AK60"/>
     <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="C71:AK71"/>
+    <mergeCell ref="Q37:S37"/>
     <mergeCell ref="M22:P22"/>
+    <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
-    <mergeCell ref="C21:L21"/>
-    <mergeCell ref="D31:L31"/>
+    <mergeCell ref="Y34:AE34"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="D70:AK70"/>
     <mergeCell ref="M28:P28"/>
+    <mergeCell ref="M42:P42"/>
     <mergeCell ref="AF29:AK29"/>
+    <mergeCell ref="AC30:AE30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
